--- a/output/nowcast.xlsx
+++ b/output/nowcast.xlsx
@@ -541,16 +541,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
       <c r="C8" t="n">
-        <v>49.4</v>
+        <v>49.3</v>
       </c>
       <c r="D8" t="n">
         <v>51</v>
       </c>
       <c r="E8" t="n">
-        <v>54.6</v>
+        <v>55</v>
       </c>
       <c r="F8" t="n">
         <v>51</v>
@@ -575,7 +575,7 @@
         <v>231</v>
       </c>
       <c r="E9" t="n">
-        <v>82.2</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="F9" t="n">
         <v>218</v>
@@ -600,7 +600,7 @@
         <v>27</v>
       </c>
       <c r="E10" t="n">
-        <v>67.3</v>
+        <v>67</v>
       </c>
       <c r="F10" t="n">
         <v>26</v>
@@ -4724,10 +4724,10 @@
         <v>-4.75</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>19.2</v>
+        <v>19.5</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>80.8</v>
+        <v>80.5</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>44.19</v>
       </c>
       <c r="AA38" s="4" t="n">
-        <v>19.2</v>
+        <v>19.5</v>
       </c>
       <c r="AB38" s="4" t="n">
         <v>3.8</v>
@@ -24860,10 +24860,10 @@
         <v>-4.62</v>
       </c>
       <c r="J235" s="4" t="n">
-        <v>20.3</v>
+        <v>20.6</v>
       </c>
       <c r="K235" s="4" t="n">
-        <v>79.7</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -49290,10 +49290,10 @@
         <v>-0.59</v>
       </c>
       <c r="J473" s="4" t="n">
-        <v>37</v>
+        <v>38.1</v>
       </c>
       <c r="K473" s="4" t="n">
-        <v>63</v>
+        <v>61.9</v>
       </c>
       <c r="L473" t="inlineStr">
         <is>
@@ -50762,10 +50762,10 @@
         <v>1.02</v>
       </c>
       <c r="J487" s="4" t="n">
-        <v>65.40000000000001</v>
+        <v>65.3</v>
       </c>
       <c r="K487" s="4" t="n">
-        <v>34.6</v>
+        <v>34.7</v>
       </c>
       <c r="L487" t="inlineStr">
         <is>
@@ -51238,16 +51238,16 @@
         </is>
       </c>
       <c r="Z491" s="4" t="n">
-        <v>22.58</v>
+        <v>22.65</v>
       </c>
       <c r="AA491" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AB491" s="4" t="n">
-        <v>22.94</v>
+        <v>22.9</v>
       </c>
       <c r="AC491" s="4" t="n">
-        <v>50.82</v>
+        <v>50.78</v>
       </c>
       <c r="AD491" s="4" t="n">
         <v>3.66</v>

--- a/output/nowcast.xlsx
+++ b/output/nowcast.xlsx
@@ -472,7 +472,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data as of 2026-09-13 · evaluated at 0 days to election (actual: 51 days out)</t>
+          <t>Data as of 2026-09-14 · evaluated at 0 days to election (actual: 50 days out)</t>
         </is>
       </c>
     </row>
@@ -541,16 +541,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>51</v>
+        <v>51.1</v>
       </c>
       <c r="C8" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
       <c r="D8" t="n">
         <v>51</v>
       </c>
       <c r="E8" t="n">
-        <v>57.3</v>
+        <v>57.7</v>
       </c>
       <c r="F8" t="n">
         <v>51</v>
@@ -575,7 +575,7 @@
         <v>232</v>
       </c>
       <c r="E9" t="n">
-        <v>84.59999999999999</v>
+        <v>84.2</v>
       </c>
       <c r="F9" t="n">
         <v>218</v>
@@ -600,7 +600,7 @@
         <v>27</v>
       </c>
       <c r="E10" t="n">
-        <v>70</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="F10" t="n">
         <v>26</v>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>-18.21</v>
+        <v>-18.22</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>0.3</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AC3" s="4" t="n">
-        <v>40.9</v>
+        <v>40.89</v>
       </c>
       <c r="AD3" s="4" t="n">
-        <v>59.1</v>
+        <v>59.11</v>
       </c>
       <c r="AE3" s="4" t="n">
         <v>0</v>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-17.24</v>
+        <v>-17.36</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>0.4</v>
@@ -1199,10 +1199,10 @@
         <v>0</v>
       </c>
       <c r="AC4" s="4" t="n">
-        <v>38.48</v>
+        <v>38.43</v>
       </c>
       <c r="AD4" s="4" t="n">
-        <v>54.52</v>
+        <v>54.57</v>
       </c>
       <c r="AE4" s="4" t="n">
         <v>0</v>
@@ -1363,7 +1363,7 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>26.6</v>
+        <v>26.62</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>100</v>
@@ -1421,10 +1421,10 @@
         <v>0</v>
       </c>
       <c r="AC6" s="4" t="n">
-        <v>63.3</v>
+        <v>63.31</v>
       </c>
       <c r="AD6" s="4" t="n">
-        <v>36.7</v>
+        <v>36.69</v>
       </c>
       <c r="AE6" s="4" t="n">
         <v>0</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>18.32</v>
+        <v>18.34</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>99.7</v>
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="AC8" s="4" t="n">
-        <v>59.16</v>
+        <v>59.17</v>
       </c>
       <c r="AD8" s="4" t="n">
-        <v>40.84</v>
+        <v>40.83</v>
       </c>
       <c r="AE8" s="4" t="n">
         <v>0</v>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-5.06</v>
+        <v>-5.07</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>18.9</v>
@@ -1803,7 +1803,7 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>72.7</v>
@@ -2011,13 +2011,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>7.44</v>
+        <v>7.43</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>88.90000000000001</v>
+        <v>88.8</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -2069,10 +2069,10 @@
         <v>0</v>
       </c>
       <c r="AC12" s="4" t="n">
-        <v>53.72</v>
+        <v>53.71</v>
       </c>
       <c r="AD12" s="4" t="n">
-        <v>46.28</v>
+        <v>46.29</v>
       </c>
       <c r="AE12" s="4" t="n">
         <v>0</v>
@@ -2120,7 +2120,7 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-38.56</v>
+        <v>-38.65</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>0</v>
@@ -2186,10 +2186,10 @@
         <v>0</v>
       </c>
       <c r="AC13" s="4" t="n">
-        <v>29.18</v>
+        <v>29.14</v>
       </c>
       <c r="AD13" s="4" t="n">
-        <v>65.81999999999999</v>
+        <v>65.86</v>
       </c>
       <c r="AE13" s="4" t="n">
         <v>0</v>
@@ -2350,13 +2350,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-6.97</v>
+        <v>-7.04</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>12.6</v>
+        <v>12.4</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>87.40000000000001</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -2408,10 +2408,10 @@
         <v>0</v>
       </c>
       <c r="AC15" s="4" t="n">
-        <v>46.51</v>
+        <v>46.48</v>
       </c>
       <c r="AD15" s="4" t="n">
-        <v>53.49</v>
+        <v>53.52</v>
       </c>
       <c r="AE15" s="4" t="n">
         <v>0</v>
@@ -2459,7 +2459,7 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>28.58</v>
+        <v>28.61</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>100</v>
@@ -2525,10 +2525,10 @@
         <v>0</v>
       </c>
       <c r="AC16" s="4" t="n">
-        <v>62.17</v>
+        <v>62.18</v>
       </c>
       <c r="AD16" s="4" t="n">
-        <v>34.53</v>
+        <v>34.52</v>
       </c>
       <c r="AE16" s="4" t="n">
         <v>0</v>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>33.96</v>
+        <v>34.03</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>100</v>
@@ -2642,10 +2642,10 @@
         <v>0</v>
       </c>
       <c r="AC17" s="4" t="n">
-        <v>64.66</v>
+        <v>64.69</v>
       </c>
       <c r="AD17" s="4" t="n">
-        <v>31.87</v>
+        <v>31.84</v>
       </c>
       <c r="AE17" s="4" t="n">
         <v>0</v>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>11.07</v>
+        <v>11.09</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>98.3</v>
@@ -2868,10 +2868,10 @@
         <v>0</v>
       </c>
       <c r="AC19" s="4" t="n">
-        <v>55.26</v>
+        <v>55.27</v>
       </c>
       <c r="AD19" s="4" t="n">
-        <v>44.24</v>
+        <v>44.23</v>
       </c>
       <c r="AE19" s="4" t="n">
         <v>0</v>
@@ -2915,7 +2915,7 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>12.31</v>
+        <v>12.29</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>98.90000000000001</v>
@@ -3032,13 +3032,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-13.47</v>
+        <v>-14.26</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>99.09999999999999</v>
+        <v>99.2</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -3064,13 +3064,13 @@
         <v>-20.84</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>33</v>
+        <v>34.99</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>38</v>
+        <v>42.97</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V21" s="4" t="n">
         <v>-8</v>
@@ -3092,16 +3092,16 @@
         </is>
       </c>
       <c r="AA21" s="4" t="n">
-        <v>12</v>
+        <v>0.5</v>
       </c>
       <c r="AB21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC21" s="4" t="n">
-        <v>38.07</v>
+        <v>42.66</v>
       </c>
       <c r="AD21" s="4" t="n">
-        <v>49.93</v>
+        <v>56.84</v>
       </c>
       <c r="AE21" s="4" t="n">
         <v>0</v>
@@ -3149,7 +3149,7 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-10.92</v>
+        <v>-10.93</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>2</v>
@@ -3320,10 +3320,10 @@
         <v>0</v>
       </c>
       <c r="AC23" s="4" t="n">
-        <v>55.04</v>
+        <v>55.03</v>
       </c>
       <c r="AD23" s="4" t="n">
-        <v>44.96</v>
+        <v>44.97</v>
       </c>
       <c r="AE23" s="4" t="n">
         <v>0</v>
@@ -3371,13 +3371,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>74.2</v>
+        <v>74.3</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>25.8</v>
+        <v>25.7</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-3.41</v>
+        <v>-3.42</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>24.9</v>
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>4.09</v>
+        <v>4.1</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>77.59999999999999</v>
@@ -4047,7 +4047,7 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>21.37</v>
+        <v>21.35</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>99.8</v>
@@ -4376,7 +4376,7 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-16.19</v>
+        <v>-16.2</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>0.5</v>
@@ -4442,10 +4442,10 @@
         <v>0</v>
       </c>
       <c r="AC33" s="4" t="n">
-        <v>38.84</v>
+        <v>38.83</v>
       </c>
       <c r="AD33" s="4" t="n">
-        <v>53.84</v>
+        <v>53.85</v>
       </c>
       <c r="AE33" s="4" t="n">
         <v>0</v>
@@ -4493,13 +4493,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-6.17</v>
+        <v>-6.26</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>15.1</v>
+        <v>14.9</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>84.90000000000001</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -4525,16 +4525,16 @@
         <v>-13.88</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>44.8</v>
+        <v>44.75</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>48.04</v>
+        <v>48.28</v>
       </c>
       <c r="U34" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-3.3</v>
+        <v>-3.59</v>
       </c>
       <c r="W34" s="5" t="n">
         <v>8589462</v>
@@ -4553,16 +4553,16 @@
         </is>
       </c>
       <c r="AA34" s="4" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="AB34" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC34" s="4" t="n">
-        <v>46.62</v>
+        <v>46.59</v>
       </c>
       <c r="AD34" s="4" t="n">
-        <v>52.75</v>
+        <v>52.82</v>
       </c>
       <c r="AE34" s="4" t="n">
         <v>0</v>
@@ -4610,7 +4610,7 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-21.27</v>
+        <v>-21.3</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>0.2</v>
@@ -4676,10 +4676,10 @@
         <v>0</v>
       </c>
       <c r="AC35" s="4" t="n">
-        <v>38.44</v>
+        <v>38.43</v>
       </c>
       <c r="AD35" s="4" t="n">
-        <v>59.22</v>
+        <v>59.23</v>
       </c>
       <c r="AE35" s="4" t="n">
         <v>0</v>
@@ -4723,7 +4723,7 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>73.09999999999999</v>
@@ -4939,13 +4939,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>-4.32</v>
+        <v>-4.29</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>21.4</v>
+        <v>21</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>78.59999999999999</v>
+        <v>79</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -4999,16 +4999,16 @@
         </is>
       </c>
       <c r="AA38" s="4" t="n">
-        <v>44.4</v>
+        <v>44.42</v>
       </c>
       <c r="AB38" s="4" t="n">
-        <v>21.4</v>
+        <v>21</v>
       </c>
       <c r="AC38" s="4" t="n">
         <v>3.8</v>
       </c>
       <c r="AD38" s="4" t="n">
-        <v>50.6</v>
+        <v>50.58</v>
       </c>
       <c r="AE38" s="4" t="n">
         <v>1.2</v>
@@ -5066,7 +5066,7 @@
         </is>
       </c>
       <c r="M39" s="4" t="n">
-        <v>-30.47</v>
+        <v>-30.48</v>
       </c>
       <c r="N39" s="4" t="n">
         <v>5.62</v>
@@ -5155,7 +5155,7 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>-2.21</v>
+        <v>-2.2</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>29.6</v>
@@ -5169,13 +5169,13 @@
         </is>
       </c>
       <c r="M40" s="4" t="n">
-        <v>-8.68</v>
+        <v>-8.69</v>
       </c>
       <c r="N40" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>-1.31</v>
+        <v>-1.32</v>
       </c>
       <c r="P40" s="4" t="n">
         <v>-0.45</v>
@@ -5264,7 +5264,7 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>-40.12</v>
+        <v>-40.13</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
         <v>5.62</v>
       </c>
       <c r="O41" s="4" t="n">
-        <v>-40.12</v>
+        <v>-40.13</v>
       </c>
       <c r="P41" s="4" t="n">
         <v>-2.23</v>
@@ -5367,7 +5367,7 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>-60.3</v>
+        <v>-60.31</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>0</v>
@@ -5387,7 +5387,7 @@
         <v>5.62</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>-60.3</v>
+        <v>-60.31</v>
       </c>
       <c r="P42" s="4" t="n">
         <v>-2.1</v>
@@ -5470,7 +5470,7 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>-22.22</v>
+        <v>-22.23</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>0.1</v>
@@ -5484,13 +5484,13 @@
         </is>
       </c>
       <c r="M43" s="4" t="n">
-        <v>-25.03</v>
+        <v>-25.04</v>
       </c>
       <c r="N43" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O43" s="4" t="n">
-        <v>-22.22</v>
+        <v>-22.23</v>
       </c>
       <c r="P43" s="4" t="n">
         <v>-0.59</v>
@@ -5522,10 +5522,10 @@
         <v>0</v>
       </c>
       <c r="AC43" s="4" t="n">
-        <v>38.89</v>
+        <v>38.88</v>
       </c>
       <c r="AD43" s="4" t="n">
-        <v>61.11</v>
+        <v>61.12</v>
       </c>
       <c r="AE43" s="4" t="n">
         <v>0</v>
@@ -5573,7 +5573,7 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>-29.92</v>
+        <v>-29.93</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>0</v>
@@ -5587,13 +5587,13 @@
         </is>
       </c>
       <c r="M44" s="4" t="n">
-        <v>-30.55</v>
+        <v>-30.56</v>
       </c>
       <c r="N44" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O44" s="4" t="n">
-        <v>-29.92</v>
+        <v>-29.93</v>
       </c>
       <c r="P44" s="4" t="n">
         <v>-2.26</v>
@@ -5676,7 +5676,7 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>35.23</v>
+        <v>35.22</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>100</v>
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="M45" s="4" t="n">
-        <v>23.69</v>
+        <v>23.68</v>
       </c>
       <c r="N45" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O45" s="4" t="n">
-        <v>35.23</v>
+        <v>35.22</v>
       </c>
       <c r="P45" s="4" t="n">
         <v>1.73</v>
@@ -5779,7 +5779,7 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>-39.46</v>
+        <v>-39.49</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>0</v>
@@ -5793,13 +5793,13 @@
         </is>
       </c>
       <c r="M46" s="4" t="n">
-        <v>-39.02</v>
+        <v>-39.06</v>
       </c>
       <c r="N46" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O46" s="4" t="n">
-        <v>-39.98</v>
+        <v>-40.02</v>
       </c>
       <c r="P46" s="4" t="n">
         <v>-1.62</v>
@@ -5839,10 +5839,10 @@
         <v>0</v>
       </c>
       <c r="AC46" s="4" t="n">
-        <v>29.48</v>
+        <v>29.46</v>
       </c>
       <c r="AD46" s="4" t="n">
-        <v>67.90000000000001</v>
+        <v>67.92</v>
       </c>
       <c r="AE46" s="4" t="n">
         <v>0</v>
@@ -5890,13 +5890,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>-4</v>
+        <v>-4.05</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>22.8</v>
+        <v>22.6</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>77.2</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -5904,13 +5904,13 @@
         </is>
       </c>
       <c r="M47" s="4" t="n">
-        <v>-9.82</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="N47" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O47" s="4" t="n">
-        <v>-6.86</v>
+        <v>-6.89</v>
       </c>
       <c r="P47" s="4" t="n">
         <v>-1.02</v>
@@ -5948,10 +5948,10 @@
         <v>0</v>
       </c>
       <c r="AC47" s="4" t="n">
-        <v>48</v>
+        <v>47.97</v>
       </c>
       <c r="AD47" s="4" t="n">
-        <v>52</v>
+        <v>52.03</v>
       </c>
       <c r="AE47" s="4" t="n">
         <v>0</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>-22.13</v>
+        <v>-22.17</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>0.1</v>
@@ -6013,13 +6013,13 @@
         </is>
       </c>
       <c r="M48" s="4" t="n">
-        <v>-20.01</v>
+        <v>-20.05</v>
       </c>
       <c r="N48" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O48" s="4" t="n">
-        <v>-22.84</v>
+        <v>-22.88</v>
       </c>
       <c r="P48" s="4" t="n">
         <v>-1.82</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AC48" s="4" t="n">
-        <v>37.55</v>
+        <v>37.53</v>
       </c>
       <c r="AD48" s="4" t="n">
-        <v>58.9</v>
+        <v>58.92</v>
       </c>
       <c r="AE48" s="4" t="n">
         <v>0</v>
@@ -6110,7 +6110,7 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>-36.1</v>
+        <v>-36.13</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>0</v>
@@ -6124,13 +6124,13 @@
         </is>
       </c>
       <c r="M49" s="4" t="n">
-        <v>-33.38</v>
+        <v>-33.42</v>
       </c>
       <c r="N49" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O49" s="4" t="n">
-        <v>-36.1</v>
+        <v>-36.13</v>
       </c>
       <c r="P49" s="4" t="n">
         <v>-2.88</v>
@@ -6162,10 +6162,10 @@
         <v>0</v>
       </c>
       <c r="AC49" s="4" t="n">
-        <v>31.95</v>
+        <v>31.93</v>
       </c>
       <c r="AD49" s="4" t="n">
-        <v>68.05</v>
+        <v>68.06999999999999</v>
       </c>
       <c r="AE49" s="4" t="n">
         <v>0</v>
@@ -6326,13 +6326,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>-0.14</v>
+        <v>-0.11</v>
       </c>
       <c r="J51" s="4" t="n">
-        <v>37.7</v>
+        <v>37.9</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>62.3</v>
+        <v>62.1</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -6392,10 +6392,10 @@
         <v>0</v>
       </c>
       <c r="AC51" s="4" t="n">
-        <v>49.35</v>
+        <v>49.37</v>
       </c>
       <c r="AD51" s="4" t="n">
-        <v>49.49</v>
+        <v>49.47</v>
       </c>
       <c r="AE51" s="4" t="n">
         <v>0</v>
@@ -7190,7 +7190,7 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>19.68</v>
+        <v>19.69</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>99.8</v>
@@ -7210,7 +7210,7 @@
         <v>5.62</v>
       </c>
       <c r="O59" s="4" t="n">
-        <v>19.68</v>
+        <v>19.69</v>
       </c>
       <c r="P59" s="4" t="n">
         <v>0.21</v>
@@ -7307,7 +7307,7 @@
         </is>
       </c>
       <c r="M60" s="4" t="n">
-        <v>27.78</v>
+        <v>27.79</v>
       </c>
       <c r="N60" s="4" t="n">
         <v>5.62</v>
@@ -7448,10 +7448,10 @@
         <v>0</v>
       </c>
       <c r="AC61" s="4" t="n">
-        <v>60.78</v>
+        <v>60.79</v>
       </c>
       <c r="AD61" s="4" t="n">
-        <v>39.22</v>
+        <v>39.21</v>
       </c>
       <c r="AE61" s="4" t="n">
         <v>0</v>
@@ -7616,7 +7616,7 @@
         </is>
       </c>
       <c r="M63" s="4" t="n">
-        <v>-18.28</v>
+        <v>-18.27</v>
       </c>
       <c r="N63" s="4" t="n">
         <v>5.62</v>
@@ -7654,10 +7654,10 @@
         <v>0</v>
       </c>
       <c r="AC63" s="4" t="n">
-        <v>41.1</v>
+        <v>41.11</v>
       </c>
       <c r="AD63" s="4" t="n">
-        <v>58.9</v>
+        <v>58.89</v>
       </c>
       <c r="AE63" s="4" t="n">
         <v>0</v>
@@ -7705,7 +7705,7 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>12.83</v>
+        <v>12.84</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>99</v>
@@ -7725,7 +7725,7 @@
         <v>5.62</v>
       </c>
       <c r="O64" s="4" t="n">
-        <v>12.83</v>
+        <v>12.84</v>
       </c>
       <c r="P64" s="4" t="n">
         <v>-0.35</v>
@@ -7818,13 +7818,13 @@
         </is>
       </c>
       <c r="M65" s="4" t="n">
-        <v>16.59</v>
+        <v>16.6</v>
       </c>
       <c r="N65" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O65" s="4" t="n">
-        <v>22.34</v>
+        <v>22.35</v>
       </c>
       <c r="P65" s="4" t="n">
         <v>0</v>
@@ -7907,7 +7907,7 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>49.41</v>
+        <v>49.42</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>100</v>
@@ -7921,13 +7921,13 @@
         </is>
       </c>
       <c r="M66" s="4" t="n">
-        <v>39.13</v>
+        <v>39.14</v>
       </c>
       <c r="N66" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O66" s="4" t="n">
-        <v>49.41</v>
+        <v>49.42</v>
       </c>
       <c r="P66" s="4" t="n">
         <v>1.66</v>
@@ -8062,10 +8062,10 @@
         <v>0</v>
       </c>
       <c r="AC67" s="4" t="n">
-        <v>65.56999999999999</v>
+        <v>65.58</v>
       </c>
       <c r="AD67" s="4" t="n">
-        <v>34.43</v>
+        <v>34.42</v>
       </c>
       <c r="AE67" s="4" t="n">
         <v>0</v>
@@ -8226,13 +8226,13 @@
         </is>
       </c>
       <c r="M69" s="4" t="n">
-        <v>73.98999999999999</v>
+        <v>74</v>
       </c>
       <c r="N69" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O69" s="4" t="n">
-        <v>79.3</v>
+        <v>79.31</v>
       </c>
       <c r="P69" s="4" t="n">
         <v>0</v>
@@ -8329,7 +8329,7 @@
         </is>
       </c>
       <c r="M70" s="4" t="n">
-        <v>80.73999999999999</v>
+        <v>80.75</v>
       </c>
       <c r="N70" s="4" t="n">
         <v>5.62</v>
@@ -8418,7 +8418,7 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>22.03</v>
+        <v>22.04</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>99.90000000000001</v>
@@ -8438,7 +8438,7 @@
         <v>5.62</v>
       </c>
       <c r="O71" s="4" t="n">
-        <v>22.03</v>
+        <v>22.04</v>
       </c>
       <c r="P71" s="4" t="n">
         <v>0.46</v>
@@ -8541,7 +8541,7 @@
         <v>5.62</v>
       </c>
       <c r="O72" s="4" t="n">
-        <v>48.07</v>
+        <v>48.08</v>
       </c>
       <c r="P72" s="4" t="n">
         <v>0</v>
@@ -8638,7 +8638,7 @@
         </is>
       </c>
       <c r="M73" s="4" t="n">
-        <v>53.76</v>
+        <v>53.77</v>
       </c>
       <c r="N73" s="4" t="n">
         <v>5.62</v>
@@ -8676,10 +8676,10 @@
         <v>0</v>
       </c>
       <c r="AC73" s="4" t="n">
-        <v>79.31999999999999</v>
+        <v>79.33</v>
       </c>
       <c r="AD73" s="4" t="n">
-        <v>20.68</v>
+        <v>20.67</v>
       </c>
       <c r="AE73" s="4" t="n">
         <v>0</v>
@@ -8727,7 +8727,7 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>63.25</v>
+        <v>63.26</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>100</v>
@@ -8747,7 +8747,7 @@
         <v>5.62</v>
       </c>
       <c r="O74" s="4" t="n">
-        <v>63.25</v>
+        <v>63.26</v>
       </c>
       <c r="P74" s="4" t="n">
         <v>3.19</v>
@@ -8844,7 +8844,7 @@
         </is>
       </c>
       <c r="M75" s="4" t="n">
-        <v>45.11</v>
+        <v>45.12</v>
       </c>
       <c r="N75" s="4" t="n">
         <v>5.62</v>
@@ -8933,7 +8933,7 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>44.35</v>
+        <v>44.36</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>100</v>
@@ -8947,13 +8947,13 @@
         </is>
       </c>
       <c r="M76" s="4" t="n">
-        <v>35.04</v>
+        <v>35.05</v>
       </c>
       <c r="N76" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O76" s="4" t="n">
-        <v>44.35</v>
+        <v>44.36</v>
       </c>
       <c r="P76" s="4" t="n">
         <v>2.1</v>
@@ -9050,7 +9050,7 @@
         </is>
       </c>
       <c r="M77" s="4" t="n">
-        <v>38.6</v>
+        <v>38.61</v>
       </c>
       <c r="N77" s="4" t="n">
         <v>5.62</v>
@@ -9088,10 +9088,10 @@
         <v>0</v>
       </c>
       <c r="AC77" s="4" t="n">
-        <v>75.31</v>
+        <v>75.31999999999999</v>
       </c>
       <c r="AD77" s="4" t="n">
-        <v>24.69</v>
+        <v>24.68</v>
       </c>
       <c r="AE77" s="4" t="n">
         <v>0</v>
@@ -9139,7 +9139,7 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>-28.19</v>
+        <v>-28.18</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>0</v>
@@ -9159,7 +9159,7 @@
         <v>5.62</v>
       </c>
       <c r="O78" s="4" t="n">
-        <v>-28.19</v>
+        <v>-28.18</v>
       </c>
       <c r="P78" s="4" t="n">
         <v>-2.51</v>
@@ -9256,7 +9256,7 @@
         </is>
       </c>
       <c r="M79" s="4" t="n">
-        <v>11.74</v>
+        <v>11.75</v>
       </c>
       <c r="N79" s="4" t="n">
         <v>5.62</v>
@@ -9345,13 +9345,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>6.5</v>
+        <v>6.52</v>
       </c>
       <c r="J80" s="4" t="n">
-        <v>85.90000000000001</v>
+        <v>86</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -9365,7 +9365,7 @@
         <v>5.62</v>
       </c>
       <c r="O80" s="4" t="n">
-        <v>7.64</v>
+        <v>7.65</v>
       </c>
       <c r="P80" s="4" t="n">
         <v>-0.27</v>
@@ -9403,10 +9403,10 @@
         <v>0</v>
       </c>
       <c r="AC80" s="4" t="n">
-        <v>53.25</v>
+        <v>53.26</v>
       </c>
       <c r="AD80" s="4" t="n">
-        <v>46.75</v>
+        <v>46.74</v>
       </c>
       <c r="AE80" s="4" t="n">
         <v>0</v>
@@ -9468,7 +9468,7 @@
         </is>
       </c>
       <c r="M81" s="4" t="n">
-        <v>-16.78</v>
+        <v>-16.77</v>
       </c>
       <c r="N81" s="4" t="n">
         <v>5.62</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="AC82" s="4" t="n">
-        <v>68.53</v>
+        <v>68.54000000000001</v>
       </c>
       <c r="AD82" s="4" t="n">
-        <v>31.47</v>
+        <v>31.46</v>
       </c>
       <c r="AE82" s="4" t="n">
         <v>0</v>
@@ -9712,10 +9712,10 @@
         <v>0</v>
       </c>
       <c r="AC83" s="4" t="n">
-        <v>60.08</v>
+        <v>60.09</v>
       </c>
       <c r="AD83" s="4" t="n">
-        <v>39.92</v>
+        <v>39.91</v>
       </c>
       <c r="AE83" s="4" t="n">
         <v>0</v>
@@ -9759,7 +9759,7 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>26.23</v>
+        <v>26.24</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>100</v>
@@ -9779,7 +9779,7 @@
         <v>5.62</v>
       </c>
       <c r="O84" s="4" t="n">
-        <v>26.23</v>
+        <v>26.24</v>
       </c>
       <c r="P84" s="4" t="n">
         <v>0.63</v>
@@ -9862,7 +9862,7 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>27.24</v>
+        <v>27.25</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>100</v>
@@ -9882,7 +9882,7 @@
         <v>5.62</v>
       </c>
       <c r="O85" s="4" t="n">
-        <v>27.24</v>
+        <v>27.25</v>
       </c>
       <c r="P85" s="4" t="n">
         <v>1.74</v>
@@ -9965,7 +9965,7 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>40.19</v>
+        <v>40.2</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>100</v>
@@ -9979,13 +9979,13 @@
         </is>
       </c>
       <c r="M86" s="4" t="n">
-        <v>29.74</v>
+        <v>29.75</v>
       </c>
       <c r="N86" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O86" s="4" t="n">
-        <v>40.19</v>
+        <v>40.2</v>
       </c>
       <c r="P86" s="4" t="n">
         <v>2.23</v>
@@ -10082,13 +10082,13 @@
         </is>
       </c>
       <c r="M87" s="4" t="n">
-        <v>41.3</v>
+        <v>41.31</v>
       </c>
       <c r="N87" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O87" s="4" t="n">
-        <v>53.76</v>
+        <v>53.77</v>
       </c>
       <c r="P87" s="4" t="n">
         <v>0</v>
@@ -10274,7 +10274,7 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>16.47</v>
+        <v>16.48</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>99.5</v>
@@ -10288,13 +10288,13 @@
         </is>
       </c>
       <c r="M89" s="4" t="n">
-        <v>17.84</v>
+        <v>17.85</v>
       </c>
       <c r="N89" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O89" s="4" t="n">
-        <v>16.47</v>
+        <v>16.48</v>
       </c>
       <c r="P89" s="4" t="n">
         <v>1.31</v>
@@ -10391,7 +10391,7 @@
         </is>
       </c>
       <c r="M90" s="4" t="n">
-        <v>29.86</v>
+        <v>29.87</v>
       </c>
       <c r="N90" s="4" t="n">
         <v>5.62</v>
@@ -10429,10 +10429,10 @@
         <v>0</v>
       </c>
       <c r="AC90" s="4" t="n">
-        <v>69.97</v>
+        <v>69.98</v>
       </c>
       <c r="AD90" s="4" t="n">
-        <v>30.03</v>
+        <v>30.02</v>
       </c>
       <c r="AE90" s="4" t="n">
         <v>0</v>
@@ -10480,7 +10480,7 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>28.78</v>
+        <v>28.79</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>100</v>
@@ -10494,13 +10494,13 @@
         </is>
       </c>
       <c r="M91" s="4" t="n">
-        <v>16.21</v>
+        <v>16.22</v>
       </c>
       <c r="N91" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O91" s="4" t="n">
-        <v>28.78</v>
+        <v>28.79</v>
       </c>
       <c r="P91" s="4" t="n">
         <v>0</v>
@@ -10597,13 +10597,13 @@
         </is>
       </c>
       <c r="M92" s="4" t="n">
-        <v>58.77</v>
+        <v>58.78</v>
       </c>
       <c r="N92" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O92" s="4" t="n">
-        <v>68.2</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="P92" s="4" t="n">
         <v>0</v>
@@ -10686,7 +10686,7 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>26.69</v>
+        <v>26.7</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>100</v>
@@ -10706,7 +10706,7 @@
         <v>5.62</v>
       </c>
       <c r="O93" s="4" t="n">
-        <v>26.69</v>
+        <v>26.7</v>
       </c>
       <c r="P93" s="4" t="n">
         <v>2.03</v>
@@ -10803,7 +10803,7 @@
         </is>
       </c>
       <c r="M94" s="4" t="n">
-        <v>43.36</v>
+        <v>43.37</v>
       </c>
       <c r="N94" s="4" t="n">
         <v>5.62</v>
@@ -10912,7 +10912,7 @@
         <v>5.62</v>
       </c>
       <c r="O95" s="4" t="n">
-        <v>76.95999999999999</v>
+        <v>76.97</v>
       </c>
       <c r="P95" s="4" t="n">
         <v>0</v>
@@ -10991,7 +10991,7 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>26.41</v>
+        <v>26.42</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>100</v>
@@ -11005,13 +11005,13 @@
         </is>
       </c>
       <c r="M96" s="4" t="n">
-        <v>18.92</v>
+        <v>18.93</v>
       </c>
       <c r="N96" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O96" s="4" t="n">
-        <v>26.41</v>
+        <v>26.42</v>
       </c>
       <c r="P96" s="4" t="n">
         <v>0</v>
@@ -11108,7 +11108,7 @@
         </is>
       </c>
       <c r="M97" s="4" t="n">
-        <v>15.94</v>
+        <v>15.95</v>
       </c>
       <c r="N97" s="4" t="n">
         <v>5.62</v>
@@ -11211,13 +11211,13 @@
         </is>
       </c>
       <c r="M98" s="4" t="n">
-        <v>-10.28</v>
+        <v>-10.27</v>
       </c>
       <c r="N98" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O98" s="4" t="n">
-        <v>-4.3</v>
+        <v>-4.29</v>
       </c>
       <c r="P98" s="4" t="n">
         <v>0</v>
@@ -11300,7 +11300,7 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>31.54</v>
+        <v>31.55</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>100</v>
@@ -11314,13 +11314,13 @@
         </is>
       </c>
       <c r="M99" s="4" t="n">
-        <v>19.48</v>
+        <v>19.49</v>
       </c>
       <c r="N99" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O99" s="4" t="n">
-        <v>31.54</v>
+        <v>31.55</v>
       </c>
       <c r="P99" s="4" t="n">
         <v>2.64</v>
@@ -11403,7 +11403,7 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>26.64</v>
+        <v>26.65</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>100</v>
@@ -11417,13 +11417,13 @@
         </is>
       </c>
       <c r="M100" s="4" t="n">
-        <v>16.72</v>
+        <v>16.73</v>
       </c>
       <c r="N100" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O100" s="4" t="n">
-        <v>26.64</v>
+        <v>26.65</v>
       </c>
       <c r="P100" s="4" t="n">
         <v>1.69</v>
@@ -11506,7 +11506,7 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>63.86</v>
+        <v>63.87</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>100</v>
@@ -11520,13 +11520,13 @@
         </is>
       </c>
       <c r="M101" s="4" t="n">
-        <v>56.69</v>
+        <v>56.7</v>
       </c>
       <c r="N101" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O101" s="4" t="n">
-        <v>63.86</v>
+        <v>63.87</v>
       </c>
       <c r="P101" s="4" t="n">
         <v>0</v>
@@ -11609,7 +11609,7 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>59.29</v>
+        <v>59.3</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>100</v>
@@ -11629,7 +11629,7 @@
         <v>5.62</v>
       </c>
       <c r="O102" s="4" t="n">
-        <v>59.29</v>
+        <v>59.3</v>
       </c>
       <c r="P102" s="4" t="n">
         <v>1.93</v>
@@ -11712,7 +11712,7 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>20.97</v>
+        <v>20.98</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>99.8</v>
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="M103" s="4" t="n">
-        <v>8.16</v>
+        <v>8.17</v>
       </c>
       <c r="N103" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O103" s="4" t="n">
-        <v>20.97</v>
+        <v>20.98</v>
       </c>
       <c r="P103" s="4" t="n">
         <v>1.69</v>
@@ -11970,10 +11970,10 @@
         <v>0</v>
       </c>
       <c r="AC105" s="4" t="n">
-        <v>61.44</v>
+        <v>61.45</v>
       </c>
       <c r="AD105" s="4" t="n">
-        <v>38.56</v>
+        <v>38.55</v>
       </c>
       <c r="AE105" s="4" t="n">
         <v>0</v>
@@ -12017,13 +12017,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>8.24</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J106" s="4" t="n">
-        <v>91.2</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="L106" t="inlineStr">
         <is>
@@ -12031,13 +12031,13 @@
         </is>
       </c>
       <c r="M106" s="4" t="n">
-        <v>5.53</v>
+        <v>5.54</v>
       </c>
       <c r="N106" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O106" s="4" t="n">
-        <v>12.14</v>
+        <v>12.15</v>
       </c>
       <c r="P106" s="4" t="n">
         <v>0.13</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AC106" s="4" t="n">
-        <v>54.12</v>
+        <v>54.15</v>
       </c>
       <c r="AD106" s="4" t="n">
-        <v>45.88</v>
+        <v>45.85</v>
       </c>
       <c r="AE106" s="4" t="n">
         <v>0</v>
@@ -12140,7 +12140,7 @@
         </is>
       </c>
       <c r="M107" s="4" t="n">
-        <v>14.45</v>
+        <v>14.46</v>
       </c>
       <c r="N107" s="4" t="n">
         <v>5.62</v>
@@ -12332,7 +12332,7 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>27.84</v>
+        <v>27.85</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>100</v>
@@ -12346,13 +12346,13 @@
         </is>
       </c>
       <c r="M109" s="4" t="n">
-        <v>21.34</v>
+        <v>21.35</v>
       </c>
       <c r="N109" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O109" s="4" t="n">
-        <v>27.84</v>
+        <v>27.85</v>
       </c>
       <c r="P109" s="4" t="n">
         <v>0</v>
@@ -12756,7 +12756,7 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>-1.14</v>
+        <v>-1.13</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>33.8</v>
@@ -12987,10 +12987,10 @@
         <v>-6.23</v>
       </c>
       <c r="J115" s="4" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>85</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="L115" t="inlineStr">
         <is>
@@ -13430,7 +13430,7 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>32.03</v>
+        <v>32.04</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>100</v>
@@ -13444,7 +13444,7 @@
         </is>
       </c>
       <c r="M119" s="4" t="n">
-        <v>25.33</v>
+        <v>25.34</v>
       </c>
       <c r="N119" s="4" t="n">
         <v>5.62</v>
@@ -13555,7 +13555,7 @@
         </is>
       </c>
       <c r="M120" s="4" t="n">
-        <v>9.27</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="N120" s="4" t="n">
         <v>5.62</v>
@@ -13593,10 +13593,10 @@
         <v>0</v>
       </c>
       <c r="AC120" s="4" t="n">
-        <v>61.42</v>
+        <v>61.43</v>
       </c>
       <c r="AD120" s="4" t="n">
-        <v>38.58</v>
+        <v>38.57</v>
       </c>
       <c r="AE120" s="4" t="n">
         <v>0</v>
@@ -13644,7 +13644,7 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>28.77</v>
+        <v>28.78</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>100</v>
@@ -13658,13 +13658,13 @@
         </is>
       </c>
       <c r="M121" s="4" t="n">
-        <v>16.4</v>
+        <v>16.41</v>
       </c>
       <c r="N121" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O121" s="4" t="n">
-        <v>28.87</v>
+        <v>28.88</v>
       </c>
       <c r="P121" s="4" t="n">
         <v>2.19</v>
@@ -13704,10 +13704,10 @@
         <v>0</v>
       </c>
       <c r="AC121" s="4" t="n">
-        <v>63.05</v>
+        <v>63.06</v>
       </c>
       <c r="AD121" s="4" t="n">
-        <v>34.88</v>
+        <v>34.87</v>
       </c>
       <c r="AE121" s="4" t="n">
         <v>0</v>
@@ -13769,13 +13769,13 @@
         </is>
       </c>
       <c r="M122" s="4" t="n">
-        <v>26.31</v>
+        <v>26.32</v>
       </c>
       <c r="N122" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O122" s="4" t="n">
-        <v>35.33</v>
+        <v>35.34</v>
       </c>
       <c r="P122" s="4" t="n">
         <v>2.02</v>
@@ -13918,10 +13918,10 @@
         <v>0</v>
       </c>
       <c r="AC123" s="4" t="n">
-        <v>57.43</v>
+        <v>57.44</v>
       </c>
       <c r="AD123" s="4" t="n">
-        <v>42.57</v>
+        <v>42.56</v>
       </c>
       <c r="AE123" s="4" t="n">
         <v>0</v>
@@ -14086,7 +14086,7 @@
         </is>
       </c>
       <c r="M125" s="4" t="n">
-        <v>-33.57</v>
+        <v>-33.58</v>
       </c>
       <c r="N125" s="4" t="n">
         <v>5.62</v>
@@ -14296,7 +14296,7 @@
         </is>
       </c>
       <c r="M127" s="4" t="n">
-        <v>-16.25</v>
+        <v>-16.26</v>
       </c>
       <c r="N127" s="4" t="n">
         <v>5.62</v>
@@ -14393,7 +14393,7 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>-8.1</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>9.199999999999999</v>
@@ -14407,7 +14407,7 @@
         </is>
       </c>
       <c r="M128" s="4" t="n">
-        <v>-7.64</v>
+        <v>-7.65</v>
       </c>
       <c r="N128" s="4" t="n">
         <v>5.62</v>
@@ -14504,7 +14504,7 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>-17.13</v>
+        <v>-17.14</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>0.4</v>
@@ -14518,13 +14518,13 @@
         </is>
       </c>
       <c r="M129" s="4" t="n">
-        <v>-17.45</v>
+        <v>-17.46</v>
       </c>
       <c r="N129" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O129" s="4" t="n">
-        <v>-17.13</v>
+        <v>-17.14</v>
       </c>
       <c r="P129" s="4" t="n">
         <v>-0.66</v>
@@ -14607,7 +14607,7 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>-23.58</v>
+        <v>-23.59</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>0.1</v>
@@ -14734,7 +14734,7 @@
         <v>5.62</v>
       </c>
       <c r="O131" s="4" t="n">
-        <v>-0.84</v>
+        <v>-0.85</v>
       </c>
       <c r="P131" s="4" t="n">
         <v>1.15</v>
@@ -14774,10 +14774,10 @@
         <v>0</v>
       </c>
       <c r="AC131" s="4" t="n">
-        <v>48.79</v>
+        <v>48.78</v>
       </c>
       <c r="AD131" s="4" t="n">
-        <v>49.22</v>
+        <v>49.23</v>
       </c>
       <c r="AE131" s="4" t="n">
         <v>0</v>
@@ -14825,13 +14825,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>-9.529999999999999</v>
+        <v>-9.52</v>
       </c>
       <c r="J132" s="4" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>94.7</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="L132" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         </is>
       </c>
       <c r="M132" s="4" t="n">
-        <v>-11.91</v>
+        <v>-11.92</v>
       </c>
       <c r="N132" s="4" t="n">
         <v>5.62</v>
@@ -14934,13 +14934,13 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>-0.75</v>
+        <v>-0.72</v>
       </c>
       <c r="J133" s="4" t="n">
-        <v>35.3</v>
+        <v>35.4</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>64.7</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="L133" t="inlineStr">
         <is>
@@ -14954,7 +14954,7 @@
         <v>5.62</v>
       </c>
       <c r="O133" s="4" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P133" s="4" t="n">
         <v>0.36</v>
@@ -14992,10 +14992,10 @@
         <v>0</v>
       </c>
       <c r="AC133" s="4" t="n">
-        <v>49.63</v>
+        <v>49.64</v>
       </c>
       <c r="AD133" s="4" t="n">
-        <v>50.37</v>
+        <v>50.36</v>
       </c>
       <c r="AE133" s="4" t="n">
         <v>0</v>
@@ -15043,7 +15043,7 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>38.77</v>
+        <v>38.76</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>100</v>
@@ -15063,7 +15063,7 @@
         <v>5.62</v>
       </c>
       <c r="O134" s="4" t="n">
-        <v>38.77</v>
+        <v>38.76</v>
       </c>
       <c r="P134" s="4" t="n">
         <v>0</v>
@@ -15142,13 +15142,13 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>-6.38</v>
+        <v>-6.4</v>
       </c>
       <c r="J135" s="4" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>85.5</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="L135" t="inlineStr">
         <is>
@@ -15156,13 +15156,13 @@
         </is>
       </c>
       <c r="M135" s="4" t="n">
-        <v>-11.19</v>
+        <v>-11.2</v>
       </c>
       <c r="N135" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O135" s="4" t="n">
-        <v>-7.99</v>
+        <v>-8</v>
       </c>
       <c r="P135" s="4" t="n">
         <v>-2.59</v>
@@ -15208,10 +15208,10 @@
         <v>0</v>
       </c>
       <c r="AC135" s="4" t="n">
-        <v>46.07</v>
+        <v>46.06</v>
       </c>
       <c r="AD135" s="4" t="n">
-        <v>52.34</v>
+        <v>52.35</v>
       </c>
       <c r="AE135" s="4" t="n">
         <v>0</v>
@@ -15279,7 +15279,7 @@
         <v>5.62</v>
       </c>
       <c r="O136" s="4" t="n">
-        <v>-11.59</v>
+        <v>-11.6</v>
       </c>
       <c r="P136" s="4" t="n">
         <v>-1.45</v>
@@ -15384,7 +15384,7 @@
         </is>
       </c>
       <c r="M137" s="4" t="n">
-        <v>-8.85</v>
+        <v>-8.859999999999999</v>
       </c>
       <c r="N137" s="4" t="n">
         <v>5.62</v>
@@ -15487,13 +15487,13 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>7.12</v>
+        <v>7.11</v>
       </c>
       <c r="J138" s="4" t="n">
-        <v>87.90000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="L138" t="inlineStr">
         <is>
@@ -15507,10 +15507,10 @@
         <v>5.62</v>
       </c>
       <c r="O138" s="4" t="n">
-        <v>6.15</v>
+        <v>6.14</v>
       </c>
       <c r="P138" s="4" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="Q138" s="4" t="n">
         <v>5.55</v>
@@ -15553,10 +15553,10 @@
         <v>0</v>
       </c>
       <c r="AC138" s="4" t="n">
-        <v>52.5</v>
+        <v>52.49</v>
       </c>
       <c r="AD138" s="4" t="n">
-        <v>45.51</v>
+        <v>45.52</v>
       </c>
       <c r="AE138" s="4" t="n">
         <v>0</v>
@@ -15618,7 +15618,7 @@
         </is>
       </c>
       <c r="M139" s="4" t="n">
-        <v>-14.37</v>
+        <v>-14.38</v>
       </c>
       <c r="N139" s="4" t="n">
         <v>5.62</v>
@@ -15703,13 +15703,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>-3.28</v>
+        <v>-3.3</v>
       </c>
       <c r="J140" s="4" t="n">
-        <v>25.5</v>
+        <v>25.4</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>74.5</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="L140" t="inlineStr">
         <is>
@@ -15723,7 +15723,7 @@
         <v>5.62</v>
       </c>
       <c r="O140" s="4" t="n">
-        <v>-4.18</v>
+        <v>-4.19</v>
       </c>
       <c r="P140" s="4" t="n">
         <v>-1.19</v>
@@ -15769,10 +15769,10 @@
         <v>0</v>
       </c>
       <c r="AC140" s="4" t="n">
-        <v>47.55</v>
+        <v>47.54</v>
       </c>
       <c r="AD140" s="4" t="n">
-        <v>50.77</v>
+        <v>50.78</v>
       </c>
       <c r="AE140" s="4" t="n">
         <v>0</v>
@@ -15820,7 +15820,7 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>-17.84</v>
+        <v>-17.85</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>0.4</v>
@@ -16038,7 +16038,7 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>-21.8</v>
+        <v>-21.81</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>0.1</v>
@@ -16052,7 +16052,7 @@
         </is>
       </c>
       <c r="M143" s="4" t="n">
-        <v>-25.18</v>
+        <v>-25.19</v>
       </c>
       <c r="N143" s="4" t="n">
         <v>5.62</v>
@@ -16209,10 +16209,10 @@
         <v>0</v>
       </c>
       <c r="AC144" s="4" t="n">
-        <v>76.04000000000001</v>
+        <v>76.03</v>
       </c>
       <c r="AD144" s="4" t="n">
-        <v>22.46</v>
+        <v>22.47</v>
       </c>
       <c r="AE144" s="4" t="n">
         <v>0</v>
@@ -16274,13 +16274,13 @@
         </is>
       </c>
       <c r="M145" s="4" t="n">
-        <v>-11.24</v>
+        <v>-11.25</v>
       </c>
       <c r="N145" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O145" s="4" t="n">
-        <v>-13.6</v>
+        <v>-13.61</v>
       </c>
       <c r="P145" s="4" t="n">
         <v>-1.45</v>
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>0.19</v>
+        <v>0.23</v>
       </c>
       <c r="J146" s="4" t="n">
-        <v>62.5</v>
+        <v>62.6</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>37.5</v>
+        <v>37.4</v>
       </c>
       <c r="L146" t="inlineStr">
         <is>
@@ -16381,7 +16381,7 @@
         </is>
       </c>
       <c r="M146" s="4" t="n">
-        <v>-3.59</v>
+        <v>-3.6</v>
       </c>
       <c r="N146" s="4" t="n">
         <v>5.62</v>
@@ -16425,10 +16425,10 @@
         <v>0</v>
       </c>
       <c r="AC146" s="4" t="n">
-        <v>50.1</v>
+        <v>50.12</v>
       </c>
       <c r="AD146" s="4" t="n">
-        <v>49.9</v>
+        <v>49.88</v>
       </c>
       <c r="AE146" s="4" t="n">
         <v>0</v>
@@ -16490,7 +16490,7 @@
         </is>
       </c>
       <c r="M147" s="4" t="n">
-        <v>20.82</v>
+        <v>20.81</v>
       </c>
       <c r="N147" s="4" t="n">
         <v>5.62</v>
@@ -16589,7 +16589,7 @@
         </is>
       </c>
       <c r="M148" s="4" t="n">
-        <v>47.94</v>
+        <v>47.93</v>
       </c>
       <c r="N148" s="4" t="n">
         <v>5.62</v>
@@ -16678,13 +16678,13 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>7.52</v>
+        <v>7.79</v>
       </c>
       <c r="J149" s="4" t="n">
-        <v>89.09999999999999</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>10.9</v>
+        <v>10.1</v>
       </c>
       <c r="L149" t="inlineStr">
         <is>
@@ -16692,13 +16692,13 @@
         </is>
       </c>
       <c r="M149" s="4" t="n">
-        <v>-1.78</v>
+        <v>-1.79</v>
       </c>
       <c r="N149" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O149" s="4" t="n">
-        <v>7.23</v>
+        <v>7.22</v>
       </c>
       <c r="P149" s="4" t="n">
         <v>0.15</v>
@@ -16710,16 +16710,16 @@
         <v>-9.220000000000001</v>
       </c>
       <c r="S149" s="4" t="n">
-        <v>42.9</v>
+        <v>51</v>
       </c>
       <c r="T149" s="4" t="n">
-        <v>32.7</v>
+        <v>39</v>
       </c>
       <c r="U149" t="n">
         <v>1</v>
       </c>
       <c r="V149" s="4" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="W149" s="5" t="n">
         <v>2998428</v>
@@ -16744,10 +16744,10 @@
         <v>0</v>
       </c>
       <c r="AC149" s="4" t="n">
-        <v>52.96</v>
+        <v>53.09</v>
       </c>
       <c r="AD149" s="4" t="n">
-        <v>45.54</v>
+        <v>45.41</v>
       </c>
       <c r="AE149" s="4" t="n">
         <v>0</v>
@@ -16815,7 +16815,7 @@
         <v>5.62</v>
       </c>
       <c r="O150" s="4" t="n">
-        <v>-9.94</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="P150" s="4" t="n">
         <v>-1.25</v>
@@ -16855,10 +16855,10 @@
         <v>0</v>
       </c>
       <c r="AC150" s="4" t="n">
-        <v>44.32</v>
+        <v>44.31</v>
       </c>
       <c r="AD150" s="4" t="n">
-        <v>54.18</v>
+        <v>54.19</v>
       </c>
       <c r="AE150" s="4" t="n">
         <v>0</v>
@@ -16906,13 +16906,13 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>-5.22</v>
+        <v>-4.71</v>
       </c>
       <c r="J151" s="4" t="n">
-        <v>18.4</v>
+        <v>20.2</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>81.59999999999999</v>
+        <v>79.8</v>
       </c>
       <c r="L151" t="inlineStr">
         <is>
@@ -16920,13 +16920,13 @@
         </is>
       </c>
       <c r="M151" s="4" t="n">
-        <v>-6.36</v>
+        <v>-6.37</v>
       </c>
       <c r="N151" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O151" s="4" t="n">
-        <v>-5.61</v>
+        <v>-5.62</v>
       </c>
       <c r="P151" s="4" t="n">
         <v>-0.8</v>
@@ -16938,13 +16938,13 @@
         <v>-14.7</v>
       </c>
       <c r="S151" s="4" t="n">
-        <v>43</v>
+        <v>44.92</v>
       </c>
       <c r="T151" s="4" t="n">
-        <v>46</v>
+        <v>45.04</v>
       </c>
       <c r="U151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V151" s="4" t="n">
         <v>-3</v>
@@ -16964,10 +16964,10 @@
         <v>0</v>
       </c>
       <c r="AC151" s="4" t="n">
-        <v>47.39</v>
+        <v>47.65</v>
       </c>
       <c r="AD151" s="4" t="n">
-        <v>52.61</v>
+        <v>52.35</v>
       </c>
       <c r="AE151" s="4" t="n">
         <v>0</v>
@@ -17029,13 +17029,13 @@
         </is>
       </c>
       <c r="M152" s="4" t="n">
-        <v>-15.85</v>
+        <v>-15.86</v>
       </c>
       <c r="N152" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O152" s="4" t="n">
-        <v>-15.35</v>
+        <v>-15.36</v>
       </c>
       <c r="P152" s="4" t="n">
         <v>-0.22</v>
@@ -17128,13 +17128,13 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>-8.09</v>
+        <v>-8.140000000000001</v>
       </c>
       <c r="J153" s="4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>90.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L153" t="inlineStr">
         <is>
@@ -17142,13 +17142,13 @@
         </is>
       </c>
       <c r="M153" s="4" t="n">
-        <v>-11.5</v>
+        <v>-11.55</v>
       </c>
       <c r="N153" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O153" s="4" t="n">
-        <v>-8.09</v>
+        <v>-8.140000000000001</v>
       </c>
       <c r="P153" s="4" t="n">
         <v>-1.91</v>
@@ -17180,10 +17180,10 @@
         <v>0</v>
       </c>
       <c r="AC153" s="4" t="n">
-        <v>45.96</v>
+        <v>45.93</v>
       </c>
       <c r="AD153" s="4" t="n">
-        <v>54.04</v>
+        <v>54.07</v>
       </c>
       <c r="AE153" s="4" t="n">
         <v>0</v>
@@ -17231,7 +17231,7 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>24.55</v>
+        <v>24.5</v>
       </c>
       <c r="J154" s="4" t="n">
         <v>99.90000000000001</v>
@@ -17245,13 +17245,13 @@
         </is>
       </c>
       <c r="M154" s="4" t="n">
-        <v>12.36</v>
+        <v>12.31</v>
       </c>
       <c r="N154" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O154" s="4" t="n">
-        <v>24.55</v>
+        <v>24.5</v>
       </c>
       <c r="P154" s="4" t="n">
         <v>1.14</v>
@@ -17283,10 +17283,10 @@
         <v>0</v>
       </c>
       <c r="AC154" s="4" t="n">
-        <v>62.27</v>
+        <v>62.25</v>
       </c>
       <c r="AD154" s="4" t="n">
-        <v>37.73</v>
+        <v>37.75</v>
       </c>
       <c r="AE154" s="4" t="n">
         <v>0</v>
@@ -17334,7 +17334,7 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>-28.66</v>
+        <v>-28.71</v>
       </c>
       <c r="J155" s="4" t="n">
         <v>0</v>
@@ -17348,13 +17348,13 @@
         </is>
       </c>
       <c r="M155" s="4" t="n">
-        <v>-26.4</v>
+        <v>-26.45</v>
       </c>
       <c r="N155" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O155" s="4" t="n">
-        <v>-28.66</v>
+        <v>-28.71</v>
       </c>
       <c r="P155" s="4" t="n">
         <v>-1.76</v>
@@ -17386,10 +17386,10 @@
         <v>0</v>
       </c>
       <c r="AC155" s="4" t="n">
-        <v>35.67</v>
+        <v>35.64</v>
       </c>
       <c r="AD155" s="4" t="n">
-        <v>64.33</v>
+        <v>64.36</v>
       </c>
       <c r="AE155" s="4" t="n">
         <v>0</v>
@@ -17437,7 +17437,7 @@
         </is>
       </c>
       <c r="I156" s="4" t="n">
-        <v>65.86</v>
+        <v>65.81</v>
       </c>
       <c r="J156" s="4" t="n">
         <v>100</v>
@@ -17451,13 +17451,13 @@
         </is>
       </c>
       <c r="M156" s="4" t="n">
-        <v>58.35</v>
+        <v>58.3</v>
       </c>
       <c r="N156" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O156" s="4" t="n">
-        <v>65.86</v>
+        <v>65.81</v>
       </c>
       <c r="P156" s="4" t="n">
         <v>0</v>
@@ -17489,10 +17489,10 @@
         <v>0</v>
       </c>
       <c r="AC156" s="4" t="n">
-        <v>82.93000000000001</v>
+        <v>82.91</v>
       </c>
       <c r="AD156" s="4" t="n">
-        <v>17.07</v>
+        <v>17.09</v>
       </c>
       <c r="AE156" s="4" t="n">
         <v>0</v>
@@ -17540,7 +17540,7 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>84.31</v>
+        <v>84.26000000000001</v>
       </c>
       <c r="J157" s="4" t="n">
         <v>100</v>
@@ -17554,13 +17554,13 @@
         </is>
       </c>
       <c r="M157" s="4" t="n">
-        <v>76.76000000000001</v>
+        <v>76.70999999999999</v>
       </c>
       <c r="N157" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O157" s="4" t="n">
-        <v>84.31</v>
+        <v>84.26000000000001</v>
       </c>
       <c r="P157" s="4" t="n">
         <v>0</v>
@@ -17592,10 +17592,10 @@
         <v>0</v>
       </c>
       <c r="AC157" s="4" t="n">
-        <v>92.16</v>
+        <v>92.13</v>
       </c>
       <c r="AD157" s="4" t="n">
-        <v>7.84</v>
+        <v>7.87</v>
       </c>
       <c r="AE157" s="4" t="n">
         <v>0</v>
@@ -17643,7 +17643,7 @@
         </is>
       </c>
       <c r="I158" s="4" t="n">
-        <v>63.61</v>
+        <v>63.56</v>
       </c>
       <c r="J158" s="4" t="n">
         <v>100</v>
@@ -17657,13 +17657,13 @@
         </is>
       </c>
       <c r="M158" s="4" t="n">
-        <v>53.89</v>
+        <v>53.84</v>
       </c>
       <c r="N158" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O158" s="4" t="n">
-        <v>63.61</v>
+        <v>63.56</v>
       </c>
       <c r="P158" s="4" t="n">
         <v>2.07</v>
@@ -17695,10 +17695,10 @@
         <v>0</v>
       </c>
       <c r="AC158" s="4" t="n">
-        <v>81.81</v>
+        <v>81.78</v>
       </c>
       <c r="AD158" s="4" t="n">
-        <v>18.19</v>
+        <v>18.22</v>
       </c>
       <c r="AE158" s="4" t="n">
         <v>0</v>
@@ -17746,7 +17746,7 @@
         </is>
       </c>
       <c r="I159" s="4" t="n">
-        <v>-14.22</v>
+        <v>-14.36</v>
       </c>
       <c r="J159" s="4" t="n">
         <v>0.8</v>
@@ -17760,13 +17760,13 @@
         </is>
       </c>
       <c r="M159" s="4" t="n">
-        <v>-18.39</v>
+        <v>-18.44</v>
       </c>
       <c r="N159" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O159" s="4" t="n">
-        <v>-20.42</v>
+        <v>-20.47</v>
       </c>
       <c r="P159" s="4" t="n">
         <v>-1.01</v>
@@ -17804,10 +17804,10 @@
         <v>0</v>
       </c>
       <c r="AC159" s="4" t="n">
-        <v>42.89</v>
+        <v>42.82</v>
       </c>
       <c r="AD159" s="4" t="n">
-        <v>57.11</v>
+        <v>57.18</v>
       </c>
       <c r="AE159" s="4" t="n">
         <v>0</v>
@@ -17855,7 +17855,7 @@
         </is>
       </c>
       <c r="I160" s="4" t="n">
-        <v>-29.03</v>
+        <v>-29.08</v>
       </c>
       <c r="J160" s="4" t="n">
         <v>0</v>
@@ -17869,13 +17869,13 @@
         </is>
       </c>
       <c r="M160" s="4" t="n">
-        <v>-26.22</v>
+        <v>-26.27</v>
       </c>
       <c r="N160" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O160" s="4" t="n">
-        <v>-29.03</v>
+        <v>-29.08</v>
       </c>
       <c r="P160" s="4" t="n">
         <v>-2.12</v>
@@ -17907,10 +17907,10 @@
         <v>0</v>
       </c>
       <c r="AC160" s="4" t="n">
-        <v>35.49</v>
+        <v>35.46</v>
       </c>
       <c r="AD160" s="4" t="n">
-        <v>64.51000000000001</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="AE160" s="4" t="n">
         <v>0</v>
@@ -17958,7 +17958,7 @@
         </is>
       </c>
       <c r="I161" s="4" t="n">
-        <v>-30.1</v>
+        <v>-30.15</v>
       </c>
       <c r="J161" s="4" t="n">
         <v>0</v>
@@ -17972,13 +17972,13 @@
         </is>
       </c>
       <c r="M161" s="4" t="n">
-        <v>-30.54</v>
+        <v>-30.59</v>
       </c>
       <c r="N161" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O161" s="4" t="n">
-        <v>-30.1</v>
+        <v>-30.15</v>
       </c>
       <c r="P161" s="4" t="n">
         <v>-1.43</v>
@@ -18010,10 +18010,10 @@
         <v>0</v>
       </c>
       <c r="AC161" s="4" t="n">
-        <v>34.95</v>
+        <v>34.93</v>
       </c>
       <c r="AD161" s="4" t="n">
-        <v>65.05</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="AE161" s="4" t="n">
         <v>0</v>
@@ -18057,7 +18057,7 @@
         </is>
       </c>
       <c r="I162" s="4" t="n">
-        <v>-15.73</v>
+        <v>-15.78</v>
       </c>
       <c r="J162" s="4" t="n">
         <v>0.6</v>
@@ -18071,13 +18071,13 @@
         </is>
       </c>
       <c r="M162" s="4" t="n">
-        <v>-17.48</v>
+        <v>-17.53</v>
       </c>
       <c r="N162" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O162" s="4" t="n">
-        <v>-15.73</v>
+        <v>-15.78</v>
       </c>
       <c r="P162" s="4" t="n">
         <v>-2.86</v>
@@ -18109,10 +18109,10 @@
         <v>0</v>
       </c>
       <c r="AC162" s="4" t="n">
-        <v>42.13</v>
+        <v>42.11</v>
       </c>
       <c r="AD162" s="4" t="n">
-        <v>57.87</v>
+        <v>57.89</v>
       </c>
       <c r="AE162" s="4" t="n">
         <v>0</v>
@@ -18156,7 +18156,7 @@
         </is>
       </c>
       <c r="I163" s="4" t="n">
-        <v>-16.83</v>
+        <v>-16.88</v>
       </c>
       <c r="J163" s="4" t="n">
         <v>0.5</v>
@@ -18170,13 +18170,13 @@
         </is>
       </c>
       <c r="M163" s="4" t="n">
-        <v>-19.91</v>
+        <v>-19.96</v>
       </c>
       <c r="N163" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O163" s="4" t="n">
-        <v>-16.83</v>
+        <v>-16.88</v>
       </c>
       <c r="P163" s="4" t="n">
         <v>-2.21</v>
@@ -18208,10 +18208,10 @@
         <v>0</v>
       </c>
       <c r="AC163" s="4" t="n">
-        <v>41.58</v>
+        <v>41.56</v>
       </c>
       <c r="AD163" s="4" t="n">
-        <v>58.42</v>
+        <v>58.44</v>
       </c>
       <c r="AE163" s="4" t="n">
         <v>0</v>
@@ -18259,13 +18259,13 @@
         </is>
       </c>
       <c r="I164" s="4" t="n">
-        <v>-11.17</v>
+        <v>-11.22</v>
       </c>
       <c r="J164" s="4" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="K164" s="4" t="n">
-        <v>98.5</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="L164" t="inlineStr">
         <is>
@@ -18273,13 +18273,13 @@
         </is>
       </c>
       <c r="M164" s="4" t="n">
-        <v>-9.369999999999999</v>
+        <v>-9.42</v>
       </c>
       <c r="N164" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O164" s="4" t="n">
-        <v>-11.17</v>
+        <v>-11.22</v>
       </c>
       <c r="P164" s="4" t="n">
         <v>-1.96</v>
@@ -18311,10 +18311,10 @@
         <v>0</v>
       </c>
       <c r="AC164" s="4" t="n">
-        <v>44.42</v>
+        <v>44.39</v>
       </c>
       <c r="AD164" s="4" t="n">
-        <v>55.58</v>
+        <v>55.61</v>
       </c>
       <c r="AE164" s="4" t="n">
         <v>0</v>
@@ -18358,7 +18358,7 @@
         </is>
       </c>
       <c r="I165" s="4" t="n">
-        <v>51.4</v>
+        <v>51.35</v>
       </c>
       <c r="J165" s="4" t="n">
         <v>100</v>
@@ -18372,13 +18372,13 @@
         </is>
       </c>
       <c r="M165" s="4" t="n">
-        <v>45.51</v>
+        <v>45.46</v>
       </c>
       <c r="N165" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O165" s="4" t="n">
-        <v>51.4</v>
+        <v>51.35</v>
       </c>
       <c r="P165" s="4" t="n">
         <v>0</v>
@@ -18410,10 +18410,10 @@
         <v>0</v>
       </c>
       <c r="AC165" s="4" t="n">
-        <v>75.7</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="AD165" s="4" t="n">
-        <v>24.3</v>
+        <v>24.32</v>
       </c>
       <c r="AE165" s="4" t="n">
         <v>0</v>
@@ -18461,7 +18461,7 @@
         </is>
       </c>
       <c r="I166" s="4" t="n">
-        <v>-21.22</v>
+        <v>-21.27</v>
       </c>
       <c r="J166" s="4" t="n">
         <v>0.2</v>
@@ -18475,13 +18475,13 @@
         </is>
       </c>
       <c r="M166" s="4" t="n">
-        <v>-33.83</v>
+        <v>-33.88</v>
       </c>
       <c r="N166" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O166" s="4" t="n">
-        <v>-21.22</v>
+        <v>-21.27</v>
       </c>
       <c r="P166" s="4" t="n">
         <v>0.62</v>
@@ -18513,10 +18513,10 @@
         <v>0</v>
       </c>
       <c r="AC166" s="4" t="n">
-        <v>39.39</v>
+        <v>39.36</v>
       </c>
       <c r="AD166" s="4" t="n">
-        <v>60.61</v>
+        <v>60.64</v>
       </c>
       <c r="AE166" s="4" t="n">
         <v>0</v>
@@ -18905,13 +18905,13 @@
         </is>
       </c>
       <c r="M170" s="4" t="n">
-        <v>-1.82</v>
+        <v>-1.83</v>
       </c>
       <c r="N170" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O170" s="4" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="P170" s="4" t="n">
         <v>0.18</v>
@@ -19008,7 +19008,7 @@
         </is>
       </c>
       <c r="I171" s="4" t="n">
-        <v>5.78</v>
+        <v>5.77</v>
       </c>
       <c r="J171" s="4" t="n">
         <v>83.5</v>
@@ -19066,10 +19066,10 @@
         <v>0</v>
       </c>
       <c r="AC171" s="4" t="n">
-        <v>52.89</v>
+        <v>52.88</v>
       </c>
       <c r="AD171" s="4" t="n">
-        <v>47.11</v>
+        <v>47.12</v>
       </c>
       <c r="AE171" s="4" t="n">
         <v>0</v>
@@ -19113,7 +19113,7 @@
         </is>
       </c>
       <c r="I172" s="4" t="n">
-        <v>-19.88</v>
+        <v>-19.89</v>
       </c>
       <c r="J172" s="4" t="n">
         <v>0.2</v>
@@ -19127,13 +19127,13 @@
         </is>
       </c>
       <c r="M172" s="4" t="n">
-        <v>-23.8</v>
+        <v>-23.81</v>
       </c>
       <c r="N172" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O172" s="4" t="n">
-        <v>-19.88</v>
+        <v>-19.89</v>
       </c>
       <c r="P172" s="4" t="n">
         <v>-1.08</v>
@@ -19216,7 +19216,7 @@
         </is>
       </c>
       <c r="I173" s="4" t="n">
-        <v>-32.41</v>
+        <v>-32.53</v>
       </c>
       <c r="J173" s="4" t="n">
         <v>0</v>
@@ -19230,13 +19230,13 @@
         </is>
       </c>
       <c r="M173" s="4" t="n">
-        <v>-44.9</v>
+        <v>-44.92</v>
       </c>
       <c r="N173" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O173" s="4" t="n">
-        <v>-41.97</v>
+        <v>-41.99</v>
       </c>
       <c r="P173" s="4" t="n">
         <v>-0.84</v>
@@ -19282,10 +19282,10 @@
         <v>0</v>
       </c>
       <c r="AC173" s="4" t="n">
-        <v>30.49</v>
+        <v>30.43</v>
       </c>
       <c r="AD173" s="4" t="n">
-        <v>59.72</v>
+        <v>59.78</v>
       </c>
       <c r="AE173" s="4" t="n">
         <v>3.81</v>
@@ -19333,7 +19333,7 @@
         </is>
       </c>
       <c r="I174" s="4" t="n">
-        <v>-27.86</v>
+        <v>-27.88</v>
       </c>
       <c r="J174" s="4" t="n">
         <v>0</v>
@@ -19347,13 +19347,13 @@
         </is>
       </c>
       <c r="M174" s="4" t="n">
-        <v>-27.08</v>
+        <v>-27.1</v>
       </c>
       <c r="N174" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O174" s="4" t="n">
-        <v>-28.61</v>
+        <v>-28.63</v>
       </c>
       <c r="P174" s="4" t="n">
         <v>-1.51</v>
@@ -19393,10 +19393,10 @@
         <v>0</v>
       </c>
       <c r="AC174" s="4" t="n">
-        <v>32.46</v>
+        <v>32.45</v>
       </c>
       <c r="AD174" s="4" t="n">
-        <v>57.54</v>
+        <v>57.55</v>
       </c>
       <c r="AE174" s="4" t="n">
         <v>5</v>
@@ -19745,7 +19745,7 @@
         </is>
       </c>
       <c r="I178" s="4" t="n">
-        <v>37.26</v>
+        <v>37.38</v>
       </c>
       <c r="J178" s="4" t="n">
         <v>100</v>
@@ -19811,10 +19811,10 @@
         <v>0</v>
       </c>
       <c r="AC178" s="4" t="n">
-        <v>60.5</v>
+        <v>60.55</v>
       </c>
       <c r="AD178" s="4" t="n">
-        <v>27.65</v>
+        <v>27.6</v>
       </c>
       <c r="AE178" s="4" t="n">
         <v>2.85</v>
@@ -21609,7 +21609,7 @@
         </is>
       </c>
       <c r="I196" s="4" t="n">
-        <v>-12.71</v>
+        <v>-12.74</v>
       </c>
       <c r="J196" s="4" t="n">
         <v>1</v>
@@ -21667,10 +21667,10 @@
         <v>0</v>
       </c>
       <c r="AC196" s="4" t="n">
-        <v>43.65</v>
+        <v>43.63</v>
       </c>
       <c r="AD196" s="4" t="n">
-        <v>56.35</v>
+        <v>56.37</v>
       </c>
       <c r="AE196" s="4" t="n">
         <v>0</v>
@@ -22146,7 +22146,7 @@
         </is>
       </c>
       <c r="I201" s="4" t="n">
-        <v>-29.4</v>
+        <v>-29.42</v>
       </c>
       <c r="J201" s="4" t="n">
         <v>0</v>
@@ -22160,13 +22160,13 @@
         </is>
       </c>
       <c r="M201" s="4" t="n">
-        <v>-27.75</v>
+        <v>-27.77</v>
       </c>
       <c r="N201" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O201" s="4" t="n">
-        <v>-29.94</v>
+        <v>-29.96</v>
       </c>
       <c r="P201" s="4" t="n">
         <v>-2.06</v>
@@ -22206,10 +22206,10 @@
         <v>0</v>
       </c>
       <c r="AC201" s="4" t="n">
-        <v>34.35</v>
+        <v>34.34</v>
       </c>
       <c r="AD201" s="4" t="n">
-        <v>62.97</v>
+        <v>62.98</v>
       </c>
       <c r="AE201" s="4" t="n">
         <v>0</v>
@@ -22257,7 +22257,7 @@
         </is>
       </c>
       <c r="I202" s="4" t="n">
-        <v>-15.19</v>
+        <v>-15.21</v>
       </c>
       <c r="J202" s="4" t="n">
         <v>0.6</v>
@@ -22271,13 +22271,13 @@
         </is>
       </c>
       <c r="M202" s="4" t="n">
-        <v>-15.32</v>
+        <v>-15.34</v>
       </c>
       <c r="N202" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O202" s="4" t="n">
-        <v>-15.76</v>
+        <v>-15.78</v>
       </c>
       <c r="P202" s="4" t="n">
         <v>-0.47</v>
@@ -22317,10 +22317,10 @@
         <v>0</v>
       </c>
       <c r="AC202" s="4" t="n">
-        <v>41.2</v>
+        <v>41.19</v>
       </c>
       <c r="AD202" s="4" t="n">
-        <v>55.96</v>
+        <v>55.97</v>
       </c>
       <c r="AE202" s="4" t="n">
         <v>0</v>
@@ -22368,7 +22368,7 @@
         </is>
       </c>
       <c r="I203" s="4" t="n">
-        <v>23.6</v>
+        <v>23.58</v>
       </c>
       <c r="J203" s="4" t="n">
         <v>99.90000000000001</v>
@@ -22382,13 +22382,13 @@
         </is>
       </c>
       <c r="M203" s="4" t="n">
-        <v>7.65</v>
+        <v>7.63</v>
       </c>
       <c r="N203" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O203" s="4" t="n">
-        <v>23.01</v>
+        <v>22.99</v>
       </c>
       <c r="P203" s="4" t="n">
         <v>3</v>
@@ -22428,10 +22428,10 @@
         <v>0</v>
       </c>
       <c r="AC203" s="4" t="n">
-        <v>59.98</v>
+        <v>59.97</v>
       </c>
       <c r="AD203" s="4" t="n">
-        <v>37.08</v>
+        <v>37.09</v>
       </c>
       <c r="AE203" s="4" t="n">
         <v>0</v>
@@ -22479,7 +22479,7 @@
         </is>
       </c>
       <c r="I204" s="4" t="n">
-        <v>-20.64</v>
+        <v>-20.66</v>
       </c>
       <c r="J204" s="4" t="n">
         <v>0.2</v>
@@ -22493,13 +22493,13 @@
         </is>
       </c>
       <c r="M204" s="4" t="n">
-        <v>-19.7</v>
+        <v>-19.73</v>
       </c>
       <c r="N204" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O204" s="4" t="n">
-        <v>-21.22</v>
+        <v>-21.24</v>
       </c>
       <c r="P204" s="4" t="n">
         <v>-1.43</v>
@@ -22539,10 +22539,10 @@
         <v>0</v>
       </c>
       <c r="AC204" s="4" t="n">
-        <v>38.54</v>
+        <v>38.53</v>
       </c>
       <c r="AD204" s="4" t="n">
-        <v>58.58</v>
+        <v>58.59</v>
       </c>
       <c r="AE204" s="4" t="n">
         <v>0</v>
@@ -22590,7 +22590,7 @@
         </is>
       </c>
       <c r="I205" s="4" t="n">
-        <v>-44.54</v>
+        <v>-44.56</v>
       </c>
       <c r="J205" s="4" t="n">
         <v>0</v>
@@ -22604,13 +22604,13 @@
         </is>
       </c>
       <c r="M205" s="4" t="n">
-        <v>-45.03</v>
+        <v>-45.04</v>
       </c>
       <c r="N205" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O205" s="4" t="n">
-        <v>-44.54</v>
+        <v>-44.56</v>
       </c>
       <c r="P205" s="4" t="n">
         <v>-1.84</v>
@@ -22642,10 +22642,10 @@
         <v>0</v>
       </c>
       <c r="AC205" s="4" t="n">
-        <v>27.73</v>
+        <v>27.72</v>
       </c>
       <c r="AD205" s="4" t="n">
-        <v>72.27</v>
+        <v>72.28</v>
       </c>
       <c r="AE205" s="4" t="n">
         <v>0</v>
@@ -22693,7 +22693,7 @@
         </is>
       </c>
       <c r="I206" s="4" t="n">
-        <v>-42.32</v>
+        <v>-42.34</v>
       </c>
       <c r="J206" s="4" t="n">
         <v>0</v>
@@ -22707,13 +22707,13 @@
         </is>
       </c>
       <c r="M206" s="4" t="n">
-        <v>-39.13</v>
+        <v>-39.15</v>
       </c>
       <c r="N206" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O206" s="4" t="n">
-        <v>-42.22</v>
+        <v>-42.24</v>
       </c>
       <c r="P206" s="4" t="n">
         <v>-3.32</v>
@@ -22753,10 +22753,10 @@
         <v>0</v>
       </c>
       <c r="AC206" s="4" t="n">
-        <v>28.26</v>
+        <v>28.25</v>
       </c>
       <c r="AD206" s="4" t="n">
-        <v>69.73</v>
+        <v>69.73999999999999</v>
       </c>
       <c r="AE206" s="4" t="n">
         <v>0</v>
@@ -22804,7 +22804,7 @@
         </is>
       </c>
       <c r="I207" s="4" t="n">
-        <v>34.74</v>
+        <v>34.72</v>
       </c>
       <c r="J207" s="4" t="n">
         <v>100</v>
@@ -22818,13 +22818,13 @@
         </is>
       </c>
       <c r="M207" s="4" t="n">
-        <v>21.62</v>
+        <v>21.6</v>
       </c>
       <c r="N207" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O207" s="4" t="n">
-        <v>34.74</v>
+        <v>34.72</v>
       </c>
       <c r="P207" s="4" t="n">
         <v>2.21</v>
@@ -22856,10 +22856,10 @@
         <v>0</v>
       </c>
       <c r="AC207" s="4" t="n">
-        <v>67.37</v>
+        <v>67.36</v>
       </c>
       <c r="AD207" s="4" t="n">
-        <v>32.63</v>
+        <v>32.64</v>
       </c>
       <c r="AE207" s="4" t="n">
         <v>0</v>
@@ -22903,7 +22903,7 @@
         </is>
       </c>
       <c r="I208" s="4" t="n">
-        <v>-29.12</v>
+        <v>-29.14</v>
       </c>
       <c r="J208" s="4" t="n">
         <v>0</v>
@@ -22917,13 +22917,13 @@
         </is>
       </c>
       <c r="M208" s="4" t="n">
-        <v>-33.91</v>
+        <v>-33.92</v>
       </c>
       <c r="N208" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O208" s="4" t="n">
-        <v>-29.58</v>
+        <v>-29.6</v>
       </c>
       <c r="P208" s="4" t="n">
         <v>-0.46</v>
@@ -22963,10 +22963,10 @@
         <v>0</v>
       </c>
       <c r="AC208" s="4" t="n">
-        <v>34.62</v>
+        <v>34.61</v>
       </c>
       <c r="AD208" s="4" t="n">
-        <v>63.06</v>
+        <v>63.07</v>
       </c>
       <c r="AE208" s="4" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
         </is>
       </c>
       <c r="I209" s="4" t="n">
-        <v>-59.81</v>
+        <v>-59.83</v>
       </c>
       <c r="J209" s="4" t="n">
         <v>0</v>
@@ -23028,13 +23028,13 @@
         </is>
       </c>
       <c r="M209" s="4" t="n">
-        <v>-61.69</v>
+        <v>-61.71</v>
       </c>
       <c r="N209" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O209" s="4" t="n">
-        <v>-59.74</v>
+        <v>-59.75</v>
       </c>
       <c r="P209" s="4" t="n">
         <v>-1.02</v>
@@ -23074,10 +23074,10 @@
         <v>0</v>
       </c>
       <c r="AC209" s="4" t="n">
-        <v>19.79</v>
+        <v>19.78</v>
       </c>
       <c r="AD209" s="4" t="n">
-        <v>78.70999999999999</v>
+        <v>78.72</v>
       </c>
       <c r="AE209" s="4" t="n">
         <v>0</v>
@@ -23121,13 +23121,13 @@
         </is>
       </c>
       <c r="I210" s="4" t="n">
-        <v>-5.11</v>
+        <v>-5.14</v>
       </c>
       <c r="J210" s="4" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="K210" s="4" t="n">
-        <v>81.2</v>
+        <v>81.3</v>
       </c>
       <c r="L210" t="inlineStr">
         <is>
@@ -23135,13 +23135,13 @@
         </is>
       </c>
       <c r="M210" s="4" t="n">
-        <v>-12.89</v>
+        <v>-12.91</v>
       </c>
       <c r="N210" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O210" s="4" t="n">
-        <v>-7.91</v>
+        <v>-7.93</v>
       </c>
       <c r="P210" s="4" t="n">
         <v>0.03</v>
@@ -23187,10 +23187,10 @@
         <v>0</v>
       </c>
       <c r="AC210" s="4" t="n">
-        <v>46.23</v>
+        <v>46.22</v>
       </c>
       <c r="AD210" s="4" t="n">
-        <v>51.21</v>
+        <v>51.22</v>
       </c>
       <c r="AE210" s="4" t="n">
         <v>0</v>
@@ -23880,7 +23880,7 @@
         </is>
       </c>
       <c r="I217" s="4" t="n">
-        <v>24.07</v>
+        <v>24.08</v>
       </c>
       <c r="J217" s="4" t="n">
         <v>99.90000000000001</v>
@@ -23894,13 +23894,13 @@
         </is>
       </c>
       <c r="M217" s="4" t="n">
-        <v>17.06</v>
+        <v>17.08</v>
       </c>
       <c r="N217" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O217" s="4" t="n">
-        <v>24.23</v>
+        <v>24.24</v>
       </c>
       <c r="P217" s="4" t="n">
         <v>0</v>
@@ -23940,10 +23940,10 @@
         <v>0</v>
       </c>
       <c r="AC217" s="4" t="n">
-        <v>60.02</v>
+        <v>60.03</v>
       </c>
       <c r="AD217" s="4" t="n">
-        <v>36.74</v>
+        <v>36.73</v>
       </c>
       <c r="AE217" s="4" t="n">
         <v>0</v>
@@ -23991,7 +23991,7 @@
         </is>
       </c>
       <c r="I218" s="4" t="n">
-        <v>33.85</v>
+        <v>33.86</v>
       </c>
       <c r="J218" s="4" t="n">
         <v>100</v>
@@ -24005,13 +24005,13 @@
         </is>
       </c>
       <c r="M218" s="4" t="n">
-        <v>27.01</v>
+        <v>27.02</v>
       </c>
       <c r="N218" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O218" s="4" t="n">
-        <v>33.85</v>
+        <v>33.86</v>
       </c>
       <c r="P218" s="4" t="n">
         <v>0</v>
@@ -24043,10 +24043,10 @@
         <v>0</v>
       </c>
       <c r="AC218" s="4" t="n">
-        <v>66.92</v>
+        <v>66.93000000000001</v>
       </c>
       <c r="AD218" s="4" t="n">
-        <v>33.08</v>
+        <v>33.07</v>
       </c>
       <c r="AE218" s="4" t="n">
         <v>0</v>
@@ -24094,7 +24094,7 @@
         </is>
       </c>
       <c r="I219" s="4" t="n">
-        <v>32.43</v>
+        <v>32.44</v>
       </c>
       <c r="J219" s="4" t="n">
         <v>100</v>
@@ -24108,13 +24108,13 @@
         </is>
       </c>
       <c r="M219" s="4" t="n">
-        <v>22.52</v>
+        <v>22.53</v>
       </c>
       <c r="N219" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O219" s="4" t="n">
-        <v>32.43</v>
+        <v>32.44</v>
       </c>
       <c r="P219" s="4" t="n">
         <v>2.54</v>
@@ -24146,10 +24146,10 @@
         <v>0</v>
       </c>
       <c r="AC219" s="4" t="n">
-        <v>66.20999999999999</v>
+        <v>66.22</v>
       </c>
       <c r="AD219" s="4" t="n">
-        <v>33.79</v>
+        <v>33.78</v>
       </c>
       <c r="AE219" s="4" t="n">
         <v>0</v>
@@ -24197,7 +24197,7 @@
         </is>
       </c>
       <c r="I220" s="4" t="n">
-        <v>32.83</v>
+        <v>32.84</v>
       </c>
       <c r="J220" s="4" t="n">
         <v>100</v>
@@ -24211,13 +24211,13 @@
         </is>
       </c>
       <c r="M220" s="4" t="n">
-        <v>23.34</v>
+        <v>23.35</v>
       </c>
       <c r="N220" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O220" s="4" t="n">
-        <v>32.83</v>
+        <v>32.84</v>
       </c>
       <c r="P220" s="4" t="n">
         <v>2.92</v>
@@ -24249,10 +24249,10 @@
         <v>0</v>
       </c>
       <c r="AC220" s="4" t="n">
-        <v>66.41</v>
+        <v>66.42</v>
       </c>
       <c r="AD220" s="4" t="n">
-        <v>33.59</v>
+        <v>33.58</v>
       </c>
       <c r="AE220" s="4" t="n">
         <v>0</v>
@@ -24300,7 +24300,7 @@
         </is>
       </c>
       <c r="I221" s="4" t="n">
-        <v>55.52</v>
+        <v>55.54</v>
       </c>
       <c r="J221" s="4" t="n">
         <v>100</v>
@@ -24314,13 +24314,13 @@
         </is>
       </c>
       <c r="M221" s="4" t="n">
-        <v>48.7</v>
+        <v>48.71</v>
       </c>
       <c r="N221" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O221" s="4" t="n">
-        <v>55.52</v>
+        <v>55.54</v>
       </c>
       <c r="P221" s="4" t="n">
         <v>0</v>
@@ -24352,10 +24352,10 @@
         <v>0</v>
       </c>
       <c r="AC221" s="4" t="n">
-        <v>77.76000000000001</v>
+        <v>77.77</v>
       </c>
       <c r="AD221" s="4" t="n">
-        <v>22.24</v>
+        <v>22.23</v>
       </c>
       <c r="AE221" s="4" t="n">
         <v>0</v>
@@ -24399,7 +24399,7 @@
         </is>
       </c>
       <c r="I222" s="4" t="n">
-        <v>30.43</v>
+        <v>30.44</v>
       </c>
       <c r="J222" s="4" t="n">
         <v>100</v>
@@ -24413,13 +24413,13 @@
         </is>
       </c>
       <c r="M222" s="4" t="n">
-        <v>23.54</v>
+        <v>23.56</v>
       </c>
       <c r="N222" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O222" s="4" t="n">
-        <v>30.43</v>
+        <v>30.44</v>
       </c>
       <c r="P222" s="4" t="n">
         <v>1.76</v>
@@ -24451,10 +24451,10 @@
         <v>0</v>
       </c>
       <c r="AC222" s="4" t="n">
-        <v>65.20999999999999</v>
+        <v>65.22</v>
       </c>
       <c r="AD222" s="4" t="n">
-        <v>34.79</v>
+        <v>34.78</v>
       </c>
       <c r="AE222" s="4" t="n">
         <v>0</v>
@@ -24502,7 +24502,7 @@
         </is>
       </c>
       <c r="I223" s="4" t="n">
-        <v>76.31999999999999</v>
+        <v>76.33</v>
       </c>
       <c r="J223" s="4" t="n">
         <v>100</v>
@@ -24516,13 +24516,13 @@
         </is>
       </c>
       <c r="M223" s="4" t="n">
-        <v>68.70999999999999</v>
+        <v>68.72</v>
       </c>
       <c r="N223" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O223" s="4" t="n">
-        <v>76.31999999999999</v>
+        <v>76.33</v>
       </c>
       <c r="P223" s="4" t="n">
         <v>0</v>
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="I224" s="4" t="n">
-        <v>45.63</v>
+        <v>45.65</v>
       </c>
       <c r="J224" s="4" t="n">
         <v>100</v>
@@ -24619,13 +24619,13 @@
         </is>
       </c>
       <c r="M224" s="4" t="n">
-        <v>30.11</v>
+        <v>30.12</v>
       </c>
       <c r="N224" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O224" s="4" t="n">
-        <v>45.63</v>
+        <v>45.65</v>
       </c>
       <c r="P224" s="4" t="n">
         <v>0</v>
@@ -24708,7 +24708,7 @@
         </is>
       </c>
       <c r="I225" s="4" t="n">
-        <v>22.7</v>
+        <v>22.71</v>
       </c>
       <c r="J225" s="4" t="n">
         <v>99.90000000000001</v>
@@ -24722,13 +24722,13 @@
         </is>
       </c>
       <c r="M225" s="4" t="n">
-        <v>13.58</v>
+        <v>13.6</v>
       </c>
       <c r="N225" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O225" s="4" t="n">
-        <v>22.7</v>
+        <v>22.71</v>
       </c>
       <c r="P225" s="4" t="n">
         <v>0.5600000000000001</v>
@@ -24811,7 +24811,7 @@
         </is>
       </c>
       <c r="I226" s="4" t="n">
-        <v>-15.67</v>
+        <v>-15.65</v>
       </c>
       <c r="J226" s="4" t="n">
         <v>0.6</v>
@@ -24825,13 +24825,13 @@
         </is>
       </c>
       <c r="M226" s="4" t="n">
-        <v>-16.12</v>
+        <v>-16.11</v>
       </c>
       <c r="N226" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O226" s="4" t="n">
-        <v>-15.55</v>
+        <v>-15.53</v>
       </c>
       <c r="P226" s="4" t="n">
         <v>-0.86</v>
@@ -24920,7 +24920,7 @@
         </is>
       </c>
       <c r="I227" s="4" t="n">
-        <v>31.56</v>
+        <v>31.58</v>
       </c>
       <c r="J227" s="4" t="n">
         <v>100</v>
@@ -24934,13 +24934,13 @@
         </is>
       </c>
       <c r="M227" s="4" t="n">
-        <v>20.1</v>
+        <v>20.12</v>
       </c>
       <c r="N227" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O227" s="4" t="n">
-        <v>31.56</v>
+        <v>31.58</v>
       </c>
       <c r="P227" s="4" t="n">
         <v>2.06</v>
@@ -24972,10 +24972,10 @@
         <v>0</v>
       </c>
       <c r="AC227" s="4" t="n">
-        <v>65.78</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="AD227" s="4" t="n">
-        <v>34.22</v>
+        <v>34.21</v>
       </c>
       <c r="AE227" s="4" t="n">
         <v>0</v>
@@ -25023,7 +25023,7 @@
         </is>
       </c>
       <c r="I228" s="4" t="n">
-        <v>35.32</v>
+        <v>35.34</v>
       </c>
       <c r="J228" s="4" t="n">
         <v>100</v>
@@ -25037,13 +25037,13 @@
         </is>
       </c>
       <c r="M228" s="4" t="n">
-        <v>25.32</v>
+        <v>25.34</v>
       </c>
       <c r="N228" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O228" s="4" t="n">
-        <v>35.32</v>
+        <v>35.34</v>
       </c>
       <c r="P228" s="4" t="n">
         <v>2.21</v>
@@ -25075,10 +25075,10 @@
         <v>0</v>
       </c>
       <c r="AC228" s="4" t="n">
-        <v>67.66</v>
+        <v>67.67</v>
       </c>
       <c r="AD228" s="4" t="n">
-        <v>32.34</v>
+        <v>32.33</v>
       </c>
       <c r="AE228" s="4" t="n">
         <v>0</v>
@@ -25126,7 +25126,7 @@
         </is>
       </c>
       <c r="I229" s="4" t="n">
-        <v>86.27</v>
+        <v>86.29000000000001</v>
       </c>
       <c r="J229" s="4" t="n">
         <v>100</v>
@@ -25140,13 +25140,13 @@
         </is>
       </c>
       <c r="M229" s="4" t="n">
-        <v>78.8</v>
+        <v>78.81999999999999</v>
       </c>
       <c r="N229" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O229" s="4" t="n">
-        <v>87.02</v>
+        <v>87.03</v>
       </c>
       <c r="P229" s="4" t="n">
         <v>0</v>
@@ -25186,10 +25186,10 @@
         <v>0</v>
       </c>
       <c r="AC229" s="4" t="n">
-        <v>90.34999999999999</v>
+        <v>90.36</v>
       </c>
       <c r="AD229" s="4" t="n">
-        <v>6.66</v>
+        <v>6.65</v>
       </c>
       <c r="AE229" s="4" t="n">
         <v>0</v>
@@ -25233,7 +25233,7 @@
         </is>
       </c>
       <c r="I230" s="4" t="n">
-        <v>40.25</v>
+        <v>40.27</v>
       </c>
       <c r="J230" s="4" t="n">
         <v>100</v>
@@ -25247,13 +25247,13 @@
         </is>
       </c>
       <c r="M230" s="4" t="n">
-        <v>35.21</v>
+        <v>35.23</v>
       </c>
       <c r="N230" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O230" s="4" t="n">
-        <v>40.25</v>
+        <v>40.27</v>
       </c>
       <c r="P230" s="4" t="n">
         <v>0</v>
@@ -25285,10 +25285,10 @@
         <v>0</v>
       </c>
       <c r="AC230" s="4" t="n">
-        <v>70.13</v>
+        <v>70.14</v>
       </c>
       <c r="AD230" s="4" t="n">
-        <v>29.87</v>
+        <v>29.86</v>
       </c>
       <c r="AE230" s="4" t="n">
         <v>0</v>
@@ -25336,7 +25336,7 @@
         </is>
       </c>
       <c r="I231" s="4" t="n">
-        <v>18.69</v>
+        <v>18.71</v>
       </c>
       <c r="J231" s="4" t="n">
         <v>99.7</v>
@@ -25350,13 +25350,13 @@
         </is>
       </c>
       <c r="M231" s="4" t="n">
-        <v>7.59</v>
+        <v>7.6</v>
       </c>
       <c r="N231" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O231" s="4" t="n">
-        <v>19.58</v>
+        <v>19.6</v>
       </c>
       <c r="P231" s="4" t="n">
         <v>2.47</v>
@@ -25396,10 +25396,10 @@
         <v>0</v>
       </c>
       <c r="AC231" s="4" t="n">
-        <v>57.23</v>
+        <v>57.24</v>
       </c>
       <c r="AD231" s="4" t="n">
-        <v>39.21</v>
+        <v>39.2</v>
       </c>
       <c r="AE231" s="4" t="n">
         <v>0</v>
@@ -25447,7 +25447,7 @@
         </is>
       </c>
       <c r="I232" s="4" t="n">
-        <v>72.31999999999999</v>
+        <v>72.34</v>
       </c>
       <c r="J232" s="4" t="n">
         <v>100</v>
@@ -25461,13 +25461,13 @@
         </is>
       </c>
       <c r="M232" s="4" t="n">
-        <v>62.68</v>
+        <v>62.7</v>
       </c>
       <c r="N232" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O232" s="4" t="n">
-        <v>72.31999999999999</v>
+        <v>72.34</v>
       </c>
       <c r="P232" s="4" t="n">
         <v>0</v>
@@ -25499,10 +25499,10 @@
         <v>0</v>
       </c>
       <c r="AC232" s="4" t="n">
-        <v>86.16</v>
+        <v>86.17</v>
       </c>
       <c r="AD232" s="4" t="n">
-        <v>13.84</v>
+        <v>13.83</v>
       </c>
       <c r="AE232" s="4" t="n">
         <v>0</v>
@@ -25550,7 +25550,7 @@
         </is>
       </c>
       <c r="I233" s="4" t="n">
-        <v>68.87</v>
+        <v>68.88</v>
       </c>
       <c r="J233" s="4" t="n">
         <v>100</v>
@@ -25564,13 +25564,13 @@
         </is>
       </c>
       <c r="M233" s="4" t="n">
-        <v>60.53</v>
+        <v>60.55</v>
       </c>
       <c r="N233" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O233" s="4" t="n">
-        <v>69.81</v>
+        <v>69.83</v>
       </c>
       <c r="P233" s="4" t="n">
         <v>3.54</v>
@@ -25610,10 +25610,10 @@
         <v>0</v>
       </c>
       <c r="AC233" s="4" t="n">
-        <v>81.23999999999999</v>
+        <v>81.25</v>
       </c>
       <c r="AD233" s="4" t="n">
-        <v>14.98</v>
+        <v>14.97</v>
       </c>
       <c r="AE233" s="4" t="n">
         <v>0</v>
@@ -25661,7 +25661,7 @@
         </is>
       </c>
       <c r="I234" s="4" t="n">
-        <v>31.43</v>
+        <v>31.42</v>
       </c>
       <c r="J234" s="4" t="n">
         <v>100</v>
@@ -25681,7 +25681,7 @@
         <v>5.62</v>
       </c>
       <c r="O234" s="4" t="n">
-        <v>31.43</v>
+        <v>31.42</v>
       </c>
       <c r="P234" s="4" t="n">
         <v>1</v>
@@ -25763,10 +25763,10 @@
         <v>-4.33</v>
       </c>
       <c r="J235" s="4" t="n">
-        <v>21.5</v>
+        <v>22.1</v>
       </c>
       <c r="K235" s="4" t="n">
-        <v>78.5</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -25780,7 +25780,7 @@
         <v>5.62</v>
       </c>
       <c r="O235" s="4" t="n">
-        <v>-5.01</v>
+        <v>-5.02</v>
       </c>
       <c r="P235" s="4" t="n">
         <v>-0.47</v>
@@ -25818,10 +25818,10 @@
         <v>0</v>
       </c>
       <c r="AC235" s="4" t="n">
-        <v>47.84</v>
+        <v>47.83</v>
       </c>
       <c r="AD235" s="4" t="n">
-        <v>52.16</v>
+        <v>52.17</v>
       </c>
       <c r="AE235" s="4" t="n">
         <v>0</v>
@@ -25869,7 +25869,7 @@
         </is>
       </c>
       <c r="I236" s="4" t="n">
-        <v>-12.77</v>
+        <v>-12.76</v>
       </c>
       <c r="J236" s="4" t="n">
         <v>1</v>
@@ -25980,7 +25980,7 @@
         </is>
       </c>
       <c r="I237" s="4" t="n">
-        <v>-28.27</v>
+        <v>-28.26</v>
       </c>
       <c r="J237" s="4" t="n">
         <v>0</v>
@@ -25994,7 +25994,7 @@
         </is>
       </c>
       <c r="M237" s="4" t="n">
-        <v>-26.31</v>
+        <v>-26.3</v>
       </c>
       <c r="N237" s="4" t="n">
         <v>5.62</v>
@@ -26040,10 +26040,10 @@
         <v>0</v>
       </c>
       <c r="AC237" s="4" t="n">
-        <v>34.26</v>
+        <v>34.27</v>
       </c>
       <c r="AD237" s="4" t="n">
-        <v>61.28</v>
+        <v>61.27</v>
       </c>
       <c r="AE237" s="4" t="n">
         <v>2.23</v>
@@ -26091,7 +26091,7 @@
         </is>
       </c>
       <c r="I238" s="4" t="n">
-        <v>21.04</v>
+        <v>21.05</v>
       </c>
       <c r="J238" s="4" t="n">
         <v>99.8</v>
@@ -26105,13 +26105,13 @@
         </is>
       </c>
       <c r="M238" s="4" t="n">
-        <v>11.35</v>
+        <v>11.36</v>
       </c>
       <c r="N238" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O238" s="4" t="n">
-        <v>21.65</v>
+        <v>21.66</v>
       </c>
       <c r="P238" s="4" t="n">
         <v>0.83</v>
@@ -26151,10 +26151,10 @@
         <v>0</v>
       </c>
       <c r="AC238" s="4" t="n">
-        <v>59.04</v>
+        <v>59.05</v>
       </c>
       <c r="AD238" s="4" t="n">
-        <v>38.52</v>
+        <v>38.51</v>
       </c>
       <c r="AE238" s="4" t="n">
         <v>0</v>
@@ -26202,7 +26202,7 @@
         </is>
       </c>
       <c r="I239" s="4" t="n">
-        <v>-2.08</v>
+        <v>-2.07</v>
       </c>
       <c r="J239" s="4" t="n">
         <v>30.1</v>
@@ -26216,13 +26216,13 @@
         </is>
       </c>
       <c r="M239" s="4" t="n">
-        <v>-1.81</v>
+        <v>-1.8</v>
       </c>
       <c r="N239" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O239" s="4" t="n">
-        <v>-1.88</v>
+        <v>-1.87</v>
       </c>
       <c r="P239" s="4" t="n">
         <v>-0.24</v>
@@ -26319,7 +26319,7 @@
         </is>
       </c>
       <c r="I240" s="4" t="n">
-        <v>-25.5</v>
+        <v>-25.49</v>
       </c>
       <c r="J240" s="4" t="n">
         <v>0.1</v>
@@ -26339,7 +26339,7 @@
         <v>5.62</v>
       </c>
       <c r="O240" s="4" t="n">
-        <v>-25.39</v>
+        <v>-25.38</v>
       </c>
       <c r="P240" s="4" t="n">
         <v>-2.12</v>
@@ -26430,7 +26430,7 @@
         </is>
       </c>
       <c r="I241" s="4" t="n">
-        <v>38.64</v>
+        <v>38.65</v>
       </c>
       <c r="J241" s="4" t="n">
         <v>100</v>
@@ -26444,13 +26444,13 @@
         </is>
       </c>
       <c r="M241" s="4" t="n">
-        <v>28.17</v>
+        <v>28.18</v>
       </c>
       <c r="N241" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O241" s="4" t="n">
-        <v>38.77</v>
+        <v>38.78</v>
       </c>
       <c r="P241" s="4" t="n">
         <v>0</v>
@@ -26541,7 +26541,7 @@
         </is>
       </c>
       <c r="I242" s="4" t="n">
-        <v>0.89</v>
+        <v>0.91</v>
       </c>
       <c r="J242" s="4" t="n">
         <v>65.3</v>
@@ -26555,7 +26555,7 @@
         </is>
       </c>
       <c r="M242" s="4" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="N242" s="4" t="n">
         <v>5.62</v>
@@ -26564,7 +26564,7 @@
         <v>2.69</v>
       </c>
       <c r="P242" s="4" t="n">
-        <v>-1.13</v>
+        <v>-1.14</v>
       </c>
       <c r="Q242" s="4" t="n">
         <v>-3.8</v>
@@ -26607,10 +26607,10 @@
         <v>0</v>
       </c>
       <c r="AC242" s="4" t="n">
-        <v>49.3</v>
+        <v>49.31</v>
       </c>
       <c r="AD242" s="4" t="n">
-        <v>48.43</v>
+        <v>48.42</v>
       </c>
       <c r="AE242" s="4" t="n">
         <v>0</v>
@@ -26658,7 +26658,7 @@
         </is>
       </c>
       <c r="I243" s="4" t="n">
-        <v>19.76</v>
+        <v>19.77</v>
       </c>
       <c r="J243" s="4" t="n">
         <v>99.8</v>
@@ -26672,13 +26672,13 @@
         </is>
       </c>
       <c r="M243" s="4" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="N243" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O243" s="4" t="n">
-        <v>19.86</v>
+        <v>19.87</v>
       </c>
       <c r="P243" s="4" t="n">
         <v>2.21</v>
@@ -26789,7 +26789,7 @@
         <v>5.62</v>
       </c>
       <c r="O244" s="4" t="n">
-        <v>-32.4</v>
+        <v>-32.39</v>
       </c>
       <c r="P244" s="4" t="n">
         <v>-3.38</v>
@@ -26876,13 +26876,13 @@
         </is>
       </c>
       <c r="I245" s="4" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="J245" s="4" t="n">
-        <v>66.3</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="K245" s="4" t="n">
-        <v>33.7</v>
+        <v>33.6</v>
       </c>
       <c r="L245" t="inlineStr">
         <is>
@@ -26890,7 +26890,7 @@
         </is>
       </c>
       <c r="M245" s="4" t="n">
-        <v>-1.75</v>
+        <v>-1.74</v>
       </c>
       <c r="N245" s="4" t="n">
         <v>5.62</v>
@@ -26942,10 +26942,10 @@
         <v>0</v>
       </c>
       <c r="AC245" s="4" t="n">
-        <v>48.32</v>
+        <v>48.33</v>
       </c>
       <c r="AD245" s="4" t="n">
-        <v>47.22</v>
+        <v>47.21</v>
       </c>
       <c r="AE245" s="4" t="n">
         <v>2.23</v>
@@ -27003,7 +27003,7 @@
         </is>
       </c>
       <c r="M246" s="4" t="n">
-        <v>20.79</v>
+        <v>20.8</v>
       </c>
       <c r="N246" s="4" t="n">
         <v>5.62</v>
@@ -27049,10 +27049,10 @@
         <v>0</v>
       </c>
       <c r="AC246" s="4" t="n">
-        <v>59.31</v>
+        <v>59.32</v>
       </c>
       <c r="AD246" s="4" t="n">
-        <v>34.07</v>
+        <v>34.06</v>
       </c>
       <c r="AE246" s="4" t="n">
         <v>2.31</v>
@@ -27100,7 +27100,7 @@
         </is>
       </c>
       <c r="I247" s="4" t="n">
-        <v>58.27</v>
+        <v>58.28</v>
       </c>
       <c r="J247" s="4" t="n">
         <v>100</v>
@@ -27120,7 +27120,7 @@
         <v>5.62</v>
       </c>
       <c r="O247" s="4" t="n">
-        <v>59.4</v>
+        <v>59.41</v>
       </c>
       <c r="P247" s="4" t="n">
         <v>2.96</v>
@@ -27160,10 +27160,10 @@
         <v>0</v>
       </c>
       <c r="AC247" s="4" t="n">
-        <v>73.18000000000001</v>
+        <v>73.19</v>
       </c>
       <c r="AD247" s="4" t="n">
-        <v>19.3</v>
+        <v>19.29</v>
       </c>
       <c r="AE247" s="4" t="n">
         <v>3.76</v>
@@ -27207,7 +27207,7 @@
         </is>
       </c>
       <c r="I248" s="4" t="n">
-        <v>53.4</v>
+        <v>53.41</v>
       </c>
       <c r="J248" s="4" t="n">
         <v>100</v>
@@ -27221,13 +27221,13 @@
         </is>
       </c>
       <c r="M248" s="4" t="n">
-        <v>48.33</v>
+        <v>48.34</v>
       </c>
       <c r="N248" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O248" s="4" t="n">
-        <v>54.03</v>
+        <v>54.04</v>
       </c>
       <c r="P248" s="4" t="n">
         <v>0</v>
@@ -27267,10 +27267,10 @@
         <v>0</v>
       </c>
       <c r="AC248" s="4" t="n">
-        <v>73.45999999999999</v>
+        <v>73.47</v>
       </c>
       <c r="AD248" s="4" t="n">
-        <v>22.32</v>
+        <v>22.31</v>
       </c>
       <c r="AE248" s="4" t="n">
         <v>2.11</v>
@@ -27318,7 +27318,7 @@
         </is>
       </c>
       <c r="I249" s="4" t="n">
-        <v>-6.19</v>
+        <v>-6.18</v>
       </c>
       <c r="J249" s="4" t="n">
         <v>15.1</v>
@@ -27423,7 +27423,7 @@
         </is>
       </c>
       <c r="I250" s="4" t="n">
-        <v>12.78</v>
+        <v>12.79</v>
       </c>
       <c r="J250" s="4" t="n">
         <v>99</v>
@@ -27437,13 +27437,13 @@
         </is>
       </c>
       <c r="M250" s="4" t="n">
-        <v>8.27</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="N250" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O250" s="4" t="n">
-        <v>13.77</v>
+        <v>13.78</v>
       </c>
       <c r="P250" s="4" t="n">
         <v>0.52</v>
@@ -27481,10 +27481,10 @@
         <v>0</v>
       </c>
       <c r="AC250" s="4" t="n">
-        <v>56.39</v>
+        <v>56.4</v>
       </c>
       <c r="AD250" s="4" t="n">
-        <v>43.61</v>
+        <v>43.6</v>
       </c>
       <c r="AE250" s="4" t="n">
         <v>0</v>
@@ -27546,7 +27546,7 @@
         </is>
       </c>
       <c r="M251" s="4" t="n">
-        <v>23.55</v>
+        <v>23.56</v>
       </c>
       <c r="N251" s="4" t="n">
         <v>5.62</v>
@@ -27584,10 +27584,10 @@
         <v>0</v>
       </c>
       <c r="AC251" s="4" t="n">
-        <v>65.06</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="AD251" s="4" t="n">
-        <v>34.94</v>
+        <v>34.93</v>
       </c>
       <c r="AE251" s="4" t="n">
         <v>0</v>
@@ -27635,7 +27635,7 @@
         </is>
       </c>
       <c r="I252" s="4" t="n">
-        <v>47.88</v>
+        <v>47.89</v>
       </c>
       <c r="J252" s="4" t="n">
         <v>100</v>
@@ -27655,7 +27655,7 @@
         <v>5.62</v>
       </c>
       <c r="O252" s="4" t="n">
-        <v>47.88</v>
+        <v>47.89</v>
       </c>
       <c r="P252" s="4" t="n">
         <v>2.11</v>
@@ -27738,7 +27738,7 @@
         </is>
       </c>
       <c r="I253" s="4" t="n">
-        <v>66.13</v>
+        <v>66.14</v>
       </c>
       <c r="J253" s="4" t="n">
         <v>100</v>
@@ -27849,7 +27849,7 @@
         </is>
       </c>
       <c r="I254" s="4" t="n">
-        <v>-16.69</v>
+        <v>-16.68</v>
       </c>
       <c r="J254" s="4" t="n">
         <v>0.5</v>
@@ -27863,13 +27863,13 @@
         </is>
       </c>
       <c r="M254" s="4" t="n">
-        <v>-17.54</v>
+        <v>-17.53</v>
       </c>
       <c r="N254" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O254" s="4" t="n">
-        <v>-16.69</v>
+        <v>-16.68</v>
       </c>
       <c r="P254" s="4" t="n">
         <v>-2.25</v>
@@ -27952,7 +27952,7 @@
         </is>
       </c>
       <c r="I255" s="4" t="n">
-        <v>-31.71</v>
+        <v>-31.7</v>
       </c>
       <c r="J255" s="4" t="n">
         <v>0</v>
@@ -27966,13 +27966,13 @@
         </is>
       </c>
       <c r="M255" s="4" t="n">
-        <v>-33.89</v>
+        <v>-33.88</v>
       </c>
       <c r="N255" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O255" s="4" t="n">
-        <v>-31.71</v>
+        <v>-31.7</v>
       </c>
       <c r="P255" s="4" t="n">
         <v>-0.93</v>
@@ -28069,7 +28069,7 @@
         </is>
       </c>
       <c r="M256" s="4" t="n">
-        <v>-11.35</v>
+        <v>-11.34</v>
       </c>
       <c r="N256" s="4" t="n">
         <v>5.62</v>
@@ -29179,7 +29179,7 @@
         <v>5.62</v>
       </c>
       <c r="O266" s="4" t="n">
-        <v>36.19</v>
+        <v>36.18</v>
       </c>
       <c r="P266" s="4" t="n">
         <v>1.61</v>
@@ -29270,7 +29270,7 @@
         </is>
       </c>
       <c r="I267" s="4" t="n">
-        <v>-22.95</v>
+        <v>-22.96</v>
       </c>
       <c r="J267" s="4" t="n">
         <v>0.1</v>
@@ -29284,13 +29284,13 @@
         </is>
       </c>
       <c r="M267" s="4" t="n">
-        <v>-25.65</v>
+        <v>-25.66</v>
       </c>
       <c r="N267" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O267" s="4" t="n">
-        <v>-23.25</v>
+        <v>-23.26</v>
       </c>
       <c r="P267" s="4" t="n">
         <v>-1.09</v>
@@ -29330,10 +29330,10 @@
         <v>0</v>
       </c>
       <c r="AC267" s="4" t="n">
-        <v>37.95</v>
+        <v>37.94</v>
       </c>
       <c r="AD267" s="4" t="n">
-        <v>60.55</v>
+        <v>60.56</v>
       </c>
       <c r="AE267" s="4" t="n">
         <v>0</v>
@@ -29381,7 +29381,7 @@
         </is>
       </c>
       <c r="I268" s="4" t="n">
-        <v>-40.93</v>
+        <v>-40.94</v>
       </c>
       <c r="J268" s="4" t="n">
         <v>0</v>
@@ -29716,13 +29716,13 @@
         </is>
       </c>
       <c r="I271" s="4" t="n">
-        <v>3.65</v>
+        <v>3.66</v>
       </c>
       <c r="J271" s="4" t="n">
-        <v>75.90000000000001</v>
+        <v>76</v>
       </c>
       <c r="K271" s="4" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="L271" t="inlineStr">
         <is>
@@ -29730,13 +29730,13 @@
         </is>
       </c>
       <c r="M271" s="4" t="n">
-        <v>-7.42</v>
+        <v>-7.41</v>
       </c>
       <c r="N271" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O271" s="4" t="n">
-        <v>4.3</v>
+        <v>4.31</v>
       </c>
       <c r="P271" s="4" t="n">
         <v>0.09</v>
@@ -29833,7 +29833,7 @@
         </is>
       </c>
       <c r="I272" s="4" t="n">
-        <v>46.68</v>
+        <v>46.69</v>
       </c>
       <c r="J272" s="4" t="n">
         <v>100</v>
@@ -29958,13 +29958,13 @@
         </is>
       </c>
       <c r="M273" s="4" t="n">
-        <v>-9.460000000000001</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="N273" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O273" s="4" t="n">
-        <v>-6.94</v>
+        <v>-6.93</v>
       </c>
       <c r="P273" s="4" t="n">
         <v>-1.35</v>
@@ -30061,7 +30061,7 @@
         </is>
       </c>
       <c r="I274" s="4" t="n">
-        <v>60.16</v>
+        <v>60.17</v>
       </c>
       <c r="J274" s="4" t="n">
         <v>100</v>
@@ -30075,7 +30075,7 @@
         </is>
       </c>
       <c r="M274" s="4" t="n">
-        <v>49.05</v>
+        <v>49.06</v>
       </c>
       <c r="N274" s="4" t="n">
         <v>5.62</v>
@@ -30121,10 +30121,10 @@
         <v>0</v>
       </c>
       <c r="AC274" s="4" t="n">
-        <v>78.17</v>
+        <v>78.18000000000001</v>
       </c>
       <c r="AD274" s="4" t="n">
-        <v>19.45</v>
+        <v>19.44</v>
       </c>
       <c r="AE274" s="4" t="n">
         <v>0</v>
@@ -30172,7 +30172,7 @@
         </is>
       </c>
       <c r="I275" s="4" t="n">
-        <v>-9.52</v>
+        <v>-9.51</v>
       </c>
       <c r="J275" s="4" t="n">
         <v>5.4</v>
@@ -30186,13 +30186,13 @@
         </is>
       </c>
       <c r="M275" s="4" t="n">
-        <v>-14.32</v>
+        <v>-14.31</v>
       </c>
       <c r="N275" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O275" s="4" t="n">
-        <v>-9.85</v>
+        <v>-9.84</v>
       </c>
       <c r="P275" s="4" t="n">
         <v>-0.82</v>
@@ -30283,7 +30283,7 @@
         </is>
       </c>
       <c r="I276" s="4" t="n">
-        <v>-12.09</v>
+        <v>-12.08</v>
       </c>
       <c r="J276" s="4" t="n">
         <v>1.1</v>
@@ -30297,13 +30297,13 @@
         </is>
       </c>
       <c r="M276" s="4" t="n">
-        <v>-14.49</v>
+        <v>-14.48</v>
       </c>
       <c r="N276" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O276" s="4" t="n">
-        <v>-12.09</v>
+        <v>-12.08</v>
       </c>
       <c r="P276" s="4" t="n">
         <v>-1.22</v>
@@ -30400,13 +30400,13 @@
         </is>
       </c>
       <c r="M277" s="4" t="n">
-        <v>-10.51</v>
+        <v>-10.5</v>
       </c>
       <c r="N277" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O277" s="4" t="n">
-        <v>-10.12</v>
+        <v>-10.11</v>
       </c>
       <c r="P277" s="4" t="n">
         <v>-1.34</v>
@@ -30503,7 +30503,7 @@
         </is>
       </c>
       <c r="I278" s="4" t="n">
-        <v>-16.62</v>
+        <v>-16.61</v>
       </c>
       <c r="J278" s="4" t="n">
         <v>0.5</v>
@@ -30517,13 +30517,13 @@
         </is>
       </c>
       <c r="M278" s="4" t="n">
-        <v>-16.54</v>
+        <v>-16.53</v>
       </c>
       <c r="N278" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O278" s="4" t="n">
-        <v>-16.18</v>
+        <v>-16.17</v>
       </c>
       <c r="P278" s="4" t="n">
         <v>-1.86</v>
@@ -30614,7 +30614,7 @@
         </is>
       </c>
       <c r="I279" s="4" t="n">
-        <v>-10.67</v>
+        <v>-10.66</v>
       </c>
       <c r="J279" s="4" t="n">
         <v>2.6</v>
@@ -30628,13 +30628,13 @@
         </is>
       </c>
       <c r="M279" s="4" t="n">
-        <v>-12.84</v>
+        <v>-12.83</v>
       </c>
       <c r="N279" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O279" s="4" t="n">
-        <v>-10.67</v>
+        <v>-10.66</v>
       </c>
       <c r="P279" s="4" t="n">
         <v>-0.22</v>
@@ -30666,10 +30666,10 @@
         <v>0</v>
       </c>
       <c r="AC279" s="4" t="n">
-        <v>44.66</v>
+        <v>44.67</v>
       </c>
       <c r="AD279" s="4" t="n">
-        <v>55.34</v>
+        <v>55.33</v>
       </c>
       <c r="AE279" s="4" t="n">
         <v>0</v>
@@ -30717,7 +30717,7 @@
         </is>
       </c>
       <c r="I280" s="4" t="n">
-        <v>-14.7</v>
+        <v>-14.69</v>
       </c>
       <c r="J280" s="4" t="n">
         <v>0.7</v>
@@ -30731,7 +30731,7 @@
         </is>
       </c>
       <c r="M280" s="4" t="n">
-        <v>-14.66</v>
+        <v>-14.65</v>
       </c>
       <c r="N280" s="4" t="n">
         <v>5.62</v>
@@ -30844,13 +30844,13 @@
         </is>
       </c>
       <c r="M281" s="4" t="n">
-        <v>-7.48</v>
+        <v>-7.47</v>
       </c>
       <c r="N281" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O281" s="4" t="n">
-        <v>-2.58</v>
+        <v>-2.57</v>
       </c>
       <c r="P281" s="4" t="n">
         <v>0</v>
@@ -30941,7 +30941,7 @@
         </is>
       </c>
       <c r="I282" s="4" t="n">
-        <v>60.59</v>
+        <v>60.6</v>
       </c>
       <c r="J282" s="4" t="n">
         <v>100</v>
@@ -30955,13 +30955,13 @@
         </is>
       </c>
       <c r="M282" s="4" t="n">
-        <v>50.77</v>
+        <v>50.78</v>
       </c>
       <c r="N282" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O282" s="4" t="n">
-        <v>60.59</v>
+        <v>60.6</v>
       </c>
       <c r="P282" s="4" t="n">
         <v>1.26</v>
@@ -31044,7 +31044,7 @@
         </is>
       </c>
       <c r="I283" s="4" t="n">
-        <v>-11.86</v>
+        <v>-11.85</v>
       </c>
       <c r="J283" s="4" t="n">
         <v>1.2</v>
@@ -31064,7 +31064,7 @@
         <v>5.62</v>
       </c>
       <c r="O283" s="4" t="n">
-        <v>-12.23</v>
+        <v>-12.22</v>
       </c>
       <c r="P283" s="4" t="n">
         <v>-0.19</v>
@@ -31104,10 +31104,10 @@
         <v>0</v>
       </c>
       <c r="AC283" s="4" t="n">
-        <v>43.25</v>
+        <v>43.26</v>
       </c>
       <c r="AD283" s="4" t="n">
-        <v>54.9</v>
+        <v>54.89</v>
       </c>
       <c r="AE283" s="4" t="n">
         <v>0</v>
@@ -31155,7 +31155,7 @@
         </is>
       </c>
       <c r="I284" s="4" t="n">
-        <v>-12.25</v>
+        <v>-12.24</v>
       </c>
       <c r="J284" s="4" t="n">
         <v>1.1</v>
@@ -31175,7 +31175,7 @@
         <v>5.62</v>
       </c>
       <c r="O284" s="4" t="n">
-        <v>-13.53</v>
+        <v>-13.52</v>
       </c>
       <c r="P284" s="4" t="n">
         <v>-2.3</v>
@@ -31375,13 +31375,13 @@
         </is>
       </c>
       <c r="I286" s="4" t="n">
-        <v>-11.08</v>
+        <v>-11.25</v>
       </c>
       <c r="J286" s="4" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="K286" s="4" t="n">
-        <v>98.3</v>
+        <v>98.7</v>
       </c>
       <c r="L286" t="inlineStr">
         <is>
@@ -31389,13 +31389,13 @@
         </is>
       </c>
       <c r="M286" s="4" t="n">
-        <v>-11.36</v>
+        <v>-11.55</v>
       </c>
       <c r="N286" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O286" s="4" t="n">
-        <v>-12.23</v>
+        <v>-12.43</v>
       </c>
       <c r="P286" s="4" t="n">
         <v>-0.99</v>
@@ -31441,10 +31441,10 @@
         <v>0</v>
       </c>
       <c r="AC286" s="4" t="n">
-        <v>42.32</v>
+        <v>42.24</v>
       </c>
       <c r="AD286" s="4" t="n">
-        <v>52.86</v>
+        <v>52.94</v>
       </c>
       <c r="AE286" s="4" t="n">
         <v>2.41</v>
@@ -31488,27 +31488,27 @@
         </is>
       </c>
       <c r="I287" s="4" t="n">
-        <v>11.27</v>
+        <v>7.73</v>
       </c>
       <c r="J287" s="4" t="n">
-        <v>98.7</v>
+        <v>89.7</v>
       </c>
       <c r="K287" s="4" t="n">
-        <v>1.3</v>
+        <v>10.3</v>
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t>Safe D</t>
+          <t>Likely D</t>
         </is>
       </c>
       <c r="M287" s="4" t="n">
-        <v>6.5</v>
+        <v>6.31</v>
       </c>
       <c r="N287" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O287" s="4" t="n">
-        <v>12.22</v>
+        <v>12.03</v>
       </c>
       <c r="P287" s="4" t="n">
         <v>0.46</v>
@@ -31520,16 +31520,16 @@
         <v>4.68</v>
       </c>
       <c r="S287" s="4" t="n">
-        <v>46.5</v>
+        <v>46</v>
       </c>
       <c r="T287" s="4" t="n">
-        <v>40.5</v>
+        <v>42</v>
       </c>
       <c r="U287" t="n">
         <v>1</v>
       </c>
       <c r="V287" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W287" s="5" t="n">
         <v>2668287</v>
@@ -31554,10 +31554,10 @@
         <v>0</v>
       </c>
       <c r="AC287" s="4" t="n">
-        <v>54.43</v>
+        <v>52.7</v>
       </c>
       <c r="AD287" s="4" t="n">
-        <v>43.41</v>
+        <v>45.14</v>
       </c>
       <c r="AE287" s="4" t="n">
         <v>0</v>
@@ -31605,7 +31605,7 @@
         </is>
       </c>
       <c r="I288" s="4" t="n">
-        <v>-54.97</v>
+        <v>-55.17</v>
       </c>
       <c r="J288" s="4" t="n">
         <v>0</v>
@@ -31619,13 +31619,13 @@
         </is>
       </c>
       <c r="M288" s="4" t="n">
-        <v>-52.31</v>
+        <v>-52.5</v>
       </c>
       <c r="N288" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O288" s="4" t="n">
-        <v>-54.78</v>
+        <v>-54.97</v>
       </c>
       <c r="P288" s="4" t="n">
         <v>-2.18</v>
@@ -31665,10 +31665,10 @@
         <v>0</v>
       </c>
       <c r="AC288" s="4" t="n">
-        <v>21.62</v>
+        <v>21.53</v>
       </c>
       <c r="AD288" s="4" t="n">
-        <v>74.42</v>
+        <v>74.51000000000001</v>
       </c>
       <c r="AE288" s="4" t="n">
         <v>1.98</v>
@@ -32580,13 +32580,13 @@
         </is>
       </c>
       <c r="I297" s="4" t="n">
-        <v>5.08</v>
+        <v>5.45</v>
       </c>
       <c r="J297" s="4" t="n">
-        <v>81.09999999999999</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K297" s="4" t="n">
-        <v>18.9</v>
+        <v>17.6</v>
       </c>
       <c r="L297" t="inlineStr">
         <is>
@@ -32615,13 +32615,13 @@
         <v>47</v>
       </c>
       <c r="T297" s="4" t="n">
-        <v>43</v>
+        <v>42.03</v>
       </c>
       <c r="U297" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V297" s="4" t="n">
-        <v>1</v>
+        <v>4.9</v>
       </c>
       <c r="W297" s="5" t="n">
         <v>4272034</v>
@@ -32640,16 +32640,16 @@
         </is>
       </c>
       <c r="AA297" s="4" t="n">
-        <v>2.43</v>
+        <v>0.97</v>
       </c>
       <c r="AB297" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC297" s="4" t="n">
-        <v>51.26</v>
+        <v>52.21</v>
       </c>
       <c r="AD297" s="4" t="n">
-        <v>46.31</v>
+        <v>46.82</v>
       </c>
       <c r="AE297" s="4" t="n">
         <v>0</v>
@@ -33569,7 +33569,7 @@
         </is>
       </c>
       <c r="M306" s="4" t="n">
-        <v>5.81</v>
+        <v>5.82</v>
       </c>
       <c r="N306" s="4" t="n">
         <v>5.62</v>
@@ -33662,21 +33662,21 @@
         </is>
       </c>
       <c r="I307" s="4" t="n">
-        <v>-4.37</v>
+        <v>-1.95</v>
       </c>
       <c r="J307" s="4" t="n">
-        <v>21.4</v>
+        <v>30.6</v>
       </c>
       <c r="K307" s="4" t="n">
-        <v>78.59999999999999</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t>Likely R</t>
+          <t>Lean R</t>
         </is>
       </c>
       <c r="M307" s="4" t="n">
-        <v>-12.01</v>
+        <v>-12</v>
       </c>
       <c r="N307" s="4" t="n">
         <v>5.62</v>
@@ -33694,16 +33694,16 @@
         <v>-14.26</v>
       </c>
       <c r="S307" s="4" t="n">
-        <v>44.92</v>
+        <v>41.17</v>
       </c>
       <c r="T307" s="4" t="n">
-        <v>45.49</v>
+        <v>40.89</v>
       </c>
       <c r="U307" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V307" s="4" t="n">
-        <v>-2.11</v>
+        <v>-2.05</v>
       </c>
       <c r="W307" s="5" t="n">
         <v>257087</v>
@@ -33722,16 +33722,16 @@
         </is>
       </c>
       <c r="AA307" s="4" t="n">
-        <v>3.6</v>
+        <v>9.23</v>
       </c>
       <c r="AB307" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC307" s="4" t="n">
-        <v>46.1</v>
+        <v>44.5</v>
       </c>
       <c r="AD307" s="4" t="n">
-        <v>50.3</v>
+        <v>46.27</v>
       </c>
       <c r="AE307" s="4" t="n">
         <v>0</v>
@@ -33779,7 +33779,7 @@
         </is>
       </c>
       <c r="I308" s="4" t="n">
-        <v>13.31</v>
+        <v>13.32</v>
       </c>
       <c r="J308" s="4" t="n">
         <v>99.09999999999999</v>
@@ -33793,13 +33793,13 @@
         </is>
       </c>
       <c r="M308" s="4" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="N308" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O308" s="4" t="n">
-        <v>12.56</v>
+        <v>12.57</v>
       </c>
       <c r="P308" s="4" t="n">
         <v>0.06</v>
@@ -33890,7 +33890,7 @@
         </is>
       </c>
       <c r="I309" s="4" t="n">
-        <v>19.17</v>
+        <v>19.18</v>
       </c>
       <c r="J309" s="4" t="n">
         <v>99.7</v>
@@ -33904,7 +33904,7 @@
         </is>
       </c>
       <c r="M309" s="4" t="n">
-        <v>5.85</v>
+        <v>5.86</v>
       </c>
       <c r="N309" s="4" t="n">
         <v>5.62</v>
@@ -33950,10 +33950,10 @@
         <v>0</v>
       </c>
       <c r="AC309" s="4" t="n">
-        <v>58.07</v>
+        <v>58.08</v>
       </c>
       <c r="AD309" s="4" t="n">
-        <v>39.39</v>
+        <v>39.38</v>
       </c>
       <c r="AE309" s="4" t="n">
         <v>0</v>
@@ -34124,7 +34124,7 @@
         </is>
       </c>
       <c r="M311" s="4" t="n">
-        <v>-11.33</v>
+        <v>-11.32</v>
       </c>
       <c r="N311" s="4" t="n">
         <v>5.62</v>
@@ -34265,10 +34265,10 @@
         <v>0</v>
       </c>
       <c r="AC312" s="4" t="n">
-        <v>57.66</v>
+        <v>57.67</v>
       </c>
       <c r="AD312" s="4" t="n">
-        <v>42.34</v>
+        <v>42.33</v>
       </c>
       <c r="AE312" s="4" t="n">
         <v>0</v>
@@ -34336,7 +34336,7 @@
         <v>5.62</v>
       </c>
       <c r="O313" s="4" t="n">
-        <v>16.95</v>
+        <v>16.96</v>
       </c>
       <c r="P313" s="4" t="n">
         <v>2.1</v>
@@ -34382,10 +34382,10 @@
         <v>0</v>
       </c>
       <c r="AC313" s="4" t="n">
-        <v>56.6</v>
+        <v>56.61</v>
       </c>
       <c r="AD313" s="4" t="n">
-        <v>41.82</v>
+        <v>41.81</v>
       </c>
       <c r="AE313" s="4" t="n">
         <v>0</v>
@@ -34447,7 +34447,7 @@
         </is>
       </c>
       <c r="M314" s="4" t="n">
-        <v>48.65</v>
+        <v>48.66</v>
       </c>
       <c r="N314" s="4" t="n">
         <v>5.62</v>
@@ -34635,7 +34635,7 @@
         </is>
       </c>
       <c r="I316" s="4" t="n">
-        <v>57.63</v>
+        <v>57.64</v>
       </c>
       <c r="J316" s="4" t="n">
         <v>100</v>
@@ -34798,10 +34798,10 @@
         <v>0</v>
       </c>
       <c r="AC317" s="4" t="n">
-        <v>80.52</v>
+        <v>80.53</v>
       </c>
       <c r="AD317" s="4" t="n">
-        <v>19.48</v>
+        <v>19.47</v>
       </c>
       <c r="AE317" s="4" t="n">
         <v>0</v>
@@ -35065,7 +35065,7 @@
         </is>
       </c>
       <c r="M320" s="4" t="n">
-        <v>-20.33</v>
+        <v>-20.32</v>
       </c>
       <c r="N320" s="4" t="n">
         <v>5.62</v>
@@ -35150,7 +35150,7 @@
         </is>
       </c>
       <c r="I321" s="4" t="n">
-        <v>73.41</v>
+        <v>73.42</v>
       </c>
       <c r="J321" s="4" t="n">
         <v>100</v>
@@ -35257,7 +35257,7 @@
         </is>
       </c>
       <c r="I322" s="4" t="n">
-        <v>73.19</v>
+        <v>73.2</v>
       </c>
       <c r="J322" s="4" t="n">
         <v>100</v>
@@ -35271,13 +35271,13 @@
         </is>
       </c>
       <c r="M322" s="4" t="n">
-        <v>65.73</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="N322" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O322" s="4" t="n">
-        <v>73.19</v>
+        <v>73.2</v>
       </c>
       <c r="P322" s="4" t="n">
         <v>0</v>
@@ -35677,7 +35677,7 @@
         </is>
       </c>
       <c r="I326" s="4" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="J326" s="4" t="n">
         <v>73.59999999999999</v>
@@ -35691,7 +35691,7 @@
         </is>
       </c>
       <c r="M326" s="4" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="N326" s="4" t="n">
         <v>5.62</v>
@@ -35735,10 +35735,10 @@
         <v>0</v>
       </c>
       <c r="AC326" s="4" t="n">
-        <v>51.51</v>
+        <v>51.52</v>
       </c>
       <c r="AD326" s="4" t="n">
-        <v>48.49</v>
+        <v>48.48</v>
       </c>
       <c r="AE326" s="4" t="n">
         <v>0</v>
@@ -35786,7 +35786,7 @@
         </is>
       </c>
       <c r="I327" s="4" t="n">
-        <v>18.75</v>
+        <v>18.79</v>
       </c>
       <c r="J327" s="4" t="n">
         <v>99.7</v>
@@ -35806,7 +35806,7 @@
         <v>5.62</v>
       </c>
       <c r="O327" s="4" t="n">
-        <v>21.48</v>
+        <v>21.49</v>
       </c>
       <c r="P327" s="4" t="n">
         <v>2.65</v>
@@ -35844,10 +35844,10 @@
         <v>0</v>
       </c>
       <c r="AC327" s="4" t="n">
-        <v>59.37</v>
+        <v>59.39</v>
       </c>
       <c r="AD327" s="4" t="n">
-        <v>40.63</v>
+        <v>40.61</v>
       </c>
       <c r="AE327" s="4" t="n">
         <v>0</v>
@@ -36097,13 +36097,13 @@
         </is>
       </c>
       <c r="I330" s="4" t="n">
-        <v>-9.449999999999999</v>
+        <v>-9.51</v>
       </c>
       <c r="J330" s="4" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="K330" s="4" t="n">
-        <v>94.5</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="L330" t="inlineStr">
         <is>
@@ -36111,7 +36111,7 @@
         </is>
       </c>
       <c r="M330" s="4" t="n">
-        <v>-19.62</v>
+        <v>-19.61</v>
       </c>
       <c r="N330" s="4" t="n">
         <v>5.62</v>
@@ -36155,10 +36155,10 @@
         <v>0</v>
       </c>
       <c r="AC330" s="4" t="n">
-        <v>45.28</v>
+        <v>45.25</v>
       </c>
       <c r="AD330" s="4" t="n">
-        <v>54.72</v>
+        <v>54.75</v>
       </c>
       <c r="AE330" s="4" t="n">
         <v>0</v>
@@ -36206,7 +36206,7 @@
         </is>
       </c>
       <c r="I331" s="4" t="n">
-        <v>23.41</v>
+        <v>23.42</v>
       </c>
       <c r="J331" s="4" t="n">
         <v>99.90000000000001</v>
@@ -36226,7 +36226,7 @@
         <v>5.62</v>
       </c>
       <c r="O331" s="4" t="n">
-        <v>23.41</v>
+        <v>23.42</v>
       </c>
       <c r="P331" s="4" t="n">
         <v>1.62</v>
@@ -36412,7 +36412,7 @@
         </is>
       </c>
       <c r="I333" s="4" t="n">
-        <v>-22.1</v>
+        <v>-22.09</v>
       </c>
       <c r="J333" s="4" t="n">
         <v>0.1</v>
@@ -36426,13 +36426,13 @@
         </is>
       </c>
       <c r="M333" s="4" t="n">
-        <v>-22.76</v>
+        <v>-22.75</v>
       </c>
       <c r="N333" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O333" s="4" t="n">
-        <v>-22.1</v>
+        <v>-22.09</v>
       </c>
       <c r="P333" s="4" t="n">
         <v>-1.84</v>
@@ -36515,7 +36515,7 @@
         </is>
       </c>
       <c r="I334" s="4" t="n">
-        <v>28.08</v>
+        <v>28.09</v>
       </c>
       <c r="J334" s="4" t="n">
         <v>100</v>
@@ -36535,7 +36535,7 @@
         <v>5.62</v>
       </c>
       <c r="O334" s="4" t="n">
-        <v>28.08</v>
+        <v>28.09</v>
       </c>
       <c r="P334" s="4" t="n">
         <v>2.4</v>
@@ -36721,13 +36721,13 @@
         </is>
       </c>
       <c r="I336" s="4" t="n">
-        <v>10.31</v>
+        <v>10.36</v>
       </c>
       <c r="J336" s="4" t="n">
-        <v>96.59999999999999</v>
+        <v>96.7</v>
       </c>
       <c r="K336" s="4" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L336" t="inlineStr">
         <is>
@@ -36741,7 +36741,7 @@
         <v>5.62</v>
       </c>
       <c r="O336" s="4" t="n">
-        <v>12.61</v>
+        <v>12.6</v>
       </c>
       <c r="P336" s="4" t="n">
         <v>0.76</v>
@@ -36787,10 +36787,10 @@
         <v>0</v>
       </c>
       <c r="AC336" s="4" t="n">
-        <v>54.26</v>
+        <v>54.28</v>
       </c>
       <c r="AD336" s="4" t="n">
-        <v>44.12</v>
+        <v>44.1</v>
       </c>
       <c r="AE336" s="4" t="n">
         <v>0</v>
@@ -36838,7 +36838,7 @@
         </is>
       </c>
       <c r="I337" s="4" t="n">
-        <v>-35.33</v>
+        <v>-35.34</v>
       </c>
       <c r="J337" s="4" t="n">
         <v>0</v>
@@ -36852,13 +36852,13 @@
         </is>
       </c>
       <c r="M337" s="4" t="n">
-        <v>-37.35</v>
+        <v>-37.36</v>
       </c>
       <c r="N337" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O337" s="4" t="n">
-        <v>-35.33</v>
+        <v>-35.34</v>
       </c>
       <c r="P337" s="4" t="n">
         <v>0</v>
@@ -36955,7 +36955,7 @@
         </is>
       </c>
       <c r="M338" s="4" t="n">
-        <v>45.73</v>
+        <v>45.72</v>
       </c>
       <c r="N338" s="4" t="n">
         <v>5.62</v>
@@ -37058,7 +37058,7 @@
         </is>
       </c>
       <c r="M339" s="4" t="n">
-        <v>-38.11</v>
+        <v>-38.12</v>
       </c>
       <c r="N339" s="4" t="n">
         <v>5.62</v>
@@ -37104,10 +37104,10 @@
         <v>0</v>
       </c>
       <c r="AC339" s="4" t="n">
-        <v>30.55</v>
+        <v>30.54</v>
       </c>
       <c r="AD339" s="4" t="n">
-        <v>67.84</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="AE339" s="4" t="n">
         <v>0</v>
@@ -37175,7 +37175,7 @@
         <v>5.62</v>
       </c>
       <c r="O340" s="4" t="n">
-        <v>-21.47</v>
+        <v>-21.48</v>
       </c>
       <c r="P340" s="4" t="n">
         <v>-2.4</v>
@@ -37215,10 +37215,10 @@
         <v>0</v>
       </c>
       <c r="AC340" s="4" t="n">
-        <v>38.75</v>
+        <v>38.74</v>
       </c>
       <c r="AD340" s="4" t="n">
-        <v>59.49</v>
+        <v>59.5</v>
       </c>
       <c r="AE340" s="4" t="n">
         <v>0</v>
@@ -37266,7 +37266,7 @@
         </is>
       </c>
       <c r="I341" s="4" t="n">
-        <v>-27.81</v>
+        <v>-27.82</v>
       </c>
       <c r="J341" s="4" t="n">
         <v>0</v>
@@ -37280,13 +37280,13 @@
         </is>
       </c>
       <c r="M341" s="4" t="n">
-        <v>-29.02</v>
+        <v>-29.03</v>
       </c>
       <c r="N341" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O341" s="4" t="n">
-        <v>-27.81</v>
+        <v>-27.82</v>
       </c>
       <c r="P341" s="4" t="n">
         <v>-2.34</v>
@@ -37369,13 +37369,13 @@
         </is>
       </c>
       <c r="I342" s="4" t="n">
-        <v>0.43</v>
+        <v>0.39</v>
       </c>
       <c r="J342" s="4" t="n">
-        <v>63.4</v>
+        <v>63.2</v>
       </c>
       <c r="K342" s="4" t="n">
-        <v>36.6</v>
+        <v>36.8</v>
       </c>
       <c r="L342" t="inlineStr">
         <is>
@@ -37427,10 +37427,10 @@
         <v>0</v>
       </c>
       <c r="AC342" s="4" t="n">
-        <v>50.22</v>
+        <v>50.19</v>
       </c>
       <c r="AD342" s="4" t="n">
-        <v>49.78</v>
+        <v>49.81</v>
       </c>
       <c r="AE342" s="4" t="n">
         <v>0</v>
@@ -37478,7 +37478,7 @@
         </is>
       </c>
       <c r="I343" s="4" t="n">
-        <v>-7.83</v>
+        <v>-7.84</v>
       </c>
       <c r="J343" s="4" t="n">
         <v>10</v>
@@ -37492,13 +37492,13 @@
         </is>
       </c>
       <c r="M343" s="4" t="n">
-        <v>-11.55</v>
+        <v>-11.56</v>
       </c>
       <c r="N343" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O343" s="4" t="n">
-        <v>-7.83</v>
+        <v>-7.84</v>
       </c>
       <c r="P343" s="4" t="n">
         <v>0</v>
@@ -37601,7 +37601,7 @@
         <v>5.62</v>
       </c>
       <c r="O344" s="4" t="n">
-        <v>11.99</v>
+        <v>11.98</v>
       </c>
       <c r="P344" s="4" t="n">
         <v>0.74</v>
@@ -37690,7 +37690,7 @@
         </is>
       </c>
       <c r="I345" s="4" t="n">
-        <v>-8.460000000000001</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="J345" s="4" t="n">
         <v>8.199999999999999</v>
@@ -37710,7 +37710,7 @@
         <v>5.62</v>
       </c>
       <c r="O345" s="4" t="n">
-        <v>-8.789999999999999</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="P345" s="4" t="n">
         <v>-0.62</v>
@@ -38013,7 +38013,7 @@
         </is>
       </c>
       <c r="I348" s="4" t="n">
-        <v>19.5</v>
+        <v>19.49</v>
       </c>
       <c r="J348" s="4" t="n">
         <v>99.7</v>
@@ -38033,7 +38033,7 @@
         <v>5.62</v>
       </c>
       <c r="O348" s="4" t="n">
-        <v>19.58</v>
+        <v>19.57</v>
       </c>
       <c r="P348" s="4" t="n">
         <v>2.15</v>
@@ -38124,7 +38124,7 @@
         </is>
       </c>
       <c r="I349" s="4" t="n">
-        <v>-19.04</v>
+        <v>-19.05</v>
       </c>
       <c r="J349" s="4" t="n">
         <v>0.3</v>
@@ -38144,7 +38144,7 @@
         <v>5.62</v>
       </c>
       <c r="O349" s="4" t="n">
-        <v>-19.04</v>
+        <v>-19.05</v>
       </c>
       <c r="P349" s="4" t="n">
         <v>-1.93</v>
@@ -38227,7 +38227,7 @@
         </is>
       </c>
       <c r="I350" s="4" t="n">
-        <v>-4.02</v>
+        <v>-4.01</v>
       </c>
       <c r="J350" s="4" t="n">
         <v>22.7</v>
@@ -38241,7 +38241,7 @@
         </is>
       </c>
       <c r="M350" s="4" t="n">
-        <v>-5.27</v>
+        <v>-5.28</v>
       </c>
       <c r="N350" s="4" t="n">
         <v>5.62</v>
@@ -38340,7 +38340,7 @@
         </is>
       </c>
       <c r="I351" s="4" t="n">
-        <v>-17.3</v>
+        <v>-17.31</v>
       </c>
       <c r="J351" s="4" t="n">
         <v>0.4</v>
@@ -38354,13 +38354,13 @@
         </is>
       </c>
       <c r="M351" s="4" t="n">
-        <v>-20.66</v>
+        <v>-20.67</v>
       </c>
       <c r="N351" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O351" s="4" t="n">
-        <v>-17.3</v>
+        <v>-17.31</v>
       </c>
       <c r="P351" s="4" t="n">
         <v>-1.7</v>
@@ -38443,7 +38443,7 @@
         </is>
       </c>
       <c r="I352" s="4" t="n">
-        <v>-51.2</v>
+        <v>-51.21</v>
       </c>
       <c r="J352" s="4" t="n">
         <v>0</v>
@@ -38457,13 +38457,13 @@
         </is>
       </c>
       <c r="M352" s="4" t="n">
-        <v>-53.92</v>
+        <v>-53.93</v>
       </c>
       <c r="N352" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O352" s="4" t="n">
-        <v>-51.09</v>
+        <v>-51.1</v>
       </c>
       <c r="P352" s="4" t="n">
         <v>-1.2</v>
@@ -38503,10 +38503,10 @@
         <v>0</v>
       </c>
       <c r="AC352" s="4" t="n">
-        <v>23.9</v>
+        <v>23.89</v>
       </c>
       <c r="AD352" s="4" t="n">
-        <v>74.03</v>
+        <v>74.04000000000001</v>
       </c>
       <c r="AE352" s="4" t="n">
         <v>0</v>
@@ -38554,7 +38554,7 @@
         </is>
       </c>
       <c r="I353" s="4" t="n">
-        <v>-42.73</v>
+        <v>-42.74</v>
       </c>
       <c r="J353" s="4" t="n">
         <v>0</v>
@@ -38568,13 +38568,13 @@
         </is>
       </c>
       <c r="M353" s="4" t="n">
-        <v>-43.63</v>
+        <v>-43.64</v>
       </c>
       <c r="N353" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O353" s="4" t="n">
-        <v>-42.73</v>
+        <v>-42.74</v>
       </c>
       <c r="P353" s="4" t="n">
         <v>0</v>
@@ -38606,10 +38606,10 @@
         <v>0</v>
       </c>
       <c r="AC353" s="4" t="n">
-        <v>28.64</v>
+        <v>28.63</v>
       </c>
       <c r="AD353" s="4" t="n">
-        <v>71.36</v>
+        <v>71.37</v>
       </c>
       <c r="AE353" s="4" t="n">
         <v>0</v>
@@ -38657,7 +38657,7 @@
         </is>
       </c>
       <c r="I354" s="4" t="n">
-        <v>-34.4</v>
+        <v>-34.41</v>
       </c>
       <c r="J354" s="4" t="n">
         <v>0</v>
@@ -38671,13 +38671,13 @@
         </is>
       </c>
       <c r="M354" s="4" t="n">
-        <v>-31.66</v>
+        <v>-31.67</v>
       </c>
       <c r="N354" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O354" s="4" t="n">
-        <v>-34.27</v>
+        <v>-34.28</v>
       </c>
       <c r="P354" s="4" t="n">
         <v>-2.65</v>
@@ -38717,10 +38717,10 @@
         <v>0</v>
       </c>
       <c r="AC354" s="4" t="n">
-        <v>31.93</v>
+        <v>31.92</v>
       </c>
       <c r="AD354" s="4" t="n">
-        <v>65.42</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="AE354" s="4" t="n">
         <v>0</v>
@@ -38768,7 +38768,7 @@
         </is>
       </c>
       <c r="I355" s="4" t="n">
-        <v>-16.47</v>
+        <v>-16.48</v>
       </c>
       <c r="J355" s="4" t="n">
         <v>0.5</v>
@@ -38782,13 +38782,13 @@
         </is>
       </c>
       <c r="M355" s="4" t="n">
-        <v>-17.41</v>
+        <v>-17.42</v>
       </c>
       <c r="N355" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O355" s="4" t="n">
-        <v>-16.32</v>
+        <v>-16.33</v>
       </c>
       <c r="P355" s="4" t="n">
         <v>-1.04</v>
@@ -38828,10 +38828,10 @@
         <v>0</v>
       </c>
       <c r="AC355" s="4" t="n">
-        <v>40.5</v>
+        <v>40.49</v>
       </c>
       <c r="AD355" s="4" t="n">
-        <v>56.46</v>
+        <v>56.47</v>
       </c>
       <c r="AE355" s="4" t="n">
         <v>0</v>
@@ -38879,7 +38879,7 @@
         </is>
       </c>
       <c r="I356" s="4" t="n">
-        <v>49.91</v>
+        <v>49.92</v>
       </c>
       <c r="J356" s="4" t="n">
         <v>100</v>
@@ -38893,13 +38893,13 @@
         </is>
       </c>
       <c r="M356" s="4" t="n">
-        <v>38.74</v>
+        <v>38.75</v>
       </c>
       <c r="N356" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O356" s="4" t="n">
-        <v>49.91</v>
+        <v>49.92</v>
       </c>
       <c r="P356" s="4" t="n">
         <v>2.08</v>
@@ -39299,7 +39299,7 @@
         </is>
       </c>
       <c r="I360" s="4" t="n">
-        <v>15.9</v>
+        <v>15.91</v>
       </c>
       <c r="J360" s="4" t="n">
         <v>99.40000000000001</v>
@@ -39359,10 +39359,10 @@
         <v>0</v>
       </c>
       <c r="AC360" s="4" t="n">
-        <v>55.23</v>
+        <v>55.24</v>
       </c>
       <c r="AD360" s="4" t="n">
-        <v>40.08</v>
+        <v>40.07</v>
       </c>
       <c r="AE360" s="4" t="n">
         <v>0</v>
@@ -39424,7 +39424,7 @@
         </is>
       </c>
       <c r="M361" s="4" t="n">
-        <v>11.27</v>
+        <v>11.28</v>
       </c>
       <c r="N361" s="4" t="n">
         <v>5.62</v>
@@ -39513,7 +39513,7 @@
         </is>
       </c>
       <c r="I362" s="4" t="n">
-        <v>-2.16</v>
+        <v>-2.14</v>
       </c>
       <c r="J362" s="4" t="n">
         <v>29.8</v>
@@ -39571,10 +39571,10 @@
         <v>0</v>
       </c>
       <c r="AC362" s="4" t="n">
-        <v>48.92</v>
+        <v>48.93</v>
       </c>
       <c r="AD362" s="4" t="n">
-        <v>51.08</v>
+        <v>51.07</v>
       </c>
       <c r="AE362" s="4" t="n">
         <v>0</v>
@@ -40141,13 +40141,13 @@
         </is>
       </c>
       <c r="I368" s="4" t="n">
-        <v>3.38</v>
+        <v>3.39</v>
       </c>
       <c r="J368" s="4" t="n">
-        <v>74.90000000000001</v>
+        <v>75</v>
       </c>
       <c r="K368" s="4" t="n">
-        <v>25.1</v>
+        <v>25</v>
       </c>
       <c r="L368" t="inlineStr">
         <is>
@@ -40520,10 +40520,10 @@
         <v>0</v>
       </c>
       <c r="AC371" s="4" t="n">
-        <v>54.72</v>
+        <v>54.73</v>
       </c>
       <c r="AD371" s="4" t="n">
-        <v>45.28</v>
+        <v>45.27</v>
       </c>
       <c r="AE371" s="4" t="n">
         <v>0</v>
@@ -41502,7 +41502,7 @@
         </is>
       </c>
       <c r="I381" s="4" t="n">
-        <v>-2.62</v>
+        <v>-2.61</v>
       </c>
       <c r="J381" s="4" t="n">
         <v>28</v>
@@ -41568,10 +41568,10 @@
         <v>0</v>
       </c>
       <c r="AC381" s="4" t="n">
-        <v>47.47</v>
+        <v>47.48</v>
       </c>
       <c r="AD381" s="4" t="n">
-        <v>50.03</v>
+        <v>50.02</v>
       </c>
       <c r="AE381" s="4" t="n">
         <v>0</v>
@@ -42154,7 +42154,7 @@
         </is>
       </c>
       <c r="I387" s="4" t="n">
-        <v>-17.09</v>
+        <v>-17.14</v>
       </c>
       <c r="J387" s="4" t="n">
         <v>0.4</v>
@@ -42212,10 +42212,10 @@
         <v>0</v>
       </c>
       <c r="AC387" s="4" t="n">
-        <v>41.46</v>
+        <v>41.43</v>
       </c>
       <c r="AD387" s="4" t="n">
-        <v>58.54</v>
+        <v>58.57</v>
       </c>
       <c r="AE387" s="4" t="n">
         <v>0</v>
@@ -42362,7 +42362,7 @@
         </is>
       </c>
       <c r="I389" s="4" t="n">
-        <v>-53.77</v>
+        <v>-53.78</v>
       </c>
       <c r="J389" s="4" t="n">
         <v>0</v>
@@ -42376,13 +42376,13 @@
         </is>
       </c>
       <c r="M389" s="4" t="n">
-        <v>-54.32</v>
+        <v>-54.33</v>
       </c>
       <c r="N389" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O389" s="4" t="n">
-        <v>-53.69</v>
+        <v>-53.7</v>
       </c>
       <c r="P389" s="4" t="n">
         <v>-1.63</v>
@@ -42422,10 +42422,10 @@
         <v>0</v>
       </c>
       <c r="AC389" s="4" t="n">
-        <v>22.74</v>
+        <v>22.73</v>
       </c>
       <c r="AD389" s="4" t="n">
-        <v>75.63</v>
+        <v>75.64</v>
       </c>
       <c r="AE389" s="4" t="n">
         <v>0</v>
@@ -42473,7 +42473,7 @@
         </is>
       </c>
       <c r="I390" s="4" t="n">
-        <v>-31.13</v>
+        <v>-31.14</v>
       </c>
       <c r="J390" s="4" t="n">
         <v>0</v>
@@ -42487,13 +42487,13 @@
         </is>
       </c>
       <c r="M390" s="4" t="n">
-        <v>-30.15</v>
+        <v>-30.17</v>
       </c>
       <c r="N390" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O390" s="4" t="n">
-        <v>-31.02</v>
+        <v>-31.03</v>
       </c>
       <c r="P390" s="4" t="n">
         <v>-1.28</v>
@@ -42533,10 +42533,10 @@
         <v>0</v>
       </c>
       <c r="AC390" s="4" t="n">
-        <v>33.69</v>
+        <v>33.68</v>
       </c>
       <c r="AD390" s="4" t="n">
-        <v>64.15000000000001</v>
+        <v>64.16</v>
       </c>
       <c r="AE390" s="4" t="n">
         <v>0</v>
@@ -42584,7 +42584,7 @@
         </is>
       </c>
       <c r="I391" s="4" t="n">
-        <v>-32.9</v>
+        <v>-32.92</v>
       </c>
       <c r="J391" s="4" t="n">
         <v>0</v>
@@ -42598,13 +42598,13 @@
         </is>
       </c>
       <c r="M391" s="4" t="n">
-        <v>-31.97</v>
+        <v>-31.98</v>
       </c>
       <c r="N391" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O391" s="4" t="n">
-        <v>-32.8</v>
+        <v>-32.82</v>
       </c>
       <c r="P391" s="4" t="n">
         <v>-2.34</v>
@@ -42644,10 +42644,10 @@
         <v>0</v>
       </c>
       <c r="AC391" s="4" t="n">
-        <v>32.88</v>
+        <v>32.87</v>
       </c>
       <c r="AD391" s="4" t="n">
-        <v>65.12</v>
+        <v>65.13</v>
       </c>
       <c r="AE391" s="4" t="n">
         <v>0</v>
@@ -42695,7 +42695,7 @@
         </is>
       </c>
       <c r="I392" s="4" t="n">
-        <v>-15.28</v>
+        <v>-15.29</v>
       </c>
       <c r="J392" s="4" t="n">
         <v>0.6</v>
@@ -42709,13 +42709,13 @@
         </is>
       </c>
       <c r="M392" s="4" t="n">
-        <v>-18.94</v>
+        <v>-18.95</v>
       </c>
       <c r="N392" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O392" s="4" t="n">
-        <v>-15.17</v>
+        <v>-15.18</v>
       </c>
       <c r="P392" s="4" t="n">
         <v>-1.26</v>
@@ -42755,10 +42755,10 @@
         <v>0</v>
       </c>
       <c r="AC392" s="4" t="n">
-        <v>41.42</v>
+        <v>41.41</v>
       </c>
       <c r="AD392" s="4" t="n">
-        <v>56.35</v>
+        <v>56.36</v>
       </c>
       <c r="AE392" s="4" t="n">
         <v>0</v>
@@ -42816,13 +42816,13 @@
         </is>
       </c>
       <c r="M393" s="4" t="n">
-        <v>-17.02</v>
+        <v>-17.03</v>
       </c>
       <c r="N393" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O393" s="4" t="n">
-        <v>-10.86</v>
+        <v>-10.87</v>
       </c>
       <c r="P393" s="4" t="n">
         <v>0.96</v>
@@ -42915,7 +42915,7 @@
         </is>
       </c>
       <c r="I394" s="4" t="n">
-        <v>-19.14</v>
+        <v>-19.16</v>
       </c>
       <c r="J394" s="4" t="n">
         <v>0.3</v>
@@ -42929,13 +42929,13 @@
         </is>
       </c>
       <c r="M394" s="4" t="n">
-        <v>-21.97</v>
+        <v>-21.99</v>
       </c>
       <c r="N394" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O394" s="4" t="n">
-        <v>-19.04</v>
+        <v>-19.05</v>
       </c>
       <c r="P394" s="4" t="n">
         <v>-2.06</v>
@@ -42975,10 +42975,10 @@
         <v>0</v>
       </c>
       <c r="AC394" s="4" t="n">
-        <v>39.59</v>
+        <v>39.58</v>
       </c>
       <c r="AD394" s="4" t="n">
-        <v>58.34</v>
+        <v>58.35</v>
       </c>
       <c r="AE394" s="4" t="n">
         <v>0</v>
@@ -43026,7 +43026,7 @@
         </is>
       </c>
       <c r="I395" s="4" t="n">
-        <v>-15.67</v>
+        <v>-15.68</v>
       </c>
       <c r="J395" s="4" t="n">
         <v>0.6</v>
@@ -43040,13 +43040,13 @@
         </is>
       </c>
       <c r="M395" s="4" t="n">
-        <v>-18.35</v>
+        <v>-18.37</v>
       </c>
       <c r="N395" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O395" s="4" t="n">
-        <v>-15.56</v>
+        <v>-15.57</v>
       </c>
       <c r="P395" s="4" t="n">
         <v>-0.6</v>
@@ -43137,7 +43137,7 @@
         </is>
       </c>
       <c r="I396" s="4" t="n">
-        <v>-18.9</v>
+        <v>-18.91</v>
       </c>
       <c r="J396" s="4" t="n">
         <v>0.3</v>
@@ -43151,13 +43151,13 @@
         </is>
       </c>
       <c r="M396" s="4" t="n">
-        <v>-16.15</v>
+        <v>-16.17</v>
       </c>
       <c r="N396" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O396" s="4" t="n">
-        <v>-18.81</v>
+        <v>-18.82</v>
       </c>
       <c r="P396" s="4" t="n">
         <v>-2.43</v>
@@ -43197,10 +43197,10 @@
         <v>0</v>
       </c>
       <c r="AC396" s="4" t="n">
-        <v>39.82</v>
+        <v>39.81</v>
       </c>
       <c r="AD396" s="4" t="n">
-        <v>58.37</v>
+        <v>58.38</v>
       </c>
       <c r="AE396" s="4" t="n">
         <v>0</v>
@@ -43244,13 +43244,13 @@
         </is>
       </c>
       <c r="I397" s="4" t="n">
-        <v>-8.31</v>
+        <v>-8.34</v>
       </c>
       <c r="J397" s="4" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="K397" s="4" t="n">
-        <v>91.40000000000001</v>
+        <v>91.5</v>
       </c>
       <c r="L397" t="inlineStr">
         <is>
@@ -43258,13 +43258,13 @@
         </is>
       </c>
       <c r="M397" s="4" t="n">
-        <v>-15</v>
+        <v>-15.02</v>
       </c>
       <c r="N397" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O397" s="4" t="n">
-        <v>-9.449999999999999</v>
+        <v>-9.460000000000001</v>
       </c>
       <c r="P397" s="4" t="n">
         <v>0.24</v>
@@ -43310,10 +43310,10 @@
         <v>0</v>
       </c>
       <c r="AC397" s="4" t="n">
-        <v>45.08</v>
+        <v>45.07</v>
       </c>
       <c r="AD397" s="4" t="n">
-        <v>53.26</v>
+        <v>53.27</v>
       </c>
       <c r="AE397" s="4" t="n">
         <v>0</v>
@@ -43361,7 +43361,7 @@
         </is>
       </c>
       <c r="I398" s="4" t="n">
-        <v>-42.64</v>
+        <v>-42.65</v>
       </c>
       <c r="J398" s="4" t="n">
         <v>0</v>
@@ -43375,13 +43375,13 @@
         </is>
       </c>
       <c r="M398" s="4" t="n">
-        <v>-43.97</v>
+        <v>-43.98</v>
       </c>
       <c r="N398" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O398" s="4" t="n">
-        <v>-42.64</v>
+        <v>-42.65</v>
       </c>
       <c r="P398" s="4" t="n">
         <v>-2.58</v>
@@ -43460,7 +43460,7 @@
         </is>
       </c>
       <c r="I399" s="4" t="n">
-        <v>-11.8</v>
+        <v>-11.81</v>
       </c>
       <c r="J399" s="4" t="n">
         <v>1.2</v>
@@ -43474,13 +43474,13 @@
         </is>
       </c>
       <c r="M399" s="4" t="n">
-        <v>-18.77</v>
+        <v>-18.78</v>
       </c>
       <c r="N399" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O399" s="4" t="n">
-        <v>-11.8</v>
+        <v>-11.81</v>
       </c>
       <c r="P399" s="4" t="n">
         <v>0.88</v>
@@ -43563,7 +43563,7 @@
         </is>
       </c>
       <c r="I400" s="4" t="n">
-        <v>-14.88</v>
+        <v>-14.89</v>
       </c>
       <c r="J400" s="4" t="n">
         <v>0.7</v>
@@ -43577,13 +43577,13 @@
         </is>
       </c>
       <c r="M400" s="4" t="n">
-        <v>-18.57</v>
+        <v>-18.58</v>
       </c>
       <c r="N400" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O400" s="4" t="n">
-        <v>-14.88</v>
+        <v>-14.89</v>
       </c>
       <c r="P400" s="4" t="n">
         <v>-0.25</v>
@@ -43680,7 +43680,7 @@
         </is>
       </c>
       <c r="M401" s="4" t="n">
-        <v>-19.42</v>
+        <v>-19.43</v>
       </c>
       <c r="N401" s="4" t="n">
         <v>5.62</v>
@@ -43769,7 +43769,7 @@
         </is>
       </c>
       <c r="I402" s="4" t="n">
-        <v>-14.57</v>
+        <v>-14.58</v>
       </c>
       <c r="J402" s="4" t="n">
         <v>0.7</v>
@@ -43783,13 +43783,13 @@
         </is>
       </c>
       <c r="M402" s="4" t="n">
-        <v>-16.26</v>
+        <v>-16.27</v>
       </c>
       <c r="N402" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O402" s="4" t="n">
-        <v>-14.57</v>
+        <v>-14.58</v>
       </c>
       <c r="P402" s="4" t="n">
         <v>-2.33</v>
@@ -43872,7 +43872,7 @@
         </is>
       </c>
       <c r="I403" s="4" t="n">
-        <v>-18.22</v>
+        <v>-18.23</v>
       </c>
       <c r="J403" s="4" t="n">
         <v>0.3</v>
@@ -43886,13 +43886,13 @@
         </is>
       </c>
       <c r="M403" s="4" t="n">
-        <v>-18.34</v>
+        <v>-18.35</v>
       </c>
       <c r="N403" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O403" s="4" t="n">
-        <v>-18.22</v>
+        <v>-18.23</v>
       </c>
       <c r="P403" s="4" t="n">
         <v>-2.94</v>
@@ -43924,10 +43924,10 @@
         <v>0</v>
       </c>
       <c r="AC403" s="4" t="n">
-        <v>40.89</v>
+        <v>40.88</v>
       </c>
       <c r="AD403" s="4" t="n">
-        <v>59.11</v>
+        <v>59.12</v>
       </c>
       <c r="AE403" s="4" t="n">
         <v>0</v>
@@ -43989,13 +43989,13 @@
         </is>
       </c>
       <c r="M404" s="4" t="n">
-        <v>30.99</v>
+        <v>30.98</v>
       </c>
       <c r="N404" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O404" s="4" t="n">
-        <v>41.54</v>
+        <v>41.53</v>
       </c>
       <c r="P404" s="4" t="n">
         <v>1.84</v>
@@ -44181,7 +44181,7 @@
         </is>
       </c>
       <c r="I406" s="4" t="n">
-        <v>-6.15</v>
+        <v>-6.16</v>
       </c>
       <c r="J406" s="4" t="n">
         <v>15.2</v>
@@ -44195,13 +44195,13 @@
         </is>
       </c>
       <c r="M406" s="4" t="n">
-        <v>-12.02</v>
+        <v>-12.03</v>
       </c>
       <c r="N406" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O406" s="4" t="n">
-        <v>-6.15</v>
+        <v>-6.16</v>
       </c>
       <c r="P406" s="4" t="n">
         <v>-1.93</v>
@@ -44280,7 +44280,7 @@
         </is>
       </c>
       <c r="I407" s="4" t="n">
-        <v>-12.53</v>
+        <v>-12.54</v>
       </c>
       <c r="J407" s="4" t="n">
         <v>1</v>
@@ -44300,7 +44300,7 @@
         <v>5.62</v>
       </c>
       <c r="O407" s="4" t="n">
-        <v>-12.53</v>
+        <v>-12.54</v>
       </c>
       <c r="P407" s="4" t="n">
         <v>-1.52</v>
@@ -44383,7 +44383,7 @@
         </is>
       </c>
       <c r="I408" s="4" t="n">
-        <v>-26.89</v>
+        <v>-26.9</v>
       </c>
       <c r="J408" s="4" t="n">
         <v>0</v>
@@ -44403,7 +44403,7 @@
         <v>5.62</v>
       </c>
       <c r="O408" s="4" t="n">
-        <v>-26.89</v>
+        <v>-26.9</v>
       </c>
       <c r="P408" s="4" t="n">
         <v>-2.36</v>
@@ -44538,10 +44538,10 @@
         <v>0</v>
       </c>
       <c r="AC409" s="4" t="n">
-        <v>40.88</v>
+        <v>40.87</v>
       </c>
       <c r="AD409" s="4" t="n">
-        <v>59.12</v>
+        <v>59.13</v>
       </c>
       <c r="AE409" s="4" t="n">
         <v>0</v>
@@ -44603,7 +44603,7 @@
         </is>
       </c>
       <c r="M410" s="4" t="n">
-        <v>-41.99</v>
+        <v>-42</v>
       </c>
       <c r="N410" s="4" t="n">
         <v>5.62</v>
@@ -44627,7 +44627,7 @@
       </c>
       <c r="V410" s="4" t="n"/>
       <c r="W410" s="5" t="n">
-        <v>98404</v>
+        <v>98699</v>
       </c>
       <c r="X410" s="5" t="n">
         <v>4036265</v>
@@ -44692,7 +44692,7 @@
         </is>
       </c>
       <c r="I411" s="4" t="n">
-        <v>-19.17</v>
+        <v>-19.18</v>
       </c>
       <c r="J411" s="4" t="n">
         <v>0.3</v>
@@ -44706,13 +44706,13 @@
         </is>
       </c>
       <c r="M411" s="4" t="n">
-        <v>-19.4</v>
+        <v>-19.41</v>
       </c>
       <c r="N411" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O411" s="4" t="n">
-        <v>-19.17</v>
+        <v>-19.18</v>
       </c>
       <c r="P411" s="4" t="n">
         <v>-1.94</v>
@@ -44795,7 +44795,7 @@
         </is>
       </c>
       <c r="I412" s="4" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="J412" s="4" t="n">
         <v>66.09999999999999</v>
@@ -44815,7 +44815,7 @@
         <v>5.62</v>
       </c>
       <c r="O412" s="4" t="n">
-        <v>-1.05</v>
+        <v>-1.06</v>
       </c>
       <c r="P412" s="4" t="n">
         <v>-0.33</v>
@@ -44853,10 +44853,10 @@
         <v>0</v>
       </c>
       <c r="AC412" s="4" t="n">
-        <v>50.56</v>
+        <v>50.55</v>
       </c>
       <c r="AD412" s="4" t="n">
-        <v>49.44</v>
+        <v>49.45</v>
       </c>
       <c r="AE412" s="4" t="n">
         <v>0</v>
@@ -44918,7 +44918,7 @@
         </is>
       </c>
       <c r="M413" s="4" t="n">
-        <v>26.96</v>
+        <v>26.95</v>
       </c>
       <c r="N413" s="4" t="n">
         <v>5.62</v>
@@ -45007,7 +45007,7 @@
         </is>
       </c>
       <c r="I414" s="4" t="n">
-        <v>-16.51</v>
+        <v>-16.52</v>
       </c>
       <c r="J414" s="4" t="n">
         <v>0.5</v>
@@ -45027,7 +45027,7 @@
         <v>5.62</v>
       </c>
       <c r="O414" s="4" t="n">
-        <v>-16.51</v>
+        <v>-16.52</v>
       </c>
       <c r="P414" s="4" t="n">
         <v>-2.2</v>
@@ -45110,7 +45110,7 @@
         </is>
       </c>
       <c r="I415" s="4" t="n">
-        <v>71.62</v>
+        <v>71.61</v>
       </c>
       <c r="J415" s="4" t="n">
         <v>100</v>
@@ -45124,13 +45124,13 @@
         </is>
       </c>
       <c r="M415" s="4" t="n">
-        <v>63.05</v>
+        <v>63.04</v>
       </c>
       <c r="N415" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O415" s="4" t="n">
-        <v>71.62</v>
+        <v>71.61</v>
       </c>
       <c r="P415" s="4" t="n">
         <v>0</v>
@@ -45364,10 +45364,10 @@
         <v>0</v>
       </c>
       <c r="AC417" s="4" t="n">
-        <v>74.88</v>
+        <v>74.87</v>
       </c>
       <c r="AD417" s="4" t="n">
-        <v>25.12</v>
+        <v>25.13</v>
       </c>
       <c r="AE417" s="4" t="n">
         <v>0</v>
@@ -45411,7 +45411,7 @@
         </is>
       </c>
       <c r="I418" s="4" t="n">
-        <v>-11.76</v>
+        <v>-11.77</v>
       </c>
       <c r="J418" s="4" t="n">
         <v>1.2</v>
@@ -45425,13 +45425,13 @@
         </is>
       </c>
       <c r="M418" s="4" t="n">
-        <v>-16.68</v>
+        <v>-16.69</v>
       </c>
       <c r="N418" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O418" s="4" t="n">
-        <v>-11.76</v>
+        <v>-11.77</v>
       </c>
       <c r="P418" s="4" t="n">
         <v>-2.02</v>
@@ -45513,10 +45513,10 @@
         <v>-12.52</v>
       </c>
       <c r="J419" s="4" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K419" s="4" t="n">
-        <v>98.90000000000001</v>
+        <v>99</v>
       </c>
       <c r="L419" t="inlineStr">
         <is>
@@ -45524,7 +45524,7 @@
         </is>
       </c>
       <c r="M419" s="4" t="n">
-        <v>-17.26</v>
+        <v>-17.27</v>
       </c>
       <c r="N419" s="4" t="n">
         <v>5.62</v>
@@ -45623,13 +45623,13 @@
         </is>
       </c>
       <c r="M420" s="4" t="n">
-        <v>-8.26</v>
+        <v>-8.27</v>
       </c>
       <c r="N420" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O420" s="4" t="n">
-        <v>-1.37</v>
+        <v>-1.38</v>
       </c>
       <c r="P420" s="4" t="n">
         <v>-0.77</v>
@@ -45726,7 +45726,7 @@
         </is>
       </c>
       <c r="I421" s="4" t="n">
-        <v>-12.17</v>
+        <v>-12.18</v>
       </c>
       <c r="J421" s="4" t="n">
         <v>1.1</v>
@@ -45746,7 +45746,7 @@
         <v>5.62</v>
       </c>
       <c r="O421" s="4" t="n">
-        <v>-12.17</v>
+        <v>-12.18</v>
       </c>
       <c r="P421" s="4" t="n">
         <v>-1.72</v>
@@ -45829,7 +45829,7 @@
         </is>
       </c>
       <c r="I422" s="4" t="n">
-        <v>-13.39</v>
+        <v>-13.4</v>
       </c>
       <c r="J422" s="4" t="n">
         <v>0.9</v>
@@ -45843,13 +45843,13 @@
         </is>
       </c>
       <c r="M422" s="4" t="n">
-        <v>-17.82</v>
+        <v>-17.83</v>
       </c>
       <c r="N422" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O422" s="4" t="n">
-        <v>-13.39</v>
+        <v>-13.4</v>
       </c>
       <c r="P422" s="4" t="n">
         <v>0</v>
@@ -45881,10 +45881,10 @@
         <v>0</v>
       </c>
       <c r="AC422" s="4" t="n">
-        <v>43.31</v>
+        <v>43.3</v>
       </c>
       <c r="AD422" s="4" t="n">
-        <v>56.69</v>
+        <v>56.7</v>
       </c>
       <c r="AE422" s="4" t="n">
         <v>0</v>
@@ -45946,13 +45946,13 @@
         </is>
       </c>
       <c r="M423" s="4" t="n">
-        <v>-18.94</v>
+        <v>-18.95</v>
       </c>
       <c r="N423" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O423" s="4" t="n">
-        <v>-22.12</v>
+        <v>-22.13</v>
       </c>
       <c r="P423" s="4" t="n">
         <v>-3.11</v>
@@ -46043,7 +46043,7 @@
         </is>
       </c>
       <c r="I424" s="4" t="n">
-        <v>-13.39</v>
+        <v>-13.4</v>
       </c>
       <c r="J424" s="4" t="n">
         <v>0.9</v>
@@ -46057,13 +46057,13 @@
         </is>
       </c>
       <c r="M424" s="4" t="n">
-        <v>-16.18</v>
+        <v>-16.19</v>
       </c>
       <c r="N424" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O424" s="4" t="n">
-        <v>-13.39</v>
+        <v>-13.4</v>
       </c>
       <c r="P424" s="4" t="n">
         <v>-1.33</v>
@@ -46146,7 +46146,7 @@
         </is>
       </c>
       <c r="I425" s="4" t="n">
-        <v>15.62</v>
+        <v>15.65</v>
       </c>
       <c r="J425" s="4" t="n">
         <v>99.40000000000001</v>
@@ -46160,13 +46160,13 @@
         </is>
       </c>
       <c r="M425" s="4" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="N425" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O425" s="4" t="n">
-        <v>20.64</v>
+        <v>20.63</v>
       </c>
       <c r="P425" s="4" t="n">
         <v>0.34</v>
@@ -46212,10 +46212,10 @@
         <v>0</v>
       </c>
       <c r="AC425" s="4" t="n">
-        <v>54.77</v>
+        <v>54.79</v>
       </c>
       <c r="AD425" s="4" t="n">
-        <v>39.98</v>
+        <v>39.96</v>
       </c>
       <c r="AE425" s="4" t="n">
         <v>0</v>
@@ -46362,7 +46362,7 @@
         </is>
       </c>
       <c r="I427" s="4" t="n">
-        <v>63.52</v>
+        <v>63.51</v>
       </c>
       <c r="J427" s="4" t="n">
         <v>100</v>
@@ -46376,13 +46376,13 @@
         </is>
       </c>
       <c r="M427" s="4" t="n">
-        <v>55.03</v>
+        <v>55.02</v>
       </c>
       <c r="N427" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O427" s="4" t="n">
-        <v>63.52</v>
+        <v>63.51</v>
       </c>
       <c r="P427" s="4" t="n">
         <v>1.56</v>
@@ -46414,10 +46414,10 @@
         <v>0</v>
       </c>
       <c r="AC427" s="4" t="n">
-        <v>81.76000000000001</v>
+        <v>81.75</v>
       </c>
       <c r="AD427" s="4" t="n">
-        <v>18.24</v>
+        <v>18.25</v>
       </c>
       <c r="AE427" s="4" t="n">
         <v>0</v>
@@ -46465,7 +46465,7 @@
         </is>
       </c>
       <c r="I428" s="4" t="n">
-        <v>-18.27</v>
+        <v>-18.28</v>
       </c>
       <c r="J428" s="4" t="n">
         <v>0.3</v>
@@ -46525,10 +46525,10 @@
         <v>0</v>
       </c>
       <c r="AC428" s="4" t="n">
-        <v>39.91</v>
+        <v>39.9</v>
       </c>
       <c r="AD428" s="4" t="n">
-        <v>57.75</v>
+        <v>57.76</v>
       </c>
       <c r="AE428" s="4" t="n">
         <v>0</v>
@@ -46572,7 +46572,7 @@
         </is>
       </c>
       <c r="I429" s="4" t="n">
-        <v>-7.77</v>
+        <v>-7.78</v>
       </c>
       <c r="J429" s="4" t="n">
         <v>10.1</v>
@@ -46592,7 +46592,7 @@
         <v>5.62</v>
       </c>
       <c r="O429" s="4" t="n">
-        <v>-7.77</v>
+        <v>-7.78</v>
       </c>
       <c r="P429" s="4" t="n">
         <v>-1.71</v>
@@ -46685,7 +46685,7 @@
         </is>
       </c>
       <c r="M430" s="4" t="n">
-        <v>41.19</v>
+        <v>41.18</v>
       </c>
       <c r="N430" s="4" t="n">
         <v>5.62</v>
@@ -46723,10 +46723,10 @@
         <v>0</v>
       </c>
       <c r="AC430" s="4" t="n">
-        <v>73.31999999999999</v>
+        <v>73.31</v>
       </c>
       <c r="AD430" s="4" t="n">
-        <v>26.68</v>
+        <v>26.69</v>
       </c>
       <c r="AE430" s="4" t="n">
         <v>0</v>
@@ -46774,13 +46774,13 @@
         </is>
       </c>
       <c r="I431" s="4" t="n">
-        <v>8.83</v>
+        <v>8.85</v>
       </c>
       <c r="J431" s="4" t="n">
-        <v>92.8</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="K431" s="4" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="L431" t="inlineStr">
         <is>
@@ -46840,10 +46840,10 @@
         <v>0</v>
       </c>
       <c r="AC431" s="4" t="n">
-        <v>52.06</v>
+        <v>52.07</v>
       </c>
       <c r="AD431" s="4" t="n">
-        <v>43.61</v>
+        <v>43.6</v>
       </c>
       <c r="AE431" s="4" t="n">
         <v>1.53</v>
@@ -46887,13 +46887,13 @@
         </is>
       </c>
       <c r="I432" s="4" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="J432" s="4" t="n">
-        <v>61.9</v>
+        <v>62.1</v>
       </c>
       <c r="K432" s="4" t="n">
-        <v>38.1</v>
+        <v>37.9</v>
       </c>
       <c r="L432" t="inlineStr">
         <is>
@@ -46901,16 +46901,16 @@
         </is>
       </c>
       <c r="M432" s="4" t="n">
-        <v>-3.86</v>
+        <v>-3.87</v>
       </c>
       <c r="N432" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O432" s="4" t="n">
-        <v>3.63</v>
+        <v>3.61</v>
       </c>
       <c r="P432" s="4" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="Q432" s="4" t="n">
         <v>0</v>
@@ -46945,10 +46945,10 @@
         <v>0</v>
       </c>
       <c r="AC432" s="4" t="n">
-        <v>50.02</v>
+        <v>50.05</v>
       </c>
       <c r="AD432" s="4" t="n">
-        <v>49.98</v>
+        <v>49.95</v>
       </c>
       <c r="AE432" s="4" t="n">
         <v>0</v>
@@ -47048,10 +47048,10 @@
         <v>0</v>
       </c>
       <c r="AC433" s="4" t="n">
-        <v>42.28</v>
+        <v>42.27</v>
       </c>
       <c r="AD433" s="4" t="n">
-        <v>57.72</v>
+        <v>57.73</v>
       </c>
       <c r="AE433" s="4" t="n">
         <v>0</v>
@@ -47113,7 +47113,7 @@
         </is>
       </c>
       <c r="M434" s="4" t="n">
-        <v>63.81</v>
+        <v>63.8</v>
       </c>
       <c r="N434" s="4" t="n">
         <v>5.62</v>
@@ -47198,7 +47198,7 @@
         </is>
       </c>
       <c r="I435" s="4" t="n">
-        <v>-13.53</v>
+        <v>-13.54</v>
       </c>
       <c r="J435" s="4" t="n">
         <v>0.9</v>
@@ -47212,7 +47212,7 @@
         </is>
       </c>
       <c r="M435" s="4" t="n">
-        <v>-16.42</v>
+        <v>-16.43</v>
       </c>
       <c r="N435" s="4" t="n">
         <v>5.62</v>
@@ -47858,13 +47858,13 @@
         </is>
       </c>
       <c r="I441" s="4" t="n">
-        <v>4.18</v>
+        <v>4.2</v>
       </c>
       <c r="J441" s="4" t="n">
-        <v>77.90000000000001</v>
+        <v>78</v>
       </c>
       <c r="K441" s="4" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="L441" t="inlineStr">
         <is>
@@ -47924,10 +47924,10 @@
         <v>0</v>
       </c>
       <c r="AC441" s="4" t="n">
-        <v>50.86</v>
+        <v>50.87</v>
       </c>
       <c r="AD441" s="4" t="n">
-        <v>46.78</v>
+        <v>46.77</v>
       </c>
       <c r="AE441" s="4" t="n">
         <v>0</v>
@@ -48197,7 +48197,7 @@
         </is>
       </c>
       <c r="I444" s="4" t="n">
-        <v>-5.25</v>
+        <v>-5.24</v>
       </c>
       <c r="J444" s="4" t="n">
         <v>18.3</v>
@@ -48964,7 +48964,7 @@
         </is>
       </c>
       <c r="I451" s="4" t="n">
-        <v>35.8</v>
+        <v>35.79</v>
       </c>
       <c r="J451" s="4" t="n">
         <v>100</v>
@@ -48978,13 +48978,13 @@
         </is>
       </c>
       <c r="M451" s="4" t="n">
-        <v>19.93</v>
+        <v>19.92</v>
       </c>
       <c r="N451" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O451" s="4" t="n">
-        <v>35.98</v>
+        <v>35.97</v>
       </c>
       <c r="P451" s="4" t="n">
         <v>1.67</v>
@@ -49287,13 +49287,13 @@
         </is>
       </c>
       <c r="I454" s="4" t="n">
-        <v>6.59</v>
+        <v>6.61</v>
       </c>
       <c r="J454" s="4" t="n">
-        <v>86.2</v>
+        <v>86.3</v>
       </c>
       <c r="K454" s="4" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="L454" t="inlineStr">
         <is>
@@ -49345,10 +49345,10 @@
         <v>0</v>
       </c>
       <c r="AC454" s="4" t="n">
-        <v>53.29</v>
+        <v>53.31</v>
       </c>
       <c r="AD454" s="4" t="n">
-        <v>46.71</v>
+        <v>46.69</v>
       </c>
       <c r="AE454" s="4" t="n">
         <v>0</v>
@@ -50331,13 +50331,13 @@
         </is>
       </c>
       <c r="I464" s="4" t="n">
-        <v>4.49</v>
+        <v>4.5</v>
       </c>
       <c r="J464" s="4" t="n">
-        <v>79</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="K464" s="4" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="L464" t="inlineStr">
         <is>
@@ -51302,13 +51302,13 @@
         </is>
       </c>
       <c r="I473" s="4" t="n">
-        <v>-0.39</v>
+        <v>-0.4</v>
       </c>
       <c r="J473" s="4" t="n">
-        <v>38.1</v>
+        <v>38</v>
       </c>
       <c r="K473" s="4" t="n">
-        <v>61.9</v>
+        <v>62</v>
       </c>
       <c r="L473" t="inlineStr">
         <is>
@@ -51407,7 +51407,7 @@
         </is>
       </c>
       <c r="I474" s="4" t="n">
-        <v>-21.78</v>
+        <v>-21.8</v>
       </c>
       <c r="J474" s="4" t="n">
         <v>0.1</v>
@@ -51421,7 +51421,7 @@
         </is>
       </c>
       <c r="M474" s="4" t="n">
-        <v>-26.49</v>
+        <v>-26.5</v>
       </c>
       <c r="N474" s="4" t="n">
         <v>5.62</v>
@@ -51465,10 +51465,10 @@
         <v>0</v>
       </c>
       <c r="AC474" s="4" t="n">
-        <v>39.11</v>
+        <v>39.1</v>
       </c>
       <c r="AD474" s="4" t="n">
-        <v>60.89</v>
+        <v>60.9</v>
       </c>
       <c r="AE474" s="4" t="n">
         <v>0</v>
@@ -51516,7 +51516,7 @@
         </is>
       </c>
       <c r="I475" s="4" t="n">
-        <v>-17.26</v>
+        <v>-17.33</v>
       </c>
       <c r="J475" s="4" t="n">
         <v>0.4</v>
@@ -51530,13 +51530,13 @@
         </is>
       </c>
       <c r="M475" s="4" t="n">
-        <v>-27.04</v>
+        <v>-27.06</v>
       </c>
       <c r="N475" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O475" s="4" t="n">
-        <v>-24.46</v>
+        <v>-24.49</v>
       </c>
       <c r="P475" s="4" t="n">
         <v>-0.87</v>
@@ -51582,10 +51582,10 @@
         <v>0</v>
       </c>
       <c r="AC475" s="4" t="n">
-        <v>39.95</v>
+        <v>39.91</v>
       </c>
       <c r="AD475" s="4" t="n">
-        <v>56.61</v>
+        <v>56.65</v>
       </c>
       <c r="AE475" s="4" t="n">
         <v>0</v>
@@ -51850,10 +51850,10 @@
         <v>-5.58</v>
       </c>
       <c r="J478" s="4" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="K478" s="4" t="n">
-        <v>82.8</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="L478" t="inlineStr">
         <is>
@@ -51964,7 +51964,7 @@
         </is>
       </c>
       <c r="I479" s="4" t="n">
-        <v>12.35</v>
+        <v>12.11</v>
       </c>
       <c r="J479" s="4" t="n">
         <v>98.90000000000001</v>
@@ -51978,7 +51978,7 @@
         </is>
       </c>
       <c r="M479" s="4" t="n">
-        <v>-0.58</v>
+        <v>-0.59</v>
       </c>
       <c r="N479" s="4" t="n">
         <v>5.62</v>
@@ -51996,16 +51996,16 @@
         <v>-2.21</v>
       </c>
       <c r="S479" s="4" t="n">
-        <v>53.62</v>
+        <v>52.7</v>
       </c>
       <c r="T479" s="4" t="n">
-        <v>42.98</v>
+        <v>42.94</v>
       </c>
       <c r="U479" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V479" s="4" t="n">
-        <v>11.11</v>
+        <v>10.78</v>
       </c>
       <c r="W479" s="5" t="n">
         <v>77279766</v>
@@ -52022,10 +52022,10 @@
         <v>0</v>
       </c>
       <c r="AC479" s="4" t="n">
-        <v>56.17</v>
+        <v>56.06</v>
       </c>
       <c r="AD479" s="4" t="n">
-        <v>43.83</v>
+        <v>43.94</v>
       </c>
       <c r="AE479" s="4" t="n">
         <v>0</v>
@@ -52069,7 +52069,7 @@
         </is>
       </c>
       <c r="I480" s="4" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.59</v>
       </c>
       <c r="J480" s="4" t="n">
         <v>36</v>
@@ -52083,13 +52083,13 @@
         </is>
       </c>
       <c r="M480" s="4" t="n">
-        <v>-6.91</v>
+        <v>-6.92</v>
       </c>
       <c r="N480" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O480" s="4" t="n">
-        <v>-3.15</v>
+        <v>-3.16</v>
       </c>
       <c r="P480" s="4" t="n">
         <v>-0.22</v>
@@ -52135,10 +52135,10 @@
         <v>0</v>
       </c>
       <c r="AC480" s="4" t="n">
-        <v>49.47</v>
+        <v>49.46</v>
       </c>
       <c r="AD480" s="4" t="n">
-        <v>50.03</v>
+        <v>50.04</v>
       </c>
       <c r="AE480" s="4" t="n">
         <v>0</v>
@@ -52186,7 +52186,7 @@
         </is>
       </c>
       <c r="I481" s="4" t="n">
-        <v>-19.76</v>
+        <v>-19.82</v>
       </c>
       <c r="J481" s="4" t="n">
         <v>0.2</v>
@@ -52200,13 +52200,13 @@
         </is>
       </c>
       <c r="M481" s="4" t="n">
-        <v>-30.53</v>
+        <v>-30.55</v>
       </c>
       <c r="N481" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O481" s="4" t="n">
-        <v>-28.21</v>
+        <v>-28.23</v>
       </c>
       <c r="P481" s="4" t="n">
         <v>-1.14</v>
@@ -52246,7 +52246,7 @@
         </is>
       </c>
       <c r="AA481" s="4" t="n">
-        <v>37.93</v>
+        <v>37.89</v>
       </c>
       <c r="AB481" s="4" t="n">
         <v>0.2</v>
@@ -52255,7 +52255,7 @@
         <v>0</v>
       </c>
       <c r="AD481" s="4" t="n">
-        <v>57.68</v>
+        <v>57.72</v>
       </c>
       <c r="AE481" s="4" t="n">
         <v>4.39</v>
@@ -52410,13 +52410,13 @@
         </is>
       </c>
       <c r="I483" s="4" t="n">
-        <v>-5.9</v>
+        <v>-5.95</v>
       </c>
       <c r="J483" s="4" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="K483" s="4" t="n">
-        <v>84</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="L483" t="inlineStr">
         <is>
@@ -52424,13 +52424,13 @@
         </is>
       </c>
       <c r="M483" s="4" t="n">
-        <v>-14.06</v>
+        <v>-14.08</v>
       </c>
       <c r="N483" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O483" s="4" t="n">
-        <v>-9.98</v>
+        <v>-10</v>
       </c>
       <c r="P483" s="4" t="n">
         <v>-0.02</v>
@@ -52476,10 +52476,10 @@
         <v>0</v>
       </c>
       <c r="AC483" s="4" t="n">
-        <v>45.58</v>
+        <v>45.56</v>
       </c>
       <c r="AD483" s="4" t="n">
-        <v>51.29</v>
+        <v>51.31</v>
       </c>
       <c r="AE483" s="4" t="n">
         <v>0</v>
@@ -52523,7 +52523,7 @@
         </is>
       </c>
       <c r="I484" s="4" t="n">
-        <v>-23.89</v>
+        <v>-23.96</v>
       </c>
       <c r="J484" s="4" t="n">
         <v>0.1</v>
@@ -52589,10 +52589,10 @@
         <v>0</v>
       </c>
       <c r="AC484" s="4" t="n">
-        <v>37.26</v>
+        <v>37.23</v>
       </c>
       <c r="AD484" s="4" t="n">
-        <v>60.65</v>
+        <v>60.68</v>
       </c>
       <c r="AE484" s="4" t="n">
         <v>0</v>
@@ -52739,7 +52739,7 @@
         </is>
       </c>
       <c r="I486" s="4" t="n">
-        <v>29.06</v>
+        <v>29.09</v>
       </c>
       <c r="J486" s="4" t="n">
         <v>100</v>
@@ -52753,7 +52753,7 @@
         </is>
       </c>
       <c r="M486" s="4" t="n">
-        <v>28.46</v>
+        <v>28.47</v>
       </c>
       <c r="N486" s="4" t="n">
         <v>5.62</v>
@@ -52805,10 +52805,10 @@
         <v>0</v>
       </c>
       <c r="AC486" s="4" t="n">
-        <v>61.15</v>
+        <v>61.17</v>
       </c>
       <c r="AD486" s="4" t="n">
-        <v>33.62</v>
+        <v>33.6</v>
       </c>
       <c r="AE486" s="4" t="n">
         <v>3.3</v>
@@ -52856,13 +52856,13 @@
         </is>
       </c>
       <c r="I487" s="4" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="J487" s="4" t="n">
-        <v>67.8</v>
+        <v>68.2</v>
       </c>
       <c r="K487" s="4" t="n">
-        <v>32.2</v>
+        <v>31.8</v>
       </c>
       <c r="L487" t="inlineStr">
         <is>
@@ -52914,10 +52914,10 @@
         <v>0</v>
       </c>
       <c r="AC487" s="4" t="n">
-        <v>50.8</v>
+        <v>50.78</v>
       </c>
       <c r="AD487" s="4" t="n">
-        <v>49.2</v>
+        <v>49.22</v>
       </c>
       <c r="AE487" s="4" t="n">
         <v>0</v>
@@ -52961,13 +52961,13 @@
         </is>
       </c>
       <c r="I488" s="4" t="n">
-        <v>4.47</v>
+        <v>4.5</v>
       </c>
       <c r="J488" s="4" t="n">
-        <v>79</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="K488" s="4" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="L488" t="inlineStr">
         <is>
@@ -53027,10 +53027,10 @@
         <v>0</v>
       </c>
       <c r="AC488" s="4" t="n">
-        <v>50.77</v>
+        <v>50.78</v>
       </c>
       <c r="AD488" s="4" t="n">
-        <v>46.42</v>
+        <v>46.41</v>
       </c>
       <c r="AE488" s="4" t="n">
         <v>2.31</v>
@@ -53074,7 +53074,7 @@
         </is>
       </c>
       <c r="I489" s="4" t="n">
-        <v>8.58</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="J489" s="4" t="n">
         <v>92.2</v>
@@ -53140,10 +53140,10 @@
         <v>0</v>
       </c>
       <c r="AC489" s="4" t="n">
-        <v>53.34</v>
+        <v>53.35</v>
       </c>
       <c r="AD489" s="4" t="n">
-        <v>44.91</v>
+        <v>44.9</v>
       </c>
       <c r="AE489" s="4" t="n">
         <v>0</v>
@@ -53191,7 +53191,7 @@
         </is>
       </c>
       <c r="I490" s="4" t="n">
-        <v>-12.27</v>
+        <v>-12.29</v>
       </c>
       <c r="J490" s="4" t="n">
         <v>1.1</v>
@@ -53257,10 +53257,10 @@
         <v>0</v>
       </c>
       <c r="AC490" s="4" t="n">
-        <v>42.31</v>
+        <v>42.3</v>
       </c>
       <c r="AD490" s="4" t="n">
-        <v>54.15</v>
+        <v>54.16</v>
       </c>
       <c r="AE490" s="4" t="n">
         <v>0</v>
@@ -53304,7 +53304,7 @@
         </is>
       </c>
       <c r="I491" s="4" t="n">
-        <v>-24.39</v>
+        <v>-24.45</v>
       </c>
       <c r="J491" s="4" t="n">
         <v>0</v>
@@ -53364,16 +53364,16 @@
         </is>
       </c>
       <c r="AA491" s="4" t="n">
-        <v>25.66</v>
+        <v>25.61</v>
       </c>
       <c r="AB491" s="4" t="n">
         <v>0.1</v>
       </c>
       <c r="AC491" s="4" t="n">
-        <v>20.63</v>
+        <v>20.67</v>
       </c>
       <c r="AD491" s="4" t="n">
-        <v>50.05</v>
+        <v>50.06</v>
       </c>
       <c r="AE491" s="4" t="n">
         <v>3.66</v>
@@ -53417,13 +53417,13 @@
         </is>
       </c>
       <c r="I492" s="4" t="n">
-        <v>7.78</v>
+        <v>7.82</v>
       </c>
       <c r="J492" s="4" t="n">
-        <v>89.90000000000001</v>
+        <v>90</v>
       </c>
       <c r="K492" s="4" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="L492" t="inlineStr">
         <is>
@@ -53449,16 +53449,16 @@
         <v>-3.27</v>
       </c>
       <c r="S492" s="4" t="n">
-        <v>48.37</v>
+        <v>48.36</v>
       </c>
       <c r="T492" s="4" t="n">
-        <v>38.13</v>
+        <v>38.21</v>
       </c>
       <c r="U492" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="V492" s="4" t="n">
-        <v>10.11</v>
+        <v>10.09</v>
       </c>
       <c r="W492" s="5" t="n">
         <v>34975789</v>
@@ -53483,10 +53483,10 @@
         <v>0</v>
       </c>
       <c r="AC492" s="4" t="n">
-        <v>52.18</v>
+        <v>52.2</v>
       </c>
       <c r="AD492" s="4" t="n">
-        <v>44.65</v>
+        <v>44.63</v>
       </c>
       <c r="AE492" s="4" t="n">
         <v>1.87</v>
@@ -53534,27 +53534,27 @@
         </is>
       </c>
       <c r="I493" s="4" t="n">
-        <v>-4.66</v>
+        <v>-1.93</v>
       </c>
       <c r="J493" s="4" t="n">
-        <v>20</v>
+        <v>30.5</v>
       </c>
       <c r="K493" s="4" t="n">
-        <v>80</v>
+        <v>69.5</v>
       </c>
       <c r="L493" t="inlineStr">
         <is>
-          <t>Likely R</t>
+          <t>Lean R</t>
         </is>
       </c>
       <c r="M493" s="4" t="n">
-        <v>-19.07</v>
+        <v>-19.27</v>
       </c>
       <c r="N493" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O493" s="4" t="n">
-        <v>-5.76</v>
+        <v>-5.96</v>
       </c>
       <c r="P493" s="4" t="n">
         <v>-0.47</v>
@@ -53566,16 +53566,16 @@
         <v>-20.84</v>
       </c>
       <c r="S493" s="4" t="n">
-        <v>47</v>
+        <v>46.1</v>
       </c>
       <c r="T493" s="4" t="n">
-        <v>46.63</v>
+        <v>42.48</v>
       </c>
       <c r="U493" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V493" s="4" t="n">
-        <v>-2.63</v>
+        <v>3.32</v>
       </c>
       <c r="W493" s="5" t="n">
         <v>0</v>
@@ -53594,16 +53594,16 @@
         </is>
       </c>
       <c r="AA493" s="4" t="n">
-        <v>46.58</v>
+        <v>47.94</v>
       </c>
       <c r="AB493" s="4" t="n">
-        <v>20</v>
+        <v>30.5</v>
       </c>
       <c r="AC493" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AD493" s="4" t="n">
-        <v>51.24</v>
+        <v>49.88</v>
       </c>
       <c r="AE493" s="4" t="n">
         <v>2.18</v>
@@ -53647,13 +53647,13 @@
         </is>
       </c>
       <c r="I494" s="4" t="n">
-        <v>6.44</v>
+        <v>6.45</v>
       </c>
       <c r="J494" s="4" t="n">
-        <v>85.7</v>
+        <v>85.8</v>
       </c>
       <c r="K494" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="L494" t="inlineStr">
         <is>
@@ -53661,13 +53661,13 @@
         </is>
       </c>
       <c r="M494" s="4" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="N494" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O494" s="4" t="n">
-        <v>9.74</v>
+        <v>9.73</v>
       </c>
       <c r="P494" s="4" t="n">
         <v>0.58</v>
@@ -53713,10 +53713,10 @@
         <v>0</v>
       </c>
       <c r="AC494" s="4" t="n">
-        <v>52.95</v>
+        <v>52.96</v>
       </c>
       <c r="AD494" s="4" t="n">
-        <v>46.55</v>
+        <v>46.54</v>
       </c>
       <c r="AE494" s="4" t="n">
         <v>0</v>
@@ -53978,13 +53978,13 @@
         </is>
       </c>
       <c r="I497" s="4" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="J497" s="4" t="n">
-        <v>70.2</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="K497" s="4" t="n">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="L497" t="inlineStr">
         <is>
@@ -53998,10 +53998,10 @@
         <v>5.62</v>
       </c>
       <c r="O497" s="4" t="n">
-        <v>-1.71</v>
+        <v>-1.72</v>
       </c>
       <c r="P497" s="4" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="Q497" s="4" t="n">
         <v>1.39</v>
@@ -54044,10 +54044,10 @@
         <v>0</v>
       </c>
       <c r="AC497" s="4" t="n">
-        <v>50.01</v>
+        <v>50</v>
       </c>
       <c r="AD497" s="4" t="n">
-        <v>47.92</v>
+        <v>47.93</v>
       </c>
       <c r="AE497" s="4" t="n">
         <v>1.57</v>
@@ -54091,7 +54091,7 @@
         </is>
       </c>
       <c r="I498" s="4" t="n">
-        <v>-31.26</v>
+        <v>-31.32</v>
       </c>
       <c r="J498" s="4" t="n">
         <v>0</v>
@@ -54157,10 +54157,10 @@
         <v>0</v>
       </c>
       <c r="AC498" s="4" t="n">
-        <v>32.09</v>
+        <v>32.07</v>
       </c>
       <c r="AD498" s="4" t="n">
-        <v>61.29</v>
+        <v>61.31</v>
       </c>
       <c r="AE498" s="4" t="n">
         <v>2.62</v>
@@ -54319,7 +54319,7 @@
         </is>
       </c>
       <c r="I500" s="4" t="n">
-        <v>23.96</v>
+        <v>23.98</v>
       </c>
       <c r="J500" s="4" t="n">
         <v>99.90000000000001</v>
@@ -54385,10 +54385,10 @@
         <v>0</v>
       </c>
       <c r="AC500" s="4" t="n">
-        <v>60.03</v>
+        <v>60.04</v>
       </c>
       <c r="AD500" s="4" t="n">
-        <v>36.82</v>
+        <v>36.81</v>
       </c>
       <c r="AE500" s="4" t="n">
         <v>0</v>
@@ -54436,7 +54436,7 @@
         </is>
       </c>
       <c r="I501" s="4" t="n">
-        <v>-5.23</v>
+        <v>-5.24</v>
       </c>
       <c r="J501" s="4" t="n">
         <v>18.3</v>
@@ -54502,10 +54502,10 @@
         <v>0</v>
       </c>
       <c r="AC501" s="4" t="n">
-        <v>45.95</v>
+        <v>45.94</v>
       </c>
       <c r="AD501" s="4" t="n">
-        <v>51.02</v>
+        <v>51.03</v>
       </c>
       <c r="AE501" s="4" t="n">
         <v>1.87</v>
@@ -54553,7 +54553,7 @@
         </is>
       </c>
       <c r="I502" s="4" t="n">
-        <v>-15.99</v>
+        <v>-16.03</v>
       </c>
       <c r="J502" s="4" t="n">
         <v>0.5</v>
@@ -54613,7 +54613,7 @@
         </is>
       </c>
       <c r="AA502" s="4" t="n">
-        <v>42.01</v>
+        <v>41.98</v>
       </c>
       <c r="AB502" s="4" t="n">
         <v>0.5</v>
@@ -54622,7 +54622,7 @@
         <v>0</v>
       </c>
       <c r="AD502" s="4" t="n">
-        <v>57.99</v>
+        <v>58.02</v>
       </c>
       <c r="AE502" s="4" t="n">
         <v>0</v>
@@ -54670,7 +54670,7 @@
         </is>
       </c>
       <c r="I503" s="4" t="n">
-        <v>-26.89</v>
+        <v>-26.95</v>
       </c>
       <c r="J503" s="4" t="n">
         <v>0</v>
@@ -54690,7 +54690,7 @@
         <v>5.62</v>
       </c>
       <c r="O503" s="4" t="n">
-        <v>-30.01</v>
+        <v>-30.02</v>
       </c>
       <c r="P503" s="4" t="n">
         <v>-3.72</v>
@@ -54736,10 +54736,10 @@
         <v>0</v>
       </c>
       <c r="AC503" s="4" t="n">
-        <v>34.52</v>
+        <v>34.49</v>
       </c>
       <c r="AD503" s="4" t="n">
-        <v>59.9</v>
+        <v>59.93</v>
       </c>
       <c r="AE503" s="4" t="n">
         <v>0</v>
@@ -54783,13 +54783,13 @@
         </is>
       </c>
       <c r="I504" s="4" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="J504" s="4" t="n">
-        <v>67.7</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="K504" s="4" t="n">
-        <v>32.3</v>
+        <v>32.1</v>
       </c>
       <c r="L504" t="inlineStr">
         <is>
@@ -54797,16 +54797,16 @@
         </is>
       </c>
       <c r="M504" s="4" t="n">
-        <v>-10.01</v>
+        <v>-10.03</v>
       </c>
       <c r="N504" s="4" t="n">
         <v>5.62</v>
       </c>
       <c r="O504" s="4" t="n">
-        <v>-0.33</v>
+        <v>-0.42</v>
       </c>
       <c r="P504" s="4" t="n">
-        <v>0.97</v>
+        <v>0.9</v>
       </c>
       <c r="Q504" s="4" t="n">
         <v>2.05</v>
@@ -54815,16 +54815,16 @@
         <v>-13.88</v>
       </c>
       <c r="S504" s="4" t="n">
-        <v>46.86</v>
+        <v>47.05</v>
       </c>
       <c r="T504" s="4" t="n">
-        <v>44.28</v>
+        <v>44.32</v>
       </c>
       <c r="U504" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="V504" s="4" t="n">
-        <v>2.64</v>
+        <v>2.78</v>
       </c>
       <c r="W504" s="5" t="n">
         <v>68560930</v>
@@ -54843,16 +54843,16 @@
         </is>
       </c>
       <c r="AA504" s="4" t="n">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="AB504" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC504" s="4" t="n">
-        <v>50.4</v>
+        <v>50.46</v>
       </c>
       <c r="AD504" s="4" t="n">
-        <v>48.92</v>
+        <v>48.9</v>
       </c>
       <c r="AE504" s="4" t="n">
         <v>0</v>
@@ -56390,10 +56390,10 @@
         <v>73</v>
       </c>
       <c r="M20" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>34</v>
+        <v>33.9</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -56451,7 +56451,7 @@
         <v>33</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -57785,7 +57785,7 @@
         <v>49</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>79.7</v>
+        <v>79.8</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -58075,7 +58075,7 @@
         <v>78</v>
       </c>
       <c r="N49" s="4" t="n">
-        <v>32.6</v>
+        <v>32.7</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -58307,7 +58307,7 @@
         <v>22</v>
       </c>
       <c r="N53" s="4" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -59641,7 +59641,7 @@
         <v>94</v>
       </c>
       <c r="N76" s="4" t="n">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
@@ -59687,7 +59687,7 @@
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="K77" t="n">
         <v>12</v>

--- a/output/nowcast.xlsx
+++ b/output/nowcast.xlsx
@@ -541,16 +541,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>51.5</v>
+        <v>51.4</v>
       </c>
       <c r="C8" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="D8" t="n">
         <v>52</v>
       </c>
       <c r="E8" t="n">
-        <v>65.7</v>
+        <v>63.1</v>
       </c>
       <c r="F8" t="n">
         <v>51</v>
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>236.6</v>
+        <v>235.9</v>
       </c>
       <c r="C9" t="n">
-        <v>198.4</v>
+        <v>199.1</v>
       </c>
       <c r="D9" t="n">
         <v>233</v>
       </c>
       <c r="E9" t="n">
-        <v>85.90000000000001</v>
+        <v>85.3</v>
       </c>
       <c r="F9" t="n">
         <v>218</v>
@@ -591,16 +591,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>26.5</v>
+        <v>26.6</v>
       </c>
       <c r="C10" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="D10" t="n">
         <v>27</v>
       </c>
       <c r="E10" t="n">
-        <v>70.09999999999999</v>
+        <v>70.7</v>
       </c>
       <c r="F10" t="n">
         <v>26</v>
@@ -925,13 +925,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>24.49</v>
+        <v>16.8</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>99.90000000000001</v>
+        <v>99.7</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -957,16 +957,16 @@
         <v>-13.8</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>52.7</v>
+        <v>40.58</v>
       </c>
       <c r="T2" s="4" t="n">
-        <v>40.2</v>
+        <v>41.38</v>
       </c>
       <c r="U2" t="n">
         <v>2</v>
       </c>
       <c r="V2" s="4" t="n">
-        <v>13.07</v>
+        <v>-0.23</v>
       </c>
       <c r="W2" s="5" t="n">
         <v>0</v>
@@ -983,10 +983,10 @@
         <v>0</v>
       </c>
       <c r="AC2" s="4" t="n">
-        <v>52.61</v>
+        <v>48.39</v>
       </c>
       <c r="AD2" s="4" t="n">
-        <v>47.39</v>
+        <v>51.61</v>
       </c>
       <c r="AE2" s="4" t="n">
         <v>0</v>
@@ -4945,13 +4945,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>-3.32</v>
+        <v>-4.87</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>24.7</v>
+        <v>18.9</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>75.3</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -4959,13 +4959,13 @@
         </is>
       </c>
       <c r="M38" s="4" t="n">
-        <v>-0.42</v>
+        <v>-2.48</v>
       </c>
       <c r="N38" s="4" t="n">
         <v>5.95</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>1.77</v>
+        <v>-0.28</v>
       </c>
       <c r="P38" s="4" t="n">
         <v>-1.03</v>
@@ -4977,16 +4977,16 @@
         <v>-13.8</v>
       </c>
       <c r="S38" s="4" t="n">
-        <v>39.82</v>
+        <v>33.66</v>
       </c>
       <c r="T38" s="4" t="n">
-        <v>52.73</v>
+        <v>47.35</v>
       </c>
       <c r="U38" t="n">
         <v>6</v>
       </c>
       <c r="V38" s="4" t="n">
-        <v>-13.63</v>
+        <v>-14.42</v>
       </c>
       <c r="W38" s="5" t="n">
         <v>0</v>
@@ -5005,16 +5005,16 @@
         </is>
       </c>
       <c r="AA38" s="4" t="n">
-        <v>44.9</v>
+        <v>44.2</v>
       </c>
       <c r="AB38" s="4" t="n">
-        <v>24.7</v>
+        <v>18.9</v>
       </c>
       <c r="AC38" s="4" t="n">
         <v>3.8</v>
       </c>
       <c r="AD38" s="4" t="n">
-        <v>50.1</v>
+        <v>50.8</v>
       </c>
       <c r="AE38" s="4" t="n">
         <v>1.2</v>
@@ -16912,13 +16912,13 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>-4.47</v>
+        <v>-4.43</v>
       </c>
       <c r="J151" s="4" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>79</v>
+        <v>78.8</v>
       </c>
       <c r="L151" t="inlineStr">
         <is>
@@ -16944,16 +16944,16 @@
         <v>-14.7</v>
       </c>
       <c r="S151" s="4" t="n">
-        <v>44.92</v>
+        <v>45.53</v>
       </c>
       <c r="T151" s="4" t="n">
-        <v>45.04</v>
+        <v>46.16</v>
       </c>
       <c r="U151" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V151" s="4" t="n">
-        <v>-3</v>
+        <v>-3.57</v>
       </c>
       <c r="W151" s="5" t="n">
         <v>661173</v>
@@ -16970,10 +16970,10 @@
         <v>0</v>
       </c>
       <c r="AC151" s="4" t="n">
-        <v>47.76</v>
+        <v>47.79</v>
       </c>
       <c r="AD151" s="4" t="n">
-        <v>52.24</v>
+        <v>52.21</v>
       </c>
       <c r="AE151" s="4" t="n">
         <v>0</v>
@@ -25769,10 +25769,10 @@
         <v>-3.94</v>
       </c>
       <c r="J235" s="4" t="n">
-        <v>22.8</v>
+        <v>22.6</v>
       </c>
       <c r="K235" s="4" t="n">
-        <v>77.2</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -51314,13 +51314,13 @@
         </is>
       </c>
       <c r="I473" s="4" t="n">
-        <v>2.29</v>
+        <v>0.42</v>
       </c>
       <c r="J473" s="4" t="n">
-        <v>72.3</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="K473" s="4" t="n">
-        <v>27.7</v>
+        <v>35.1</v>
       </c>
       <c r="L473" t="inlineStr">
         <is>
@@ -51328,13 +51328,13 @@
         </is>
       </c>
       <c r="M473" s="4" t="n">
-        <v>-8.52</v>
+        <v>-10.62</v>
       </c>
       <c r="N473" s="4" t="n">
         <v>5.95</v>
       </c>
       <c r="O473" s="4" t="n">
-        <v>0.83</v>
+        <v>-1.28</v>
       </c>
       <c r="P473" s="4" t="n">
         <v>0.34</v>
@@ -51346,16 +51346,16 @@
         <v>-13.8</v>
       </c>
       <c r="S473" s="4" t="n">
-        <v>50.13</v>
+        <v>47.77</v>
       </c>
       <c r="T473" s="4" t="n">
-        <v>47.75</v>
+        <v>47.35</v>
       </c>
       <c r="U473" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V473" s="4" t="n">
-        <v>2.18</v>
+        <v>0.4</v>
       </c>
       <c r="W473" s="5" t="n">
         <v>18545132</v>
@@ -51372,10 +51372,10 @@
         <v>0</v>
       </c>
       <c r="AC473" s="4" t="n">
-        <v>49.47</v>
+        <v>48.54</v>
       </c>
       <c r="AD473" s="4" t="n">
-        <v>48.03</v>
+        <v>48.96</v>
       </c>
       <c r="AE473" s="4" t="n">
         <v>2.5</v>
@@ -52871,10 +52871,10 @@
         <v>1.76</v>
       </c>
       <c r="J487" s="4" t="n">
-        <v>68.5</v>
+        <v>68.8</v>
       </c>
       <c r="K487" s="4" t="n">
-        <v>31.5</v>
+        <v>31.2</v>
       </c>
       <c r="L487" t="inlineStr">
         <is>
@@ -53316,7 +53316,7 @@
         </is>
       </c>
       <c r="I491" s="4" t="n">
-        <v>-24.44</v>
+        <v>-24.47</v>
       </c>
       <c r="J491" s="4" t="n">
         <v>0</v>
@@ -53376,13 +53376,13 @@
         </is>
       </c>
       <c r="AA491" s="4" t="n">
-        <v>25.64</v>
+        <v>25.61</v>
       </c>
       <c r="AB491" s="4" t="n">
         <v>0.1</v>
       </c>
       <c r="AC491" s="4" t="n">
-        <v>20.62</v>
+        <v>20.64</v>
       </c>
       <c r="AD491" s="4" t="n">
         <v>50.08</v>
@@ -55339,7 +55339,7 @@
         </is>
       </c>
       <c r="J2" s="4" t="n">
-        <v>17.3</v>
+        <v>17.1</v>
       </c>
       <c r="K2" t="n">
         <v>17</v>
@@ -55351,7 +55351,7 @@
         <v>21</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -55414,7 +55414,7 @@
         <v>10</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>

--- a/output/nowcast.xlsx
+++ b/output/nowcast.xlsx
@@ -541,16 +541,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>51.4</v>
+        <v>51.3</v>
       </c>
       <c r="C8" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="D8" t="n">
         <v>52</v>
       </c>
       <c r="E8" t="n">
-        <v>63.1</v>
+        <v>62.2</v>
       </c>
       <c r="F8" t="n">
         <v>51</v>
@@ -566,10 +566,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>235.9</v>
+        <v>236.2</v>
       </c>
       <c r="C9" t="n">
-        <v>199.1</v>
+        <v>198.8</v>
       </c>
       <c r="D9" t="n">
         <v>233</v>
@@ -591,16 +591,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>26.6</v>
+        <v>26.5</v>
       </c>
       <c r="C10" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="D10" t="n">
         <v>27</v>
       </c>
       <c r="E10" t="n">
-        <v>70.7</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="F10" t="n">
         <v>26</v>
@@ -4948,10 +4948,10 @@
         <v>-4.87</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>18.9</v>
+        <v>19.3</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>81.09999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>44.2</v>
       </c>
       <c r="AB38" s="4" t="n">
-        <v>18.9</v>
+        <v>19.3</v>
       </c>
       <c r="AC38" s="4" t="n">
         <v>3.8</v>
@@ -25769,10 +25769,10 @@
         <v>-3.94</v>
       </c>
       <c r="J235" s="4" t="n">
-        <v>22.6</v>
+        <v>23.2</v>
       </c>
       <c r="K235" s="4" t="n">
-        <v>77.40000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -51317,10 +51317,10 @@
         <v>0.42</v>
       </c>
       <c r="J473" s="4" t="n">
-        <v>64.90000000000001</v>
+        <v>63.9</v>
       </c>
       <c r="K473" s="4" t="n">
-        <v>35.1</v>
+        <v>36.1</v>
       </c>
       <c r="L473" t="inlineStr">
         <is>
@@ -52871,10 +52871,10 @@
         <v>1.76</v>
       </c>
       <c r="J487" s="4" t="n">
-        <v>68.8</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="K487" s="4" t="n">
-        <v>31.2</v>
+        <v>30.6</v>
       </c>
       <c r="L487" t="inlineStr">
         <is>
@@ -53316,7 +53316,7 @@
         </is>
       </c>
       <c r="I491" s="4" t="n">
-        <v>-24.47</v>
+        <v>-24.44</v>
       </c>
       <c r="J491" s="4" t="n">
         <v>0</v>
@@ -53382,10 +53382,10 @@
         <v>0.1</v>
       </c>
       <c r="AC491" s="4" t="n">
-        <v>20.64</v>
+        <v>20.68</v>
       </c>
       <c r="AD491" s="4" t="n">
-        <v>50.08</v>
+        <v>50.05</v>
       </c>
       <c r="AE491" s="4" t="n">
         <v>3.66</v>

--- a/output/nowcast.xlsx
+++ b/output/nowcast.xlsx
@@ -541,16 +541,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>51.9</v>
+        <v>51.6</v>
       </c>
       <c r="C8" t="n">
-        <v>48.1</v>
+        <v>48.4</v>
       </c>
       <c r="D8" t="n">
         <v>53</v>
       </c>
       <c r="E8" t="n">
-        <v>67.5</v>
+        <v>61.1</v>
       </c>
       <c r="F8" t="n">
         <v>51</v>
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>237.9</v>
+        <v>237.8</v>
       </c>
       <c r="C9" t="n">
-        <v>197.1</v>
+        <v>197.2</v>
       </c>
       <c r="D9" t="n">
         <v>235</v>
       </c>
       <c r="E9" t="n">
-        <v>87.5</v>
+        <v>86.8</v>
       </c>
       <c r="F9" t="n">
         <v>218</v>
@@ -600,7 +600,7 @@
         <v>27</v>
       </c>
       <c r="E10" t="n">
-        <v>72.40000000000001</v>
+        <v>70.7</v>
       </c>
       <c r="F10" t="n">
         <v>26</v>
@@ -1812,14 +1812,14 @@
         <v>3.42</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>75.09999999999999</v>
+        <v>73.8</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>24.9</v>
+        <v>26.2</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Likely D</t>
+          <t>Lean D</t>
         </is>
       </c>
       <c r="M10" s="4" t="n">
@@ -3380,10 +3380,10 @@
         <v>3.79</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>76.5</v>
+        <v>76.3</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>23.5</v>
+        <v>23.7</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -3602,10 +3602,10 @@
         <v>-1.77</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>31.3</v>
+        <v>37.5</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>68.7</v>
+        <v>62.5</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -3826,10 +3826,10 @@
         <v>3.33</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>74.7</v>
+        <v>73.2</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>25.3</v>
+        <v>26.8</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -4732,14 +4732,14 @@
         <v>3.47</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>75.3</v>
+        <v>74.2</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>24.7</v>
+        <v>25.8</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Likely D</t>
+          <t>Lean D</t>
         </is>
       </c>
       <c r="M36" s="4" t="n">
@@ -4948,10 +4948,10 @@
         <v>-4.33</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>21.1</v>
+        <v>20.7</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>78.90000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>44.47</v>
       </c>
       <c r="AB38" s="4" t="n">
-        <v>21.1</v>
+        <v>20.7</v>
       </c>
       <c r="AC38" s="4" t="n">
         <v>3.8</v>
@@ -5164,10 +5164,10 @@
         <v>-1.43</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>32.6</v>
+        <v>39.9</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>67.40000000000001</v>
+        <v>60.1</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -5899,10 +5899,10 @@
         <v>-3.74</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>23.7</v>
+        <v>24.1</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>76.3</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -6335,10 +6335,10 @@
         <v>0.7</v>
       </c>
       <c r="J51" s="4" t="n">
-        <v>64.5</v>
+        <v>55</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>35.5</v>
+        <v>45</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -12765,10 +12765,10 @@
         <v>-0.35</v>
       </c>
       <c r="J113" s="4" t="n">
-        <v>36.9</v>
+        <v>47.5</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>63.1</v>
+        <v>52.5</v>
       </c>
       <c r="L113" t="inlineStr">
         <is>
@@ -12882,14 +12882,14 @@
         <v>-3.54</v>
       </c>
       <c r="J114" s="4" t="n">
-        <v>24.5</v>
+        <v>25.4</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>75.5</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>Likely R</t>
+          <t>Lean R</t>
         </is>
       </c>
       <c r="M114" s="4" t="n">
@@ -14723,10 +14723,10 @@
         <v>0.47</v>
       </c>
       <c r="J131" s="4" t="n">
-        <v>63.6</v>
+        <v>53.3</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>36.4</v>
+        <v>46.7</v>
       </c>
       <c r="L131" t="inlineStr">
         <is>
@@ -14943,10 +14943,10 @@
         <v>0.36</v>
       </c>
       <c r="J133" s="4" t="n">
-        <v>63.2</v>
+        <v>52.6</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>36.8</v>
+        <v>47.4</v>
       </c>
       <c r="L133" t="inlineStr">
         <is>
@@ -15712,10 +15712,10 @@
         <v>-2.59</v>
       </c>
       <c r="J140" s="4" t="n">
-        <v>28.1</v>
+        <v>31.8</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>71.90000000000001</v>
+        <v>68.2</v>
       </c>
       <c r="L140" t="inlineStr">
         <is>
@@ -16376,10 +16376,10 @@
         <v>1.35</v>
       </c>
       <c r="J146" s="4" t="n">
-        <v>67.09999999999999</v>
+        <v>59.6</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>32.9</v>
+        <v>40.4</v>
       </c>
       <c r="L146" t="inlineStr">
         <is>
@@ -18900,14 +18900,14 @@
         <v>3.5</v>
       </c>
       <c r="J170" s="4" t="n">
-        <v>75.40000000000001</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="K170" s="4" t="n">
-        <v>24.6</v>
+        <v>25.6</v>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>Likely D</t>
+          <t>Lean D</t>
         </is>
       </c>
       <c r="M170" s="4" t="n">
@@ -25769,10 +25769,10 @@
         <v>-3.71</v>
       </c>
       <c r="J235" s="4" t="n">
-        <v>23.7</v>
+        <v>23.2</v>
       </c>
       <c r="K235" s="4" t="n">
-        <v>76.3</v>
+        <v>76.8</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -26211,10 +26211,10 @@
         <v>-1.36</v>
       </c>
       <c r="J239" s="4" t="n">
-        <v>32.9</v>
+        <v>40.4</v>
       </c>
       <c r="K239" s="4" t="n">
-        <v>67.09999999999999</v>
+        <v>59.6</v>
       </c>
       <c r="L239" t="inlineStr">
         <is>
@@ -26550,10 +26550,10 @@
         <v>1.83</v>
       </c>
       <c r="J242" s="4" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="K242" s="4" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="L242" t="inlineStr">
         <is>
@@ -26885,10 +26885,10 @@
         <v>1.98</v>
       </c>
       <c r="J245" s="4" t="n">
-        <v>69.59999999999999</v>
+        <v>64</v>
       </c>
       <c r="K245" s="4" t="n">
-        <v>30.4</v>
+        <v>36</v>
       </c>
       <c r="L245" t="inlineStr">
         <is>
@@ -29491,10 +29491,10 @@
         <v>-3.15</v>
       </c>
       <c r="J269" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K269" s="4" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L269" t="inlineStr">
         <is>
@@ -30845,10 +30845,10 @@
         <v>-2.26</v>
       </c>
       <c r="J281" s="4" t="n">
-        <v>29.3</v>
+        <v>34.1</v>
       </c>
       <c r="K281" s="4" t="n">
-        <v>70.7</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="L281" t="inlineStr">
         <is>
@@ -33683,10 +33683,10 @@
         <v>-1.57</v>
       </c>
       <c r="J307" s="4" t="n">
-        <v>32</v>
+        <v>38.9</v>
       </c>
       <c r="K307" s="4" t="n">
-        <v>68</v>
+        <v>61.1</v>
       </c>
       <c r="L307" t="inlineStr">
         <is>
@@ -34022,10 +34022,10 @@
         <v>-3.1</v>
       </c>
       <c r="J310" s="4" t="n">
-        <v>26.1</v>
+        <v>28.3</v>
       </c>
       <c r="K310" s="4" t="n">
-        <v>73.90000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="L310" t="inlineStr">
         <is>
@@ -35698,10 +35698,10 @@
         <v>3.8</v>
       </c>
       <c r="J326" s="4" t="n">
-        <v>76.5</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="K326" s="4" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="L326" t="inlineStr">
         <is>
@@ -37390,10 +37390,10 @@
         <v>1.01</v>
       </c>
       <c r="J342" s="4" t="n">
-        <v>65.7</v>
+        <v>57.2</v>
       </c>
       <c r="K342" s="4" t="n">
-        <v>34.3</v>
+        <v>42.8</v>
       </c>
       <c r="L342" t="inlineStr">
         <is>
@@ -38248,10 +38248,10 @@
         <v>-3.07</v>
       </c>
       <c r="J350" s="4" t="n">
-        <v>26.2</v>
+        <v>28.5</v>
       </c>
       <c r="K350" s="4" t="n">
-        <v>73.8</v>
+        <v>71.5</v>
       </c>
       <c r="L350" t="inlineStr">
         <is>
@@ -39534,10 +39534,10 @@
         <v>-2.13</v>
       </c>
       <c r="J362" s="4" t="n">
-        <v>29.9</v>
+        <v>35</v>
       </c>
       <c r="K362" s="4" t="n">
-        <v>70.09999999999999</v>
+        <v>65</v>
       </c>
       <c r="L362" t="inlineStr">
         <is>
@@ -40271,10 +40271,10 @@
         <v>1.59</v>
       </c>
       <c r="J369" s="4" t="n">
-        <v>68</v>
+        <v>61.2</v>
       </c>
       <c r="K369" s="4" t="n">
-        <v>32</v>
+        <v>38.8</v>
       </c>
       <c r="L369" t="inlineStr">
         <is>
@@ -41523,10 +41523,10 @@
         <v>-2.59</v>
       </c>
       <c r="J381" s="4" t="n">
-        <v>28.1</v>
+        <v>31.8</v>
       </c>
       <c r="K381" s="4" t="n">
-        <v>71.90000000000001</v>
+        <v>68.2</v>
       </c>
       <c r="L381" t="inlineStr">
         <is>
@@ -44816,10 +44816,10 @@
         <v>1.7</v>
       </c>
       <c r="J412" s="4" t="n">
-        <v>68.40000000000001</v>
+        <v>62</v>
       </c>
       <c r="K412" s="4" t="n">
-        <v>31.6</v>
+        <v>38</v>
       </c>
       <c r="L412" t="inlineStr">
         <is>
@@ -45630,10 +45630,10 @@
         <v>-1.23</v>
       </c>
       <c r="J420" s="4" t="n">
-        <v>33.4</v>
+        <v>41.3</v>
       </c>
       <c r="K420" s="4" t="n">
-        <v>66.59999999999999</v>
+        <v>58.7</v>
       </c>
       <c r="L420" t="inlineStr">
         <is>
@@ -46908,10 +46908,10 @@
         <v>1.13</v>
       </c>
       <c r="J432" s="4" t="n">
-        <v>66.2</v>
+        <v>58</v>
       </c>
       <c r="K432" s="4" t="n">
-        <v>33.8</v>
+        <v>42</v>
       </c>
       <c r="L432" t="inlineStr">
         <is>
@@ -47770,10 +47770,10 @@
         <v>-2.36</v>
       </c>
       <c r="J440" s="4" t="n">
-        <v>29</v>
+        <v>33.4</v>
       </c>
       <c r="K440" s="4" t="n">
-        <v>71</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="L440" t="inlineStr">
         <is>
@@ -50140,14 +50140,14 @@
         <v>-3.42</v>
       </c>
       <c r="J462" s="4" t="n">
-        <v>24.9</v>
+        <v>26.2</v>
       </c>
       <c r="K462" s="4" t="n">
-        <v>75.09999999999999</v>
+        <v>73.8</v>
       </c>
       <c r="L462" t="inlineStr">
         <is>
-          <t>Likely R</t>
+          <t>Lean R</t>
         </is>
       </c>
       <c r="M462" s="4" t="n">
@@ -51323,10 +51323,10 @@
         <v>0.72</v>
       </c>
       <c r="J473" s="4" t="n">
-        <v>65.3</v>
+        <v>55.6</v>
       </c>
       <c r="K473" s="4" t="n">
-        <v>34.7</v>
+        <v>44.4</v>
       </c>
       <c r="L473" t="inlineStr">
         <is>
@@ -52090,10 +52090,10 @@
         <v>0.04</v>
       </c>
       <c r="J480" s="4" t="n">
-        <v>61.9</v>
+        <v>50.3</v>
       </c>
       <c r="K480" s="4" t="n">
-        <v>38.1</v>
+        <v>49.7</v>
       </c>
       <c r="L480" t="inlineStr">
         <is>
@@ -52431,14 +52431,14 @@
         <v>-3.41</v>
       </c>
       <c r="J483" s="4" t="n">
-        <v>25</v>
+        <v>26.3</v>
       </c>
       <c r="K483" s="4" t="n">
-        <v>75</v>
+        <v>73.7</v>
       </c>
       <c r="L483" t="inlineStr">
         <is>
-          <t>Likely R</t>
+          <t>Lean R</t>
         </is>
       </c>
       <c r="M483" s="4" t="n">
@@ -52877,10 +52877,10 @@
         <v>2.1</v>
       </c>
       <c r="J487" s="4" t="n">
-        <v>69.90000000000001</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="K487" s="4" t="n">
-        <v>30.1</v>
+        <v>35.4</v>
       </c>
       <c r="L487" t="inlineStr">
         <is>
@@ -53322,7 +53322,7 @@
         </is>
       </c>
       <c r="I491" s="4" t="n">
-        <v>-23.94</v>
+        <v>-24.02</v>
       </c>
       <c r="J491" s="4" t="n">
         <v>0</v>
@@ -53382,16 +53382,16 @@
         </is>
       </c>
       <c r="AA491" s="4" t="n">
-        <v>25.73</v>
+        <v>25.69</v>
       </c>
       <c r="AB491" s="4" t="n">
         <v>0.1</v>
       </c>
       <c r="AC491" s="4" t="n">
-        <v>20.95</v>
+        <v>20.94</v>
       </c>
       <c r="AD491" s="4" t="n">
-        <v>49.67</v>
+        <v>49.71</v>
       </c>
       <c r="AE491" s="4" t="n">
         <v>3.66</v>
@@ -53555,10 +53555,10 @@
         <v>-1.74</v>
       </c>
       <c r="J493" s="4" t="n">
-        <v>31.2</v>
+        <v>37.5</v>
       </c>
       <c r="K493" s="4" t="n">
-        <v>68.8</v>
+        <v>62.5</v>
       </c>
       <c r="L493" t="inlineStr">
         <is>
@@ -53615,7 +53615,7 @@
         <v>48.04</v>
       </c>
       <c r="AB493" s="4" t="n">
-        <v>31.2</v>
+        <v>37.5</v>
       </c>
       <c r="AC493" s="4" t="n">
         <v>0</v>
@@ -53999,10 +53999,10 @@
         <v>2.45</v>
       </c>
       <c r="J497" s="4" t="n">
-        <v>71.40000000000001</v>
+        <v>67.3</v>
       </c>
       <c r="K497" s="4" t="n">
-        <v>28.6</v>
+        <v>32.7</v>
       </c>
       <c r="L497" t="inlineStr">
         <is>
@@ -54804,10 +54804,10 @@
         <v>1.96</v>
       </c>
       <c r="J504" s="4" t="n">
-        <v>69.5</v>
+        <v>63.8</v>
       </c>
       <c r="K504" s="4" t="n">
-        <v>30.5</v>
+        <v>36.2</v>
       </c>
       <c r="L504" t="inlineStr">
         <is>

--- a/output/nowcast.xlsx
+++ b/output/nowcast.xlsx
@@ -550,7 +550,7 @@
         <v>53</v>
       </c>
       <c r="E8" t="n">
-        <v>66.09999999999999</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="F8" t="n">
         <v>51</v>
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>240.2</v>
+        <v>239.8</v>
       </c>
       <c r="C9" t="n">
-        <v>194.8</v>
+        <v>195.2</v>
       </c>
       <c r="D9" t="n">
         <v>236</v>
       </c>
       <c r="E9" t="n">
-        <v>88</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="F9" t="n">
         <v>218</v>
@@ -600,7 +600,7 @@
         <v>27</v>
       </c>
       <c r="E10" t="n">
-        <v>69.5</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="F10" t="n">
         <v>26</v>
@@ -1819,7 +1819,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Tilt D</t>
+          <t>Toss-up</t>
         </is>
       </c>
       <c r="M10" s="4" t="n">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Tilt R</t>
+          <t>Toss-up</t>
         </is>
       </c>
       <c r="M26" s="4" t="n">
@@ -4948,10 +4948,10 @@
         <v>-3.73</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>77.09999999999999</v>
+        <v>77</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>44.76</v>
       </c>
       <c r="AB38" s="4" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="AC38" s="4" t="n">
         <v>3.8</v>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Tilt R</t>
+          <t>Toss-up</t>
         </is>
       </c>
       <c r="M40" s="4" t="n">
@@ -6342,7 +6342,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Tilt D</t>
+          <t>Toss-up</t>
         </is>
       </c>
       <c r="M51" s="4" t="n">
@@ -12772,7 +12772,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>Tilt D</t>
+          <t>Toss-up</t>
         </is>
       </c>
       <c r="M113" s="4" t="n">
@@ -14736,7 +14736,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>Tilt D</t>
+          <t>Toss-up</t>
         </is>
       </c>
       <c r="M131" s="4" t="n">
@@ -14956,7 +14956,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>Tilt D</t>
+          <t>Toss-up</t>
         </is>
       </c>
       <c r="M133" s="4" t="n">
@@ -25775,10 +25775,10 @@
         <v>-3.17</v>
       </c>
       <c r="J235" s="4" t="n">
-        <v>28.9</v>
+        <v>28.4</v>
       </c>
       <c r="K235" s="4" t="n">
-        <v>71.09999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -26224,7 +26224,7 @@
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>Tilt R</t>
+          <t>Toss-up</t>
         </is>
       </c>
       <c r="M239" s="4" t="n">
@@ -33696,7 +33696,7 @@
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t>Tilt R</t>
+          <t>Toss-up</t>
         </is>
       </c>
       <c r="M307" s="4" t="n">
@@ -45643,7 +45643,7 @@
       </c>
       <c r="L420" t="inlineStr">
         <is>
-          <t>Tilt R</t>
+          <t>Toss-up</t>
         </is>
       </c>
       <c r="M420" s="4" t="n">
@@ -51329,14 +51329,14 @@
         <v>1.17</v>
       </c>
       <c r="J473" s="4" t="n">
-        <v>58.7</v>
+        <v>58.3</v>
       </c>
       <c r="K473" s="4" t="n">
-        <v>41.3</v>
+        <v>41.7</v>
       </c>
       <c r="L473" t="inlineStr">
         <is>
-          <t>Tilt D</t>
+          <t>Toss-up</t>
         </is>
       </c>
       <c r="M473" s="4" t="n">
@@ -52103,7 +52103,7 @@
       </c>
       <c r="L480" t="inlineStr">
         <is>
-          <t>Tilt D</t>
+          <t>Toss-up</t>
         </is>
       </c>
       <c r="M480" s="4" t="n">
@@ -52883,10 +52883,10 @@
         <v>2.54</v>
       </c>
       <c r="J487" s="4" t="n">
-        <v>67.7</v>
+        <v>67.2</v>
       </c>
       <c r="K487" s="4" t="n">
-        <v>32.3</v>
+        <v>32.8</v>
       </c>
       <c r="L487" t="inlineStr">
         <is>
@@ -53328,7 +53328,7 @@
         </is>
       </c>
       <c r="I491" s="4" t="n">
-        <v>-23.73</v>
+        <v>-23.62</v>
       </c>
       <c r="J491" s="4" t="n">
         <v>0</v>
@@ -53388,13 +53388,13 @@
         </is>
       </c>
       <c r="AA491" s="4" t="n">
-        <v>25.75</v>
+        <v>25.86</v>
       </c>
       <c r="AB491" s="4" t="n">
         <v>0.1</v>
       </c>
       <c r="AC491" s="4" t="n">
-        <v>21.11</v>
+        <v>21</v>
       </c>
       <c r="AD491" s="4" t="n">
         <v>49.48</v>
@@ -53568,7 +53568,7 @@
       </c>
       <c r="L493" t="inlineStr">
         <is>
-          <t>Tilt R</t>
+          <t>Toss-up</t>
         </is>
       </c>
       <c r="M493" s="4" t="n">

--- a/output/nowcast.xlsx
+++ b/output/nowcast.xlsx
@@ -479,7 +479,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Generic ballot D+6.7 · House popular vote D+9.3</t>
+          <t>Generic ballot D+6.7 · House popular vote D+9.4</t>
         </is>
       </c>
     </row>
@@ -541,16 +541,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>52.1</v>
+        <v>52.3</v>
       </c>
       <c r="C8" t="n">
-        <v>47.9</v>
+        <v>47.7</v>
       </c>
       <c r="D8" t="n">
         <v>53</v>
       </c>
       <c r="E8" t="n">
-        <v>68</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="F8" t="n">
         <v>51</v>
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>241.1</v>
+        <v>241.5</v>
       </c>
       <c r="C9" t="n">
-        <v>193.9</v>
+        <v>193.5</v>
       </c>
       <c r="D9" t="n">
         <v>236</v>
       </c>
       <c r="E9" t="n">
-        <v>88.40000000000001</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="F9" t="n">
         <v>218</v>
@@ -600,7 +600,7 @@
         <v>28</v>
       </c>
       <c r="E10" t="n">
-        <v>71.8</v>
+        <v>71.3</v>
       </c>
       <c r="F10" t="n">
         <v>26</v>
@@ -2126,7 +2126,7 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-38.51</v>
+        <v>-31.05</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>0</v>
@@ -2158,16 +2158,16 @@
         <v>-37.52</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>29</v>
+        <v>27.82</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>50.5</v>
+        <v>41.81</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-22.85</v>
+        <v>-14.14</v>
       </c>
       <c r="W13" s="5" t="n">
         <v>136953</v>
@@ -2186,16 +2186,16 @@
         </is>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>5</v>
+        <v>10.13</v>
       </c>
       <c r="AB13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC13" s="4" t="n">
-        <v>29.21</v>
+        <v>30.98</v>
       </c>
       <c r="AD13" s="4" t="n">
-        <v>65.79000000000001</v>
+        <v>58.89</v>
       </c>
       <c r="AE13" s="4" t="n">
         <v>0</v>
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>23.07</v>
+        <v>22.4</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>99.90000000000001</v>
@@ -4085,16 +4085,16 @@
         <v>14.16</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>42.35</v>
+        <v>41.75</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>16.26</v>
+        <v>17.47</v>
       </c>
       <c r="U30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>26.83</v>
+        <v>24.76</v>
       </c>
       <c r="W30" s="5" t="n">
         <v>0</v>
@@ -4113,16 +4113,16 @@
         </is>
       </c>
       <c r="AA30" s="4" t="n">
-        <v>22.7</v>
+        <v>23.27</v>
       </c>
       <c r="AB30" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC30" s="4" t="n">
-        <v>47.57</v>
+        <v>46.96</v>
       </c>
       <c r="AD30" s="4" t="n">
-        <v>29.73</v>
+        <v>29.77</v>
       </c>
       <c r="AE30" s="4" t="n">
         <v>0</v>
@@ -4948,10 +4948,10 @@
         <v>-3.17</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>26.5</v>
+        <v>27.7</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>73.5</v>
+        <v>72.3</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>45.04</v>
       </c>
       <c r="AB38" s="4" t="n">
-        <v>26.5</v>
+        <v>27.7</v>
       </c>
       <c r="AC38" s="4" t="n">
         <v>3.8</v>
@@ -19228,7 +19228,7 @@
         </is>
       </c>
       <c r="I173" s="4" t="n">
-        <v>-32.53</v>
+        <v>-31.17</v>
       </c>
       <c r="J173" s="4" t="n">
         <v>0</v>
@@ -19242,13 +19242,13 @@
         </is>
       </c>
       <c r="M173" s="4" t="n">
-        <v>-44.88</v>
+        <v>-43.02</v>
       </c>
       <c r="N173" s="4" t="n">
         <v>6.68</v>
       </c>
       <c r="O173" s="4" t="n">
-        <v>-40.9</v>
+        <v>-39.03</v>
       </c>
       <c r="P173" s="4" t="n">
         <v>-0.84</v>
@@ -19294,10 +19294,10 @@
         <v>0</v>
       </c>
       <c r="AC173" s="4" t="n">
-        <v>30.43</v>
+        <v>31.05</v>
       </c>
       <c r="AD173" s="4" t="n">
-        <v>59.78</v>
+        <v>59.16</v>
       </c>
       <c r="AE173" s="4" t="n">
         <v>3.81</v>
@@ -19345,13 +19345,13 @@
         </is>
       </c>
       <c r="I174" s="4" t="n">
-        <v>-26.78</v>
+        <v>-24.92</v>
       </c>
       <c r="J174" s="4" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K174" s="4" t="n">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="L174" t="inlineStr">
         <is>
@@ -19359,13 +19359,13 @@
         </is>
       </c>
       <c r="M174" s="4" t="n">
-        <v>-27.07</v>
+        <v>-25.2</v>
       </c>
       <c r="N174" s="4" t="n">
         <v>6.68</v>
       </c>
       <c r="O174" s="4" t="n">
-        <v>-27.53</v>
+        <v>-25.67</v>
       </c>
       <c r="P174" s="4" t="n">
         <v>-1.51</v>
@@ -19405,10 +19405,10 @@
         <v>0</v>
       </c>
       <c r="AC174" s="4" t="n">
-        <v>32.95</v>
+        <v>33.79</v>
       </c>
       <c r="AD174" s="4" t="n">
-        <v>57.05</v>
+        <v>56.21</v>
       </c>
       <c r="AE174" s="4" t="n">
         <v>5</v>
@@ -25781,10 +25781,10 @@
         <v>-0.47</v>
       </c>
       <c r="J235" s="4" t="n">
-        <v>46.5</v>
+        <v>45.2</v>
       </c>
       <c r="K235" s="4" t="n">
-        <v>53.5</v>
+        <v>54.8</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -41346,7 +41346,7 @@
         </is>
       </c>
       <c r="I379" s="4" t="n">
-        <v>45.37</v>
+        <v>45.22</v>
       </c>
       <c r="J379" s="4" t="n">
         <v>100</v>
@@ -41360,13 +41360,13 @@
         </is>
       </c>
       <c r="M379" s="4" t="n">
-        <v>28.19</v>
+        <v>28.03</v>
       </c>
       <c r="N379" s="4" t="n">
         <v>6.68</v>
       </c>
       <c r="O379" s="4" t="n">
-        <v>45.53</v>
+        <v>45.37</v>
       </c>
       <c r="P379" s="4" t="n">
         <v>2.51</v>
@@ -41406,10 +41406,10 @@
         <v>0</v>
       </c>
       <c r="AC379" s="4" t="n">
-        <v>70.44</v>
+        <v>70.36</v>
       </c>
       <c r="AD379" s="4" t="n">
-        <v>26.47</v>
+        <v>26.55</v>
       </c>
       <c r="AE379" s="4" t="n">
         <v>0</v>
@@ -41457,7 +41457,7 @@
         </is>
       </c>
       <c r="I380" s="4" t="n">
-        <v>19.77</v>
+        <v>19.62</v>
       </c>
       <c r="J380" s="4" t="n">
         <v>99.8</v>
@@ -41471,13 +41471,13 @@
         </is>
       </c>
       <c r="M380" s="4" t="n">
-        <v>12.33</v>
+        <v>12.17</v>
       </c>
       <c r="N380" s="4" t="n">
         <v>6.68</v>
       </c>
       <c r="O380" s="4" t="n">
-        <v>19.77</v>
+        <v>19.62</v>
       </c>
       <c r="P380" s="4" t="n">
         <v>-0.57</v>
@@ -41509,10 +41509,10 @@
         <v>0</v>
       </c>
       <c r="AC380" s="4" t="n">
-        <v>59.89</v>
+        <v>59.81</v>
       </c>
       <c r="AD380" s="4" t="n">
-        <v>40.11</v>
+        <v>40.19</v>
       </c>
       <c r="AE380" s="4" t="n">
         <v>0</v>
@@ -47470,13 +47470,13 @@
         </is>
       </c>
       <c r="I437" s="4" t="n">
-        <v>-33.63</v>
+        <v>-15.58</v>
       </c>
       <c r="J437" s="4" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="K437" s="4" t="n">
-        <v>100</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="L437" t="inlineStr">
         <is>
@@ -47501,12 +47501,18 @@
       <c r="R437" s="4" t="n">
         <v>-29.9</v>
       </c>
-      <c r="S437" s="4" t="n"/>
-      <c r="T437" s="4" t="n"/>
+      <c r="S437" s="4" t="n">
+        <v>33.04</v>
+      </c>
+      <c r="T437" s="4" t="n">
+        <v>32.18</v>
+      </c>
       <c r="U437" t="n">
-        <v>0</v>
-      </c>
-      <c r="V437" s="4" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="V437" s="4" t="n">
+        <v>-1.64</v>
+      </c>
       <c r="W437" s="5" t="n">
         <v>60225</v>
       </c>
@@ -47530,10 +47536,10 @@
         <v>0</v>
       </c>
       <c r="AC437" s="4" t="n">
-        <v>28.87</v>
+        <v>36.72</v>
       </c>
       <c r="AD437" s="4" t="n">
-        <v>58.13</v>
+        <v>50.28</v>
       </c>
       <c r="AE437" s="4" t="n">
         <v>7</v>
@@ -51359,10 +51365,10 @@
         <v>1.41</v>
       </c>
       <c r="J473" s="4" t="n">
-        <v>61.3</v>
+        <v>61</v>
       </c>
       <c r="K473" s="4" t="n">
-        <v>38.7</v>
+        <v>39</v>
       </c>
       <c r="L473" t="inlineStr">
         <is>
@@ -52240,13 +52246,13 @@
         </is>
       </c>
       <c r="I481" s="4" t="n">
-        <v>-19.31</v>
+        <v>-10.34</v>
       </c>
       <c r="J481" s="4" t="n">
-        <v>0.2</v>
+        <v>2.3</v>
       </c>
       <c r="K481" s="4" t="n">
-        <v>99.8</v>
+        <v>97.7</v>
       </c>
       <c r="L481" t="inlineStr">
         <is>
@@ -52254,13 +52260,13 @@
         </is>
       </c>
       <c r="M481" s="4" t="n">
-        <v>-30.52</v>
+        <v>-28.65</v>
       </c>
       <c r="N481" s="4" t="n">
         <v>6.68</v>
       </c>
       <c r="O481" s="4" t="n">
-        <v>-27.14</v>
+        <v>-25.27</v>
       </c>
       <c r="P481" s="4" t="n">
         <v>-1.14</v>
@@ -52272,16 +52278,16 @@
         <v>-37.52</v>
       </c>
       <c r="S481" s="4" t="n">
-        <v>29.96</v>
+        <v>44.02</v>
       </c>
       <c r="T481" s="4" t="n">
-        <v>39.02</v>
+        <v>38.97</v>
       </c>
       <c r="U481" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V481" s="4" t="n">
-        <v>-8.93</v>
+        <v>5.47</v>
       </c>
       <c r="W481" s="5" t="n">
         <v>0</v>
@@ -52300,16 +52306,16 @@
         </is>
       </c>
       <c r="AA481" s="4" t="n">
-        <v>38.15</v>
+        <v>42.63</v>
       </c>
       <c r="AB481" s="4" t="n">
-        <v>0.2</v>
+        <v>2.3</v>
       </c>
       <c r="AC481" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AD481" s="4" t="n">
-        <v>57.46</v>
+        <v>52.98</v>
       </c>
       <c r="AE481" s="4" t="n">
         <v>4.39</v>
@@ -52919,10 +52925,10 @@
         <v>1.98</v>
       </c>
       <c r="J487" s="4" t="n">
-        <v>64.7</v>
+        <v>63.1</v>
       </c>
       <c r="K487" s="4" t="n">
-        <v>35.3</v>
+        <v>36.9</v>
       </c>
       <c r="L487" t="inlineStr">
         <is>
@@ -53364,7 +53370,7 @@
         </is>
       </c>
       <c r="I491" s="4" t="n">
-        <v>-21.59</v>
+        <v>-21.54</v>
       </c>
       <c r="J491" s="4" t="n">
         <v>0</v>
@@ -53424,16 +53430,16 @@
         </is>
       </c>
       <c r="AA491" s="4" t="n">
-        <v>27.74</v>
+        <v>27.75</v>
       </c>
       <c r="AB491" s="4" t="n">
         <v>0.2</v>
       </c>
       <c r="AC491" s="4" t="n">
-        <v>19.27</v>
+        <v>19.3</v>
       </c>
       <c r="AD491" s="4" t="n">
-        <v>49.33</v>
+        <v>49.29</v>
       </c>
       <c r="AE491" s="4" t="n">
         <v>3.66</v>
@@ -54379,7 +54385,7 @@
         </is>
       </c>
       <c r="I500" s="4" t="n">
-        <v>24.72</v>
+        <v>24.62</v>
       </c>
       <c r="J500" s="4" t="n">
         <v>99.90000000000001</v>
@@ -54393,13 +54399,13 @@
         </is>
       </c>
       <c r="M500" s="4" t="n">
-        <v>17.98</v>
+        <v>17.81</v>
       </c>
       <c r="N500" s="4" t="n">
         <v>6.68</v>
       </c>
       <c r="O500" s="4" t="n">
-        <v>28.15</v>
+        <v>27.98</v>
       </c>
       <c r="P500" s="4" t="n">
         <v>2.03</v>
@@ -54445,10 +54451,10 @@
         <v>0</v>
       </c>
       <c r="AC500" s="4" t="n">
-        <v>59.73</v>
+        <v>59.68</v>
       </c>
       <c r="AD500" s="4" t="n">
-        <v>36.05</v>
+        <v>36.1</v>
       </c>
       <c r="AE500" s="4" t="n">
         <v>0</v>
@@ -54846,10 +54852,10 @@
         <v>3.05</v>
       </c>
       <c r="J504" s="4" t="n">
-        <v>71.40000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="K504" s="4" t="n">
-        <v>28.6</v>
+        <v>28.7</v>
       </c>
       <c r="L504" t="inlineStr">
         <is>
@@ -54875,16 +54881,16 @@
         <v>-13.88</v>
       </c>
       <c r="S504" s="4" t="n">
-        <v>47.78</v>
+        <v>47.74</v>
       </c>
       <c r="T504" s="4" t="n">
-        <v>44.61</v>
+        <v>44.67</v>
       </c>
       <c r="U504" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="V504" s="4" t="n">
-        <v>4.29</v>
+        <v>4.23</v>
       </c>
       <c r="W504" s="5" t="n">
         <v>68560930</v>
@@ -54903,7 +54909,7 @@
         </is>
       </c>
       <c r="AA504" s="4" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="AB504" s="4" t="n">
         <v>0</v>
@@ -54912,7 +54918,7 @@
         <v>51.02</v>
       </c>
       <c r="AD504" s="4" t="n">
-        <v>48</v>
+        <v>48.01</v>
       </c>
       <c r="AE504" s="4" t="n">
         <v>0</v>
@@ -56789,16 +56795,16 @@
         </is>
       </c>
       <c r="J26" s="4" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="K26" t="n">
         <v>13</v>
-      </c>
-      <c r="K26" t="n">
-        <v>12</v>
       </c>
       <c r="L26" t="n">
         <v>8</v>
       </c>
       <c r="M26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N26" s="4" t="n">
         <v>0.2</v>
@@ -56847,7 +56853,7 @@
         </is>
       </c>
       <c r="J27" s="4" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="K27" t="n">
         <v>7</v>
@@ -56859,7 +56865,7 @@
         <v>10</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>

--- a/output/nowcast.xlsx
+++ b/output/nowcast.xlsx
@@ -541,16 +541,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>52.3</v>
+        <v>52.2</v>
       </c>
       <c r="C8" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
       <c r="D8" t="n">
         <v>53</v>
       </c>
       <c r="E8" t="n">
-        <v>68.8</v>
+        <v>68.3</v>
       </c>
       <c r="F8" t="n">
         <v>51</v>
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>241.5</v>
+        <v>242</v>
       </c>
       <c r="C9" t="n">
-        <v>193.5</v>
+        <v>193</v>
       </c>
       <c r="D9" t="n">
         <v>236</v>
       </c>
       <c r="E9" t="n">
-        <v>89</v>
+        <v>89.5</v>
       </c>
       <c r="F9" t="n">
         <v>218</v>
@@ -591,16 +591,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>26.8</v>
       </c>
       <c r="C10" t="n">
-        <v>23</v>
+        <v>23.2</v>
       </c>
       <c r="D10" t="n">
         <v>28</v>
       </c>
       <c r="E10" t="n">
-        <v>72</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="F10" t="n">
         <v>26</v>
@@ -3823,17 +3823,17 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>4.31</v>
+        <v>3.37</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>78.40000000000001</v>
+        <v>73.5</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>21.6</v>
+        <v>26.5</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Likely D</t>
+          <t>Lean D</t>
         </is>
       </c>
       <c r="M28" s="4" t="n">
@@ -3855,16 +3855,16 @@
         <v>14.89</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>43.16</v>
+        <v>44.92</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>45.29</v>
+        <v>46.35</v>
       </c>
       <c r="U28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.58</v>
+        <v>-0.83</v>
       </c>
       <c r="W28" s="5" t="n">
         <v>0</v>
@@ -3883,16 +3883,16 @@
         </is>
       </c>
       <c r="AA28" s="4" t="n">
-        <v>3.46</v>
+        <v>3.17</v>
       </c>
       <c r="AB28" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC28" s="4" t="n">
-        <v>50.35</v>
+        <v>50.05</v>
       </c>
       <c r="AD28" s="4" t="n">
-        <v>46.19</v>
+        <v>46.78</v>
       </c>
       <c r="AE28" s="4" t="n">
         <v>0</v>
@@ -4729,17 +4729,17 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>4.27</v>
+        <v>3.58</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>78.3</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>21.7</v>
+        <v>25.1</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Likely D</t>
+          <t>Lean D</t>
         </is>
       </c>
       <c r="M36" s="4" t="n">
@@ -4761,16 +4761,16 @@
         <v>-0.87</v>
       </c>
       <c r="S36" s="4" t="n">
-        <v>46.33</v>
+        <v>47.02</v>
       </c>
       <c r="T36" s="4" t="n">
-        <v>43.81</v>
+        <v>44.86</v>
       </c>
       <c r="U36" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V36" s="4" t="n">
-        <v>4.37</v>
+        <v>2.96</v>
       </c>
       <c r="W36" s="5" t="n">
         <v>1426778</v>
@@ -4787,10 +4787,10 @@
         <v>0</v>
       </c>
       <c r="AC36" s="4" t="n">
-        <v>52.14</v>
+        <v>51.79</v>
       </c>
       <c r="AD36" s="4" t="n">
-        <v>47.86</v>
+        <v>48.21</v>
       </c>
       <c r="AE36" s="4" t="n">
         <v>0</v>
@@ -4948,10 +4948,10 @@
         <v>-3.04</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>27.7</v>
+        <v>28.4</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>72.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>45.1</v>
       </c>
       <c r="AB38" s="4" t="n">
-        <v>27.7</v>
+        <v>28.4</v>
       </c>
       <c r="AC38" s="4" t="n">
         <v>3.8</v>
@@ -18790,7 +18790,7 @@
         </is>
       </c>
       <c r="I169" s="4" t="n">
-        <v>14.13</v>
+        <v>14.15</v>
       </c>
       <c r="J169" s="4" t="n">
         <v>99.2</v>
@@ -18804,13 +18804,13 @@
         </is>
       </c>
       <c r="M169" s="4" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="N169" s="4" t="n">
         <v>6.77</v>
       </c>
       <c r="O169" s="4" t="n">
-        <v>16.68</v>
+        <v>16.7</v>
       </c>
       <c r="P169" s="4" t="n">
         <v>0.08</v>
@@ -18903,13 +18903,13 @@
         </is>
       </c>
       <c r="I170" s="4" t="n">
-        <v>4.71</v>
+        <v>4.73</v>
       </c>
       <c r="J170" s="4" t="n">
-        <v>79.8</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="K170" s="4" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="L170" t="inlineStr">
         <is>
@@ -18917,13 +18917,13 @@
         </is>
       </c>
       <c r="M170" s="4" t="n">
-        <v>-1.07</v>
+        <v>-1.05</v>
       </c>
       <c r="N170" s="4" t="n">
         <v>6.77</v>
       </c>
       <c r="O170" s="4" t="n">
-        <v>5.02</v>
+        <v>5.04</v>
       </c>
       <c r="P170" s="4" t="n">
         <v>0.15</v>
@@ -18969,10 +18969,10 @@
         <v>0</v>
       </c>
       <c r="AC170" s="4" t="n">
-        <v>49.6</v>
+        <v>49.61</v>
       </c>
       <c r="AD170" s="4" t="n">
-        <v>45.14</v>
+        <v>45.13</v>
       </c>
       <c r="AE170" s="4" t="n">
         <v>2.63</v>
@@ -19020,7 +19020,7 @@
         </is>
       </c>
       <c r="I171" s="4" t="n">
-        <v>7.84</v>
+        <v>7.86</v>
       </c>
       <c r="J171" s="4" t="n">
         <v>90.09999999999999</v>
@@ -19034,13 +19034,13 @@
         </is>
       </c>
       <c r="M171" s="4" t="n">
-        <v>4.03</v>
+        <v>4.05</v>
       </c>
       <c r="N171" s="4" t="n">
         <v>6.77</v>
       </c>
       <c r="O171" s="4" t="n">
-        <v>9.25</v>
+        <v>9.27</v>
       </c>
       <c r="P171" s="4" t="n">
         <v>0.12</v>
@@ -19078,10 +19078,10 @@
         <v>0</v>
       </c>
       <c r="AC171" s="4" t="n">
-        <v>53.92</v>
+        <v>53.93</v>
       </c>
       <c r="AD171" s="4" t="n">
-        <v>46.08</v>
+        <v>46.07</v>
       </c>
       <c r="AE171" s="4" t="n">
         <v>0</v>
@@ -19125,7 +19125,7 @@
         </is>
       </c>
       <c r="I172" s="4" t="n">
-        <v>-17.98</v>
+        <v>-17.96</v>
       </c>
       <c r="J172" s="4" t="n">
         <v>0.4</v>
@@ -19139,13 +19139,13 @@
         </is>
       </c>
       <c r="M172" s="4" t="n">
-        <v>-23.04</v>
+        <v>-23.02</v>
       </c>
       <c r="N172" s="4" t="n">
         <v>6.77</v>
       </c>
       <c r="O172" s="4" t="n">
-        <v>-17.98</v>
+        <v>-17.96</v>
       </c>
       <c r="P172" s="4" t="n">
         <v>-1.08</v>
@@ -19177,10 +19177,10 @@
         <v>0</v>
       </c>
       <c r="AC172" s="4" t="n">
-        <v>41.01</v>
+        <v>41.02</v>
       </c>
       <c r="AD172" s="4" t="n">
-        <v>58.99</v>
+        <v>58.98</v>
       </c>
       <c r="AE172" s="4" t="n">
         <v>0</v>
@@ -25781,10 +25781,10 @@
         <v>-0.4</v>
       </c>
       <c r="J235" s="4" t="n">
-        <v>47.5</v>
+        <v>47.8</v>
       </c>
       <c r="K235" s="4" t="n">
-        <v>52.5</v>
+        <v>52.2</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -29754,13 +29754,13 @@
         </is>
       </c>
       <c r="M271" s="4" t="n">
-        <v>-6.95</v>
+        <v>-6.94</v>
       </c>
       <c r="N271" s="4" t="n">
         <v>6.77</v>
       </c>
       <c r="O271" s="4" t="n">
-        <v>6.05</v>
+        <v>6.06</v>
       </c>
       <c r="P271" s="4" t="n">
         <v>0.22</v>
@@ -29857,7 +29857,7 @@
         </is>
       </c>
       <c r="I272" s="4" t="n">
-        <v>48.3</v>
+        <v>48.31</v>
       </c>
       <c r="J272" s="4" t="n">
         <v>100</v>
@@ -29982,7 +29982,7 @@
         </is>
       </c>
       <c r="M273" s="4" t="n">
-        <v>-8.99</v>
+        <v>-8.98</v>
       </c>
       <c r="N273" s="4" t="n">
         <v>6.77</v>
@@ -30034,10 +30034,10 @@
         <v>0</v>
       </c>
       <c r="AC273" s="4" t="n">
-        <v>46.89</v>
+        <v>46.9</v>
       </c>
       <c r="AD273" s="4" t="n">
-        <v>51.61</v>
+        <v>51.6</v>
       </c>
       <c r="AE273" s="4" t="n">
         <v>0</v>
@@ -30085,7 +30085,7 @@
         </is>
       </c>
       <c r="I274" s="4" t="n">
-        <v>61.78</v>
+        <v>61.79</v>
       </c>
       <c r="J274" s="4" t="n">
         <v>100</v>
@@ -30099,7 +30099,7 @@
         </is>
       </c>
       <c r="M274" s="4" t="n">
-        <v>49.52</v>
+        <v>49.53</v>
       </c>
       <c r="N274" s="4" t="n">
         <v>6.77</v>
@@ -30196,7 +30196,7 @@
         </is>
       </c>
       <c r="I275" s="4" t="n">
-        <v>-7.9</v>
+        <v>-7.89</v>
       </c>
       <c r="J275" s="4" t="n">
         <v>9.800000000000001</v>
@@ -30210,13 +30210,13 @@
         </is>
       </c>
       <c r="M275" s="4" t="n">
-        <v>-13.85</v>
+        <v>-13.84</v>
       </c>
       <c r="N275" s="4" t="n">
         <v>6.77</v>
       </c>
       <c r="O275" s="4" t="n">
-        <v>-8.23</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="P275" s="4" t="n">
         <v>-0.82</v>
@@ -30307,7 +30307,7 @@
         </is>
       </c>
       <c r="I276" s="4" t="n">
-        <v>-10.47</v>
+        <v>-10.46</v>
       </c>
       <c r="J276" s="4" t="n">
         <v>3.1</v>
@@ -30321,13 +30321,13 @@
         </is>
       </c>
       <c r="M276" s="4" t="n">
-        <v>-14.02</v>
+        <v>-14.01</v>
       </c>
       <c r="N276" s="4" t="n">
         <v>6.77</v>
       </c>
       <c r="O276" s="4" t="n">
-        <v>-10.47</v>
+        <v>-10.46</v>
       </c>
       <c r="P276" s="4" t="n">
         <v>-1.22</v>
@@ -30424,13 +30424,13 @@
         </is>
       </c>
       <c r="M277" s="4" t="n">
-        <v>-10.04</v>
+        <v>-10.03</v>
       </c>
       <c r="N277" s="4" t="n">
         <v>6.77</v>
       </c>
       <c r="O277" s="4" t="n">
-        <v>-8.5</v>
+        <v>-8.49</v>
       </c>
       <c r="P277" s="4" t="n">
         <v>-1.34</v>
@@ -30476,10 +30476,10 @@
         <v>0</v>
       </c>
       <c r="AC277" s="4" t="n">
-        <v>45.37</v>
+        <v>45.38</v>
       </c>
       <c r="AD277" s="4" t="n">
-        <v>53.13</v>
+        <v>53.12</v>
       </c>
       <c r="AE277" s="4" t="n">
         <v>0</v>
@@ -30527,7 +30527,7 @@
         </is>
       </c>
       <c r="I278" s="4" t="n">
-        <v>-15</v>
+        <v>-14.99</v>
       </c>
       <c r="J278" s="4" t="n">
         <v>0.7</v>
@@ -30541,13 +30541,13 @@
         </is>
       </c>
       <c r="M278" s="4" t="n">
-        <v>-16.07</v>
+        <v>-16.06</v>
       </c>
       <c r="N278" s="4" t="n">
         <v>6.77</v>
       </c>
       <c r="O278" s="4" t="n">
-        <v>-14.56</v>
+        <v>-14.55</v>
       </c>
       <c r="P278" s="4" t="n">
         <v>-1.86</v>
@@ -30587,10 +30587,10 @@
         <v>0</v>
       </c>
       <c r="AC278" s="4" t="n">
-        <v>41.75</v>
+        <v>41.76</v>
       </c>
       <c r="AD278" s="4" t="n">
-        <v>56.49</v>
+        <v>56.48</v>
       </c>
       <c r="AE278" s="4" t="n">
         <v>0</v>
@@ -30638,7 +30638,7 @@
         </is>
       </c>
       <c r="I279" s="4" t="n">
-        <v>-7.73</v>
+        <v>-7.72</v>
       </c>
       <c r="J279" s="4" t="n">
         <v>10.3</v>
@@ -30652,13 +30652,13 @@
         </is>
       </c>
       <c r="M279" s="4" t="n">
-        <v>-12.37</v>
+        <v>-12.36</v>
       </c>
       <c r="N279" s="4" t="n">
         <v>6.77</v>
       </c>
       <c r="O279" s="4" t="n">
-        <v>-9.050000000000001</v>
+        <v>-9.039999999999999</v>
       </c>
       <c r="P279" s="4" t="n">
         <v>-0.22</v>
@@ -30747,7 +30747,7 @@
         </is>
       </c>
       <c r="I280" s="4" t="n">
-        <v>-12.88</v>
+        <v>-12.87</v>
       </c>
       <c r="J280" s="4" t="n">
         <v>1</v>
@@ -30761,7 +30761,7 @@
         </is>
       </c>
       <c r="M280" s="4" t="n">
-        <v>-14.19</v>
+        <v>-14.18</v>
       </c>
       <c r="N280" s="4" t="n">
         <v>6.77</v>
@@ -30813,10 +30813,10 @@
         <v>0</v>
       </c>
       <c r="AC280" s="4" t="n">
-        <v>42.8</v>
+        <v>42.81</v>
       </c>
       <c r="AD280" s="4" t="n">
-        <v>55.46</v>
+        <v>55.45</v>
       </c>
       <c r="AE280" s="4" t="n">
         <v>0</v>
@@ -30874,13 +30874,13 @@
         </is>
       </c>
       <c r="M281" s="4" t="n">
-        <v>-7.01</v>
+        <v>-7</v>
       </c>
       <c r="N281" s="4" t="n">
         <v>6.77</v>
       </c>
       <c r="O281" s="4" t="n">
-        <v>-0.96</v>
+        <v>-0.95</v>
       </c>
       <c r="P281" s="4" t="n">
         <v>0</v>
@@ -30977,7 +30977,7 @@
         </is>
       </c>
       <c r="I282" s="4" t="n">
-        <v>62.21</v>
+        <v>62.22</v>
       </c>
       <c r="J282" s="4" t="n">
         <v>100</v>
@@ -30991,13 +30991,13 @@
         </is>
       </c>
       <c r="M282" s="4" t="n">
-        <v>51.24</v>
+        <v>51.25</v>
       </c>
       <c r="N282" s="4" t="n">
         <v>6.77</v>
       </c>
       <c r="O282" s="4" t="n">
-        <v>62.21</v>
+        <v>62.22</v>
       </c>
       <c r="P282" s="4" t="n">
         <v>1.26</v>
@@ -31080,7 +31080,7 @@
         </is>
       </c>
       <c r="I283" s="4" t="n">
-        <v>-10.24</v>
+        <v>-10.23</v>
       </c>
       <c r="J283" s="4" t="n">
         <v>3.6</v>
@@ -31100,7 +31100,7 @@
         <v>6.77</v>
       </c>
       <c r="O283" s="4" t="n">
-        <v>-10.61</v>
+        <v>-10.6</v>
       </c>
       <c r="P283" s="4" t="n">
         <v>-0.19</v>
@@ -31191,7 +31191,7 @@
         </is>
       </c>
       <c r="I284" s="4" t="n">
-        <v>-10.45</v>
+        <v>-10.44</v>
       </c>
       <c r="J284" s="4" t="n">
         <v>3.1</v>
@@ -31211,7 +31211,7 @@
         <v>6.77</v>
       </c>
       <c r="O284" s="4" t="n">
-        <v>-11.91</v>
+        <v>-11.9</v>
       </c>
       <c r="P284" s="4" t="n">
         <v>-2.3</v>
@@ -38933,7 +38933,7 @@
         </is>
       </c>
       <c r="I356" s="4" t="n">
-        <v>51.35</v>
+        <v>51.11</v>
       </c>
       <c r="J356" s="4" t="n">
         <v>100</v>
@@ -38947,13 +38947,13 @@
         </is>
       </c>
       <c r="M356" s="4" t="n">
-        <v>39.03</v>
+        <v>38.79</v>
       </c>
       <c r="N356" s="4" t="n">
         <v>6.77</v>
       </c>
       <c r="O356" s="4" t="n">
-        <v>51.35</v>
+        <v>51.11</v>
       </c>
       <c r="P356" s="4" t="n">
         <v>2.08</v>
@@ -38985,10 +38985,10 @@
         <v>0</v>
       </c>
       <c r="AC356" s="4" t="n">
-        <v>75.67</v>
+        <v>75.56</v>
       </c>
       <c r="AD356" s="4" t="n">
-        <v>24.33</v>
+        <v>24.44</v>
       </c>
       <c r="AE356" s="4" t="n">
         <v>0</v>
@@ -39036,7 +39036,7 @@
         </is>
       </c>
       <c r="I357" s="4" t="n">
-        <v>-27.13</v>
+        <v>-27.36</v>
       </c>
       <c r="J357" s="4" t="n">
         <v>0</v>
@@ -39050,13 +39050,13 @@
         </is>
       </c>
       <c r="M357" s="4" t="n">
-        <v>-27.8</v>
+        <v>-28.03</v>
       </c>
       <c r="N357" s="4" t="n">
         <v>6.77</v>
       </c>
       <c r="O357" s="4" t="n">
-        <v>-27.13</v>
+        <v>-27.36</v>
       </c>
       <c r="P357" s="4" t="n">
         <v>-1.49</v>
@@ -39088,10 +39088,10 @@
         <v>0</v>
       </c>
       <c r="AC357" s="4" t="n">
-        <v>36.44</v>
+        <v>36.32</v>
       </c>
       <c r="AD357" s="4" t="n">
-        <v>63.56</v>
+        <v>63.68</v>
       </c>
       <c r="AE357" s="4" t="n">
         <v>0</v>
@@ -39139,7 +39139,7 @@
         </is>
       </c>
       <c r="I358" s="4" t="n">
-        <v>57.05</v>
+        <v>56.82</v>
       </c>
       <c r="J358" s="4" t="n">
         <v>100</v>
@@ -39153,13 +39153,13 @@
         </is>
       </c>
       <c r="M358" s="4" t="n">
-        <v>47.6</v>
+        <v>47.37</v>
       </c>
       <c r="N358" s="4" t="n">
         <v>6.77</v>
       </c>
       <c r="O358" s="4" t="n">
-        <v>57.05</v>
+        <v>56.82</v>
       </c>
       <c r="P358" s="4" t="n">
         <v>0</v>
@@ -39191,10 +39191,10 @@
         <v>0</v>
       </c>
       <c r="AC358" s="4" t="n">
-        <v>78.53</v>
+        <v>78.41</v>
       </c>
       <c r="AD358" s="4" t="n">
-        <v>21.47</v>
+        <v>21.59</v>
       </c>
       <c r="AE358" s="4" t="n">
         <v>0</v>
@@ -39242,7 +39242,7 @@
         </is>
       </c>
       <c r="I359" s="4" t="n">
-        <v>17.62</v>
+        <v>17.39</v>
       </c>
       <c r="J359" s="4" t="n">
         <v>99.59999999999999</v>
@@ -39256,13 +39256,13 @@
         </is>
       </c>
       <c r="M359" s="4" t="n">
-        <v>12.1</v>
+        <v>11.87</v>
       </c>
       <c r="N359" s="4" t="n">
         <v>6.77</v>
       </c>
       <c r="O359" s="4" t="n">
-        <v>18.8</v>
+        <v>18.56</v>
       </c>
       <c r="P359" s="4" t="n">
         <v>0.38</v>
@@ -39302,10 +39302,10 @@
         <v>0</v>
       </c>
       <c r="AC359" s="4" t="n">
-        <v>56.05</v>
+        <v>55.94</v>
       </c>
       <c r="AD359" s="4" t="n">
-        <v>39.25</v>
+        <v>39.36</v>
       </c>
       <c r="AE359" s="4" t="n">
         <v>0</v>
@@ -39353,7 +39353,7 @@
         </is>
       </c>
       <c r="I360" s="4" t="n">
-        <v>17.34</v>
+        <v>17.1</v>
       </c>
       <c r="J360" s="4" t="n">
         <v>99.59999999999999</v>
@@ -39367,13 +39367,13 @@
         </is>
       </c>
       <c r="M360" s="4" t="n">
-        <v>8.33</v>
+        <v>8.1</v>
       </c>
       <c r="N360" s="4" t="n">
         <v>6.77</v>
       </c>
       <c r="O360" s="4" t="n">
-        <v>18.51</v>
+        <v>18.28</v>
       </c>
       <c r="P360" s="4" t="n">
         <v>1.57</v>
@@ -39413,10 +39413,10 @@
         <v>0</v>
       </c>
       <c r="AC360" s="4" t="n">
-        <v>55.92</v>
+        <v>55.81</v>
       </c>
       <c r="AD360" s="4" t="n">
-        <v>39.39</v>
+        <v>39.5</v>
       </c>
       <c r="AE360" s="4" t="n">
         <v>0</v>
@@ -39464,7 +39464,7 @@
         </is>
       </c>
       <c r="I361" s="4" t="n">
-        <v>19.88</v>
+        <v>19.65</v>
       </c>
       <c r="J361" s="4" t="n">
         <v>99.8</v>
@@ -39478,13 +39478,13 @@
         </is>
       </c>
       <c r="M361" s="4" t="n">
-        <v>11.56</v>
+        <v>11.32</v>
       </c>
       <c r="N361" s="4" t="n">
         <v>6.77</v>
       </c>
       <c r="O361" s="4" t="n">
-        <v>19.88</v>
+        <v>19.65</v>
       </c>
       <c r="P361" s="4" t="n">
         <v>2.46</v>
@@ -39516,10 +39516,10 @@
         <v>0</v>
       </c>
       <c r="AC361" s="4" t="n">
-        <v>59.94</v>
+        <v>59.82</v>
       </c>
       <c r="AD361" s="4" t="n">
-        <v>40.06</v>
+        <v>40.18</v>
       </c>
       <c r="AE361" s="4" t="n">
         <v>0</v>
@@ -44235,13 +44235,13 @@
         </is>
       </c>
       <c r="I406" s="4" t="n">
-        <v>-4.21</v>
+        <v>-6.29</v>
       </c>
       <c r="J406" s="4" t="n">
-        <v>22</v>
+        <v>14.8</v>
       </c>
       <c r="K406" s="4" t="n">
-        <v>78</v>
+        <v>85.2</v>
       </c>
       <c r="L406" t="inlineStr">
         <is>
@@ -44266,12 +44266,18 @@
       <c r="R406" s="4" t="n">
         <v>-20.07</v>
       </c>
-      <c r="S406" s="4" t="n"/>
-      <c r="T406" s="4" t="n"/>
+      <c r="S406" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="T406" s="4" t="n">
+        <v>45</v>
+      </c>
       <c r="U406" t="n">
-        <v>0</v>
-      </c>
-      <c r="V406" s="4" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="V406" s="4" t="n">
+        <v>-8.470000000000001</v>
+      </c>
       <c r="W406" s="5" t="n">
         <v>55358</v>
       </c>
@@ -44287,10 +44293,10 @@
         <v>0</v>
       </c>
       <c r="AC406" s="4" t="n">
-        <v>47.9</v>
+        <v>46.86</v>
       </c>
       <c r="AD406" s="4" t="n">
-        <v>52.1</v>
+        <v>53.14</v>
       </c>
       <c r="AE406" s="4" t="n">
         <v>0</v>
@@ -50179,13 +50185,13 @@
         </is>
       </c>
       <c r="I462" s="4" t="n">
-        <v>-2.55</v>
+        <v>-2.66</v>
       </c>
       <c r="J462" s="4" t="n">
-        <v>32.1</v>
+        <v>31.3</v>
       </c>
       <c r="K462" s="4" t="n">
-        <v>67.90000000000001</v>
+        <v>68.7</v>
       </c>
       <c r="L462" t="inlineStr">
         <is>
@@ -50193,13 +50199,13 @@
         </is>
       </c>
       <c r="M462" s="4" t="n">
-        <v>-2.54</v>
+        <v>-2.71</v>
       </c>
       <c r="N462" s="4" t="n">
         <v>6.77</v>
       </c>
       <c r="O462" s="4" t="n">
-        <v>-2.52</v>
+        <v>-2.69</v>
       </c>
       <c r="P462" s="4" t="n">
         <v>-1.44</v>
@@ -50237,10 +50243,10 @@
         <v>0</v>
       </c>
       <c r="AC462" s="4" t="n">
-        <v>48.72</v>
+        <v>48.67</v>
       </c>
       <c r="AD462" s="4" t="n">
-        <v>51.28</v>
+        <v>51.33</v>
       </c>
       <c r="AE462" s="4" t="n">
         <v>0</v>
@@ -50288,7 +50294,7 @@
         </is>
       </c>
       <c r="I463" s="4" t="n">
-        <v>51.17</v>
+        <v>50.99</v>
       </c>
       <c r="J463" s="4" t="n">
         <v>100</v>
@@ -50302,13 +50308,13 @@
         </is>
       </c>
       <c r="M463" s="4" t="n">
-        <v>42.45</v>
+        <v>42.27</v>
       </c>
       <c r="N463" s="4" t="n">
         <v>6.77</v>
       </c>
       <c r="O463" s="4" t="n">
-        <v>51.17</v>
+        <v>50.99</v>
       </c>
       <c r="P463" s="4" t="n">
         <v>0</v>
@@ -50340,10 +50346,10 @@
         <v>0</v>
       </c>
       <c r="AC463" s="4" t="n">
-        <v>75.58</v>
+        <v>75.5</v>
       </c>
       <c r="AD463" s="4" t="n">
-        <v>24.42</v>
+        <v>24.5</v>
       </c>
       <c r="AE463" s="4" t="n">
         <v>0</v>
@@ -50391,13 +50397,13 @@
         </is>
       </c>
       <c r="I464" s="4" t="n">
-        <v>6.24</v>
+        <v>6.12</v>
       </c>
       <c r="J464" s="4" t="n">
-        <v>85.09999999999999</v>
+        <v>84.7</v>
       </c>
       <c r="K464" s="4" t="n">
-        <v>14.9</v>
+        <v>15.3</v>
       </c>
       <c r="L464" t="inlineStr">
         <is>
@@ -50405,13 +50411,13 @@
         </is>
       </c>
       <c r="M464" s="4" t="n">
-        <v>-5.37</v>
+        <v>-5.54</v>
       </c>
       <c r="N464" s="4" t="n">
         <v>6.77</v>
       </c>
       <c r="O464" s="4" t="n">
-        <v>7.94</v>
+        <v>7.76</v>
       </c>
       <c r="P464" s="4" t="n">
         <v>0.17</v>
@@ -50457,10 +50463,10 @@
         <v>0</v>
       </c>
       <c r="AC464" s="4" t="n">
-        <v>51.77</v>
+        <v>51.71</v>
       </c>
       <c r="AD464" s="4" t="n">
-        <v>45.69</v>
+        <v>45.75</v>
       </c>
       <c r="AE464" s="4" t="n">
         <v>0</v>
@@ -50508,7 +50514,7 @@
         </is>
       </c>
       <c r="I465" s="4" t="n">
-        <v>64.45</v>
+        <v>64.28</v>
       </c>
       <c r="J465" s="4" t="n">
         <v>100</v>
@@ -50522,13 +50528,13 @@
         </is>
       </c>
       <c r="M465" s="4" t="n">
-        <v>54.17</v>
+        <v>54</v>
       </c>
       <c r="N465" s="4" t="n">
         <v>6.77</v>
       </c>
       <c r="O465" s="4" t="n">
-        <v>64.58</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="P465" s="4" t="n">
         <v>0</v>
@@ -50568,10 +50574,10 @@
         <v>0</v>
       </c>
       <c r="AC465" s="4" t="n">
-        <v>80.16</v>
+        <v>80.08</v>
       </c>
       <c r="AD465" s="4" t="n">
-        <v>17.33</v>
+        <v>17.41</v>
       </c>
       <c r="AE465" s="4" t="n">
         <v>0</v>
@@ -50619,7 +50625,7 @@
         </is>
       </c>
       <c r="I466" s="4" t="n">
-        <v>-22.59</v>
+        <v>-22.76</v>
       </c>
       <c r="J466" s="4" t="n">
         <v>0.1</v>
@@ -50633,13 +50639,13 @@
         </is>
       </c>
       <c r="M466" s="4" t="n">
-        <v>-21.6</v>
+        <v>-21.78</v>
       </c>
       <c r="N466" s="4" t="n">
         <v>6.77</v>
       </c>
       <c r="O466" s="4" t="n">
-        <v>-22.59</v>
+        <v>-22.76</v>
       </c>
       <c r="P466" s="4" t="n">
         <v>-2.32</v>
@@ -50671,10 +50677,10 @@
         <v>0</v>
       </c>
       <c r="AC466" s="4" t="n">
-        <v>38.71</v>
+        <v>38.62</v>
       </c>
       <c r="AD466" s="4" t="n">
-        <v>61.29</v>
+        <v>61.38</v>
       </c>
       <c r="AE466" s="4" t="n">
         <v>0</v>
@@ -50722,7 +50728,7 @@
         </is>
       </c>
       <c r="I467" s="4" t="n">
-        <v>-17.15</v>
+        <v>-17.3</v>
       </c>
       <c r="J467" s="4" t="n">
         <v>0.4</v>
@@ -50736,13 +50742,13 @@
         </is>
       </c>
       <c r="M467" s="4" t="n">
-        <v>-15.21</v>
+        <v>-15.39</v>
       </c>
       <c r="N467" s="4" t="n">
         <v>6.77</v>
       </c>
       <c r="O467" s="4" t="n">
-        <v>-15.22</v>
+        <v>-15.39</v>
       </c>
       <c r="P467" s="4" t="n">
         <v>-1.13</v>
@@ -50788,10 +50794,10 @@
         <v>0</v>
       </c>
       <c r="AC467" s="4" t="n">
-        <v>39.43</v>
+        <v>39.36</v>
       </c>
       <c r="AD467" s="4" t="n">
-        <v>55.75</v>
+        <v>55.82</v>
       </c>
       <c r="AE467" s="4" t="n">
         <v>2.41</v>
@@ -50835,7 +50841,7 @@
         </is>
       </c>
       <c r="I468" s="4" t="n">
-        <v>-16.2</v>
+        <v>-16.38</v>
       </c>
       <c r="J468" s="4" t="n">
         <v>0.5</v>
@@ -50849,13 +50855,13 @@
         </is>
       </c>
       <c r="M468" s="4" t="n">
-        <v>-20.83</v>
+        <v>-21.01</v>
       </c>
       <c r="N468" s="4" t="n">
         <v>6.77</v>
       </c>
       <c r="O468" s="4" t="n">
-        <v>-16.2</v>
+        <v>-16.38</v>
       </c>
       <c r="P468" s="4" t="n">
         <v>-1.15</v>
@@ -50887,10 +50893,10 @@
         <v>0</v>
       </c>
       <c r="AC468" s="4" t="n">
-        <v>41.9</v>
+        <v>41.81</v>
       </c>
       <c r="AD468" s="4" t="n">
-        <v>58.1</v>
+        <v>58.19</v>
       </c>
       <c r="AE468" s="4" t="n">
         <v>0</v>
@@ -50938,7 +50944,7 @@
         </is>
       </c>
       <c r="I469" s="4" t="n">
-        <v>-12.56</v>
+        <v>-12.74</v>
       </c>
       <c r="J469" s="4" t="n">
         <v>1</v>
@@ -50952,13 +50958,13 @@
         </is>
       </c>
       <c r="M469" s="4" t="n">
-        <v>-15.01</v>
+        <v>-15.18</v>
       </c>
       <c r="N469" s="4" t="n">
         <v>6.77</v>
       </c>
       <c r="O469" s="4" t="n">
-        <v>-12.56</v>
+        <v>-12.74</v>
       </c>
       <c r="P469" s="4" t="n">
         <v>-1.69</v>
@@ -50990,10 +50996,10 @@
         <v>0</v>
       </c>
       <c r="AC469" s="4" t="n">
-        <v>43.72</v>
+        <v>43.63</v>
       </c>
       <c r="AD469" s="4" t="n">
-        <v>56.28</v>
+        <v>56.37</v>
       </c>
       <c r="AE469" s="4" t="n">
         <v>0</v>
@@ -51365,10 +51371,10 @@
         <v>1.49</v>
       </c>
       <c r="J473" s="4" t="n">
-        <v>61.8</v>
+        <v>60.6</v>
       </c>
       <c r="K473" s="4" t="n">
-        <v>38.2</v>
+        <v>39.4</v>
       </c>
       <c r="L473" t="inlineStr">
         <is>
@@ -52129,13 +52135,13 @@
         </is>
       </c>
       <c r="I480" s="4" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="J480" s="4" t="n">
-        <v>61.7</v>
+        <v>62.4</v>
       </c>
       <c r="K480" s="4" t="n">
-        <v>38.3</v>
+        <v>37.6</v>
       </c>
       <c r="L480" t="inlineStr">
         <is>
@@ -52161,16 +52167,16 @@
         <v>-13.45</v>
       </c>
       <c r="S480" s="4" t="n">
-        <v>46.22</v>
+        <v>46.25</v>
       </c>
       <c r="T480" s="4" t="n">
-        <v>43.93</v>
+        <v>44.05</v>
       </c>
       <c r="U480" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V480" s="4" t="n">
-        <v>3.56</v>
+        <v>3.5</v>
       </c>
       <c r="W480" s="5" t="n">
         <v>6276527</v>
@@ -52195,10 +52201,10 @@
         <v>0</v>
       </c>
       <c r="AC480" s="4" t="n">
-        <v>50.57</v>
+        <v>50.62</v>
       </c>
       <c r="AD480" s="4" t="n">
-        <v>48.93</v>
+        <v>48.88</v>
       </c>
       <c r="AE480" s="4" t="n">
         <v>0</v>
@@ -52925,10 +52931,10 @@
         <v>2.05</v>
       </c>
       <c r="J487" s="4" t="n">
-        <v>64.09999999999999</v>
+        <v>64.5</v>
       </c>
       <c r="K487" s="4" t="n">
-        <v>35.9</v>
+        <v>35.5</v>
       </c>
       <c r="L487" t="inlineStr">
         <is>
@@ -53370,7 +53376,7 @@
         </is>
       </c>
       <c r="I491" s="4" t="n">
-        <v>-21.38</v>
+        <v>-21.41</v>
       </c>
       <c r="J491" s="4" t="n">
         <v>0</v>
@@ -53430,16 +53436,16 @@
         </is>
       </c>
       <c r="AA491" s="4" t="n">
-        <v>27.82</v>
+        <v>27.8</v>
       </c>
       <c r="AB491" s="4" t="n">
         <v>0.2</v>
       </c>
       <c r="AC491" s="4" t="n">
-        <v>19.32</v>
+        <v>19.33</v>
       </c>
       <c r="AD491" s="4" t="n">
-        <v>49.2</v>
+        <v>49.21</v>
       </c>
       <c r="AE491" s="4" t="n">
         <v>3.66</v>
@@ -53483,13 +53489,13 @@
         </is>
       </c>
       <c r="I492" s="4" t="n">
-        <v>9.66</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J492" s="4" t="n">
-        <v>95</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="K492" s="4" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L492" t="inlineStr">
         <is>
@@ -53515,16 +53521,16 @@
         <v>-3.27</v>
       </c>
       <c r="S492" s="4" t="n">
-        <v>50.93</v>
+        <v>50.73</v>
       </c>
       <c r="T492" s="4" t="n">
-        <v>40.02</v>
+        <v>39.82</v>
       </c>
       <c r="U492" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V492" s="4" t="n">
-        <v>11.86</v>
+        <v>11.84</v>
       </c>
       <c r="W492" s="5" t="n">
         <v>34975789</v>
@@ -53543,13 +53549,13 @@
         </is>
       </c>
       <c r="AA492" s="4" t="n">
-        <v>0.55</v>
+        <v>0.51</v>
       </c>
       <c r="AB492" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC492" s="4" t="n">
-        <v>53.5</v>
+        <v>53.54</v>
       </c>
       <c r="AD492" s="4" t="n">
         <v>44.08</v>
@@ -54274,7 +54280,7 @@
         </is>
       </c>
       <c r="I499" s="4" t="n">
-        <v>23.68</v>
+        <v>23.45</v>
       </c>
       <c r="J499" s="4" t="n">
         <v>99.90000000000001</v>
@@ -54288,13 +54294,13 @@
         </is>
       </c>
       <c r="M499" s="4" t="n">
-        <v>12.53</v>
+        <v>12.3</v>
       </c>
       <c r="N499" s="4" t="n">
         <v>6.77</v>
       </c>
       <c r="O499" s="4" t="n">
-        <v>22.98</v>
+        <v>22.75</v>
       </c>
       <c r="P499" s="4" t="n">
         <v>2.47</v>
@@ -54334,10 +54340,10 @@
         <v>0</v>
       </c>
       <c r="AC499" s="4" t="n">
-        <v>56.05</v>
+        <v>55.95</v>
       </c>
       <c r="AD499" s="4" t="n">
-        <v>34.59</v>
+        <v>34.69</v>
       </c>
       <c r="AE499" s="4" t="n">
         <v>4.68</v>
@@ -54619,13 +54625,13 @@
         </is>
       </c>
       <c r="I502" s="4" t="n">
-        <v>-15.24</v>
+        <v>-14.66</v>
       </c>
       <c r="J502" s="4" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K502" s="4" t="n">
-        <v>99.40000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="L502" t="inlineStr">
         <is>
@@ -54651,16 +54657,16 @@
         <v>-29.98</v>
       </c>
       <c r="S502" s="4" t="n">
-        <v>41.27</v>
+        <v>42.84</v>
       </c>
       <c r="T502" s="4" t="n">
-        <v>46.07</v>
+        <v>47.96</v>
       </c>
       <c r="U502" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V502" s="4" t="n">
-        <v>-5.67</v>
+        <v>-6.58</v>
       </c>
       <c r="W502" s="5" t="n">
         <v>0</v>
@@ -54679,16 +54685,16 @@
         </is>
       </c>
       <c r="AA502" s="4" t="n">
-        <v>42.38</v>
+        <v>42.67</v>
       </c>
       <c r="AB502" s="4" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="AC502" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AD502" s="4" t="n">
-        <v>57.62</v>
+        <v>57.33</v>
       </c>
       <c r="AE502" s="4" t="n">
         <v>0</v>
@@ -59069,7 +59075,7 @@
         <v>47</v>
       </c>
       <c r="N65" s="4" t="n">
-        <v>97.2</v>
+        <v>97</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -59115,7 +59121,7 @@
         </is>
       </c>
       <c r="J66" s="4" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="K66" t="n">
         <v>20</v>
@@ -59127,7 +59133,7 @@
         <v>22</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>97.90000000000001</v>
+        <v>97.8</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -59463,7 +59469,7 @@
         </is>
       </c>
       <c r="J72" s="4" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="K72" t="n">
         <v>9</v>
@@ -60159,7 +60165,7 @@
         </is>
       </c>
       <c r="J84" s="4" t="n">
-        <v>51.5</v>
+        <v>51.4</v>
       </c>
       <c r="K84" t="n">
         <v>51</v>
@@ -60171,7 +60177,7 @@
         <v>67</v>
       </c>
       <c r="N84" s="4" t="n">
-        <v>57</v>
+        <v>56.5</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
@@ -60217,7 +60223,7 @@
         </is>
       </c>
       <c r="J85" s="4" t="n">
-        <v>17.7</v>
+        <v>17.6</v>
       </c>
       <c r="K85" t="n">
         <v>18</v>
@@ -60226,10 +60232,10 @@
         <v>14</v>
       </c>
       <c r="M85" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N85" s="4" t="n">
-        <v>70.90000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>

--- a/output/nowcast.xlsx
+++ b/output/nowcast.xlsx
@@ -550,7 +550,7 @@
         <v>53</v>
       </c>
       <c r="E8" t="n">
-        <v>68.7</v>
+        <v>68.5</v>
       </c>
       <c r="F8" t="n">
         <v>51</v>
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>241.3</v>
+        <v>241.7</v>
       </c>
       <c r="C9" t="n">
-        <v>193.7</v>
+        <v>193.3</v>
       </c>
       <c r="D9" t="n">
         <v>237</v>
       </c>
       <c r="E9" t="n">
-        <v>88.40000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="F9" t="n">
         <v>218</v>
@@ -600,7 +600,7 @@
         <v>28</v>
       </c>
       <c r="E10" t="n">
-        <v>69.3</v>
+        <v>69.2</v>
       </c>
       <c r="F10" t="n">
         <v>26</v>
@@ -3038,13 +3038,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-11.43</v>
+        <v>-10.47</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>98.7</v>
+        <v>97</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -3070,16 +3070,16 @@
         <v>-20.84</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>35.5</v>
+        <v>35.68</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>43.36</v>
+        <v>43.26</v>
       </c>
       <c r="U21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-7.72</v>
+        <v>-7.23</v>
       </c>
       <c r="W21" s="5" t="n">
         <v>0</v>
@@ -3098,16 +3098,16 @@
         </is>
       </c>
       <c r="AA21" s="4" t="n">
-        <v>3.33</v>
+        <v>3.52</v>
       </c>
       <c r="AB21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC21" s="4" t="n">
-        <v>42.81</v>
+        <v>43.19</v>
       </c>
       <c r="AD21" s="4" t="n">
-        <v>53.86</v>
+        <v>53.29</v>
       </c>
       <c r="AE21" s="4" t="n">
         <v>0</v>
@@ -4948,10 +4948,10 @@
         <v>-2.4</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>32.7</v>
+        <v>33.3</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>67.3</v>
+        <v>66.7</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>45.42</v>
       </c>
       <c r="AB38" s="4" t="n">
-        <v>32.7</v>
+        <v>33.3</v>
       </c>
       <c r="AC38" s="4" t="n">
         <v>3.8</v>
@@ -23133,17 +23133,17 @@
         </is>
       </c>
       <c r="I210" s="4" t="n">
-        <v>-4.06</v>
+        <v>-2.42</v>
       </c>
       <c r="J210" s="4" t="n">
-        <v>22.5</v>
+        <v>33</v>
       </c>
       <c r="K210" s="4" t="n">
-        <v>77.5</v>
+        <v>67</v>
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>Likely R</t>
+          <t>Lean R</t>
         </is>
       </c>
       <c r="M210" s="4" t="n">
@@ -23165,16 +23165,16 @@
         <v>-15.31</v>
       </c>
       <c r="S210" s="4" t="n">
-        <v>44.91</v>
+        <v>42.78</v>
       </c>
       <c r="T210" s="4" t="n">
-        <v>44.86</v>
+        <v>39.1</v>
       </c>
       <c r="U210" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V210" s="4" t="n">
-        <v>-1.2</v>
+        <v>1.15</v>
       </c>
       <c r="W210" s="5" t="n">
         <v>1463855</v>
@@ -23199,10 +23199,10 @@
         <v>0</v>
       </c>
       <c r="AC210" s="4" t="n">
-        <v>46.74</v>
+        <v>47.54</v>
       </c>
       <c r="AD210" s="4" t="n">
-        <v>50.7</v>
+        <v>49.9</v>
       </c>
       <c r="AE210" s="4" t="n">
         <v>0</v>
@@ -25781,10 +25781,10 @@
         <v>-0.34</v>
       </c>
       <c r="J235" s="4" t="n">
-        <v>47.2</v>
+        <v>47.4</v>
       </c>
       <c r="K235" s="4" t="n">
-        <v>52.8</v>
+        <v>52.6</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -31411,13 +31411,13 @@
         </is>
       </c>
       <c r="I286" s="4" t="n">
-        <v>-6.35</v>
+        <v>-6.2</v>
       </c>
       <c r="J286" s="4" t="n">
-        <v>14.6</v>
+        <v>15.1</v>
       </c>
       <c r="K286" s="4" t="n">
-        <v>85.40000000000001</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="L286" t="inlineStr">
         <is>
@@ -31425,13 +31425,13 @@
         </is>
       </c>
       <c r="M286" s="4" t="n">
-        <v>-10.85</v>
+        <v>-10.61</v>
       </c>
       <c r="N286" s="4" t="n">
         <v>6.74</v>
       </c>
       <c r="O286" s="4" t="n">
-        <v>-10.6</v>
+        <v>-10.36</v>
       </c>
       <c r="P286" s="4" t="n">
         <v>-0.99</v>
@@ -31477,10 +31477,10 @@
         <v>0</v>
       </c>
       <c r="AC286" s="4" t="n">
-        <v>44.57</v>
+        <v>44.64</v>
       </c>
       <c r="AD286" s="4" t="n">
-        <v>50.61</v>
+        <v>50.54</v>
       </c>
       <c r="AE286" s="4" t="n">
         <v>2.41</v>
@@ -31524,13 +31524,13 @@
         </is>
       </c>
       <c r="I287" s="4" t="n">
-        <v>10.52</v>
+        <v>10.66</v>
       </c>
       <c r="J287" s="4" t="n">
-        <v>97.09999999999999</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="K287" s="4" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="L287" t="inlineStr">
         <is>
@@ -31538,13 +31538,13 @@
         </is>
       </c>
       <c r="M287" s="4" t="n">
-        <v>7.01</v>
+        <v>7.25</v>
       </c>
       <c r="N287" s="4" t="n">
         <v>6.74</v>
       </c>
       <c r="O287" s="4" t="n">
-        <v>13.92</v>
+        <v>14.16</v>
       </c>
       <c r="P287" s="4" t="n">
         <v>0.53</v>
@@ -31590,10 +31590,10 @@
         <v>0</v>
       </c>
       <c r="AC287" s="4" t="n">
-        <v>54.07</v>
+        <v>54.13</v>
       </c>
       <c r="AD287" s="4" t="n">
-        <v>43.77</v>
+        <v>43.71</v>
       </c>
       <c r="AE287" s="4" t="n">
         <v>0</v>
@@ -31641,7 +31641,7 @@
         </is>
       </c>
       <c r="I288" s="4" t="n">
-        <v>-53.34</v>
+        <v>-53.1</v>
       </c>
       <c r="J288" s="4" t="n">
         <v>0</v>
@@ -31655,13 +31655,13 @@
         </is>
       </c>
       <c r="M288" s="4" t="n">
-        <v>-51.8</v>
+        <v>-51.56</v>
       </c>
       <c r="N288" s="4" t="n">
         <v>6.74</v>
       </c>
       <c r="O288" s="4" t="n">
-        <v>-53.15</v>
+        <v>-52.91</v>
       </c>
       <c r="P288" s="4" t="n">
         <v>-2.18</v>
@@ -31701,10 +31701,10 @@
         <v>0</v>
       </c>
       <c r="AC288" s="4" t="n">
-        <v>22.4</v>
+        <v>22.52</v>
       </c>
       <c r="AD288" s="4" t="n">
-        <v>73.64</v>
+        <v>73.52</v>
       </c>
       <c r="AE288" s="4" t="n">
         <v>1.98</v>
@@ -41556,13 +41556,13 @@
         </is>
       </c>
       <c r="I381" s="4" t="n">
-        <v>-1.5</v>
+        <v>-1.56</v>
       </c>
       <c r="J381" s="4" t="n">
-        <v>39.4</v>
+        <v>38.9</v>
       </c>
       <c r="K381" s="4" t="n">
-        <v>60.6</v>
+        <v>61.1</v>
       </c>
       <c r="L381" t="inlineStr">
         <is>
@@ -41588,16 +41588,16 @@
         <v>-13.29</v>
       </c>
       <c r="S381" s="4" t="n">
-        <v>40.06</v>
+        <v>40.04</v>
       </c>
       <c r="T381" s="4" t="n">
-        <v>41.08</v>
+        <v>42.96</v>
       </c>
       <c r="U381" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V381" s="4" t="n">
-        <v>-3.03</v>
+        <v>-3.02</v>
       </c>
       <c r="W381" s="5" t="n">
         <v>2279585</v>
@@ -41616,16 +41616,16 @@
         </is>
       </c>
       <c r="AA381" s="4" t="n">
-        <v>0.5</v>
+        <v>1.55</v>
       </c>
       <c r="AB381" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC381" s="4" t="n">
-        <v>49</v>
+        <v>48.46</v>
       </c>
       <c r="AD381" s="4" t="n">
-        <v>50.5</v>
+        <v>49.99</v>
       </c>
       <c r="AE381" s="4" t="n">
         <v>0</v>
@@ -51401,10 +51401,10 @@
         <v>1.45</v>
       </c>
       <c r="J473" s="4" t="n">
-        <v>60.4</v>
+        <v>60.8</v>
       </c>
       <c r="K473" s="4" t="n">
-        <v>39.6</v>
+        <v>39.2</v>
       </c>
       <c r="L473" t="inlineStr">
         <is>
@@ -52961,10 +52961,10 @@
         <v>2.12</v>
       </c>
       <c r="J487" s="4" t="n">
-        <v>63.3</v>
+        <v>64.3</v>
       </c>
       <c r="K487" s="4" t="n">
-        <v>36.7</v>
+        <v>35.7</v>
       </c>
       <c r="L487" t="inlineStr">
         <is>
@@ -53406,7 +53406,7 @@
         </is>
       </c>
       <c r="I491" s="4" t="n">
-        <v>-21.54</v>
+        <v>-21.56</v>
       </c>
       <c r="J491" s="4" t="n">
         <v>0</v>
@@ -53466,16 +53466,16 @@
         </is>
       </c>
       <c r="AA491" s="4" t="n">
-        <v>27.78</v>
+        <v>27.75</v>
       </c>
       <c r="AB491" s="4" t="n">
         <v>0.2</v>
       </c>
       <c r="AC491" s="4" t="n">
-        <v>19.24</v>
+        <v>19.28</v>
       </c>
       <c r="AD491" s="4" t="n">
-        <v>49.32</v>
+        <v>49.31</v>
       </c>
       <c r="AE491" s="4" t="n">
         <v>3.66</v>
@@ -53636,13 +53636,13 @@
         </is>
       </c>
       <c r="I493" s="4" t="n">
-        <v>-1.07</v>
+        <v>-0.72</v>
       </c>
       <c r="J493" s="4" t="n">
-        <v>42.2</v>
+        <v>44.8</v>
       </c>
       <c r="K493" s="4" t="n">
-        <v>57.8</v>
+        <v>55.2</v>
       </c>
       <c r="L493" t="inlineStr">
         <is>
@@ -53650,13 +53650,13 @@
         </is>
       </c>
       <c r="M493" s="4" t="n">
-        <v>-18.56</v>
+        <v>-18.32</v>
       </c>
       <c r="N493" s="4" t="n">
         <v>6.74</v>
       </c>
       <c r="O493" s="4" t="n">
-        <v>-4.01</v>
+        <v>-3.77</v>
       </c>
       <c r="P493" s="4" t="n">
         <v>-0.35</v>
@@ -53668,16 +53668,16 @@
         <v>-20.84</v>
       </c>
       <c r="S493" s="4" t="n">
-        <v>46.59</v>
+        <v>45.97</v>
       </c>
       <c r="T493" s="4" t="n">
-        <v>44.84</v>
+        <v>44.93</v>
       </c>
       <c r="U493" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V493" s="4" t="n">
-        <v>2.01</v>
+        <v>1.67</v>
       </c>
       <c r="W493" s="5" t="n">
         <v>0</v>
@@ -53696,16 +53696,16 @@
         </is>
       </c>
       <c r="AA493" s="4" t="n">
-        <v>48.38</v>
+        <v>48.55</v>
       </c>
       <c r="AB493" s="4" t="n">
-        <v>42.2</v>
+        <v>44.8</v>
       </c>
       <c r="AC493" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AD493" s="4" t="n">
-        <v>49.44</v>
+        <v>49.27</v>
       </c>
       <c r="AE493" s="4" t="n">
         <v>2.18</v>
@@ -58400,7 +58400,7 @@
         <v>18.6</v>
       </c>
       <c r="K53" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L53" t="n">
         <v>15</v>

--- a/output/nowcast.xlsx
+++ b/output/nowcast.xlsx
@@ -550,7 +550,7 @@
         <v>53</v>
       </c>
       <c r="E8" t="n">
-        <v>68.5</v>
+        <v>68.2</v>
       </c>
       <c r="F8" t="n">
         <v>51</v>
@@ -575,7 +575,7 @@
         <v>237</v>
       </c>
       <c r="E9" t="n">
-        <v>88.5</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="F9" t="n">
         <v>218</v>
@@ -591,16 +591,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>26.9</v>
+        <v>26.8</v>
       </c>
       <c r="C10" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="D10" t="n">
         <v>28</v>
       </c>
       <c r="E10" t="n">
-        <v>69.2</v>
+        <v>69</v>
       </c>
       <c r="F10" t="n">
         <v>26</v>
@@ -4948,10 +4948,10 @@
         <v>-2.4</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>33.3</v>
+        <v>32.7</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>66.7</v>
+        <v>67.3</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>45.42</v>
       </c>
       <c r="AB38" s="4" t="n">
-        <v>33.3</v>
+        <v>32.7</v>
       </c>
       <c r="AC38" s="4" t="n">
         <v>3.8</v>
@@ -25781,10 +25781,10 @@
         <v>-0.34</v>
       </c>
       <c r="J235" s="4" t="n">
-        <v>47.4</v>
+        <v>48.2</v>
       </c>
       <c r="K235" s="4" t="n">
-        <v>52.6</v>
+        <v>51.8</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -31748,13 +31748,13 @@
         </is>
       </c>
       <c r="I289" s="4" t="n">
-        <v>5.76</v>
+        <v>5.75</v>
       </c>
       <c r="J289" s="4" t="n">
-        <v>83.5</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K289" s="4" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="L289" t="inlineStr">
         <is>
@@ -31762,7 +31762,7 @@
         </is>
       </c>
       <c r="M289" s="4" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N289" s="4" t="n">
         <v>6.74</v>
@@ -31857,7 +31857,7 @@
         </is>
       </c>
       <c r="I290" s="4" t="n">
-        <v>17.98</v>
+        <v>17.97</v>
       </c>
       <c r="J290" s="4" t="n">
         <v>99.59999999999999</v>
@@ -31871,13 +31871,13 @@
         </is>
       </c>
       <c r="M290" s="4" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="N290" s="4" t="n">
         <v>6.74</v>
       </c>
       <c r="O290" s="4" t="n">
-        <v>16.83</v>
+        <v>16.82</v>
       </c>
       <c r="P290" s="4" t="n">
         <v>0.92</v>
@@ -33282,7 +33282,7 @@
         </is>
       </c>
       <c r="I303" s="4" t="n">
-        <v>28.9</v>
+        <v>28.58</v>
       </c>
       <c r="J303" s="4" t="n">
         <v>100</v>
@@ -33296,13 +33296,13 @@
         </is>
       </c>
       <c r="M303" s="4" t="n">
-        <v>17.28</v>
+        <v>16.96</v>
       </c>
       <c r="N303" s="4" t="n">
         <v>6.74</v>
       </c>
       <c r="O303" s="4" t="n">
-        <v>28.9</v>
+        <v>28.58</v>
       </c>
       <c r="P303" s="4" t="n">
         <v>1.68</v>
@@ -33334,10 +33334,10 @@
         <v>0</v>
       </c>
       <c r="AC303" s="4" t="n">
-        <v>64.45</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="AD303" s="4" t="n">
-        <v>35.55</v>
+        <v>35.71</v>
       </c>
       <c r="AE303" s="4" t="n">
         <v>0</v>
@@ -33385,7 +33385,7 @@
         </is>
       </c>
       <c r="I304" s="4" t="n">
-        <v>14.85</v>
+        <v>14.62</v>
       </c>
       <c r="J304" s="4" t="n">
         <v>99.3</v>
@@ -33399,13 +33399,13 @@
         </is>
       </c>
       <c r="M304" s="4" t="n">
-        <v>4.43</v>
+        <v>4.11</v>
       </c>
       <c r="N304" s="4" t="n">
         <v>6.74</v>
       </c>
       <c r="O304" s="4" t="n">
-        <v>19.25</v>
+        <v>18.93</v>
       </c>
       <c r="P304" s="4" t="n">
         <v>0.62</v>
@@ -33443,10 +33443,10 @@
         <v>0</v>
       </c>
       <c r="AC304" s="4" t="n">
-        <v>57.42</v>
+        <v>57.31</v>
       </c>
       <c r="AD304" s="4" t="n">
-        <v>42.58</v>
+        <v>42.69</v>
       </c>
       <c r="AE304" s="4" t="n">
         <v>0</v>
@@ -33494,13 +33494,13 @@
         </is>
       </c>
       <c r="I305" s="4" t="n">
-        <v>25.91</v>
+        <v>25.59</v>
       </c>
       <c r="J305" s="4" t="n">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="K305" s="4" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L305" t="inlineStr">
         <is>
@@ -33508,13 +33508,13 @@
         </is>
       </c>
       <c r="M305" s="4" t="n">
-        <v>11.03</v>
+        <v>10.71</v>
       </c>
       <c r="N305" s="4" t="n">
         <v>6.74</v>
       </c>
       <c r="O305" s="4" t="n">
-        <v>25.91</v>
+        <v>25.59</v>
       </c>
       <c r="P305" s="4" t="n">
         <v>0.73</v>
@@ -33546,10 +33546,10 @@
         <v>0</v>
       </c>
       <c r="AC305" s="4" t="n">
-        <v>62.96</v>
+        <v>62.8</v>
       </c>
       <c r="AD305" s="4" t="n">
-        <v>37.04</v>
+        <v>37.2</v>
       </c>
       <c r="AE305" s="4" t="n">
         <v>0</v>
@@ -41556,13 +41556,13 @@
         </is>
       </c>
       <c r="I381" s="4" t="n">
-        <v>-1.56</v>
+        <v>-1.54</v>
       </c>
       <c r="J381" s="4" t="n">
-        <v>38.9</v>
+        <v>39.1</v>
       </c>
       <c r="K381" s="4" t="n">
-        <v>61.1</v>
+        <v>60.9</v>
       </c>
       <c r="L381" t="inlineStr">
         <is>
@@ -41570,13 +41570,13 @@
         </is>
       </c>
       <c r="M381" s="4" t="n">
-        <v>-7.66</v>
+        <v>-7.61</v>
       </c>
       <c r="N381" s="4" t="n">
         <v>6.74</v>
       </c>
       <c r="O381" s="4" t="n">
-        <v>-0.9</v>
+        <v>-0.85</v>
       </c>
       <c r="P381" s="4" t="n">
         <v>0.47</v>
@@ -41622,10 +41622,10 @@
         <v>0</v>
       </c>
       <c r="AC381" s="4" t="n">
-        <v>48.46</v>
+        <v>48.47</v>
       </c>
       <c r="AD381" s="4" t="n">
-        <v>49.99</v>
+        <v>49.98</v>
       </c>
       <c r="AE381" s="4" t="n">
         <v>0</v>
@@ -41673,13 +41673,13 @@
         </is>
       </c>
       <c r="I382" s="4" t="n">
-        <v>-8.93</v>
+        <v>-8.880000000000001</v>
       </c>
       <c r="J382" s="4" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="K382" s="4" t="n">
-        <v>93.09999999999999</v>
+        <v>93</v>
       </c>
       <c r="L382" t="inlineStr">
         <is>
@@ -41687,13 +41687,13 @@
         </is>
       </c>
       <c r="M382" s="4" t="n">
-        <v>-8.84</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="N382" s="4" t="n">
         <v>6.74</v>
       </c>
       <c r="O382" s="4" t="n">
-        <v>-8.82</v>
+        <v>-8.77</v>
       </c>
       <c r="P382" s="4" t="n">
         <v>-1.93</v>
@@ -41733,10 +41733,10 @@
         <v>0</v>
       </c>
       <c r="AC382" s="4" t="n">
-        <v>44.61</v>
+        <v>44.63</v>
       </c>
       <c r="AD382" s="4" t="n">
-        <v>53.35</v>
+        <v>53.33</v>
       </c>
       <c r="AE382" s="4" t="n">
         <v>0</v>
@@ -41784,7 +41784,7 @@
         </is>
       </c>
       <c r="I383" s="4" t="n">
-        <v>-38.56</v>
+        <v>-38.51</v>
       </c>
       <c r="J383" s="4" t="n">
         <v>0</v>
@@ -41798,13 +41798,13 @@
         </is>
       </c>
       <c r="M383" s="4" t="n">
-        <v>-37.3</v>
+        <v>-37.25</v>
       </c>
       <c r="N383" s="4" t="n">
         <v>6.74</v>
       </c>
       <c r="O383" s="4" t="n">
-        <v>-38.9</v>
+        <v>-38.85</v>
       </c>
       <c r="P383" s="4" t="n">
         <v>-1.36</v>
@@ -41844,10 +41844,10 @@
         <v>0</v>
       </c>
       <c r="AC383" s="4" t="n">
-        <v>30.19</v>
+        <v>30.22</v>
       </c>
       <c r="AD383" s="4" t="n">
-        <v>68.09999999999999</v>
+        <v>68.06999999999999</v>
       </c>
       <c r="AE383" s="4" t="n">
         <v>0</v>
@@ -41895,7 +41895,7 @@
         </is>
       </c>
       <c r="I384" s="4" t="n">
-        <v>-14.9</v>
+        <v>-14.85</v>
       </c>
       <c r="J384" s="4" t="n">
         <v>0.7</v>
@@ -41909,13 +41909,13 @@
         </is>
       </c>
       <c r="M384" s="4" t="n">
-        <v>-18.15</v>
+        <v>-18.1</v>
       </c>
       <c r="N384" s="4" t="n">
         <v>6.74</v>
       </c>
       <c r="O384" s="4" t="n">
-        <v>-15.35</v>
+        <v>-15.3</v>
       </c>
       <c r="P384" s="4" t="n">
         <v>-2.31</v>
@@ -41955,10 +41955,10 @@
         <v>0</v>
       </c>
       <c r="AC384" s="4" t="n">
-        <v>41.6</v>
+        <v>41.62</v>
       </c>
       <c r="AD384" s="4" t="n">
-        <v>56.16</v>
+        <v>56.14</v>
       </c>
       <c r="AE384" s="4" t="n">
         <v>0</v>
@@ -42002,7 +42002,7 @@
         </is>
       </c>
       <c r="I385" s="4" t="n">
-        <v>-12.05</v>
+        <v>-12</v>
       </c>
       <c r="J385" s="4" t="n">
         <v>1.1</v>
@@ -42016,13 +42016,13 @@
         </is>
       </c>
       <c r="M385" s="4" t="n">
-        <v>-17.12</v>
+        <v>-17.07</v>
       </c>
       <c r="N385" s="4" t="n">
         <v>6.74</v>
       </c>
       <c r="O385" s="4" t="n">
-        <v>-12.05</v>
+        <v>-12</v>
       </c>
       <c r="P385" s="4" t="n">
         <v>-1.2</v>
@@ -42054,10 +42054,10 @@
         <v>0</v>
       </c>
       <c r="AC385" s="4" t="n">
-        <v>43.98</v>
+        <v>44</v>
       </c>
       <c r="AD385" s="4" t="n">
-        <v>56.02</v>
+        <v>56</v>
       </c>
       <c r="AE385" s="4" t="n">
         <v>0</v>
@@ -42105,7 +42105,7 @@
         </is>
       </c>
       <c r="I386" s="4" t="n">
-        <v>38.86</v>
+        <v>38.91</v>
       </c>
       <c r="J386" s="4" t="n">
         <v>100</v>
@@ -42119,13 +42119,13 @@
         </is>
       </c>
       <c r="M386" s="4" t="n">
-        <v>30.61</v>
+        <v>30.66</v>
       </c>
       <c r="N386" s="4" t="n">
         <v>6.74</v>
       </c>
       <c r="O386" s="4" t="n">
-        <v>38.86</v>
+        <v>38.91</v>
       </c>
       <c r="P386" s="4" t="n">
         <v>0</v>
@@ -42157,10 +42157,10 @@
         <v>0</v>
       </c>
       <c r="AC386" s="4" t="n">
-        <v>69.43000000000001</v>
+        <v>69.45</v>
       </c>
       <c r="AD386" s="4" t="n">
-        <v>30.57</v>
+        <v>30.55</v>
       </c>
       <c r="AE386" s="4" t="n">
         <v>0</v>
@@ -42208,7 +42208,7 @@
         </is>
       </c>
       <c r="I387" s="4" t="n">
-        <v>-16.08</v>
+        <v>-16.04</v>
       </c>
       <c r="J387" s="4" t="n">
         <v>0.5</v>
@@ -42222,13 +42222,13 @@
         </is>
       </c>
       <c r="M387" s="4" t="n">
-        <v>-19.72</v>
+        <v>-19.67</v>
       </c>
       <c r="N387" s="4" t="n">
         <v>6.74</v>
       </c>
       <c r="O387" s="4" t="n">
-        <v>-18.8</v>
+        <v>-18.75</v>
       </c>
       <c r="P387" s="4" t="n">
         <v>-1.22</v>
@@ -42266,10 +42266,10 @@
         <v>0</v>
       </c>
       <c r="AC387" s="4" t="n">
-        <v>41.96</v>
+        <v>41.98</v>
       </c>
       <c r="AD387" s="4" t="n">
-        <v>58.04</v>
+        <v>58.02</v>
       </c>
       <c r="AE387" s="4" t="n">
         <v>0</v>
@@ -51401,10 +51401,10 @@
         <v>1.45</v>
       </c>
       <c r="J473" s="4" t="n">
-        <v>60.8</v>
+        <v>61.3</v>
       </c>
       <c r="K473" s="4" t="n">
-        <v>39.2</v>
+        <v>38.7</v>
       </c>
       <c r="L473" t="inlineStr">
         <is>
@@ -52961,10 +52961,10 @@
         <v>2.12</v>
       </c>
       <c r="J487" s="4" t="n">
-        <v>64.3</v>
+        <v>64.7</v>
       </c>
       <c r="K487" s="4" t="n">
-        <v>35.7</v>
+        <v>35.3</v>
       </c>
       <c r="L487" t="inlineStr">
         <is>
@@ -53406,7 +53406,7 @@
         </is>
       </c>
       <c r="I491" s="4" t="n">
-        <v>-21.56</v>
+        <v>-21.55</v>
       </c>
       <c r="J491" s="4" t="n">
         <v>0</v>
@@ -53466,13 +53466,13 @@
         </is>
       </c>
       <c r="AA491" s="4" t="n">
-        <v>27.75</v>
+        <v>27.76</v>
       </c>
       <c r="AB491" s="4" t="n">
         <v>0.2</v>
       </c>
       <c r="AC491" s="4" t="n">
-        <v>19.28</v>
+        <v>19.26</v>
       </c>
       <c r="AD491" s="4" t="n">
         <v>49.31</v>
@@ -53749,13 +53749,13 @@
         </is>
       </c>
       <c r="I494" s="4" t="n">
-        <v>8.220000000000001</v>
+        <v>8.18</v>
       </c>
       <c r="J494" s="4" t="n">
-        <v>91.09999999999999</v>
+        <v>91</v>
       </c>
       <c r="K494" s="4" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="L494" t="inlineStr">
         <is>
@@ -53781,13 +53781,13 @@
         <v>2.82</v>
       </c>
       <c r="S494" s="4" t="n">
-        <v>48.4</v>
+        <v>48.41</v>
       </c>
       <c r="T494" s="4" t="n">
         <v>43.57</v>
       </c>
       <c r="U494" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="V494" s="4" t="n">
         <v>5.74</v>
@@ -53815,10 +53815,10 @@
         <v>0</v>
       </c>
       <c r="AC494" s="4" t="n">
-        <v>53.84</v>
+        <v>53.82</v>
       </c>
       <c r="AD494" s="4" t="n">
-        <v>45.66</v>
+        <v>45.68</v>
       </c>
       <c r="AE494" s="4" t="n">
         <v>0</v>
@@ -53977,7 +53977,7 @@
         </is>
       </c>
       <c r="I496" s="4" t="n">
-        <v>21.39</v>
+        <v>19.79</v>
       </c>
       <c r="J496" s="4" t="n">
         <v>99.8</v>
@@ -54008,12 +54008,18 @@
       <c r="R496" s="4" t="n">
         <v>6.14</v>
       </c>
-      <c r="S496" s="4" t="n"/>
-      <c r="T496" s="4" t="n"/>
+      <c r="S496" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="T496" s="4" t="n">
+        <v>38</v>
+      </c>
       <c r="U496" t="n">
-        <v>0</v>
-      </c>
-      <c r="V496" s="4" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="V496" s="4" t="n">
+        <v>16.45</v>
+      </c>
       <c r="W496" s="5" t="n">
         <v>5626629</v>
       </c>
@@ -54029,10 +54035,10 @@
         <v>0</v>
       </c>
       <c r="AC496" s="4" t="n">
-        <v>60.69</v>
+        <v>59.9</v>
       </c>
       <c r="AD496" s="4" t="n">
-        <v>39.31</v>
+        <v>40.1</v>
       </c>
       <c r="AE496" s="4" t="n">
         <v>0</v>
@@ -54538,13 +54544,13 @@
         </is>
       </c>
       <c r="I501" s="4" t="n">
-        <v>-2.92</v>
+        <v>-2.66</v>
       </c>
       <c r="J501" s="4" t="n">
-        <v>29.6</v>
+        <v>31.3</v>
       </c>
       <c r="K501" s="4" t="n">
-        <v>70.40000000000001</v>
+        <v>68.7</v>
       </c>
       <c r="L501" t="inlineStr">
         <is>
@@ -54570,16 +54576,16 @@
         <v>-18.12</v>
       </c>
       <c r="S501" s="4" t="n">
-        <v>40.14</v>
+        <v>39.96</v>
       </c>
       <c r="T501" s="4" t="n">
-        <v>42.99</v>
+        <v>42.79</v>
       </c>
       <c r="U501" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="V501" s="4" t="n">
-        <v>-1.18</v>
+        <v>-1.05</v>
       </c>
       <c r="W501" s="5" t="n">
         <v>10804040</v>
@@ -54598,16 +54604,16 @@
         </is>
       </c>
       <c r="AA501" s="4" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AB501" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC501" s="4" t="n">
-        <v>47.04</v>
+        <v>47.14</v>
       </c>
       <c r="AD501" s="4" t="n">
-        <v>49.87</v>
+        <v>49.72</v>
       </c>
       <c r="AE501" s="4" t="n">
         <v>1.87</v>
@@ -58455,10 +58461,10 @@
         </is>
       </c>
       <c r="J54" s="4" t="n">
-        <v>223.5</v>
+        <v>223.4</v>
       </c>
       <c r="K54" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L54" t="n">
         <v>143</v>
@@ -58571,7 +58577,7 @@
         </is>
       </c>
       <c r="J56" s="4" t="n">
-        <v>46.4</v>
+        <v>46.3</v>
       </c>
       <c r="K56" t="n">
         <v>47</v>

--- a/output/nowcast.xlsx
+++ b/output/nowcast.xlsx
@@ -541,16 +541,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>52.4</v>
+        <v>52.3</v>
       </c>
       <c r="C8" t="n">
-        <v>47.6</v>
+        <v>47.7</v>
       </c>
       <c r="D8" t="n">
         <v>53</v>
       </c>
       <c r="E8" t="n">
-        <v>69.8</v>
+        <v>69.7</v>
       </c>
       <c r="F8" t="n">
         <v>51</v>
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>241.3</v>
+        <v>241.4</v>
       </c>
       <c r="C9" t="n">
-        <v>193.7</v>
+        <v>193.6</v>
       </c>
       <c r="D9" t="n">
         <v>237</v>
       </c>
       <c r="E9" t="n">
-        <v>88.5</v>
+        <v>88.2</v>
       </c>
       <c r="F9" t="n">
         <v>218</v>
@@ -925,13 +925,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>15.81</v>
+        <v>17.98</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>99.59999999999999</v>
+        <v>99.8</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -957,16 +957,16 @@
         <v>-13.8</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>40.58</v>
+        <v>50.22</v>
       </c>
       <c r="T2" s="4" t="n">
-        <v>41.38</v>
+        <v>46.97</v>
       </c>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V2" s="4" t="n">
-        <v>0.61</v>
+        <v>3.47</v>
       </c>
       <c r="W2" s="5" t="n">
         <v>0</v>
@@ -983,10 +983,10 @@
         <v>0</v>
       </c>
       <c r="AC2" s="4" t="n">
-        <v>48.21</v>
+        <v>49.46</v>
       </c>
       <c r="AD2" s="4" t="n">
-        <v>51.79</v>
+        <v>50.54</v>
       </c>
       <c r="AE2" s="4" t="n">
         <v>0</v>
@@ -2017,13 +2017,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>8.859999999999999</v>
+        <v>9.02</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>92.90000000000001</v>
+        <v>93.3</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -2049,16 +2049,16 @@
         <v>-13.45</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>51.58</v>
+        <v>51.65</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>42.26</v>
+        <v>42.07</v>
       </c>
       <c r="U12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>10.15</v>
+        <v>10.28</v>
       </c>
       <c r="W12" s="5" t="n">
         <v>19860206</v>
@@ -2075,10 +2075,10 @@
         <v>0</v>
       </c>
       <c r="AC12" s="4" t="n">
-        <v>54.43</v>
+        <v>54.51</v>
       </c>
       <c r="AD12" s="4" t="n">
-        <v>45.57</v>
+        <v>45.49</v>
       </c>
       <c r="AE12" s="4" t="n">
         <v>0</v>
@@ -2356,13 +2356,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-7.09</v>
+        <v>-6.85</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>12.2</v>
+        <v>13</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>87.8</v>
+        <v>87</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -2388,16 +2388,16 @@
         <v>-16.41</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>45.06</v>
+        <v>44.5</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>50.2</v>
+        <v>49.56</v>
       </c>
       <c r="U15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-4.96</v>
+        <v>-4.98</v>
       </c>
       <c r="W15" s="5" t="n">
         <v>0</v>
@@ -2414,10 +2414,10 @@
         <v>0</v>
       </c>
       <c r="AC15" s="4" t="n">
-        <v>46.45</v>
+        <v>46.57</v>
       </c>
       <c r="AD15" s="4" t="n">
-        <v>53.55</v>
+        <v>53.43</v>
       </c>
       <c r="AE15" s="4" t="n">
         <v>0</v>
@@ -3599,13 +3599,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>50.9</v>
+        <v>51.1</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>49.1</v>
+        <v>48.9</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -3631,16 +3631,16 @@
         <v>-11.31</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>49.05</v>
+        <v>49.03</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>45.08</v>
+        <v>45.06</v>
       </c>
       <c r="U26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>4.56</v>
+        <v>4.39</v>
       </c>
       <c r="W26" s="5" t="n">
         <v>15928993</v>
@@ -3659,16 +3659,16 @@
         </is>
       </c>
       <c r="AA26" s="4" t="n">
-        <v>1.06</v>
+        <v>0.73</v>
       </c>
       <c r="AB26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC26" s="4" t="n">
-        <v>49.53</v>
+        <v>49.71</v>
       </c>
       <c r="AD26" s="4" t="n">
-        <v>49.41</v>
+        <v>49.56</v>
       </c>
       <c r="AE26" s="4" t="n">
         <v>0</v>
@@ -4499,13 +4499,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-4.38</v>
+        <v>-3.93</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>21.3</v>
+        <v>23</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>78.7</v>
+        <v>77</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -4531,16 +4531,16 @@
         <v>-13.88</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>46.44</v>
+        <v>46.8</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>48.78</v>
+        <v>48.39</v>
       </c>
       <c r="U34" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-1.57</v>
+        <v>-0.93</v>
       </c>
       <c r="W34" s="5" t="n">
         <v>8433631</v>
@@ -4559,16 +4559,16 @@
         </is>
       </c>
       <c r="AA34" s="4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AB34" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC34" s="4" t="n">
-        <v>47.54</v>
+        <v>47.8</v>
       </c>
       <c r="AD34" s="4" t="n">
-        <v>51.9</v>
+        <v>51.7</v>
       </c>
       <c r="AE34" s="4" t="n">
         <v>0</v>
@@ -4945,13 +4945,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>-3.29</v>
+        <v>-3.03</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>26.4</v>
+        <v>27.9</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>73.59999999999999</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -4959,13 +4959,13 @@
         </is>
       </c>
       <c r="M38" s="4" t="n">
-        <v>-2.04</v>
+        <v>-1.49</v>
       </c>
       <c r="N38" s="4" t="n">
         <v>6.75</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>1.27</v>
+        <v>1.82</v>
       </c>
       <c r="P38" s="4" t="n">
         <v>-0.72</v>
@@ -5005,16 +5005,16 @@
         </is>
       </c>
       <c r="AA38" s="4" t="n">
-        <v>45.05</v>
+        <v>45.18</v>
       </c>
       <c r="AB38" s="4" t="n">
-        <v>26.4</v>
+        <v>27.9</v>
       </c>
       <c r="AC38" s="4" t="n">
         <v>3.8</v>
       </c>
       <c r="AD38" s="4" t="n">
-        <v>49.95</v>
+        <v>49.82</v>
       </c>
       <c r="AE38" s="4" t="n">
         <v>1.2</v>
@@ -18790,7 +18790,7 @@
         </is>
       </c>
       <c r="I169" s="4" t="n">
-        <v>14.07</v>
+        <v>14.09</v>
       </c>
       <c r="J169" s="4" t="n">
         <v>99.2</v>
@@ -18804,13 +18804,13 @@
         </is>
       </c>
       <c r="M169" s="4" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="N169" s="4" t="n">
         <v>6.75</v>
       </c>
       <c r="O169" s="4" t="n">
-        <v>16.58</v>
+        <v>16.62</v>
       </c>
       <c r="P169" s="4" t="n">
         <v>0.09</v>
@@ -18856,10 +18856,10 @@
         <v>0</v>
       </c>
       <c r="AC169" s="4" t="n">
-        <v>50.76</v>
+        <v>50.77</v>
       </c>
       <c r="AD169" s="4" t="n">
-        <v>38.24</v>
+        <v>38.23</v>
       </c>
       <c r="AE169" s="4" t="n">
         <v>0</v>
@@ -18903,13 +18903,13 @@
         </is>
       </c>
       <c r="I170" s="4" t="n">
-        <v>4.6</v>
+        <v>4.62</v>
       </c>
       <c r="J170" s="4" t="n">
-        <v>79.40000000000001</v>
+        <v>79.5</v>
       </c>
       <c r="K170" s="4" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="L170" t="inlineStr">
         <is>
@@ -18917,13 +18917,13 @@
         </is>
       </c>
       <c r="M170" s="4" t="n">
-        <v>-1.15</v>
+        <v>-1.12</v>
       </c>
       <c r="N170" s="4" t="n">
         <v>6.75</v>
       </c>
       <c r="O170" s="4" t="n">
-        <v>4.88</v>
+        <v>4.91</v>
       </c>
       <c r="P170" s="4" t="n">
         <v>0.11</v>
@@ -18969,10 +18969,10 @@
         <v>0</v>
       </c>
       <c r="AC170" s="4" t="n">
-        <v>49.55</v>
+        <v>49.56</v>
       </c>
       <c r="AD170" s="4" t="n">
-        <v>45.19</v>
+        <v>45.18</v>
       </c>
       <c r="AE170" s="4" t="n">
         <v>2.63</v>
@@ -19020,13 +19020,13 @@
         </is>
       </c>
       <c r="I171" s="4" t="n">
-        <v>7.75</v>
+        <v>7.78</v>
       </c>
       <c r="J171" s="4" t="n">
-        <v>89.8</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="K171" s="4" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="L171" t="inlineStr">
         <is>
@@ -19034,13 +19034,13 @@
         </is>
       </c>
       <c r="M171" s="4" t="n">
-        <v>3.94</v>
+        <v>3.97</v>
       </c>
       <c r="N171" s="4" t="n">
         <v>6.75</v>
       </c>
       <c r="O171" s="4" t="n">
-        <v>9.16</v>
+        <v>9.19</v>
       </c>
       <c r="P171" s="4" t="n">
         <v>0.14</v>
@@ -19078,10 +19078,10 @@
         <v>0</v>
       </c>
       <c r="AC171" s="4" t="n">
-        <v>53.88</v>
+        <v>53.89</v>
       </c>
       <c r="AD171" s="4" t="n">
-        <v>46.12</v>
+        <v>46.11</v>
       </c>
       <c r="AE171" s="4" t="n">
         <v>0</v>
@@ -19125,7 +19125,7 @@
         </is>
       </c>
       <c r="I172" s="4" t="n">
-        <v>-18.09</v>
+        <v>-18.05</v>
       </c>
       <c r="J172" s="4" t="n">
         <v>0.4</v>
@@ -19139,13 +19139,13 @@
         </is>
       </c>
       <c r="M172" s="4" t="n">
-        <v>-23.13</v>
+        <v>-23.1</v>
       </c>
       <c r="N172" s="4" t="n">
         <v>6.75</v>
       </c>
       <c r="O172" s="4" t="n">
-        <v>-18.09</v>
+        <v>-18.05</v>
       </c>
       <c r="P172" s="4" t="n">
         <v>-1.08</v>
@@ -19177,10 +19177,10 @@
         <v>0</v>
       </c>
       <c r="AC172" s="4" t="n">
-        <v>40.96</v>
+        <v>40.97</v>
       </c>
       <c r="AD172" s="4" t="n">
-        <v>59.04</v>
+        <v>59.03</v>
       </c>
       <c r="AE172" s="4" t="n">
         <v>0</v>
@@ -22158,7 +22158,7 @@
         </is>
       </c>
       <c r="I201" s="4" t="n">
-        <v>-27.54</v>
+        <v>-27.49</v>
       </c>
       <c r="J201" s="4" t="n">
         <v>0</v>
@@ -22172,13 +22172,13 @@
         </is>
       </c>
       <c r="M201" s="4" t="n">
-        <v>-27.02</v>
+        <v>-26.96</v>
       </c>
       <c r="N201" s="4" t="n">
         <v>6.75</v>
       </c>
       <c r="O201" s="4" t="n">
-        <v>-28.08</v>
+        <v>-28.03</v>
       </c>
       <c r="P201" s="4" t="n">
         <v>-2.06</v>
@@ -22218,10 +22218,10 @@
         <v>0</v>
       </c>
       <c r="AC201" s="4" t="n">
-        <v>35.26</v>
+        <v>35.28</v>
       </c>
       <c r="AD201" s="4" t="n">
-        <v>62.06</v>
+        <v>62.04</v>
       </c>
       <c r="AE201" s="4" t="n">
         <v>0</v>
@@ -22269,7 +22269,7 @@
         </is>
       </c>
       <c r="I202" s="4" t="n">
-        <v>-13.33</v>
+        <v>-13.28</v>
       </c>
       <c r="J202" s="4" t="n">
         <v>0.9</v>
@@ -22283,13 +22283,13 @@
         </is>
       </c>
       <c r="M202" s="4" t="n">
-        <v>-14.59</v>
+        <v>-14.54</v>
       </c>
       <c r="N202" s="4" t="n">
         <v>6.75</v>
       </c>
       <c r="O202" s="4" t="n">
-        <v>-13.9</v>
+        <v>-13.84</v>
       </c>
       <c r="P202" s="4" t="n">
         <v>-0.47</v>
@@ -22329,10 +22329,10 @@
         <v>0</v>
       </c>
       <c r="AC202" s="4" t="n">
-        <v>42.11</v>
+        <v>42.13</v>
       </c>
       <c r="AD202" s="4" t="n">
-        <v>55.05</v>
+        <v>55.03</v>
       </c>
       <c r="AE202" s="4" t="n">
         <v>0</v>
@@ -22380,7 +22380,7 @@
         </is>
       </c>
       <c r="I203" s="4" t="n">
-        <v>25.46</v>
+        <v>25.51</v>
       </c>
       <c r="J203" s="4" t="n">
         <v>99.90000000000001</v>
@@ -22394,13 +22394,13 @@
         </is>
       </c>
       <c r="M203" s="4" t="n">
-        <v>8.380000000000001</v>
+        <v>8.44</v>
       </c>
       <c r="N203" s="4" t="n">
         <v>6.75</v>
       </c>
       <c r="O203" s="4" t="n">
-        <v>24.87</v>
+        <v>24.92</v>
       </c>
       <c r="P203" s="4" t="n">
         <v>3</v>
@@ -22440,10 +22440,10 @@
         <v>0</v>
       </c>
       <c r="AC203" s="4" t="n">
-        <v>60.89</v>
+        <v>60.91</v>
       </c>
       <c r="AD203" s="4" t="n">
-        <v>36.17</v>
+        <v>36.15</v>
       </c>
       <c r="AE203" s="4" t="n">
         <v>0</v>
@@ -22491,7 +22491,7 @@
         </is>
       </c>
       <c r="I204" s="4" t="n">
-        <v>-18.78</v>
+        <v>-18.73</v>
       </c>
       <c r="J204" s="4" t="n">
         <v>0.3</v>
@@ -22505,13 +22505,13 @@
         </is>
       </c>
       <c r="M204" s="4" t="n">
-        <v>-18.97</v>
+        <v>-18.92</v>
       </c>
       <c r="N204" s="4" t="n">
         <v>6.75</v>
       </c>
       <c r="O204" s="4" t="n">
-        <v>-19.36</v>
+        <v>-19.3</v>
       </c>
       <c r="P204" s="4" t="n">
         <v>-1.43</v>
@@ -22551,10 +22551,10 @@
         <v>0</v>
       </c>
       <c r="AC204" s="4" t="n">
-        <v>39.44</v>
+        <v>39.47</v>
       </c>
       <c r="AD204" s="4" t="n">
-        <v>57.68</v>
+        <v>57.65</v>
       </c>
       <c r="AE204" s="4" t="n">
         <v>0</v>
@@ -25781,10 +25781,10 @@
         <v>-0.4</v>
       </c>
       <c r="J235" s="4" t="n">
-        <v>47.1</v>
+        <v>48.3</v>
       </c>
       <c r="K235" s="4" t="n">
-        <v>52.9</v>
+        <v>51.7</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -36789,7 +36789,7 @@
         <v>6.75</v>
       </c>
       <c r="O336" s="4" t="n">
-        <v>14.67</v>
+        <v>14.68</v>
       </c>
       <c r="P336" s="4" t="n">
         <v>0.72</v>
@@ -36886,7 +36886,7 @@
         </is>
       </c>
       <c r="I337" s="4" t="n">
-        <v>-33.23</v>
+        <v>-33.22</v>
       </c>
       <c r="J337" s="4" t="n">
         <v>0</v>
@@ -36900,13 +36900,13 @@
         </is>
       </c>
       <c r="M337" s="4" t="n">
-        <v>-36.38</v>
+        <v>-36.37</v>
       </c>
       <c r="N337" s="4" t="n">
         <v>6.75</v>
       </c>
       <c r="O337" s="4" t="n">
-        <v>-33.23</v>
+        <v>-33.22</v>
       </c>
       <c r="P337" s="4" t="n">
         <v>0</v>
@@ -37003,7 +37003,7 @@
         </is>
       </c>
       <c r="M338" s="4" t="n">
-        <v>46.7</v>
+        <v>46.71</v>
       </c>
       <c r="N338" s="4" t="n">
         <v>6.75</v>
@@ -37041,10 +37041,10 @@
         <v>0</v>
       </c>
       <c r="AC338" s="4" t="n">
-        <v>77.83</v>
+        <v>77.84</v>
       </c>
       <c r="AD338" s="4" t="n">
-        <v>22.17</v>
+        <v>22.16</v>
       </c>
       <c r="AE338" s="4" t="n">
         <v>0</v>
@@ -37092,7 +37092,7 @@
         </is>
       </c>
       <c r="I339" s="4" t="n">
-        <v>-35.81</v>
+        <v>-35.8</v>
       </c>
       <c r="J339" s="4" t="n">
         <v>0</v>
@@ -37106,13 +37106,13 @@
         </is>
       </c>
       <c r="M339" s="4" t="n">
-        <v>-37.14</v>
+        <v>-37.13</v>
       </c>
       <c r="N339" s="4" t="n">
         <v>6.75</v>
       </c>
       <c r="O339" s="4" t="n">
-        <v>-35.73</v>
+        <v>-35.72</v>
       </c>
       <c r="P339" s="4" t="n">
         <v>-3.26</v>
@@ -37203,7 +37203,7 @@
         </is>
       </c>
       <c r="I340" s="4" t="n">
-        <v>-19.02</v>
+        <v>-19.01</v>
       </c>
       <c r="J340" s="4" t="n">
         <v>0.3</v>
@@ -37314,7 +37314,7 @@
         </is>
       </c>
       <c r="I341" s="4" t="n">
-        <v>-25.71</v>
+        <v>-25.7</v>
       </c>
       <c r="J341" s="4" t="n">
         <v>0.1</v>
@@ -37328,13 +37328,13 @@
         </is>
       </c>
       <c r="M341" s="4" t="n">
-        <v>-28.05</v>
+        <v>-28.04</v>
       </c>
       <c r="N341" s="4" t="n">
         <v>6.75</v>
       </c>
       <c r="O341" s="4" t="n">
-        <v>-25.71</v>
+        <v>-25.7</v>
       </c>
       <c r="P341" s="4" t="n">
         <v>-2.34</v>
@@ -37431,7 +37431,7 @@
         </is>
       </c>
       <c r="M342" s="4" t="n">
-        <v>-5.58</v>
+        <v>-5.57</v>
       </c>
       <c r="N342" s="4" t="n">
         <v>6.75</v>
@@ -37526,13 +37526,13 @@
         </is>
       </c>
       <c r="I343" s="4" t="n">
-        <v>-5.73</v>
+        <v>-5.72</v>
       </c>
       <c r="J343" s="4" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="K343" s="4" t="n">
-        <v>83.40000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="L343" t="inlineStr">
         <is>
@@ -37540,13 +37540,13 @@
         </is>
       </c>
       <c r="M343" s="4" t="n">
-        <v>-10.58</v>
+        <v>-10.57</v>
       </c>
       <c r="N343" s="4" t="n">
         <v>6.75</v>
       </c>
       <c r="O343" s="4" t="n">
-        <v>-5.73</v>
+        <v>-5.72</v>
       </c>
       <c r="P343" s="4" t="n">
         <v>0</v>
@@ -37629,7 +37629,7 @@
         </is>
       </c>
       <c r="I344" s="4" t="n">
-        <v>7.85</v>
+        <v>7.86</v>
       </c>
       <c r="J344" s="4" t="n">
         <v>90.09999999999999</v>
@@ -37649,7 +37649,7 @@
         <v>6.75</v>
       </c>
       <c r="O344" s="4" t="n">
-        <v>14.09</v>
+        <v>14.1</v>
       </c>
       <c r="P344" s="4" t="n">
         <v>0.74</v>
@@ -37738,7 +37738,7 @@
         </is>
       </c>
       <c r="I345" s="4" t="n">
-        <v>-6.08</v>
+        <v>-6.07</v>
       </c>
       <c r="J345" s="4" t="n">
         <v>15.5</v>
@@ -37752,13 +37752,13 @@
         </is>
       </c>
       <c r="M345" s="4" t="n">
-        <v>-2.18</v>
+        <v>-2.17</v>
       </c>
       <c r="N345" s="4" t="n">
         <v>6.75</v>
       </c>
       <c r="O345" s="4" t="n">
-        <v>-6.19</v>
+        <v>-6.18</v>
       </c>
       <c r="P345" s="4" t="n">
         <v>-0.12</v>
@@ -37907,10 +37907,10 @@
         <v>0</v>
       </c>
       <c r="AC346" s="4" t="n">
-        <v>86.78</v>
+        <v>86.79000000000001</v>
       </c>
       <c r="AD346" s="4" t="n">
-        <v>13.22</v>
+        <v>13.21</v>
       </c>
       <c r="AE346" s="4" t="n">
         <v>0</v>
@@ -38061,7 +38061,7 @@
         </is>
       </c>
       <c r="I348" s="4" t="n">
-        <v>21.59</v>
+        <v>21.6</v>
       </c>
       <c r="J348" s="4" t="n">
         <v>99.8</v>
@@ -38081,7 +38081,7 @@
         <v>6.75</v>
       </c>
       <c r="O348" s="4" t="n">
-        <v>21.67</v>
+        <v>21.68</v>
       </c>
       <c r="P348" s="4" t="n">
         <v>2.15</v>
@@ -38121,10 +38121,10 @@
         <v>0</v>
       </c>
       <c r="AC348" s="4" t="n">
-        <v>59.84</v>
+        <v>59.85</v>
       </c>
       <c r="AD348" s="4" t="n">
-        <v>38.59</v>
+        <v>38.58</v>
       </c>
       <c r="AE348" s="4" t="n">
         <v>0</v>
@@ -38172,7 +38172,7 @@
         </is>
       </c>
       <c r="I349" s="4" t="n">
-        <v>-16.94</v>
+        <v>-16.93</v>
       </c>
       <c r="J349" s="4" t="n">
         <v>0.5</v>
@@ -38192,7 +38192,7 @@
         <v>6.75</v>
       </c>
       <c r="O349" s="4" t="n">
-        <v>-16.94</v>
+        <v>-16.93</v>
       </c>
       <c r="P349" s="4" t="n">
         <v>-1.93</v>
@@ -38275,7 +38275,7 @@
         </is>
       </c>
       <c r="I350" s="4" t="n">
-        <v>-2.18</v>
+        <v>-2.17</v>
       </c>
       <c r="J350" s="4" t="n">
         <v>34.7</v>
@@ -38289,13 +38289,13 @@
         </is>
       </c>
       <c r="M350" s="4" t="n">
-        <v>-4.3</v>
+        <v>-4.29</v>
       </c>
       <c r="N350" s="4" t="n">
         <v>6.75</v>
       </c>
       <c r="O350" s="4" t="n">
-        <v>-2.45</v>
+        <v>-2.44</v>
       </c>
       <c r="P350" s="4" t="n">
         <v>-0.9</v>
@@ -43421,7 +43421,7 @@
         </is>
       </c>
       <c r="I398" s="4" t="n">
-        <v>-40.83</v>
+        <v>-40.73</v>
       </c>
       <c r="J398" s="4" t="n">
         <v>0</v>
@@ -43435,13 +43435,13 @@
         </is>
       </c>
       <c r="M398" s="4" t="n">
-        <v>-43.29</v>
+        <v>-43.19</v>
       </c>
       <c r="N398" s="4" t="n">
         <v>6.75</v>
       </c>
       <c r="O398" s="4" t="n">
-        <v>-40.83</v>
+        <v>-40.73</v>
       </c>
       <c r="P398" s="4" t="n">
         <v>-2.58</v>
@@ -43473,10 +43473,10 @@
         <v>0</v>
       </c>
       <c r="AC398" s="4" t="n">
-        <v>29.59</v>
+        <v>29.64</v>
       </c>
       <c r="AD398" s="4" t="n">
-        <v>70.41</v>
+        <v>70.36</v>
       </c>
       <c r="AE398" s="4" t="n">
         <v>0</v>
@@ -43520,13 +43520,13 @@
         </is>
       </c>
       <c r="I399" s="4" t="n">
-        <v>-9.99</v>
+        <v>-9.890000000000001</v>
       </c>
       <c r="J399" s="4" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="K399" s="4" t="n">
-        <v>95.8</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="L399" t="inlineStr">
         <is>
@@ -43534,13 +43534,13 @@
         </is>
       </c>
       <c r="M399" s="4" t="n">
-        <v>-18.09</v>
+        <v>-17.99</v>
       </c>
       <c r="N399" s="4" t="n">
         <v>6.75</v>
       </c>
       <c r="O399" s="4" t="n">
-        <v>-9.99</v>
+        <v>-9.890000000000001</v>
       </c>
       <c r="P399" s="4" t="n">
         <v>0.88</v>
@@ -43572,10 +43572,10 @@
         <v>0</v>
       </c>
       <c r="AC399" s="4" t="n">
-        <v>45</v>
+        <v>45.05</v>
       </c>
       <c r="AD399" s="4" t="n">
-        <v>55</v>
+        <v>54.95</v>
       </c>
       <c r="AE399" s="4" t="n">
         <v>0</v>
@@ -43623,7 +43623,7 @@
         </is>
       </c>
       <c r="I400" s="4" t="n">
-        <v>-13.07</v>
+        <v>-12.97</v>
       </c>
       <c r="J400" s="4" t="n">
         <v>1</v>
@@ -43637,13 +43637,13 @@
         </is>
       </c>
       <c r="M400" s="4" t="n">
-        <v>-17.89</v>
+        <v>-17.79</v>
       </c>
       <c r="N400" s="4" t="n">
         <v>6.75</v>
       </c>
       <c r="O400" s="4" t="n">
-        <v>-13.07</v>
+        <v>-12.97</v>
       </c>
       <c r="P400" s="4" t="n">
         <v>-0.25</v>
@@ -43675,10 +43675,10 @@
         <v>0</v>
       </c>
       <c r="AC400" s="4" t="n">
-        <v>43.46</v>
+        <v>43.51</v>
       </c>
       <c r="AD400" s="4" t="n">
-        <v>56.54</v>
+        <v>56.49</v>
       </c>
       <c r="AE400" s="4" t="n">
         <v>0</v>
@@ -43726,7 +43726,7 @@
         </is>
       </c>
       <c r="I401" s="4" t="n">
-        <v>-18.51</v>
+        <v>-18.41</v>
       </c>
       <c r="J401" s="4" t="n">
         <v>0.3</v>
@@ -43740,13 +43740,13 @@
         </is>
       </c>
       <c r="M401" s="4" t="n">
-        <v>-18.74</v>
+        <v>-18.64</v>
       </c>
       <c r="N401" s="4" t="n">
         <v>6.75</v>
       </c>
       <c r="O401" s="4" t="n">
-        <v>-18.51</v>
+        <v>-18.41</v>
       </c>
       <c r="P401" s="4" t="n">
         <v>-1.91</v>
@@ -43778,10 +43778,10 @@
         <v>0</v>
       </c>
       <c r="AC401" s="4" t="n">
-        <v>40.75</v>
+        <v>40.8</v>
       </c>
       <c r="AD401" s="4" t="n">
-        <v>59.25</v>
+        <v>59.2</v>
       </c>
       <c r="AE401" s="4" t="n">
         <v>0</v>
@@ -43829,7 +43829,7 @@
         </is>
       </c>
       <c r="I402" s="4" t="n">
-        <v>-12.76</v>
+        <v>-12.66</v>
       </c>
       <c r="J402" s="4" t="n">
         <v>1</v>
@@ -43843,13 +43843,13 @@
         </is>
       </c>
       <c r="M402" s="4" t="n">
-        <v>-15.58</v>
+        <v>-15.48</v>
       </c>
       <c r="N402" s="4" t="n">
         <v>6.75</v>
       </c>
       <c r="O402" s="4" t="n">
-        <v>-12.76</v>
+        <v>-12.66</v>
       </c>
       <c r="P402" s="4" t="n">
         <v>-2.33</v>
@@ -43881,10 +43881,10 @@
         <v>0</v>
       </c>
       <c r="AC402" s="4" t="n">
-        <v>43.62</v>
+        <v>43.67</v>
       </c>
       <c r="AD402" s="4" t="n">
-        <v>56.38</v>
+        <v>56.33</v>
       </c>
       <c r="AE402" s="4" t="n">
         <v>0</v>
@@ -43932,7 +43932,7 @@
         </is>
       </c>
       <c r="I403" s="4" t="n">
-        <v>-16.41</v>
+        <v>-16.31</v>
       </c>
       <c r="J403" s="4" t="n">
         <v>0.5</v>
@@ -43946,13 +43946,13 @@
         </is>
       </c>
       <c r="M403" s="4" t="n">
-        <v>-17.66</v>
+        <v>-17.56</v>
       </c>
       <c r="N403" s="4" t="n">
         <v>6.75</v>
       </c>
       <c r="O403" s="4" t="n">
-        <v>-16.41</v>
+        <v>-16.31</v>
       </c>
       <c r="P403" s="4" t="n">
         <v>-2.94</v>
@@ -43984,10 +43984,10 @@
         <v>0</v>
       </c>
       <c r="AC403" s="4" t="n">
-        <v>41.79</v>
+        <v>41.84</v>
       </c>
       <c r="AD403" s="4" t="n">
-        <v>58.21</v>
+        <v>58.16</v>
       </c>
       <c r="AE403" s="4" t="n">
         <v>0</v>
@@ -44035,7 +44035,7 @@
         </is>
       </c>
       <c r="I404" s="4" t="n">
-        <v>42.63</v>
+        <v>42.73</v>
       </c>
       <c r="J404" s="4" t="n">
         <v>100</v>
@@ -44049,13 +44049,13 @@
         </is>
       </c>
       <c r="M404" s="4" t="n">
-        <v>31.67</v>
+        <v>31.77</v>
       </c>
       <c r="N404" s="4" t="n">
         <v>6.75</v>
       </c>
       <c r="O404" s="4" t="n">
-        <v>43.35</v>
+        <v>43.45</v>
       </c>
       <c r="P404" s="4" t="n">
         <v>1.84</v>
@@ -44095,10 +44095,10 @@
         <v>0</v>
       </c>
       <c r="AC404" s="4" t="n">
-        <v>69.25</v>
+        <v>69.3</v>
       </c>
       <c r="AD404" s="4" t="n">
-        <v>27.86</v>
+        <v>27.81</v>
       </c>
       <c r="AE404" s="4" t="n">
         <v>0</v>
@@ -44142,7 +44142,7 @@
         </is>
       </c>
       <c r="I405" s="4" t="n">
-        <v>-15.5</v>
+        <v>-15.4</v>
       </c>
       <c r="J405" s="4" t="n">
         <v>0.6</v>
@@ -44156,13 +44156,13 @@
         </is>
       </c>
       <c r="M405" s="4" t="n">
-        <v>-20.37</v>
+        <v>-20.27</v>
       </c>
       <c r="N405" s="4" t="n">
         <v>6.75</v>
       </c>
       <c r="O405" s="4" t="n">
-        <v>-15.5</v>
+        <v>-15.4</v>
       </c>
       <c r="P405" s="4" t="n">
         <v>-2.72</v>
@@ -44194,10 +44194,10 @@
         <v>0</v>
       </c>
       <c r="AC405" s="4" t="n">
-        <v>42.25</v>
+        <v>42.3</v>
       </c>
       <c r="AD405" s="4" t="n">
-        <v>57.75</v>
+        <v>57.7</v>
       </c>
       <c r="AE405" s="4" t="n">
         <v>0</v>
@@ -44241,13 +44241,13 @@
         </is>
       </c>
       <c r="I406" s="4" t="n">
-        <v>-6.22</v>
+        <v>-6.17</v>
       </c>
       <c r="J406" s="4" t="n">
-        <v>15</v>
+        <v>15.2</v>
       </c>
       <c r="K406" s="4" t="n">
-        <v>85</v>
+        <v>84.8</v>
       </c>
       <c r="L406" t="inlineStr">
         <is>
@@ -44255,13 +44255,13 @@
         </is>
       </c>
       <c r="M406" s="4" t="n">
-        <v>-11.34</v>
+        <v>-11.24</v>
       </c>
       <c r="N406" s="4" t="n">
         <v>6.75</v>
       </c>
       <c r="O406" s="4" t="n">
-        <v>-4.29</v>
+        <v>-4.19</v>
       </c>
       <c r="P406" s="4" t="n">
         <v>-1.88</v>
@@ -44299,10 +44299,10 @@
         <v>0</v>
       </c>
       <c r="AC406" s="4" t="n">
-        <v>46.89</v>
+        <v>46.92</v>
       </c>
       <c r="AD406" s="4" t="n">
-        <v>53.11</v>
+        <v>53.08</v>
       </c>
       <c r="AE406" s="4" t="n">
         <v>0</v>
@@ -44346,13 +44346,13 @@
         </is>
       </c>
       <c r="I407" s="4" t="n">
-        <v>-10.28</v>
+        <v>-10.23</v>
       </c>
       <c r="J407" s="4" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K407" s="4" t="n">
-        <v>96.5</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="L407" t="inlineStr">
         <is>
@@ -44360,13 +44360,13 @@
         </is>
       </c>
       <c r="M407" s="4" t="n">
-        <v>-16.02</v>
+        <v>-15.92</v>
       </c>
       <c r="N407" s="4" t="n">
         <v>6.75</v>
       </c>
       <c r="O407" s="4" t="n">
-        <v>-10.72</v>
+        <v>-10.62</v>
       </c>
       <c r="P407" s="4" t="n">
         <v>-1.52</v>
@@ -44404,10 +44404,10 @@
         <v>0</v>
       </c>
       <c r="AC407" s="4" t="n">
-        <v>44.86</v>
+        <v>44.89</v>
       </c>
       <c r="AD407" s="4" t="n">
-        <v>55.14</v>
+        <v>55.11</v>
       </c>
       <c r="AE407" s="4" t="n">
         <v>0</v>
@@ -44455,7 +44455,7 @@
         </is>
       </c>
       <c r="I408" s="4" t="n">
-        <v>-25.08</v>
+        <v>-24.98</v>
       </c>
       <c r="J408" s="4" t="n">
         <v>0.1</v>
@@ -44469,13 +44469,13 @@
         </is>
       </c>
       <c r="M408" s="4" t="n">
-        <v>-28.71</v>
+        <v>-28.61</v>
       </c>
       <c r="N408" s="4" t="n">
         <v>6.75</v>
       </c>
       <c r="O408" s="4" t="n">
-        <v>-25.08</v>
+        <v>-24.98</v>
       </c>
       <c r="P408" s="4" t="n">
         <v>-2.36</v>
@@ -44507,10 +44507,10 @@
         <v>0</v>
       </c>
       <c r="AC408" s="4" t="n">
-        <v>37.46</v>
+        <v>37.51</v>
       </c>
       <c r="AD408" s="4" t="n">
-        <v>62.54</v>
+        <v>62.49</v>
       </c>
       <c r="AE408" s="4" t="n">
         <v>0</v>
@@ -44558,7 +44558,7 @@
         </is>
       </c>
       <c r="I409" s="4" t="n">
-        <v>-16.44</v>
+        <v>-16.34</v>
       </c>
       <c r="J409" s="4" t="n">
         <v>0.5</v>
@@ -44572,13 +44572,13 @@
         </is>
       </c>
       <c r="M409" s="4" t="n">
-        <v>-17.66</v>
+        <v>-17.56</v>
       </c>
       <c r="N409" s="4" t="n">
         <v>6.75</v>
       </c>
       <c r="O409" s="4" t="n">
-        <v>-16.44</v>
+        <v>-16.34</v>
       </c>
       <c r="P409" s="4" t="n">
         <v>0</v>
@@ -44610,10 +44610,10 @@
         <v>0</v>
       </c>
       <c r="AC409" s="4" t="n">
-        <v>41.78</v>
+        <v>41.83</v>
       </c>
       <c r="AD409" s="4" t="n">
-        <v>58.22</v>
+        <v>58.17</v>
       </c>
       <c r="AE409" s="4" t="n">
         <v>0</v>
@@ -44661,7 +44661,7 @@
         </is>
       </c>
       <c r="I410" s="4" t="n">
-        <v>-38.37</v>
+        <v>-38.27</v>
       </c>
       <c r="J410" s="4" t="n">
         <v>0</v>
@@ -44675,13 +44675,13 @@
         </is>
       </c>
       <c r="M410" s="4" t="n">
-        <v>-41.31</v>
+        <v>-41.21</v>
       </c>
       <c r="N410" s="4" t="n">
         <v>6.75</v>
       </c>
       <c r="O410" s="4" t="n">
-        <v>-38.37</v>
+        <v>-38.27</v>
       </c>
       <c r="P410" s="4" t="n">
         <v>-2.47</v>
@@ -44713,10 +44713,10 @@
         <v>0</v>
       </c>
       <c r="AC410" s="4" t="n">
-        <v>30.82</v>
+        <v>30.87</v>
       </c>
       <c r="AD410" s="4" t="n">
-        <v>69.18000000000001</v>
+        <v>69.13</v>
       </c>
       <c r="AE410" s="4" t="n">
         <v>0</v>
@@ -44764,7 +44764,7 @@
         </is>
       </c>
       <c r="I411" s="4" t="n">
-        <v>-17.36</v>
+        <v>-17.26</v>
       </c>
       <c r="J411" s="4" t="n">
         <v>0.4</v>
@@ -44778,13 +44778,13 @@
         </is>
       </c>
       <c r="M411" s="4" t="n">
-        <v>-18.72</v>
+        <v>-18.62</v>
       </c>
       <c r="N411" s="4" t="n">
         <v>6.75</v>
       </c>
       <c r="O411" s="4" t="n">
-        <v>-17.36</v>
+        <v>-17.26</v>
       </c>
       <c r="P411" s="4" t="n">
         <v>-1.94</v>
@@ -44816,10 +44816,10 @@
         <v>0</v>
       </c>
       <c r="AC411" s="4" t="n">
-        <v>41.32</v>
+        <v>41.37</v>
       </c>
       <c r="AD411" s="4" t="n">
-        <v>58.68</v>
+        <v>58.63</v>
       </c>
       <c r="AE411" s="4" t="n">
         <v>0</v>
@@ -44867,13 +44867,13 @@
         </is>
       </c>
       <c r="I412" s="4" t="n">
-        <v>3.78</v>
+        <v>3.84</v>
       </c>
       <c r="J412" s="4" t="n">
-        <v>76.2</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="K412" s="4" t="n">
-        <v>23.8</v>
+        <v>23.4</v>
       </c>
       <c r="L412" t="inlineStr">
         <is>
@@ -44881,13 +44881,13 @@
         </is>
       </c>
       <c r="M412" s="4" t="n">
-        <v>-7.41</v>
+        <v>-7.31</v>
       </c>
       <c r="N412" s="4" t="n">
         <v>6.75</v>
       </c>
       <c r="O412" s="4" t="n">
-        <v>0.87</v>
+        <v>0.97</v>
       </c>
       <c r="P412" s="4" t="n">
         <v>-0.22</v>
@@ -44925,10 +44925,10 @@
         <v>0</v>
       </c>
       <c r="AC412" s="4" t="n">
-        <v>51.89</v>
+        <v>51.92</v>
       </c>
       <c r="AD412" s="4" t="n">
-        <v>48.11</v>
+        <v>48.08</v>
       </c>
       <c r="AE412" s="4" t="n">
         <v>0</v>
@@ -44976,7 +44976,7 @@
         </is>
       </c>
       <c r="I413" s="4" t="n">
-        <v>38.89</v>
+        <v>38.99</v>
       </c>
       <c r="J413" s="4" t="n">
         <v>100</v>
@@ -44990,13 +44990,13 @@
         </is>
       </c>
       <c r="M413" s="4" t="n">
-        <v>27.64</v>
+        <v>27.74</v>
       </c>
       <c r="N413" s="4" t="n">
         <v>6.75</v>
       </c>
       <c r="O413" s="4" t="n">
-        <v>38.89</v>
+        <v>38.99</v>
       </c>
       <c r="P413" s="4" t="n">
         <v>0</v>
@@ -45028,10 +45028,10 @@
         <v>0</v>
       </c>
       <c r="AC413" s="4" t="n">
-        <v>69.45</v>
+        <v>69.5</v>
       </c>
       <c r="AD413" s="4" t="n">
-        <v>30.55</v>
+        <v>30.5</v>
       </c>
       <c r="AE413" s="4" t="n">
         <v>0</v>
@@ -45079,7 +45079,7 @@
         </is>
       </c>
       <c r="I414" s="4" t="n">
-        <v>-14.7</v>
+        <v>-14.6</v>
       </c>
       <c r="J414" s="4" t="n">
         <v>0.7</v>
@@ -45093,13 +45093,13 @@
         </is>
       </c>
       <c r="M414" s="4" t="n">
-        <v>-15.49</v>
+        <v>-15.39</v>
       </c>
       <c r="N414" s="4" t="n">
         <v>6.75</v>
       </c>
       <c r="O414" s="4" t="n">
-        <v>-14.7</v>
+        <v>-14.6</v>
       </c>
       <c r="P414" s="4" t="n">
         <v>-2.2</v>
@@ -45131,10 +45131,10 @@
         <v>0</v>
       </c>
       <c r="AC414" s="4" t="n">
-        <v>42.65</v>
+        <v>42.7</v>
       </c>
       <c r="AD414" s="4" t="n">
-        <v>57.35</v>
+        <v>57.3</v>
       </c>
       <c r="AE414" s="4" t="n">
         <v>0</v>
@@ -45182,7 +45182,7 @@
         </is>
       </c>
       <c r="I415" s="4" t="n">
-        <v>73.43000000000001</v>
+        <v>73.53</v>
       </c>
       <c r="J415" s="4" t="n">
         <v>100</v>
@@ -45196,13 +45196,13 @@
         </is>
       </c>
       <c r="M415" s="4" t="n">
-        <v>63.73</v>
+        <v>63.83</v>
       </c>
       <c r="N415" s="4" t="n">
         <v>6.75</v>
       </c>
       <c r="O415" s="4" t="n">
-        <v>73.43000000000001</v>
+        <v>73.53</v>
       </c>
       <c r="P415" s="4" t="n">
         <v>0</v>
@@ -45234,10 +45234,10 @@
         <v>0</v>
       </c>
       <c r="AC415" s="4" t="n">
-        <v>86.70999999999999</v>
+        <v>86.76000000000001</v>
       </c>
       <c r="AD415" s="4" t="n">
-        <v>13.29</v>
+        <v>13.24</v>
       </c>
       <c r="AE415" s="4" t="n">
         <v>0</v>
@@ -45281,7 +45281,7 @@
         </is>
       </c>
       <c r="I416" s="4" t="n">
-        <v>-40.43</v>
+        <v>-40.33</v>
       </c>
       <c r="J416" s="4" t="n">
         <v>0</v>
@@ -45295,13 +45295,13 @@
         </is>
       </c>
       <c r="M416" s="4" t="n">
-        <v>-45.67</v>
+        <v>-45.57</v>
       </c>
       <c r="N416" s="4" t="n">
         <v>6.75</v>
       </c>
       <c r="O416" s="4" t="n">
-        <v>-40.43</v>
+        <v>-40.33</v>
       </c>
       <c r="P416" s="4" t="n">
         <v>-2.39</v>
@@ -45333,10 +45333,10 @@
         <v>0</v>
       </c>
       <c r="AC416" s="4" t="n">
-        <v>29.79</v>
+        <v>29.84</v>
       </c>
       <c r="AD416" s="4" t="n">
-        <v>70.20999999999999</v>
+        <v>70.16</v>
       </c>
       <c r="AE416" s="4" t="n">
         <v>0</v>
@@ -45384,7 +45384,7 @@
         </is>
       </c>
       <c r="I417" s="4" t="n">
-        <v>51.57</v>
+        <v>51.67</v>
       </c>
       <c r="J417" s="4" t="n">
         <v>100</v>
@@ -45398,13 +45398,13 @@
         </is>
       </c>
       <c r="M417" s="4" t="n">
-        <v>37.48</v>
+        <v>37.58</v>
       </c>
       <c r="N417" s="4" t="n">
         <v>6.75</v>
       </c>
       <c r="O417" s="4" t="n">
-        <v>51.57</v>
+        <v>51.67</v>
       </c>
       <c r="P417" s="4" t="n">
         <v>1.31</v>
@@ -45436,10 +45436,10 @@
         <v>0</v>
       </c>
       <c r="AC417" s="4" t="n">
-        <v>75.78</v>
+        <v>75.83</v>
       </c>
       <c r="AD417" s="4" t="n">
-        <v>24.22</v>
+        <v>24.17</v>
       </c>
       <c r="AE417" s="4" t="n">
         <v>0</v>
@@ -45483,13 +45483,13 @@
         </is>
       </c>
       <c r="I418" s="4" t="n">
-        <v>-9.949999999999999</v>
+        <v>-9.85</v>
       </c>
       <c r="J418" s="4" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="K418" s="4" t="n">
-        <v>95.7</v>
+        <v>95.5</v>
       </c>
       <c r="L418" t="inlineStr">
         <is>
@@ -45497,13 +45497,13 @@
         </is>
       </c>
       <c r="M418" s="4" t="n">
-        <v>-16</v>
+        <v>-15.9</v>
       </c>
       <c r="N418" s="4" t="n">
         <v>6.75</v>
       </c>
       <c r="O418" s="4" t="n">
-        <v>-9.949999999999999</v>
+        <v>-9.85</v>
       </c>
       <c r="P418" s="4" t="n">
         <v>-2.02</v>
@@ -45535,10 +45535,10 @@
         <v>0</v>
       </c>
       <c r="AC418" s="4" t="n">
-        <v>45.03</v>
+        <v>45.08</v>
       </c>
       <c r="AD418" s="4" t="n">
-        <v>54.97</v>
+        <v>54.92</v>
       </c>
       <c r="AE418" s="4" t="n">
         <v>0</v>
@@ -45582,13 +45582,13 @@
         </is>
       </c>
       <c r="I419" s="4" t="n">
-        <v>-10.7</v>
+        <v>-10.6</v>
       </c>
       <c r="J419" s="4" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="K419" s="4" t="n">
-        <v>97.5</v>
+        <v>97.3</v>
       </c>
       <c r="L419" t="inlineStr">
         <is>
@@ -45596,13 +45596,13 @@
         </is>
       </c>
       <c r="M419" s="4" t="n">
-        <v>-16.58</v>
+        <v>-16.48</v>
       </c>
       <c r="N419" s="4" t="n">
         <v>6.75</v>
       </c>
       <c r="O419" s="4" t="n">
-        <v>-10.7</v>
+        <v>-10.6</v>
       </c>
       <c r="P419" s="4" t="n">
         <v>-0.8100000000000001</v>
@@ -45634,10 +45634,10 @@
         <v>0</v>
       </c>
       <c r="AC419" s="4" t="n">
-        <v>44.65</v>
+        <v>44.7</v>
       </c>
       <c r="AD419" s="4" t="n">
-        <v>55.35</v>
+        <v>55.3</v>
       </c>
       <c r="AE419" s="4" t="n">
         <v>0</v>
@@ -45681,13 +45681,13 @@
         </is>
       </c>
       <c r="I420" s="4" t="n">
-        <v>-0.11</v>
+        <v>-0.03</v>
       </c>
       <c r="J420" s="4" t="n">
-        <v>49.2</v>
+        <v>49.8</v>
       </c>
       <c r="K420" s="4" t="n">
-        <v>50.8</v>
+        <v>50.2</v>
       </c>
       <c r="L420" t="inlineStr">
         <is>
@@ -45695,13 +45695,13 @@
         </is>
       </c>
       <c r="M420" s="4" t="n">
-        <v>-7.58</v>
+        <v>-7.48</v>
       </c>
       <c r="N420" s="4" t="n">
         <v>6.75</v>
       </c>
       <c r="O420" s="4" t="n">
-        <v>0.37</v>
+        <v>0.47</v>
       </c>
       <c r="P420" s="4" t="n">
         <v>-0.84</v>
@@ -45747,10 +45747,10 @@
         <v>0</v>
       </c>
       <c r="AC420" s="4" t="n">
-        <v>49.01</v>
+        <v>49.06</v>
       </c>
       <c r="AD420" s="4" t="n">
-        <v>49.13</v>
+        <v>49.08</v>
       </c>
       <c r="AE420" s="4" t="n">
         <v>0</v>
@@ -45798,13 +45798,13 @@
         </is>
       </c>
       <c r="I421" s="4" t="n">
-        <v>-10.36</v>
+        <v>-10.26</v>
       </c>
       <c r="J421" s="4" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="K421" s="4" t="n">
-        <v>96.7</v>
+        <v>96.5</v>
       </c>
       <c r="L421" t="inlineStr">
         <is>
@@ -45812,13 +45812,13 @@
         </is>
       </c>
       <c r="M421" s="4" t="n">
-        <v>-10.91</v>
+        <v>-10.81</v>
       </c>
       <c r="N421" s="4" t="n">
         <v>6.75</v>
       </c>
       <c r="O421" s="4" t="n">
-        <v>-10.36</v>
+        <v>-10.26</v>
       </c>
       <c r="P421" s="4" t="n">
         <v>-1.72</v>
@@ -45850,10 +45850,10 @@
         <v>0</v>
       </c>
       <c r="AC421" s="4" t="n">
-        <v>44.82</v>
+        <v>44.87</v>
       </c>
       <c r="AD421" s="4" t="n">
-        <v>55.18</v>
+        <v>55.13</v>
       </c>
       <c r="AE421" s="4" t="n">
         <v>0</v>
@@ -45901,13 +45901,13 @@
         </is>
       </c>
       <c r="I422" s="4" t="n">
-        <v>-11.58</v>
+        <v>-11.48</v>
       </c>
       <c r="J422" s="4" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="K422" s="4" t="n">
-        <v>98.8</v>
+        <v>98.7</v>
       </c>
       <c r="L422" t="inlineStr">
         <is>
@@ -45915,13 +45915,13 @@
         </is>
       </c>
       <c r="M422" s="4" t="n">
-        <v>-17.14</v>
+        <v>-17.04</v>
       </c>
       <c r="N422" s="4" t="n">
         <v>6.75</v>
       </c>
       <c r="O422" s="4" t="n">
-        <v>-11.58</v>
+        <v>-11.48</v>
       </c>
       <c r="P422" s="4" t="n">
         <v>0</v>
@@ -45953,10 +45953,10 @@
         <v>0</v>
       </c>
       <c r="AC422" s="4" t="n">
-        <v>44.21</v>
+        <v>44.26</v>
       </c>
       <c r="AD422" s="4" t="n">
-        <v>55.79</v>
+        <v>55.74</v>
       </c>
       <c r="AE422" s="4" t="n">
         <v>0</v>
@@ -46004,7 +46004,7 @@
         </is>
       </c>
       <c r="I423" s="4" t="n">
-        <v>-19.92</v>
+        <v>-19.82</v>
       </c>
       <c r="J423" s="4" t="n">
         <v>0.2</v>
@@ -46018,13 +46018,13 @@
         </is>
       </c>
       <c r="M423" s="4" t="n">
-        <v>-18.26</v>
+        <v>-18.16</v>
       </c>
       <c r="N423" s="4" t="n">
         <v>6.75</v>
       </c>
       <c r="O423" s="4" t="n">
-        <v>-20.31</v>
+        <v>-20.21</v>
       </c>
       <c r="P423" s="4" t="n">
         <v>-3.11</v>
@@ -46064,10 +46064,10 @@
         <v>0</v>
       </c>
       <c r="AC423" s="4" t="n">
-        <v>39.25</v>
+        <v>39.3</v>
       </c>
       <c r="AD423" s="4" t="n">
-        <v>58.77</v>
+        <v>58.72</v>
       </c>
       <c r="AE423" s="4" t="n">
         <v>0</v>
@@ -46115,13 +46115,13 @@
         </is>
       </c>
       <c r="I424" s="4" t="n">
-        <v>-11.58</v>
+        <v>-11.48</v>
       </c>
       <c r="J424" s="4" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="K424" s="4" t="n">
-        <v>98.8</v>
+        <v>98.7</v>
       </c>
       <c r="L424" t="inlineStr">
         <is>
@@ -46129,13 +46129,13 @@
         </is>
       </c>
       <c r="M424" s="4" t="n">
-        <v>-15.5</v>
+        <v>-15.4</v>
       </c>
       <c r="N424" s="4" t="n">
         <v>6.75</v>
       </c>
       <c r="O424" s="4" t="n">
-        <v>-11.58</v>
+        <v>-11.48</v>
       </c>
       <c r="P424" s="4" t="n">
         <v>-1.33</v>
@@ -46167,10 +46167,10 @@
         <v>0</v>
       </c>
       <c r="AC424" s="4" t="n">
-        <v>44.21</v>
+        <v>44.26</v>
       </c>
       <c r="AD424" s="4" t="n">
-        <v>55.79</v>
+        <v>55.74</v>
       </c>
       <c r="AE424" s="4" t="n">
         <v>0</v>
@@ -46218,13 +46218,13 @@
         </is>
       </c>
       <c r="I425" s="4" t="n">
-        <v>18.1</v>
+        <v>18.17</v>
       </c>
       <c r="J425" s="4" t="n">
-        <v>99.59999999999999</v>
+        <v>99.7</v>
       </c>
       <c r="K425" s="4" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="L425" t="inlineStr">
         <is>
@@ -46232,13 +46232,13 @@
         </is>
       </c>
       <c r="M425" s="4" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="N425" s="4" t="n">
         <v>6.75</v>
       </c>
       <c r="O425" s="4" t="n">
-        <v>22.56</v>
+        <v>22.66</v>
       </c>
       <c r="P425" s="4" t="n">
         <v>0.45</v>
@@ -46284,10 +46284,10 @@
         <v>0</v>
       </c>
       <c r="AC425" s="4" t="n">
-        <v>55.95</v>
+        <v>55.98</v>
       </c>
       <c r="AD425" s="4" t="n">
-        <v>38.8</v>
+        <v>38.77</v>
       </c>
       <c r="AE425" s="4" t="n">
         <v>0</v>
@@ -46335,7 +46335,7 @@
         </is>
       </c>
       <c r="I426" s="4" t="n">
-        <v>56.36</v>
+        <v>56.46</v>
       </c>
       <c r="J426" s="4" t="n">
         <v>100</v>
@@ -46349,13 +46349,13 @@
         </is>
       </c>
       <c r="M426" s="4" t="n">
-        <v>40</v>
+        <v>40.1</v>
       </c>
       <c r="N426" s="4" t="n">
         <v>6.75</v>
       </c>
       <c r="O426" s="4" t="n">
-        <v>56.36</v>
+        <v>56.46</v>
       </c>
       <c r="P426" s="4" t="n">
         <v>0</v>
@@ -46387,10 +46387,10 @@
         <v>0</v>
       </c>
       <c r="AC426" s="4" t="n">
-        <v>78.18000000000001</v>
+        <v>78.23</v>
       </c>
       <c r="AD426" s="4" t="n">
-        <v>21.82</v>
+        <v>21.77</v>
       </c>
       <c r="AE426" s="4" t="n">
         <v>0</v>
@@ -46434,7 +46434,7 @@
         </is>
       </c>
       <c r="I427" s="4" t="n">
-        <v>65.33</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="J427" s="4" t="n">
         <v>100</v>
@@ -46448,13 +46448,13 @@
         </is>
       </c>
       <c r="M427" s="4" t="n">
-        <v>55.71</v>
+        <v>55.81</v>
       </c>
       <c r="N427" s="4" t="n">
         <v>6.75</v>
       </c>
       <c r="O427" s="4" t="n">
-        <v>65.33</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="P427" s="4" t="n">
         <v>1.56</v>
@@ -46486,10 +46486,10 @@
         <v>0</v>
       </c>
       <c r="AC427" s="4" t="n">
-        <v>82.66</v>
+        <v>82.70999999999999</v>
       </c>
       <c r="AD427" s="4" t="n">
-        <v>17.34</v>
+        <v>17.29</v>
       </c>
       <c r="AE427" s="4" t="n">
         <v>0</v>
@@ -46537,7 +46537,7 @@
         </is>
       </c>
       <c r="I428" s="4" t="n">
-        <v>-16.46</v>
+        <v>-16.36</v>
       </c>
       <c r="J428" s="4" t="n">
         <v>0.5</v>
@@ -46551,13 +46551,13 @@
         </is>
       </c>
       <c r="M428" s="4" t="n">
-        <v>-16.42</v>
+        <v>-16.32</v>
       </c>
       <c r="N428" s="4" t="n">
         <v>6.75</v>
       </c>
       <c r="O428" s="4" t="n">
-        <v>-15.87</v>
+        <v>-15.77</v>
       </c>
       <c r="P428" s="4" t="n">
         <v>-1.61</v>
@@ -46597,10 +46597,10 @@
         <v>0</v>
       </c>
       <c r="AC428" s="4" t="n">
-        <v>40.79</v>
+        <v>40.84</v>
       </c>
       <c r="AD428" s="4" t="n">
-        <v>56.87</v>
+        <v>56.82</v>
       </c>
       <c r="AE428" s="4" t="n">
         <v>0</v>
@@ -46644,13 +46644,13 @@
         </is>
       </c>
       <c r="I429" s="4" t="n">
-        <v>-5.96</v>
+        <v>-5.86</v>
       </c>
       <c r="J429" s="4" t="n">
-        <v>15.8</v>
+        <v>16.2</v>
       </c>
       <c r="K429" s="4" t="n">
-        <v>84.2</v>
+        <v>83.8</v>
       </c>
       <c r="L429" t="inlineStr">
         <is>
@@ -46658,13 +46658,13 @@
         </is>
       </c>
       <c r="M429" s="4" t="n">
-        <v>-11.27</v>
+        <v>-11.17</v>
       </c>
       <c r="N429" s="4" t="n">
         <v>6.75</v>
       </c>
       <c r="O429" s="4" t="n">
-        <v>-5.96</v>
+        <v>-5.86</v>
       </c>
       <c r="P429" s="4" t="n">
         <v>-1.71</v>
@@ -46696,10 +46696,10 @@
         <v>0</v>
       </c>
       <c r="AC429" s="4" t="n">
-        <v>47.02</v>
+        <v>47.07</v>
       </c>
       <c r="AD429" s="4" t="n">
-        <v>52.98</v>
+        <v>52.93</v>
       </c>
       <c r="AE429" s="4" t="n">
         <v>0</v>
@@ -46743,7 +46743,7 @@
         </is>
       </c>
       <c r="I430" s="4" t="n">
-        <v>48.45</v>
+        <v>48.55</v>
       </c>
       <c r="J430" s="4" t="n">
         <v>100</v>
@@ -46757,13 +46757,13 @@
         </is>
       </c>
       <c r="M430" s="4" t="n">
-        <v>41.87</v>
+        <v>41.97</v>
       </c>
       <c r="N430" s="4" t="n">
         <v>6.75</v>
       </c>
       <c r="O430" s="4" t="n">
-        <v>48.45</v>
+        <v>48.55</v>
       </c>
       <c r="P430" s="4" t="n">
         <v>0</v>
@@ -46795,10 +46795,10 @@
         <v>0</v>
       </c>
       <c r="AC430" s="4" t="n">
-        <v>74.22</v>
+        <v>74.27</v>
       </c>
       <c r="AD430" s="4" t="n">
-        <v>25.78</v>
+        <v>25.73</v>
       </c>
       <c r="AE430" s="4" t="n">
         <v>0</v>
@@ -46846,13 +46846,13 @@
         </is>
       </c>
       <c r="I431" s="4" t="n">
-        <v>11.16</v>
+        <v>11.23</v>
       </c>
       <c r="J431" s="4" t="n">
-        <v>98.5</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="K431" s="4" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="L431" t="inlineStr">
         <is>
@@ -46860,13 +46860,13 @@
         </is>
       </c>
       <c r="M431" s="4" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.59</v>
       </c>
       <c r="N431" s="4" t="n">
         <v>6.75</v>
       </c>
       <c r="O431" s="4" t="n">
-        <v>13.74</v>
+        <v>13.84</v>
       </c>
       <c r="P431" s="4" t="n">
         <v>0.36</v>
@@ -46912,10 +46912,10 @@
         <v>0</v>
       </c>
       <c r="AC431" s="4" t="n">
-        <v>53.17</v>
+        <v>53.21</v>
       </c>
       <c r="AD431" s="4" t="n">
-        <v>42.5</v>
+        <v>42.46</v>
       </c>
       <c r="AE431" s="4" t="n">
         <v>1.53</v>
@@ -46959,13 +46959,13 @@
         </is>
       </c>
       <c r="I432" s="4" t="n">
-        <v>2.67</v>
+        <v>2.74</v>
       </c>
       <c r="J432" s="4" t="n">
-        <v>68.7</v>
+        <v>69.2</v>
       </c>
       <c r="K432" s="4" t="n">
-        <v>31.3</v>
+        <v>30.8</v>
       </c>
       <c r="L432" t="inlineStr">
         <is>
@@ -46973,13 +46973,13 @@
         </is>
       </c>
       <c r="M432" s="4" t="n">
-        <v>-3.18</v>
+        <v>-3.08</v>
       </c>
       <c r="N432" s="4" t="n">
         <v>6.75</v>
       </c>
       <c r="O432" s="4" t="n">
-        <v>5.23</v>
+        <v>5.33</v>
       </c>
       <c r="P432" s="4" t="n">
         <v>-0.22</v>
@@ -47017,10 +47017,10 @@
         <v>0</v>
       </c>
       <c r="AC432" s="4" t="n">
-        <v>51.33</v>
+        <v>51.37</v>
       </c>
       <c r="AD432" s="4" t="n">
-        <v>48.67</v>
+        <v>48.63</v>
       </c>
       <c r="AE432" s="4" t="n">
         <v>0</v>
@@ -47068,7 +47068,7 @@
         </is>
       </c>
       <c r="I433" s="4" t="n">
-        <v>-13.64</v>
+        <v>-13.54</v>
       </c>
       <c r="J433" s="4" t="n">
         <v>0.9</v>
@@ -47082,13 +47082,13 @@
         </is>
       </c>
       <c r="M433" s="4" t="n">
-        <v>-18.3</v>
+        <v>-18.2</v>
       </c>
       <c r="N433" s="4" t="n">
         <v>6.75</v>
       </c>
       <c r="O433" s="4" t="n">
-        <v>-13.64</v>
+        <v>-13.54</v>
       </c>
       <c r="P433" s="4" t="n">
         <v>0</v>
@@ -47120,10 +47120,10 @@
         <v>0</v>
       </c>
       <c r="AC433" s="4" t="n">
-        <v>43.18</v>
+        <v>43.23</v>
       </c>
       <c r="AD433" s="4" t="n">
-        <v>56.82</v>
+        <v>56.77</v>
       </c>
       <c r="AE433" s="4" t="n">
         <v>0</v>
@@ -47171,7 +47171,7 @@
         </is>
       </c>
       <c r="I434" s="4" t="n">
-        <v>73.51000000000001</v>
+        <v>73.61</v>
       </c>
       <c r="J434" s="4" t="n">
         <v>100</v>
@@ -47185,13 +47185,13 @@
         </is>
       </c>
       <c r="M434" s="4" t="n">
-        <v>64.48999999999999</v>
+        <v>64.59</v>
       </c>
       <c r="N434" s="4" t="n">
         <v>6.75</v>
       </c>
       <c r="O434" s="4" t="n">
-        <v>73.51000000000001</v>
+        <v>73.61</v>
       </c>
       <c r="P434" s="4" t="n">
         <v>1.49</v>
@@ -47223,10 +47223,10 @@
         <v>0</v>
       </c>
       <c r="AC434" s="4" t="n">
-        <v>86.76000000000001</v>
+        <v>86.81</v>
       </c>
       <c r="AD434" s="4" t="n">
-        <v>13.24</v>
+        <v>13.19</v>
       </c>
       <c r="AE434" s="4" t="n">
         <v>0</v>
@@ -47270,7 +47270,7 @@
         </is>
       </c>
       <c r="I435" s="4" t="n">
-        <v>-11.72</v>
+        <v>-11.62</v>
       </c>
       <c r="J435" s="4" t="n">
         <v>1.2</v>
@@ -47284,13 +47284,13 @@
         </is>
       </c>
       <c r="M435" s="4" t="n">
-        <v>-15.74</v>
+        <v>-15.64</v>
       </c>
       <c r="N435" s="4" t="n">
         <v>6.75</v>
       </c>
       <c r="O435" s="4" t="n">
-        <v>-11.17</v>
+        <v>-11.07</v>
       </c>
       <c r="P435" s="4" t="n">
         <v>-2.01</v>
@@ -47330,10 +47330,10 @@
         <v>0</v>
       </c>
       <c r="AC435" s="4" t="n">
-        <v>43.18</v>
+        <v>43.23</v>
       </c>
       <c r="AD435" s="4" t="n">
-        <v>54.64</v>
+        <v>54.59</v>
       </c>
       <c r="AE435" s="4" t="n">
         <v>0</v>
@@ -51404,27 +51404,27 @@
         </is>
       </c>
       <c r="I473" s="4" t="n">
-        <v>3.01</v>
+        <v>3.28</v>
       </c>
       <c r="J473" s="4" t="n">
-        <v>72.3</v>
+        <v>75</v>
       </c>
       <c r="K473" s="4" t="n">
-        <v>27.7</v>
+        <v>25</v>
       </c>
       <c r="L473" t="inlineStr">
         <is>
-          <t>Lean D</t>
+          <t>Likely D</t>
         </is>
       </c>
       <c r="M473" s="4" t="n">
-        <v>-10.71</v>
+        <v>-10.09</v>
       </c>
       <c r="N473" s="4" t="n">
         <v>6.75</v>
       </c>
       <c r="O473" s="4" t="n">
-        <v>-0.66</v>
+        <v>-0.03</v>
       </c>
       <c r="P473" s="4" t="n">
         <v>0.26</v>
@@ -51462,10 +51462,10 @@
         <v>0</v>
       </c>
       <c r="AC473" s="4" t="n">
-        <v>49.83</v>
+        <v>49.96</v>
       </c>
       <c r="AD473" s="4" t="n">
-        <v>47.67</v>
+        <v>47.54</v>
       </c>
       <c r="AE473" s="4" t="n">
         <v>2.5</v>
@@ -52171,13 +52171,13 @@
         </is>
       </c>
       <c r="I480" s="4" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="J480" s="4" t="n">
-        <v>59.5</v>
+        <v>59.6</v>
       </c>
       <c r="K480" s="4" t="n">
-        <v>40.5</v>
+        <v>40.4</v>
       </c>
       <c r="L480" t="inlineStr">
         <is>
@@ -52185,13 +52185,13 @@
         </is>
       </c>
       <c r="M480" s="4" t="n">
-        <v>-6.56</v>
+        <v>-6.52</v>
       </c>
       <c r="N480" s="4" t="n">
         <v>6.75</v>
       </c>
       <c r="O480" s="4" t="n">
-        <v>-1.67</v>
+        <v>-1.63</v>
       </c>
       <c r="P480" s="4" t="n">
         <v>-0.22</v>
@@ -52512,13 +52512,13 @@
         </is>
       </c>
       <c r="I483" s="4" t="n">
-        <v>-2.13</v>
+        <v>-2.11</v>
       </c>
       <c r="J483" s="4" t="n">
-        <v>35</v>
+        <v>35.1</v>
       </c>
       <c r="K483" s="4" t="n">
-        <v>65</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="L483" t="inlineStr">
         <is>
@@ -52526,13 +52526,13 @@
         </is>
       </c>
       <c r="M483" s="4" t="n">
-        <v>-14.09</v>
+        <v>-14.03</v>
       </c>
       <c r="N483" s="4" t="n">
         <v>6.75</v>
       </c>
       <c r="O483" s="4" t="n">
-        <v>-8.539999999999999</v>
+        <v>-8.48</v>
       </c>
       <c r="P483" s="4" t="n">
         <v>0.32</v>
@@ -52578,10 +52578,10 @@
         <v>0</v>
       </c>
       <c r="AC483" s="4" t="n">
-        <v>47.63</v>
+        <v>47.64</v>
       </c>
       <c r="AD483" s="4" t="n">
-        <v>49.7</v>
+        <v>49.69</v>
       </c>
       <c r="AE483" s="4" t="n">
         <v>0</v>
@@ -52967,10 +52967,10 @@
         <v>1.84</v>
       </c>
       <c r="J487" s="4" t="n">
-        <v>63.3</v>
+        <v>63.2</v>
       </c>
       <c r="K487" s="4" t="n">
-        <v>36.7</v>
+        <v>36.8</v>
       </c>
       <c r="L487" t="inlineStr">
         <is>
@@ -53412,7 +53412,7 @@
         </is>
       </c>
       <c r="I491" s="4" t="n">
-        <v>-21.55</v>
+        <v>-21.59</v>
       </c>
       <c r="J491" s="4" t="n">
         <v>0</v>
@@ -53472,16 +53472,16 @@
         </is>
       </c>
       <c r="AA491" s="4" t="n">
-        <v>27.78</v>
+        <v>27.73</v>
       </c>
       <c r="AB491" s="4" t="n">
         <v>0.2</v>
       </c>
       <c r="AC491" s="4" t="n">
-        <v>19.23</v>
+        <v>19.28</v>
       </c>
       <c r="AD491" s="4" t="n">
-        <v>49.33</v>
+        <v>49.32</v>
       </c>
       <c r="AE491" s="4" t="n">
         <v>3.66</v>
@@ -54095,10 +54095,10 @@
         <v>3.47</v>
       </c>
       <c r="J497" s="4" t="n">
-        <v>74.09999999999999</v>
+        <v>74.2</v>
       </c>
       <c r="K497" s="4" t="n">
-        <v>25.9</v>
+        <v>25.8</v>
       </c>
       <c r="L497" t="inlineStr">
         <is>
@@ -54106,7 +54106,7 @@
         </is>
       </c>
       <c r="M497" s="4" t="n">
-        <v>-7.52</v>
+        <v>-7.51</v>
       </c>
       <c r="N497" s="4" t="n">
         <v>6.75</v>
@@ -54897,13 +54897,13 @@
         </is>
       </c>
       <c r="I504" s="4" t="n">
-        <v>3.12</v>
+        <v>3.16</v>
       </c>
       <c r="J504" s="4" t="n">
-        <v>71.8</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="K504" s="4" t="n">
-        <v>28.2</v>
+        <v>27.9</v>
       </c>
       <c r="L504" t="inlineStr">
         <is>
@@ -54911,13 +54911,13 @@
         </is>
       </c>
       <c r="M504" s="4" t="n">
-        <v>-9.56</v>
+        <v>-9.44</v>
       </c>
       <c r="N504" s="4" t="n">
         <v>6.75</v>
       </c>
       <c r="O504" s="4" t="n">
-        <v>0.39</v>
+        <v>0.5</v>
       </c>
       <c r="P504" s="4" t="n">
         <v>0.11</v>
@@ -54963,10 +54963,10 @@
         <v>0</v>
       </c>
       <c r="AC504" s="4" t="n">
-        <v>51.24</v>
+        <v>51.27</v>
       </c>
       <c r="AD504" s="4" t="n">
-        <v>48.15</v>
+        <v>48.12</v>
       </c>
       <c r="AE504" s="4" t="n">
         <v>0</v>
@@ -55441,7 +55441,7 @@
         </is>
       </c>
       <c r="J2" s="4" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="K2" t="n">
         <v>17</v>
@@ -55453,7 +55453,7 @@
         <v>21</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -55516,7 +55516,7 @@
         <v>10</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -57191,7 +57191,7 @@
         </is>
       </c>
       <c r="J32" s="4" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
       <c r="K32" t="n">
         <v>49</v>
@@ -57203,7 +57203,7 @@
         <v>70</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -59743,7 +59743,7 @@
         </is>
       </c>
       <c r="J76" s="4" t="n">
-        <v>72.5</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="K76" t="n">
         <v>70</v>
@@ -59755,7 +59755,7 @@
         <v>96</v>
       </c>
       <c r="N76" s="4" t="n">
-        <v>34.1</v>
+        <v>34.3</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
@@ -59813,7 +59813,7 @@
         <v>16</v>
       </c>
       <c r="N77" s="4" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>

--- a/output/nowcast.xlsx
+++ b/output/nowcast.xlsx
@@ -541,16 +541,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>52.3</v>
+        <v>52.4</v>
       </c>
       <c r="C8" t="n">
-        <v>47.7</v>
+        <v>47.6</v>
       </c>
       <c r="D8" t="n">
         <v>53</v>
       </c>
       <c r="E8" t="n">
-        <v>68.90000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="F8" t="n">
         <v>51</v>
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>242</v>
+        <v>241.9</v>
       </c>
       <c r="C9" t="n">
-        <v>193</v>
+        <v>193.1</v>
       </c>
       <c r="D9" t="n">
         <v>238</v>
       </c>
       <c r="E9" t="n">
-        <v>89.3</v>
+        <v>89</v>
       </c>
       <c r="F9" t="n">
         <v>218</v>
@@ -591,16 +591,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>26.8</v>
+        <v>26.9</v>
       </c>
       <c r="C10" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="D10" t="n">
         <v>28</v>
       </c>
       <c r="E10" t="n">
-        <v>69.09999999999999</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F10" t="n">
         <v>26</v>
@@ -928,10 +928,10 @@
         <v>9.15</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>95.3</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -4948,14 +4948,14 @@
         <v>-3.45</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>25</v>
+        <v>25.1</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>75</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Likely R</t>
+          <t>Lean R</t>
         </is>
       </c>
       <c r="M38" s="4" t="n">
@@ -5008,7 +5008,7 @@
         <v>44.97</v>
       </c>
       <c r="AB38" s="4" t="n">
-        <v>25</v>
+        <v>25.1</v>
       </c>
       <c r="AC38" s="4" t="n">
         <v>3.8</v>
@@ -25781,10 +25781,10 @@
         <v>-0.37</v>
       </c>
       <c r="J235" s="4" t="n">
-        <v>47.5</v>
+        <v>45.6</v>
       </c>
       <c r="K235" s="4" t="n">
-        <v>52.5</v>
+        <v>54.4</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -47728,13 +47728,13 @@
         </is>
       </c>
       <c r="I439" s="4" t="n">
-        <v>-25.54</v>
+        <v>-19.1</v>
       </c>
       <c r="J439" s="4" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="K439" s="4" t="n">
-        <v>99.90000000000001</v>
+        <v>99.7</v>
       </c>
       <c r="L439" t="inlineStr">
         <is>
@@ -47760,16 +47760,16 @@
         <v>-33.43</v>
       </c>
       <c r="S439" s="4" t="n">
-        <v>32.9</v>
+        <v>37.85</v>
       </c>
       <c r="T439" s="4" t="n">
-        <v>41.7</v>
+        <v>36.12</v>
       </c>
       <c r="U439" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V439" s="4" t="n">
-        <v>-8.220000000000001</v>
+        <v>1.41</v>
       </c>
       <c r="W439" s="5" t="n">
         <v>53579</v>
@@ -47788,16 +47788,16 @@
         </is>
       </c>
       <c r="AA439" s="4" t="n">
-        <v>5.7</v>
+        <v>5.03</v>
       </c>
       <c r="AB439" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC439" s="4" t="n">
-        <v>32.5</v>
+        <v>35.58</v>
       </c>
       <c r="AD439" s="4" t="n">
-        <v>54.8</v>
+        <v>52.39</v>
       </c>
       <c r="AE439" s="4" t="n">
         <v>7</v>
@@ -52967,10 +52967,10 @@
         <v>1.88</v>
       </c>
       <c r="J487" s="4" t="n">
-        <v>62.9</v>
+        <v>63.2</v>
       </c>
       <c r="K487" s="4" t="n">
-        <v>37.1</v>
+        <v>36.8</v>
       </c>
       <c r="L487" t="inlineStr">
         <is>
@@ -53412,7 +53412,7 @@
         </is>
       </c>
       <c r="I491" s="4" t="n">
-        <v>-21.57</v>
+        <v>-21.48</v>
       </c>
       <c r="J491" s="4" t="n">
         <v>0</v>
@@ -53472,16 +53472,16 @@
         </is>
       </c>
       <c r="AA491" s="4" t="n">
-        <v>27.75</v>
+        <v>27.78</v>
       </c>
       <c r="AB491" s="4" t="n">
         <v>0.2</v>
       </c>
       <c r="AC491" s="4" t="n">
-        <v>19.28</v>
+        <v>19.29</v>
       </c>
       <c r="AD491" s="4" t="n">
-        <v>49.32</v>
+        <v>49.27</v>
       </c>
       <c r="AE491" s="4" t="n">
         <v>3.66</v>

--- a/output/nowcast.xlsx
+++ b/output/nowcast.xlsx
@@ -550,7 +550,7 @@
         <v>53</v>
       </c>
       <c r="E8" t="n">
-        <v>69.7</v>
+        <v>70</v>
       </c>
       <c r="F8" t="n">
         <v>51</v>
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>241.9</v>
+        <v>242.1</v>
       </c>
       <c r="C9" t="n">
-        <v>193.1</v>
+        <v>192.9</v>
       </c>
       <c r="D9" t="n">
         <v>238</v>
       </c>
       <c r="E9" t="n">
-        <v>88.40000000000001</v>
+        <v>88.8</v>
       </c>
       <c r="F9" t="n">
         <v>218</v>
@@ -600,7 +600,7 @@
         <v>28</v>
       </c>
       <c r="E10" t="n">
-        <v>68.40000000000001</v>
+        <v>68.3</v>
       </c>
       <c r="F10" t="n">
         <v>26</v>
@@ -928,10 +928,10 @@
         <v>9.130000000000001</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>95.5</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -4948,10 +4948,10 @@
         <v>-3.32</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>26.2</v>
+        <v>25</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>73.8</v>
+        <v>75</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>45.03</v>
       </c>
       <c r="AB38" s="4" t="n">
-        <v>26.2</v>
+        <v>25</v>
       </c>
       <c r="AC38" s="4" t="n">
         <v>3.8</v>
@@ -25781,10 +25781,10 @@
         <v>-0.38</v>
       </c>
       <c r="J235" s="4" t="n">
-        <v>48.3</v>
+        <v>47.1</v>
       </c>
       <c r="K235" s="4" t="n">
-        <v>51.7</v>
+        <v>52.9</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -51407,10 +51407,10 @@
         <v>2.75</v>
       </c>
       <c r="J473" s="4" t="n">
-        <v>70</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="K473" s="4" t="n">
-        <v>30</v>
+        <v>29.6</v>
       </c>
       <c r="L473" t="inlineStr">
         <is>
@@ -52973,10 +52973,10 @@
         <v>2.19</v>
       </c>
       <c r="J487" s="4" t="n">
-        <v>65.7</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="K487" s="4" t="n">
-        <v>34.3</v>
+        <v>34.4</v>
       </c>
       <c r="L487" t="inlineStr">
         <is>
@@ -53418,7 +53418,7 @@
         </is>
       </c>
       <c r="I491" s="4" t="n">
-        <v>-21.59</v>
+        <v>-21.56</v>
       </c>
       <c r="J491" s="4" t="n">
         <v>0</v>
@@ -53478,16 +53478,16 @@
         </is>
       </c>
       <c r="AA491" s="4" t="n">
-        <v>27.72</v>
+        <v>27.77</v>
       </c>
       <c r="AB491" s="4" t="n">
         <v>0.2</v>
       </c>
       <c r="AC491" s="4" t="n">
-        <v>19.3</v>
+        <v>19.24</v>
       </c>
       <c r="AD491" s="4" t="n">
-        <v>49.31</v>
+        <v>49.33</v>
       </c>
       <c r="AE491" s="4" t="n">
         <v>3.66</v>

--- a/output/nowcast.xlsx
+++ b/output/nowcast.xlsx
@@ -550,7 +550,7 @@
         <v>53</v>
       </c>
       <c r="E8" t="n">
-        <v>70.40000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F8" t="n">
         <v>51</v>
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>242.6</v>
+        <v>242.9</v>
       </c>
       <c r="C9" t="n">
-        <v>192.4</v>
+        <v>192.1</v>
       </c>
       <c r="D9" t="n">
         <v>239</v>
       </c>
       <c r="E9" t="n">
-        <v>89.40000000000001</v>
+        <v>89.8</v>
       </c>
       <c r="F9" t="n">
         <v>218</v>
@@ -591,16 +591,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>26.9</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="D10" t="n">
         <v>28</v>
       </c>
       <c r="E10" t="n">
-        <v>68.7</v>
+        <v>69.7</v>
       </c>
       <c r="F10" t="n">
         <v>26</v>
@@ -4945,13 +4945,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>-3.3</v>
+        <v>-3.29</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>25.7</v>
+        <v>26.4</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>74.3</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -4959,13 +4959,13 @@
         </is>
       </c>
       <c r="M38" s="4" t="n">
-        <v>-2.58</v>
+        <v>-2.56</v>
       </c>
       <c r="N38" s="4" t="n">
         <v>7.01</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="P38" s="4" t="n">
         <v>-0.6</v>
@@ -5005,16 +5005,16 @@
         </is>
       </c>
       <c r="AA38" s="4" t="n">
-        <v>45.04</v>
+        <v>45.05</v>
       </c>
       <c r="AB38" s="4" t="n">
-        <v>25.7</v>
+        <v>26.4</v>
       </c>
       <c r="AC38" s="4" t="n">
         <v>3.8</v>
       </c>
       <c r="AD38" s="4" t="n">
-        <v>49.96</v>
+        <v>49.95</v>
       </c>
       <c r="AE38" s="4" t="n">
         <v>1.2</v>
@@ -22164,7 +22164,7 @@
         </is>
       </c>
       <c r="I201" s="4" t="n">
-        <v>-26.96</v>
+        <v>-26.92</v>
       </c>
       <c r="J201" s="4" t="n">
         <v>0</v>
@@ -22178,13 +22178,13 @@
         </is>
       </c>
       <c r="M201" s="4" t="n">
-        <v>-26.69</v>
+        <v>-26.65</v>
       </c>
       <c r="N201" s="4" t="n">
         <v>7.01</v>
       </c>
       <c r="O201" s="4" t="n">
-        <v>-27.49</v>
+        <v>-27.45</v>
       </c>
       <c r="P201" s="4" t="n">
         <v>-2.06</v>
@@ -22224,10 +22224,10 @@
         <v>0</v>
       </c>
       <c r="AC201" s="4" t="n">
-        <v>35.54</v>
+        <v>35.56</v>
       </c>
       <c r="AD201" s="4" t="n">
-        <v>61.78</v>
+        <v>61.76</v>
       </c>
       <c r="AE201" s="4" t="n">
         <v>0</v>
@@ -22275,7 +22275,7 @@
         </is>
       </c>
       <c r="I202" s="4" t="n">
-        <v>-12.74</v>
+        <v>-12.7</v>
       </c>
       <c r="J202" s="4" t="n">
         <v>1</v>
@@ -22289,13 +22289,13 @@
         </is>
       </c>
       <c r="M202" s="4" t="n">
-        <v>-14.27</v>
+        <v>-14.22</v>
       </c>
       <c r="N202" s="4" t="n">
         <v>7.01</v>
       </c>
       <c r="O202" s="4" t="n">
-        <v>-13.31</v>
+        <v>-13.27</v>
       </c>
       <c r="P202" s="4" t="n">
         <v>-0.47</v>
@@ -22335,10 +22335,10 @@
         <v>0</v>
       </c>
       <c r="AC202" s="4" t="n">
-        <v>42.39</v>
+        <v>42.41</v>
       </c>
       <c r="AD202" s="4" t="n">
-        <v>54.77</v>
+        <v>54.75</v>
       </c>
       <c r="AE202" s="4" t="n">
         <v>0</v>
@@ -22386,7 +22386,7 @@
         </is>
       </c>
       <c r="I203" s="4" t="n">
-        <v>26.04</v>
+        <v>26.09</v>
       </c>
       <c r="J203" s="4" t="n">
         <v>100</v>
@@ -22400,13 +22400,13 @@
         </is>
       </c>
       <c r="M203" s="4" t="n">
-        <v>8.710000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="N203" s="4" t="n">
         <v>7.01</v>
       </c>
       <c r="O203" s="4" t="n">
-        <v>25.46</v>
+        <v>25.5</v>
       </c>
       <c r="P203" s="4" t="n">
         <v>3</v>
@@ -22446,10 +22446,10 @@
         <v>0</v>
       </c>
       <c r="AC203" s="4" t="n">
-        <v>61.17</v>
+        <v>61.19</v>
       </c>
       <c r="AD203" s="4" t="n">
-        <v>35.89</v>
+        <v>35.87</v>
       </c>
       <c r="AE203" s="4" t="n">
         <v>0</v>
@@ -22497,7 +22497,7 @@
         </is>
       </c>
       <c r="I204" s="4" t="n">
-        <v>-18.2</v>
+        <v>-18.15</v>
       </c>
       <c r="J204" s="4" t="n">
         <v>0.3</v>
@@ -22511,13 +22511,13 @@
         </is>
       </c>
       <c r="M204" s="4" t="n">
-        <v>-18.65</v>
+        <v>-18.61</v>
       </c>
       <c r="N204" s="4" t="n">
         <v>7.01</v>
       </c>
       <c r="O204" s="4" t="n">
-        <v>-18.77</v>
+        <v>-18.73</v>
       </c>
       <c r="P204" s="4" t="n">
         <v>-1.43</v>
@@ -22557,10 +22557,10 @@
         <v>0</v>
       </c>
       <c r="AC204" s="4" t="n">
-        <v>39.72</v>
+        <v>39.74</v>
       </c>
       <c r="AD204" s="4" t="n">
-        <v>57.4</v>
+        <v>57.38</v>
       </c>
       <c r="AE204" s="4" t="n">
         <v>0</v>
@@ -25787,10 +25787,10 @@
         <v>-0.26</v>
       </c>
       <c r="J235" s="4" t="n">
-        <v>47.6</v>
+        <v>46.9</v>
       </c>
       <c r="K235" s="4" t="n">
-        <v>52.4</v>
+        <v>53.1</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -25913,7 +25913,7 @@
         <v>7.01</v>
       </c>
       <c r="O236" s="4" t="n">
-        <v>-10.84</v>
+        <v>-10.85</v>
       </c>
       <c r="P236" s="4" t="n">
         <v>-0.55</v>
@@ -26129,7 +26129,7 @@
         </is>
       </c>
       <c r="M238" s="4" t="n">
-        <v>11.73</v>
+        <v>11.72</v>
       </c>
       <c r="N238" s="4" t="n">
         <v>7.01</v>
@@ -26226,7 +26226,7 @@
         </is>
       </c>
       <c r="I239" s="4" t="n">
-        <v>-0.93</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="J239" s="4" t="n">
         <v>43.4</v>
@@ -26240,13 +26240,13 @@
         </is>
       </c>
       <c r="M239" s="4" t="n">
-        <v>-1.43</v>
+        <v>-1.44</v>
       </c>
       <c r="N239" s="4" t="n">
         <v>7.01</v>
       </c>
       <c r="O239" s="4" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.08</v>
       </c>
       <c r="P239" s="4" t="n">
         <v>-0.2</v>
@@ -26363,7 +26363,7 @@
         <v>7.01</v>
       </c>
       <c r="O240" s="4" t="n">
-        <v>-23.62</v>
+        <v>-23.63</v>
       </c>
       <c r="P240" s="4" t="n">
         <v>-2.12</v>
@@ -26403,10 +26403,10 @@
         <v>0</v>
       </c>
       <c r="AC240" s="4" t="n">
-        <v>36.53</v>
+        <v>36.52</v>
       </c>
       <c r="AD240" s="4" t="n">
-        <v>59.25</v>
+        <v>59.26</v>
       </c>
       <c r="AE240" s="4" t="n">
         <v>2.11</v>
@@ -26454,7 +26454,7 @@
         </is>
       </c>
       <c r="I241" s="4" t="n">
-        <v>40.41</v>
+        <v>40.4</v>
       </c>
       <c r="J241" s="4" t="n">
         <v>100</v>
@@ -26474,7 +26474,7 @@
         <v>7.01</v>
       </c>
       <c r="O241" s="4" t="n">
-        <v>40.54</v>
+        <v>40.53</v>
       </c>
       <c r="P241" s="4" t="n">
         <v>0</v>
@@ -26579,7 +26579,7 @@
         </is>
       </c>
       <c r="M242" s="4" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="N242" s="4" t="n">
         <v>7.01</v>
@@ -26631,10 +26631,10 @@
         <v>0</v>
       </c>
       <c r="AC242" s="4" t="n">
-        <v>50.6</v>
+        <v>50.59</v>
       </c>
       <c r="AD242" s="4" t="n">
-        <v>47.13</v>
+        <v>47.14</v>
       </c>
       <c r="AE242" s="4" t="n">
         <v>0</v>
@@ -26793,7 +26793,7 @@
         </is>
       </c>
       <c r="I244" s="4" t="n">
-        <v>-30.73</v>
+        <v>-30.74</v>
       </c>
       <c r="J244" s="4" t="n">
         <v>0</v>
@@ -27027,7 +27027,7 @@
         </is>
       </c>
       <c r="M246" s="4" t="n">
-        <v>21.17</v>
+        <v>21.16</v>
       </c>
       <c r="N246" s="4" t="n">
         <v>7.01</v>
@@ -27124,7 +27124,7 @@
         </is>
       </c>
       <c r="I247" s="4" t="n">
-        <v>60.04</v>
+        <v>60.03</v>
       </c>
       <c r="J247" s="4" t="n">
         <v>100</v>
@@ -27231,7 +27231,7 @@
         </is>
       </c>
       <c r="I248" s="4" t="n">
-        <v>55.17</v>
+        <v>55.16</v>
       </c>
       <c r="J248" s="4" t="n">
         <v>100</v>
@@ -27245,13 +27245,13 @@
         </is>
       </c>
       <c r="M248" s="4" t="n">
-        <v>48.71</v>
+        <v>48.7</v>
       </c>
       <c r="N248" s="4" t="n">
         <v>7.01</v>
       </c>
       <c r="O248" s="4" t="n">
-        <v>55.8</v>
+        <v>55.79</v>
       </c>
       <c r="P248" s="4" t="n">
         <v>0</v>
@@ -51416,13 +51416,13 @@
         </is>
       </c>
       <c r="I473" s="4" t="n">
-        <v>2.46</v>
+        <v>2.57</v>
       </c>
       <c r="J473" s="4" t="n">
-        <v>68.2</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="K473" s="4" t="n">
-        <v>31.8</v>
+        <v>30.9</v>
       </c>
       <c r="L473" t="inlineStr">
         <is>
@@ -51448,16 +51448,16 @@
         <v>-13.8</v>
       </c>
       <c r="S473" s="4" t="n">
-        <v>48.64</v>
+        <v>48.69</v>
       </c>
       <c r="T473" s="4" t="n">
-        <v>45.63</v>
+        <v>45.71</v>
       </c>
       <c r="U473" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="V473" s="4" t="n">
-        <v>3.78</v>
+        <v>3.82</v>
       </c>
       <c r="W473" s="5" t="n">
         <v>18545132</v>
@@ -51474,10 +51474,10 @@
         <v>0</v>
       </c>
       <c r="AC473" s="4" t="n">
-        <v>49.55</v>
+        <v>49.61</v>
       </c>
       <c r="AD473" s="4" t="n">
-        <v>47.95</v>
+        <v>47.89</v>
       </c>
       <c r="AE473" s="4" t="n">
         <v>2.5</v>
@@ -52530,17 +52530,17 @@
         </is>
       </c>
       <c r="I483" s="4" t="n">
-        <v>-1.49</v>
+        <v>-1.28</v>
       </c>
       <c r="J483" s="4" t="n">
-        <v>39.4</v>
+        <v>40.9</v>
       </c>
       <c r="K483" s="4" t="n">
-        <v>60.6</v>
+        <v>59.1</v>
       </c>
       <c r="L483" t="inlineStr">
         <is>
-          <t>Lean R</t>
+          <t>Toss-up</t>
         </is>
       </c>
       <c r="M483" s="4" t="n">
@@ -52562,16 +52562,16 @@
         <v>-16.41</v>
       </c>
       <c r="S483" s="4" t="n">
-        <v>46.47</v>
+        <v>46.49</v>
       </c>
       <c r="T483" s="4" t="n">
-        <v>45.07</v>
+        <v>45.1</v>
       </c>
       <c r="U483" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V483" s="4" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="W483" s="5" t="n">
         <v>4169078</v>
@@ -52590,16 +52590,16 @@
         </is>
       </c>
       <c r="AA483" s="4" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="AB483" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC483" s="4" t="n">
-        <v>48.27</v>
+        <v>48.39</v>
       </c>
       <c r="AD483" s="4" t="n">
-        <v>49.74</v>
+        <v>49.65</v>
       </c>
       <c r="AE483" s="4" t="n">
         <v>0</v>
@@ -52985,10 +52985,10 @@
         <v>2.33</v>
       </c>
       <c r="J487" s="4" t="n">
-        <v>66.5</v>
+        <v>66.7</v>
       </c>
       <c r="K487" s="4" t="n">
-        <v>33.5</v>
+        <v>33.3</v>
       </c>
       <c r="L487" t="inlineStr">
         <is>
@@ -53087,13 +53087,13 @@
         </is>
       </c>
       <c r="I488" s="4" t="n">
-        <v>5.91</v>
+        <v>5.88</v>
       </c>
       <c r="J488" s="4" t="n">
-        <v>84</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K488" s="4" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="L488" t="inlineStr">
         <is>
@@ -53119,16 +53119,16 @@
         <v>-1.44</v>
       </c>
       <c r="S488" s="4" t="n">
-        <v>48.78</v>
+        <v>48.77</v>
       </c>
       <c r="T488" s="4" t="n">
         <v>45.75</v>
       </c>
       <c r="U488" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V488" s="4" t="n">
-        <v>3.62</v>
+        <v>3.63</v>
       </c>
       <c r="W488" s="5" t="n">
         <v>14514336</v>
@@ -53153,10 +53153,10 @@
         <v>0</v>
       </c>
       <c r="AC488" s="4" t="n">
-        <v>51.46</v>
+        <v>51.45</v>
       </c>
       <c r="AD488" s="4" t="n">
-        <v>45.73</v>
+        <v>45.74</v>
       </c>
       <c r="AE488" s="4" t="n">
         <v>2.31</v>
@@ -53430,7 +53430,7 @@
         </is>
       </c>
       <c r="I491" s="4" t="n">
-        <v>-21.58</v>
+        <v>-21.67</v>
       </c>
       <c r="J491" s="4" t="n">
         <v>0</v>
@@ -53490,16 +53490,16 @@
         </is>
       </c>
       <c r="AA491" s="4" t="n">
-        <v>27.73</v>
+        <v>27.69</v>
       </c>
       <c r="AB491" s="4" t="n">
         <v>0.2</v>
       </c>
       <c r="AC491" s="4" t="n">
-        <v>19.3</v>
+        <v>19.28</v>
       </c>
       <c r="AD491" s="4" t="n">
-        <v>49.31</v>
+        <v>49.37</v>
       </c>
       <c r="AE491" s="4" t="n">
         <v>3.66</v>
@@ -58091,7 +58091,7 @@
         <v>55</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>

--- a/output/nowcast.xlsx
+++ b/output/nowcast.xlsx
@@ -541,16 +541,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>52.3</v>
+        <v>52.4</v>
       </c>
       <c r="C8" t="n">
-        <v>47.7</v>
+        <v>47.6</v>
       </c>
       <c r="D8" t="n">
         <v>53</v>
       </c>
       <c r="E8" t="n">
-        <v>68.8</v>
+        <v>69.8</v>
       </c>
       <c r="F8" t="n">
         <v>51</v>
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>243</v>
+        <v>242.9</v>
       </c>
       <c r="C9" t="n">
-        <v>192</v>
+        <v>192.1</v>
       </c>
       <c r="D9" t="n">
         <v>239</v>
       </c>
       <c r="E9" t="n">
-        <v>90.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="F9" t="n">
         <v>218</v>
@@ -600,7 +600,7 @@
         <v>28</v>
       </c>
       <c r="E10" t="n">
-        <v>69.8</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="F10" t="n">
         <v>26</v>
@@ -4948,10 +4948,10 @@
         <v>-3.21</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>26.2</v>
+        <v>26.1</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>73.8</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>45.09</v>
       </c>
       <c r="AB38" s="4" t="n">
-        <v>26.2</v>
+        <v>26.1</v>
       </c>
       <c r="AC38" s="4" t="n">
         <v>3.8</v>
@@ -25793,10 +25793,10 @@
         <v>-0.3</v>
       </c>
       <c r="J235" s="4" t="n">
-        <v>47.7</v>
+        <v>47.4</v>
       </c>
       <c r="K235" s="4" t="n">
-        <v>52.3</v>
+        <v>52.6</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -51425,10 +51425,10 @@
         <v>2.56</v>
       </c>
       <c r="J473" s="4" t="n">
-        <v>68.40000000000001</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="K473" s="4" t="n">
-        <v>31.6</v>
+        <v>31.1</v>
       </c>
       <c r="L473" t="inlineStr">
         <is>
@@ -52991,10 +52991,10 @@
         <v>2.3</v>
       </c>
       <c r="J487" s="4" t="n">
-        <v>66.09999999999999</v>
+        <v>66.3</v>
       </c>
       <c r="K487" s="4" t="n">
-        <v>33.9</v>
+        <v>33.7</v>
       </c>
       <c r="L487" t="inlineStr">
         <is>
@@ -53436,7 +53436,7 @@
         </is>
       </c>
       <c r="I491" s="4" t="n">
-        <v>-21.77</v>
+        <v>-21.62</v>
       </c>
       <c r="J491" s="4" t="n">
         <v>0</v>
@@ -53496,16 +53496,16 @@
         </is>
       </c>
       <c r="AA491" s="4" t="n">
-        <v>27.68</v>
+        <v>27.75</v>
       </c>
       <c r="AB491" s="4" t="n">
         <v>0.2</v>
       </c>
       <c r="AC491" s="4" t="n">
-        <v>19.21</v>
+        <v>19.22</v>
       </c>
       <c r="AD491" s="4" t="n">
-        <v>49.45</v>
+        <v>49.37</v>
       </c>
       <c r="AE491" s="4" t="n">
         <v>3.66</v>
@@ -58097,7 +58097,7 @@
         <v>55</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>

--- a/output/nowcast.xlsx
+++ b/output/nowcast.xlsx
@@ -550,7 +550,7 @@
         <v>53</v>
       </c>
       <c r="E8" t="n">
-        <v>69.8</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="F8" t="n">
         <v>51</v>
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>243.1</v>
+        <v>242.5</v>
       </c>
       <c r="C9" t="n">
-        <v>191.9</v>
+        <v>192.5</v>
       </c>
       <c r="D9" t="n">
         <v>239</v>
       </c>
       <c r="E9" t="n">
-        <v>90.8</v>
+        <v>90.3</v>
       </c>
       <c r="F9" t="n">
         <v>218</v>
@@ -600,7 +600,7 @@
         <v>28</v>
       </c>
       <c r="E10" t="n">
-        <v>69.5</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="F10" t="n">
         <v>26</v>
@@ -4948,10 +4948,10 @@
         <v>-3.11</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>28.5</v>
+        <v>27.8</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>71.5</v>
+        <v>72.2</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>45.13</v>
       </c>
       <c r="AB38" s="4" t="n">
-        <v>28.5</v>
+        <v>27.8</v>
       </c>
       <c r="AC38" s="4" t="n">
         <v>3.8</v>
@@ -25793,10 +25793,10 @@
         <v>-0.3</v>
       </c>
       <c r="J235" s="4" t="n">
-        <v>48.2</v>
+        <v>47.5</v>
       </c>
       <c r="K235" s="4" t="n">
-        <v>51.8</v>
+        <v>52.5</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -47978,13 +47978,13 @@
         </is>
       </c>
       <c r="I441" s="4" t="n">
-        <v>6.71</v>
+        <v>5.84</v>
       </c>
       <c r="J441" s="4" t="n">
-        <v>86.59999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="K441" s="4" t="n">
-        <v>13.4</v>
+        <v>16.3</v>
       </c>
       <c r="L441" t="inlineStr">
         <is>
@@ -48010,16 +48010,16 @@
         <v>-0.27</v>
       </c>
       <c r="S441" s="4" t="n">
-        <v>47</v>
+        <v>46.04</v>
       </c>
       <c r="T441" s="4" t="n">
-        <v>47</v>
+        <v>43.17</v>
       </c>
       <c r="U441" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V441" s="4" t="n">
-        <v>-0.68</v>
+        <v>2.85</v>
       </c>
       <c r="W441" s="5" t="n">
         <v>4659795</v>
@@ -48044,10 +48044,10 @@
         <v>0</v>
       </c>
       <c r="AC441" s="4" t="n">
-        <v>52.09</v>
+        <v>51.67</v>
       </c>
       <c r="AD441" s="4" t="n">
-        <v>45.55</v>
+        <v>45.97</v>
       </c>
       <c r="AE441" s="4" t="n">
         <v>0</v>
@@ -51431,10 +51431,10 @@
         <v>2.59</v>
       </c>
       <c r="J473" s="4" t="n">
-        <v>68.7</v>
+        <v>68</v>
       </c>
       <c r="K473" s="4" t="n">
-        <v>31.3</v>
+        <v>32</v>
       </c>
       <c r="L473" t="inlineStr">
         <is>
@@ -52997,10 +52997,10 @@
         <v>2.33</v>
       </c>
       <c r="J487" s="4" t="n">
-        <v>65.40000000000001</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="K487" s="4" t="n">
-        <v>34.6</v>
+        <v>33.6</v>
       </c>
       <c r="L487" t="inlineStr">
         <is>
@@ -53442,7 +53442,7 @@
         </is>
       </c>
       <c r="I491" s="4" t="n">
-        <v>-21.69</v>
+        <v>-21.65</v>
       </c>
       <c r="J491" s="4" t="n">
         <v>0</v>
@@ -53508,10 +53508,10 @@
         <v>0.2</v>
       </c>
       <c r="AC491" s="4" t="n">
-        <v>19.24</v>
+        <v>19.28</v>
       </c>
       <c r="AD491" s="4" t="n">
-        <v>49.39</v>
+        <v>49.36</v>
       </c>
       <c r="AE491" s="4" t="n">
         <v>3.66</v>
@@ -58103,7 +58103,7 @@
         <v>55</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>

--- a/output/nowcast.xlsx
+++ b/output/nowcast.xlsx
@@ -550,7 +550,7 @@
         <v>53</v>
       </c>
       <c r="E8" t="n">
-        <v>69.90000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="F8" t="n">
         <v>51</v>
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>242.5</v>
+        <v>242.9</v>
       </c>
       <c r="C9" t="n">
-        <v>192.5</v>
+        <v>192.1</v>
       </c>
       <c r="D9" t="n">
         <v>239</v>
       </c>
       <c r="E9" t="n">
-        <v>90.3</v>
+        <v>89.7</v>
       </c>
       <c r="F9" t="n">
         <v>218</v>
@@ -600,7 +600,7 @@
         <v>28</v>
       </c>
       <c r="E10" t="n">
-        <v>69.40000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="F10" t="n">
         <v>26</v>
@@ -718,7 +718,7 @@
     <col width="10" customWidth="1" min="19" max="19"/>
     <col width="10" customWidth="1" min="20" max="20"/>
     <col width="12" customWidth="1" min="21" max="21"/>
-    <col width="13" customWidth="1" min="22" max="22"/>
+    <col width="21" customWidth="1" min="22" max="22"/>
     <col width="11" customWidth="1" min="23" max="23"/>
     <col width="11" customWidth="1" min="24" max="24"/>
     <col width="30" customWidth="1" min="25" max="25"/>
@@ -4053,10 +4053,10 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>26.34</v>
+        <v>14.25</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>100</v>
+        <v>99.2</v>
       </c>
       <c r="K30" s="4" t="n">
         <v>0</v>
@@ -4094,7 +4094,7 @@
         <v>5</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>32.53</v>
+        <v>-0.8699999999999974</v>
       </c>
       <c r="W30" s="5" t="n">
         <v>0</v>
@@ -4113,16 +4113,16 @@
         </is>
       </c>
       <c r="AA30" s="4" t="n">
-        <v>30</v>
+        <v>35.48</v>
       </c>
       <c r="AB30" s="4" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AC30" s="4" t="n">
-        <v>44.22</v>
+        <v>49.73</v>
       </c>
       <c r="AD30" s="4" t="n">
-        <v>25.78</v>
+        <v>14.79</v>
       </c>
       <c r="AE30" s="4" t="n">
         <v>0</v>
@@ -4948,10 +4948,10 @@
         <v>-3.11</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>27.8</v>
+        <v>27.4</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>72.2</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>45.13</v>
       </c>
       <c r="AB38" s="4" t="n">
-        <v>27.8</v>
+        <v>27.4</v>
       </c>
       <c r="AC38" s="4" t="n">
         <v>3.8</v>
@@ -25793,10 +25793,10 @@
         <v>-0.3</v>
       </c>
       <c r="J235" s="4" t="n">
-        <v>47.5</v>
+        <v>47.2</v>
       </c>
       <c r="K235" s="4" t="n">
-        <v>52.5</v>
+        <v>52.8</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -41358,7 +41358,7 @@
         </is>
       </c>
       <c r="I379" s="4" t="n">
-        <v>47.44</v>
+        <v>45.39</v>
       </c>
       <c r="J379" s="4" t="n">
         <v>100</v>
@@ -41372,13 +41372,13 @@
         </is>
       </c>
       <c r="M379" s="4" t="n">
-        <v>29.87</v>
+        <v>27.81</v>
       </c>
       <c r="N379" s="4" t="n">
         <v>7.07</v>
       </c>
       <c r="O379" s="4" t="n">
-        <v>47.6</v>
+        <v>45.54</v>
       </c>
       <c r="P379" s="4" t="n">
         <v>2.51</v>
@@ -41418,10 +41418,10 @@
         <v>0</v>
       </c>
       <c r="AC379" s="4" t="n">
-        <v>71.44</v>
+        <v>70.45</v>
       </c>
       <c r="AD379" s="4" t="n">
-        <v>25.47</v>
+        <v>26.46</v>
       </c>
       <c r="AE379" s="4" t="n">
         <v>0</v>
@@ -41469,13 +41469,13 @@
         </is>
       </c>
       <c r="I380" s="4" t="n">
-        <v>18.61</v>
+        <v>17.72</v>
       </c>
       <c r="J380" s="4" t="n">
-        <v>99.7</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="K380" s="4" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="L380" t="inlineStr">
         <is>
@@ -41483,13 +41483,13 @@
         </is>
       </c>
       <c r="M380" s="4" t="n">
-        <v>14.01</v>
+        <v>11.96</v>
       </c>
       <c r="N380" s="4" t="n">
         <v>7.07</v>
       </c>
       <c r="O380" s="4" t="n">
-        <v>21.85</v>
+        <v>19.8</v>
       </c>
       <c r="P380" s="4" t="n">
         <v>-0.57</v>
@@ -41527,10 +41527,10 @@
         <v>0</v>
       </c>
       <c r="AC380" s="4" t="n">
-        <v>59.3</v>
+        <v>58.86</v>
       </c>
       <c r="AD380" s="4" t="n">
-        <v>40.7</v>
+        <v>41.14</v>
       </c>
       <c r="AE380" s="4" t="n">
         <v>0</v>
@@ -51431,10 +51431,10 @@
         <v>2.59</v>
       </c>
       <c r="J473" s="4" t="n">
-        <v>68</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="K473" s="4" t="n">
-        <v>32</v>
+        <v>31.4</v>
       </c>
       <c r="L473" t="inlineStr">
         <is>
@@ -52997,10 +52997,10 @@
         <v>2.33</v>
       </c>
       <c r="J487" s="4" t="n">
-        <v>66.40000000000001</v>
+        <v>66.5</v>
       </c>
       <c r="K487" s="4" t="n">
-        <v>33.6</v>
+        <v>33.5</v>
       </c>
       <c r="L487" t="inlineStr">
         <is>
@@ -53442,7 +53442,7 @@
         </is>
       </c>
       <c r="I491" s="4" t="n">
-        <v>-21.65</v>
+        <v>-21.7</v>
       </c>
       <c r="J491" s="4" t="n">
         <v>0</v>
@@ -53502,16 +53502,16 @@
         </is>
       </c>
       <c r="AA491" s="4" t="n">
-        <v>27.7</v>
+        <v>27.69</v>
       </c>
       <c r="AB491" s="4" t="n">
         <v>0.2</v>
       </c>
       <c r="AC491" s="4" t="n">
-        <v>19.28</v>
+        <v>19.26</v>
       </c>
       <c r="AD491" s="4" t="n">
-        <v>49.36</v>
+        <v>49.39</v>
       </c>
       <c r="AE491" s="4" t="n">
         <v>3.66</v>
@@ -54463,7 +54463,7 @@
         </is>
       </c>
       <c r="I500" s="4" t="n">
-        <v>29.86</v>
+        <v>28.25</v>
       </c>
       <c r="J500" s="4" t="n">
         <v>100</v>
@@ -54477,13 +54477,13 @@
         </is>
       </c>
       <c r="M500" s="4" t="n">
-        <v>18.8</v>
+        <v>15.75</v>
       </c>
       <c r="N500" s="4" t="n">
         <v>7.07</v>
       </c>
       <c r="O500" s="4" t="n">
-        <v>29.36</v>
+        <v>26.31</v>
       </c>
       <c r="P500" s="4" t="n">
         <v>2.03</v>
@@ -54529,10 +54529,10 @@
         <v>0</v>
       </c>
       <c r="AC500" s="4" t="n">
-        <v>60.8</v>
+        <v>60.05</v>
       </c>
       <c r="AD500" s="4" t="n">
-        <v>32.84</v>
+        <v>33.59</v>
       </c>
       <c r="AE500" s="4" t="n">
         <v>0</v>
@@ -58103,7 +58103,7 @@
         <v>55</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -59367,19 +59367,19 @@
         </is>
       </c>
       <c r="J69" s="4" t="n">
-        <v>64.90000000000001</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="K69" t="n">
         <v>66</v>
       </c>
       <c r="L69" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M69" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="N69" s="4" t="n">
-        <v>99.5</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -59425,7 +59425,7 @@
         </is>
       </c>
       <c r="J70" s="4" t="n">
-        <v>34.4</v>
+        <v>34.2</v>
       </c>
       <c r="K70" t="n">
         <v>35</v>
@@ -59437,7 +59437,7 @@
         <v>36</v>
       </c>
       <c r="N70" s="4" t="n">
-        <v>99.5</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>

--- a/output/nowcast.xlsx
+++ b/output/nowcast.xlsx
@@ -541,16 +541,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>52.5</v>
+        <v>52.4</v>
       </c>
       <c r="C8" t="n">
-        <v>47.5</v>
+        <v>47.6</v>
       </c>
       <c r="D8" t="n">
         <v>53</v>
       </c>
       <c r="E8" t="n">
-        <v>70.5</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="F8" t="n">
         <v>51</v>
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>243.2</v>
+        <v>243.3</v>
       </c>
       <c r="C9" t="n">
-        <v>191.8</v>
+        <v>191.7</v>
       </c>
       <c r="D9" t="n">
         <v>239</v>
       </c>
       <c r="E9" t="n">
-        <v>90.09999999999999</v>
+        <v>90</v>
       </c>
       <c r="F9" t="n">
         <v>218</v>
@@ -600,7 +600,7 @@
         <v>28</v>
       </c>
       <c r="E10" t="n">
-        <v>70</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="F10" t="n">
         <v>26</v>
@@ -3712,13 +3712,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-28.56</v>
+        <v>-14.37</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>100</v>
+        <v>99.2</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -3743,12 +3743,18 @@
       <c r="R27" s="4" t="n">
         <v>-34.95</v>
       </c>
-      <c r="S27" s="4" t="n"/>
-      <c r="T27" s="4" t="n"/>
+      <c r="S27" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="T27" s="4" t="n">
+        <v>39</v>
+      </c>
       <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" s="4" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="V27" s="4" t="n">
+        <v>-3</v>
+      </c>
       <c r="W27" s="5" t="n">
         <v>0</v>
       </c>
@@ -3766,16 +3772,16 @@
         </is>
       </c>
       <c r="AA27" s="4" t="n">
-        <v>2.62</v>
+        <v>7</v>
       </c>
       <c r="AB27" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC27" s="4" t="n">
-        <v>34.78</v>
+        <v>39.82</v>
       </c>
       <c r="AD27" s="4" t="n">
-        <v>62.6</v>
+        <v>53.18</v>
       </c>
       <c r="AE27" s="4" t="n">
         <v>0</v>
@@ -4053,7 +4059,7 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>14.26</v>
+        <v>14.3</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>99.2</v>
@@ -4119,10 +4125,10 @@
         <v>0.8</v>
       </c>
       <c r="AC30" s="4" t="n">
-        <v>49.75</v>
+        <v>49.8</v>
       </c>
       <c r="AD30" s="4" t="n">
-        <v>14.75</v>
+        <v>14.7</v>
       </c>
       <c r="AE30" s="4" t="n">
         <v>0</v>
@@ -4948,10 +4954,10 @@
         <v>-3.01</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>28</v>
+        <v>28.7</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>72</v>
+        <v>71.3</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -5008,7 +5014,7 @@
         <v>45.19</v>
       </c>
       <c r="AB38" s="4" t="n">
-        <v>28</v>
+        <v>28.7</v>
       </c>
       <c r="AC38" s="4" t="n">
         <v>3.8</v>
@@ -25793,10 +25799,10 @@
         <v>-0.25</v>
       </c>
       <c r="J235" s="4" t="n">
-        <v>49</v>
+        <v>48.7</v>
       </c>
       <c r="K235" s="4" t="n">
-        <v>51</v>
+        <v>51.3</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -38412,13 +38418,13 @@
         </is>
       </c>
       <c r="I351" s="4" t="n">
-        <v>-15.3</v>
+        <v>-11.9</v>
       </c>
       <c r="J351" s="4" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="K351" s="4" t="n">
-        <v>99.40000000000001</v>
+        <v>98.8</v>
       </c>
       <c r="L351" t="inlineStr">
         <is>
@@ -38426,13 +38432,13 @@
         </is>
       </c>
       <c r="M351" s="4" t="n">
-        <v>-20.17</v>
+        <v>-16.77</v>
       </c>
       <c r="N351" s="4" t="n">
         <v>7.13</v>
       </c>
       <c r="O351" s="4" t="n">
-        <v>-15.3</v>
+        <v>-11.9</v>
       </c>
       <c r="P351" s="4" t="n">
         <v>-1.7</v>
@@ -38464,10 +38470,10 @@
         <v>0</v>
       </c>
       <c r="AC351" s="4" t="n">
-        <v>42.35</v>
+        <v>44.05</v>
       </c>
       <c r="AD351" s="4" t="n">
-        <v>57.65</v>
+        <v>55.95</v>
       </c>
       <c r="AE351" s="4" t="n">
         <v>0</v>
@@ -38515,7 +38521,7 @@
         </is>
       </c>
       <c r="I352" s="4" t="n">
-        <v>-49.2</v>
+        <v>-45.8</v>
       </c>
       <c r="J352" s="4" t="n">
         <v>0</v>
@@ -38529,13 +38535,13 @@
         </is>
       </c>
       <c r="M352" s="4" t="n">
-        <v>-53.44</v>
+        <v>-50.03</v>
       </c>
       <c r="N352" s="4" t="n">
         <v>7.13</v>
       </c>
       <c r="O352" s="4" t="n">
-        <v>-49.1</v>
+        <v>-45.69</v>
       </c>
       <c r="P352" s="4" t="n">
         <v>-1.2</v>
@@ -38575,10 +38581,10 @@
         <v>0</v>
       </c>
       <c r="AC352" s="4" t="n">
-        <v>24.87</v>
+        <v>26.54</v>
       </c>
       <c r="AD352" s="4" t="n">
-        <v>73.06</v>
+        <v>71.39</v>
       </c>
       <c r="AE352" s="4" t="n">
         <v>0</v>
@@ -38626,7 +38632,7 @@
         </is>
       </c>
       <c r="I353" s="4" t="n">
-        <v>-40.73</v>
+        <v>-37.33</v>
       </c>
       <c r="J353" s="4" t="n">
         <v>0</v>
@@ -38640,13 +38646,13 @@
         </is>
       </c>
       <c r="M353" s="4" t="n">
-        <v>-43.14</v>
+        <v>-39.74</v>
       </c>
       <c r="N353" s="4" t="n">
         <v>7.13</v>
       </c>
       <c r="O353" s="4" t="n">
-        <v>-40.73</v>
+        <v>-37.33</v>
       </c>
       <c r="P353" s="4" t="n">
         <v>0</v>
@@ -38678,10 +38684,10 @@
         <v>0</v>
       </c>
       <c r="AC353" s="4" t="n">
-        <v>29.64</v>
+        <v>31.34</v>
       </c>
       <c r="AD353" s="4" t="n">
-        <v>70.36</v>
+        <v>68.66</v>
       </c>
       <c r="AE353" s="4" t="n">
         <v>0</v>
@@ -38729,7 +38735,7 @@
         </is>
       </c>
       <c r="I354" s="4" t="n">
-        <v>-32.14</v>
+        <v>-28.73</v>
       </c>
       <c r="J354" s="4" t="n">
         <v>0</v>
@@ -38743,13 +38749,13 @@
         </is>
       </c>
       <c r="M354" s="4" t="n">
-        <v>-31.17</v>
+        <v>-27.76</v>
       </c>
       <c r="N354" s="4" t="n">
         <v>7.13</v>
       </c>
       <c r="O354" s="4" t="n">
-        <v>-32.01</v>
+        <v>-28.6</v>
       </c>
       <c r="P354" s="4" t="n">
         <v>-2.38</v>
@@ -38789,10 +38795,10 @@
         <v>0</v>
       </c>
       <c r="AC354" s="4" t="n">
-        <v>33.03</v>
+        <v>34.69</v>
       </c>
       <c r="AD354" s="4" t="n">
-        <v>64.31999999999999</v>
+        <v>62.66</v>
       </c>
       <c r="AE354" s="4" t="n">
         <v>0</v>
@@ -38840,27 +38846,27 @@
         </is>
       </c>
       <c r="I355" s="4" t="n">
-        <v>-11.57</v>
+        <v>-9.460000000000001</v>
       </c>
       <c r="J355" s="4" t="n">
-        <v>1.2</v>
+        <v>5.5</v>
       </c>
       <c r="K355" s="4" t="n">
-        <v>98.8</v>
+        <v>94.5</v>
       </c>
       <c r="L355" t="inlineStr">
         <is>
-          <t>Safe R</t>
+          <t>Likely R</t>
         </is>
       </c>
       <c r="M355" s="4" t="n">
-        <v>-16.93</v>
+        <v>-13.52</v>
       </c>
       <c r="N355" s="4" t="n">
         <v>7.13</v>
       </c>
       <c r="O355" s="4" t="n">
-        <v>-13.98</v>
+        <v>-10.57</v>
       </c>
       <c r="P355" s="4" t="n">
         <v>-0.7</v>
@@ -38906,10 +38912,10 @@
         <v>0</v>
       </c>
       <c r="AC355" s="4" t="n">
-        <v>42.87</v>
+        <v>43.9</v>
       </c>
       <c r="AD355" s="4" t="n">
-        <v>54.09</v>
+        <v>53.06</v>
       </c>
       <c r="AE355" s="4" t="n">
         <v>0</v>
@@ -51443,10 +51449,10 @@
         <v>2.64</v>
       </c>
       <c r="J473" s="4" t="n">
-        <v>67.8</v>
+        <v>69</v>
       </c>
       <c r="K473" s="4" t="n">
-        <v>32.2</v>
+        <v>31</v>
       </c>
       <c r="L473" t="inlineStr">
         <is>
@@ -53009,10 +53015,10 @@
         <v>2.39</v>
       </c>
       <c r="J487" s="4" t="n">
-        <v>66.5</v>
+        <v>67.8</v>
       </c>
       <c r="K487" s="4" t="n">
-        <v>33.5</v>
+        <v>32.2</v>
       </c>
       <c r="L487" t="inlineStr">
         <is>
@@ -53454,7 +53460,7 @@
         </is>
       </c>
       <c r="I491" s="4" t="n">
-        <v>-21.72</v>
+        <v>-21.62</v>
       </c>
       <c r="J491" s="4" t="n">
         <v>0</v>
@@ -53514,16 +53520,16 @@
         </is>
       </c>
       <c r="AA491" s="4" t="n">
-        <v>27.71</v>
+        <v>27.74</v>
       </c>
       <c r="AB491" s="4" t="n">
         <v>0.2</v>
       </c>
       <c r="AC491" s="4" t="n">
-        <v>19.21</v>
+        <v>19.24</v>
       </c>
       <c r="AD491" s="4" t="n">
-        <v>49.43</v>
+        <v>49.36</v>
       </c>
       <c r="AE491" s="4" t="n">
         <v>3.66</v>
@@ -54247,7 +54253,7 @@
         </is>
       </c>
       <c r="I498" s="4" t="n">
-        <v>-30.33</v>
+        <v>-27.5</v>
       </c>
       <c r="J498" s="4" t="n">
         <v>0</v>
@@ -54261,13 +54267,13 @@
         </is>
       </c>
       <c r="M498" s="4" t="n">
-        <v>-33.26</v>
+        <v>-29.72</v>
       </c>
       <c r="N498" s="4" t="n">
         <v>7.13</v>
       </c>
       <c r="O498" s="4" t="n">
-        <v>-32.79</v>
+        <v>-29.25</v>
       </c>
       <c r="P498" s="4" t="n">
         <v>-3.18</v>
@@ -54313,10 +54319,10 @@
         <v>0</v>
       </c>
       <c r="AC498" s="4" t="n">
-        <v>32.53</v>
+        <v>33.85</v>
       </c>
       <c r="AD498" s="4" t="n">
-        <v>60.85</v>
+        <v>59.53</v>
       </c>
       <c r="AE498" s="4" t="n">
         <v>2.62</v>
@@ -58103,7 +58109,7 @@
         </is>
       </c>
       <c r="J47" s="4" t="n">
-        <v>42.4</v>
+        <v>42.5</v>
       </c>
       <c r="K47" t="n">
         <v>43</v>
@@ -59031,19 +59037,19 @@
         </is>
       </c>
       <c r="J63" s="4" t="n">
-        <v>22.9</v>
+        <v>23.5</v>
       </c>
       <c r="K63" t="n">
         <v>22</v>
       </c>
       <c r="L63" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M63" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N63" s="4" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -59089,7 +59095,7 @@
         </is>
       </c>
       <c r="J64" s="4" t="n">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="K64" t="n">
         <v>8</v>

--- a/output/nowcast.xlsx
+++ b/output/nowcast.xlsx
@@ -550,7 +550,7 @@
         <v>53</v>
       </c>
       <c r="E8" t="n">
-        <v>70</v>
+        <v>69.8</v>
       </c>
       <c r="F8" t="n">
         <v>51</v>
@@ -572,10 +572,10 @@
         <v>190.8</v>
       </c>
       <c r="D9" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E9" t="n">
-        <v>90.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="F9" t="n">
         <v>218</v>
@@ -591,16 +591,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>27.1</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="D10" t="n">
         <v>28</v>
       </c>
       <c r="E10" t="n">
-        <v>70.90000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="F10" t="n">
         <v>26</v>
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>41.1</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="18">
@@ -4059,7 +4059,7 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>14.37</v>
+        <v>14.3</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>99.2</v>
@@ -4119,16 +4119,16 @@
         </is>
       </c>
       <c r="AA30" s="4" t="n">
-        <v>35.45</v>
+        <v>35.52</v>
       </c>
       <c r="AB30" s="4" t="n">
         <v>0.8</v>
       </c>
       <c r="AC30" s="4" t="n">
-        <v>49.82</v>
+        <v>49.81</v>
       </c>
       <c r="AD30" s="4" t="n">
-        <v>14.73</v>
+        <v>14.67</v>
       </c>
       <c r="AE30" s="4" t="n">
         <v>0</v>
@@ -4960,10 +4960,10 @@
         <v>-2.9</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>28.9</v>
+        <v>28.4</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>71.09999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -5020,7 +5020,7 @@
         <v>45.24</v>
       </c>
       <c r="AB38" s="4" t="n">
-        <v>28.9</v>
+        <v>28.4</v>
       </c>
       <c r="AC38" s="4" t="n">
         <v>3.8</v>
@@ -25805,10 +25805,10 @@
         <v>-0.13</v>
       </c>
       <c r="J235" s="4" t="n">
-        <v>48.5</v>
+        <v>49.1</v>
       </c>
       <c r="K235" s="4" t="n">
-        <v>51.5</v>
+        <v>50.9</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -29530,27 +29530,27 @@
         </is>
       </c>
       <c r="I269" s="4" t="n">
-        <v>-1.88</v>
+        <v>0.7</v>
       </c>
       <c r="J269" s="4" t="n">
-        <v>36.7</v>
+        <v>55</v>
       </c>
       <c r="K269" s="4" t="n">
-        <v>63.3</v>
+        <v>45</v>
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>Lean R</t>
+          <t>Toss-up</t>
         </is>
       </c>
       <c r="M269" s="4" t="n">
-        <v>-10.96</v>
+        <v>-6.03</v>
       </c>
       <c r="N269" s="4" t="n">
         <v>7.15</v>
       </c>
       <c r="O269" s="4" t="n">
-        <v>-5.2</v>
+        <v>-0.27</v>
       </c>
       <c r="P269" s="4" t="n">
         <v>-0.41</v>
@@ -29596,10 +29596,10 @@
         <v>0</v>
       </c>
       <c r="AC269" s="4" t="n">
-        <v>47.75</v>
+        <v>49.01</v>
       </c>
       <c r="AD269" s="4" t="n">
-        <v>49.59</v>
+        <v>48.33</v>
       </c>
       <c r="AE269" s="4" t="n">
         <v>0</v>
@@ -29647,13 +29647,13 @@
         </is>
       </c>
       <c r="I270" s="4" t="n">
-        <v>-27.33</v>
+        <v>-23.89</v>
       </c>
       <c r="J270" s="4" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K270" s="4" t="n">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="L270" t="inlineStr">
         <is>
@@ -29661,13 +29661,13 @@
         </is>
       </c>
       <c r="M270" s="4" t="n">
-        <v>-29.92</v>
+        <v>-24.99</v>
       </c>
       <c r="N270" s="4" t="n">
         <v>7.15</v>
       </c>
       <c r="O270" s="4" t="n">
-        <v>-30.74</v>
+        <v>-25.8</v>
       </c>
       <c r="P270" s="4" t="n">
         <v>-2.65</v>
@@ -29713,10 +29713,10 @@
         <v>0</v>
       </c>
       <c r="AC270" s="4" t="n">
-        <v>31.74</v>
+        <v>33.25</v>
       </c>
       <c r="AD270" s="4" t="n">
-        <v>55.62</v>
+        <v>54.11</v>
       </c>
       <c r="AE270" s="4" t="n">
         <v>3.64</v>
@@ -51455,10 +51455,10 @@
         <v>2.74</v>
       </c>
       <c r="J473" s="4" t="n">
-        <v>69.90000000000001</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="K473" s="4" t="n">
-        <v>30.1</v>
+        <v>30.9</v>
       </c>
       <c r="L473" t="inlineStr">
         <is>
@@ -53021,10 +53021,10 @@
         <v>2.37</v>
       </c>
       <c r="J487" s="4" t="n">
-        <v>66.7</v>
+        <v>66.3</v>
       </c>
       <c r="K487" s="4" t="n">
-        <v>33.3</v>
+        <v>33.7</v>
       </c>
       <c r="L487" t="inlineStr">
         <is>
@@ -53466,7 +53466,7 @@
         </is>
       </c>
       <c r="I491" s="4" t="n">
-        <v>-18.61</v>
+        <v>-18.57</v>
       </c>
       <c r="J491" s="4" t="n">
         <v>0</v>
@@ -53526,16 +53526,16 @@
         </is>
       </c>
       <c r="AA491" s="4" t="n">
-        <v>29.96</v>
+        <v>30.02</v>
       </c>
       <c r="AB491" s="4" t="n">
         <v>0.3</v>
       </c>
       <c r="AC491" s="4" t="n">
-        <v>17.81</v>
+        <v>17.73</v>
       </c>
       <c r="AD491" s="4" t="n">
-        <v>48.57</v>
+        <v>48.59</v>
       </c>
       <c r="AE491" s="4" t="n">
         <v>3.66</v>
@@ -58115,19 +58115,19 @@
         </is>
       </c>
       <c r="J47" s="4" t="n">
-        <v>42.9</v>
+        <v>44.6</v>
       </c>
       <c r="K47" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L47" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M47" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>12.8</v>
+        <v>18.4</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -58173,10 +58173,10 @@
         </is>
       </c>
       <c r="J48" s="4" t="n">
-        <v>19.9</v>
+        <v>20.4</v>
       </c>
       <c r="K48" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L48" t="n">
         <v>16</v>
@@ -58185,7 +58185,7 @@
         <v>24</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>

--- a/output/nowcast.xlsx
+++ b/output/nowcast.xlsx
@@ -550,7 +550,7 @@
         <v>53</v>
       </c>
       <c r="E8" t="n">
-        <v>69.8</v>
+        <v>70.5</v>
       </c>
       <c r="F8" t="n">
         <v>51</v>
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>244.2</v>
+        <v>243.9</v>
       </c>
       <c r="C9" t="n">
-        <v>190.8</v>
+        <v>191.1</v>
       </c>
       <c r="D9" t="n">
         <v>240</v>
       </c>
       <c r="E9" t="n">
-        <v>90.40000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F9" t="n">
         <v>218</v>
@@ -600,7 +600,7 @@
         <v>28</v>
       </c>
       <c r="E10" t="n">
-        <v>70.40000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="F10" t="n">
         <v>26</v>
@@ -4059,7 +4059,7 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>14.3</v>
+        <v>14.29</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>99.2</v>
@@ -4119,16 +4119,16 @@
         </is>
       </c>
       <c r="AA30" s="4" t="n">
-        <v>35.52</v>
+        <v>35.5</v>
       </c>
       <c r="AB30" s="4" t="n">
         <v>0.8</v>
       </c>
       <c r="AC30" s="4" t="n">
-        <v>49.81</v>
+        <v>49.79</v>
       </c>
       <c r="AD30" s="4" t="n">
-        <v>14.67</v>
+        <v>14.71</v>
       </c>
       <c r="AE30" s="4" t="n">
         <v>0</v>
@@ -4960,10 +4960,10 @@
         <v>-2.9</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>28.4</v>
+        <v>29.3</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>71.59999999999999</v>
+        <v>70.7</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -5020,7 +5020,7 @@
         <v>45.24</v>
       </c>
       <c r="AB38" s="4" t="n">
-        <v>28.4</v>
+        <v>29.3</v>
       </c>
       <c r="AC38" s="4" t="n">
         <v>3.8</v>
@@ -25805,10 +25805,10 @@
         <v>-0.13</v>
       </c>
       <c r="J235" s="4" t="n">
-        <v>49.1</v>
+        <v>49.8</v>
       </c>
       <c r="K235" s="4" t="n">
-        <v>50.9</v>
+        <v>50.2</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -29530,13 +29530,13 @@
         </is>
       </c>
       <c r="I269" s="4" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="J269" s="4" t="n">
-        <v>55</v>
+        <v>54.9</v>
       </c>
       <c r="K269" s="4" t="n">
-        <v>45</v>
+        <v>45.1</v>
       </c>
       <c r="L269" t="inlineStr">
         <is>
@@ -29544,13 +29544,13 @@
         </is>
       </c>
       <c r="M269" s="4" t="n">
-        <v>-6.03</v>
+        <v>-6.05</v>
       </c>
       <c r="N269" s="4" t="n">
         <v>7.15</v>
       </c>
       <c r="O269" s="4" t="n">
-        <v>-0.27</v>
+        <v>-0.29</v>
       </c>
       <c r="P269" s="4" t="n">
         <v>-0.41</v>
@@ -29596,10 +29596,10 @@
         <v>0</v>
       </c>
       <c r="AC269" s="4" t="n">
-        <v>49.01</v>
+        <v>49</v>
       </c>
       <c r="AD269" s="4" t="n">
-        <v>48.33</v>
+        <v>48.34</v>
       </c>
       <c r="AE269" s="4" t="n">
         <v>0</v>
@@ -29647,7 +29647,7 @@
         </is>
       </c>
       <c r="I270" s="4" t="n">
-        <v>-23.89</v>
+        <v>-23.91</v>
       </c>
       <c r="J270" s="4" t="n">
         <v>0.1</v>
@@ -29661,13 +29661,13 @@
         </is>
       </c>
       <c r="M270" s="4" t="n">
-        <v>-24.99</v>
+        <v>-25.02</v>
       </c>
       <c r="N270" s="4" t="n">
         <v>7.15</v>
       </c>
       <c r="O270" s="4" t="n">
-        <v>-25.8</v>
+        <v>-25.83</v>
       </c>
       <c r="P270" s="4" t="n">
         <v>-2.65</v>
@@ -29713,10 +29713,10 @@
         <v>0</v>
       </c>
       <c r="AC270" s="4" t="n">
-        <v>33.25</v>
+        <v>33.24</v>
       </c>
       <c r="AD270" s="4" t="n">
-        <v>54.11</v>
+        <v>54.12</v>
       </c>
       <c r="AE270" s="4" t="n">
         <v>3.64</v>
@@ -51455,10 +51455,10 @@
         <v>2.74</v>
       </c>
       <c r="J473" s="4" t="n">
-        <v>69.09999999999999</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="K473" s="4" t="n">
-        <v>30.9</v>
+        <v>30.1</v>
       </c>
       <c r="L473" t="inlineStr">
         <is>
@@ -53021,10 +53021,10 @@
         <v>2.37</v>
       </c>
       <c r="J487" s="4" t="n">
-        <v>66.3</v>
+        <v>65.5</v>
       </c>
       <c r="K487" s="4" t="n">
-        <v>33.7</v>
+        <v>34.5</v>
       </c>
       <c r="L487" t="inlineStr">
         <is>
@@ -53466,7 +53466,7 @@
         </is>
       </c>
       <c r="I491" s="4" t="n">
-        <v>-18.57</v>
+        <v>-18.71</v>
       </c>
       <c r="J491" s="4" t="n">
         <v>0</v>
@@ -53526,16 +53526,16 @@
         </is>
       </c>
       <c r="AA491" s="4" t="n">
-        <v>30.02</v>
+        <v>29.93</v>
       </c>
       <c r="AB491" s="4" t="n">
         <v>0.3</v>
       </c>
       <c r="AC491" s="4" t="n">
-        <v>17.73</v>
+        <v>17.76</v>
       </c>
       <c r="AD491" s="4" t="n">
-        <v>48.59</v>
+        <v>48.64</v>
       </c>
       <c r="AE491" s="4" t="n">
         <v>3.66</v>

--- a/output/nowcast.xlsx
+++ b/output/nowcast.xlsx
@@ -541,10 +541,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>52.7</v>
+        <v>52.6</v>
       </c>
       <c r="C8" t="n">
-        <v>47.3</v>
+        <v>47.4</v>
       </c>
       <c r="D8" t="n">
         <v>53</v>
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>244.7</v>
+        <v>245.2</v>
       </c>
       <c r="C9" t="n">
-        <v>190.3</v>
+        <v>189.8</v>
       </c>
       <c r="D9" t="n">
         <v>243</v>
       </c>
       <c r="E9" t="n">
-        <v>91</v>
+        <v>91.5</v>
       </c>
       <c r="F9" t="n">
         <v>218</v>
@@ -600,7 +600,7 @@
         <v>28</v>
       </c>
       <c r="E10" t="n">
-        <v>72.7</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="F10" t="n">
         <v>26</v>
@@ -4059,7 +4059,7 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>14.41</v>
+        <v>14.38</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>99.2</v>
@@ -4119,16 +4119,16 @@
         </is>
       </c>
       <c r="AA30" s="4" t="n">
-        <v>35.11</v>
+        <v>35.09</v>
       </c>
       <c r="AB30" s="4" t="n">
         <v>0.8</v>
       </c>
       <c r="AC30" s="4" t="n">
-        <v>49.52</v>
+        <v>49.48</v>
       </c>
       <c r="AD30" s="4" t="n">
-        <v>15.37</v>
+        <v>15.43</v>
       </c>
       <c r="AE30" s="4" t="n">
         <v>0</v>
@@ -4960,10 +4960,10 @@
         <v>-2.5</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>32.4</v>
+        <v>31.1</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>67.59999999999999</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -5020,7 +5020,7 @@
         <v>45.43</v>
       </c>
       <c r="AB38" s="4" t="n">
-        <v>32.4</v>
+        <v>31.1</v>
       </c>
       <c r="AC38" s="4" t="n">
         <v>3.8</v>
@@ -51455,10 +51455,10 @@
         <v>2.84</v>
       </c>
       <c r="J473" s="4" t="n">
-        <v>70</v>
+        <v>70.2</v>
       </c>
       <c r="K473" s="4" t="n">
-        <v>30</v>
+        <v>29.8</v>
       </c>
       <c r="L473" t="inlineStr">
         <is>
@@ -53021,10 +53021,10 @@
         <v>2.49</v>
       </c>
       <c r="J487" s="4" t="n">
-        <v>67.40000000000001</v>
+        <v>67.7</v>
       </c>
       <c r="K487" s="4" t="n">
-        <v>32.6</v>
+        <v>32.3</v>
       </c>
       <c r="L487" t="inlineStr">
         <is>
@@ -53466,7 +53466,7 @@
         </is>
       </c>
       <c r="I491" s="4" t="n">
-        <v>-20.86</v>
+        <v>-20.87</v>
       </c>
       <c r="J491" s="4" t="n">
         <v>0</v>

--- a/output/nowcast.xlsx
+++ b/output/nowcast.xlsx
@@ -550,7 +550,7 @@
         <v>53</v>
       </c>
       <c r="E8" t="n">
-        <v>72.09999999999999</v>
+        <v>71.2</v>
       </c>
       <c r="F8" t="n">
         <v>51</v>
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>245.2</v>
+        <v>244.6</v>
       </c>
       <c r="C9" t="n">
-        <v>189.8</v>
+        <v>190.4</v>
       </c>
       <c r="D9" t="n">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E9" t="n">
-        <v>91.5</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="F9" t="n">
         <v>218</v>
@@ -600,7 +600,7 @@
         <v>28</v>
       </c>
       <c r="E10" t="n">
-        <v>72.40000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="F10" t="n">
         <v>26</v>
@@ -925,13 +925,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>10.84</v>
+        <v>13.19</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>98.8</v>
+        <v>99.2</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -957,16 +957,16 @@
         <v>-13.8</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>41.99</v>
+        <v>44.15</v>
       </c>
       <c r="T2" s="4" t="n">
-        <v>46.91</v>
+        <v>47.8</v>
       </c>
       <c r="U2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="V2" s="4" t="n">
-        <v>-4.34</v>
+        <v>-3.54</v>
       </c>
       <c r="W2" s="5" t="n">
         <v>0</v>
@@ -983,10 +983,10 @@
         <v>0</v>
       </c>
       <c r="AC2" s="4" t="n">
-        <v>47.18</v>
+        <v>47.59</v>
       </c>
       <c r="AD2" s="4" t="n">
-        <v>52.82</v>
+        <v>52.41</v>
       </c>
       <c r="AE2" s="4" t="n">
         <v>0</v>
@@ -1030,13 +1030,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>-15.68</v>
+        <v>-14.65</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>99.40000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -1062,16 +1062,16 @@
         <v>-30.88</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>38.79</v>
+        <v>39.05</v>
       </c>
       <c r="T3" s="4" t="n">
-        <v>50.66</v>
+        <v>50.78</v>
       </c>
       <c r="U3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V3" s="4" t="n">
-        <v>-10.95</v>
+        <v>-10.32</v>
       </c>
       <c r="W3" s="5" t="n">
         <v>0</v>
@@ -1088,10 +1088,10 @@
         <v>0</v>
       </c>
       <c r="AC3" s="4" t="n">
-        <v>42.16</v>
+        <v>42.68</v>
       </c>
       <c r="AD3" s="4" t="n">
-        <v>57.84</v>
+        <v>57.32</v>
       </c>
       <c r="AE3" s="4" t="n">
         <v>0</v>
@@ -1369,7 +1369,7 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>25.46</v>
+        <v>25.44</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>99.90000000000001</v>
@@ -1410,7 +1410,7 @@
         <v>12</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>20.45</v>
+        <v>20.42</v>
       </c>
       <c r="W6" s="5" t="n">
         <v>24217949</v>
@@ -1427,10 +1427,10 @@
         <v>0</v>
       </c>
       <c r="AC6" s="4" t="n">
-        <v>62.73</v>
+        <v>62.72</v>
       </c>
       <c r="AD6" s="4" t="n">
-        <v>37.27</v>
+        <v>37.28</v>
       </c>
       <c r="AE6" s="4" t="n">
         <v>0</v>
@@ -1632,7 +1632,7 @@
         <v>11</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>18.66</v>
+        <v>18.65</v>
       </c>
       <c r="W8" s="5" t="n">
         <v>0</v>
@@ -1649,10 +1649,10 @@
         <v>0</v>
       </c>
       <c r="AC8" s="4" t="n">
-        <v>59.97</v>
+        <v>59.96</v>
       </c>
       <c r="AD8" s="4" t="n">
-        <v>40.03</v>
+        <v>40.04</v>
       </c>
       <c r="AE8" s="4" t="n">
         <v>0</v>
@@ -1809,13 +1809,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.98</v>
+        <v>1.06</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>57</v>
+        <v>57.5</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>43</v>
+        <v>42.5</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1841,16 +1841,16 @@
         <v>-2.21</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>44.77</v>
+        <v>44.55</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>46.35</v>
+        <v>46.1</v>
       </c>
       <c r="U10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.52</v>
+        <v>-0.49</v>
       </c>
       <c r="W10" s="5" t="n">
         <v>5774631</v>
@@ -1867,10 +1867,10 @@
         <v>0</v>
       </c>
       <c r="AC10" s="4" t="n">
-        <v>50.49</v>
+        <v>50.53</v>
       </c>
       <c r="AD10" s="4" t="n">
-        <v>49.51</v>
+        <v>49.47</v>
       </c>
       <c r="AE10" s="4" t="n">
         <v>0</v>
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>8.66</v>
+        <v>8.67</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>92.40000000000001</v>
@@ -2049,7 +2049,7 @@
         <v>-13.45</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>51.57</v>
+        <v>51.56</v>
       </c>
       <c r="T12" s="4" t="n">
         <v>42.92</v>
@@ -2058,7 +2058,7 @@
         <v>20</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>9.359999999999999</v>
+        <v>9.35</v>
       </c>
       <c r="W12" s="5" t="n">
         <v>19860206</v>
@@ -2075,10 +2075,10 @@
         <v>0</v>
       </c>
       <c r="AC12" s="4" t="n">
-        <v>54.33</v>
+        <v>54.34</v>
       </c>
       <c r="AD12" s="4" t="n">
-        <v>45.67</v>
+        <v>45.66</v>
       </c>
       <c r="AE12" s="4" t="n">
         <v>0</v>
@@ -2126,7 +2126,7 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-32.62</v>
+        <v>-32.63</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>2</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-13.46</v>
+        <v>-13.49</v>
       </c>
       <c r="W13" s="5" t="n">
         <v>229513</v>
@@ -2243,7 +2243,7 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>20.21</v>
+        <v>20.2</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>99.8</v>
@@ -2284,7 +2284,7 @@
         <v>2</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>17.43</v>
+        <v>17.42</v>
       </c>
       <c r="W14" s="5" t="n">
         <v>25619035</v>
@@ -2356,13 +2356,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-6.18</v>
+        <v>-6.33</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>15.1</v>
+        <v>14.6</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>84.90000000000001</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -2388,16 +2388,16 @@
         <v>-16.41</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>44.43</v>
+        <v>44.25</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>48.39</v>
+        <v>48.21</v>
       </c>
       <c r="U15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-3.53</v>
+        <v>-3.55</v>
       </c>
       <c r="W15" s="5" t="n">
         <v>0</v>
@@ -2414,10 +2414,10 @@
         <v>0</v>
       </c>
       <c r="AC15" s="4" t="n">
-        <v>46.91</v>
+        <v>46.83</v>
       </c>
       <c r="AD15" s="4" t="n">
-        <v>53.09</v>
+        <v>53.17</v>
       </c>
       <c r="AE15" s="4" t="n">
         <v>0</v>
@@ -2623,7 +2623,7 @@
         <v>2</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>27.3</v>
+        <v>27.29</v>
       </c>
       <c r="W17" s="5" t="n">
         <v>0</v>
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>13.01</v>
+        <v>13</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>99</v>
@@ -2736,7 +2736,7 @@
         <v>15</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>12.91</v>
+        <v>12.89</v>
       </c>
       <c r="W18" s="5" t="n">
         <v>0</v>
@@ -2761,10 +2761,10 @@
         <v>0</v>
       </c>
       <c r="AC18" s="4" t="n">
-        <v>54.24</v>
+        <v>54.23</v>
       </c>
       <c r="AD18" s="4" t="n">
-        <v>41.75</v>
+        <v>41.76</v>
       </c>
       <c r="AE18" s="4" t="n">
         <v>0</v>
@@ -2808,13 +2808,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>11.99</v>
+        <v>12.01</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>98.8</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -2840,16 +2840,16 @@
         <v>-1.44</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>50.58</v>
+        <v>50.45</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>42.87</v>
+        <v>42.81</v>
       </c>
       <c r="U19" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>8.48</v>
+        <v>8.42</v>
       </c>
       <c r="W19" s="5" t="n">
         <v>5958887</v>
@@ -2874,10 +2874,10 @@
         <v>0</v>
       </c>
       <c r="AC19" s="4" t="n">
-        <v>55.71</v>
+        <v>55.72</v>
       </c>
       <c r="AD19" s="4" t="n">
-        <v>43.79</v>
+        <v>43.78</v>
       </c>
       <c r="AE19" s="4" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>10.19</v>
+        <v>10.18</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>96.3</v>
@@ -2962,7 +2962,7 @@
         <v>10</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>9.42</v>
+        <v>9.41</v>
       </c>
       <c r="W20" s="5" t="n">
         <v>13333454</v>
@@ -3038,13 +3038,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-8.49</v>
+        <v>-7.8</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>8.1</v>
+        <v>10.1</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>91.90000000000001</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -3070,16 +3070,16 @@
         <v>-20.84</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>40.76</v>
+        <v>41</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>44.06</v>
+        <v>43.54</v>
       </c>
       <c r="U21" t="n">
         <v>8</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-3.31</v>
+        <v>-2.48</v>
       </c>
       <c r="W21" s="5" t="n">
         <v>0</v>
@@ -3098,16 +3098,16 @@
         </is>
       </c>
       <c r="AA21" s="4" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AB21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC21" s="4" t="n">
-        <v>45.03</v>
+        <v>45.39</v>
       </c>
       <c r="AD21" s="4" t="n">
-        <v>53.39</v>
+        <v>53.07</v>
       </c>
       <c r="AE21" s="4" t="n">
         <v>0</v>
@@ -3155,7 +3155,7 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-9.76</v>
+        <v>-9.77</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>4.7</v>
@@ -3187,16 +3187,16 @@
         <v>2.82</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>40.69</v>
+        <v>40.61</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>50.06</v>
+        <v>50.18</v>
       </c>
       <c r="U22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-8.699999999999999</v>
+        <v>-8.84</v>
       </c>
       <c r="W22" s="5" t="n">
         <v>908163</v>
@@ -3377,13 +3377,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>4.08</v>
+        <v>4.1</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>77.5</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -3409,16 +3409,16 @@
         <v>-3.15</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>40.86</v>
+        <v>40.71</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>41.45</v>
+        <v>41.23</v>
       </c>
       <c r="U24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="W24" s="5" t="n">
         <v>4285307</v>
@@ -3437,16 +3437,16 @@
         </is>
       </c>
       <c r="AA24" s="4" t="n">
-        <v>4.79</v>
+        <v>4.91</v>
       </c>
       <c r="AB24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC24" s="4" t="n">
-        <v>49.55</v>
+        <v>49.5</v>
       </c>
       <c r="AD24" s="4" t="n">
-        <v>45.66</v>
+        <v>45.59</v>
       </c>
       <c r="AE24" s="4" t="n">
         <v>0</v>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>14.99</v>
+        <v>14.86</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>99.3</v>
@@ -3526,16 +3526,16 @@
         <v>12.68</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>53.51</v>
+        <v>53.42</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>39.74</v>
+        <v>39.92</v>
       </c>
       <c r="U25" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>14.41</v>
+        <v>14.2</v>
       </c>
       <c r="W25" s="5" t="n">
         <v>16594119</v>
@@ -3552,10 +3552,10 @@
         <v>0</v>
       </c>
       <c r="AC25" s="4" t="n">
-        <v>57.49</v>
+        <v>57.43</v>
       </c>
       <c r="AD25" s="4" t="n">
-        <v>42.51</v>
+        <v>42.57</v>
       </c>
       <c r="AE25" s="4" t="n">
         <v>0</v>
@@ -3631,16 +3631,16 @@
         <v>-11.31</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>49.47</v>
+        <v>49.49</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>43.98</v>
+        <v>43.96</v>
       </c>
       <c r="U26" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>5.94</v>
+        <v>5.95</v>
       </c>
       <c r="W26" s="5" t="n">
         <v>15928993</v>
@@ -3712,13 +3712,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-15.52</v>
+        <v>-14.67</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>99.40000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -3744,16 +3744,16 @@
         <v>-34.95</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>36</v>
+        <v>40.31</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>39</v>
+        <v>43.79</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-2.86</v>
+        <v>-4.79</v>
       </c>
       <c r="W27" s="5" t="n">
         <v>0</v>
@@ -3772,16 +3772,16 @@
         </is>
       </c>
       <c r="AA27" s="4" t="n">
-        <v>7</v>
+        <v>3.65</v>
       </c>
       <c r="AB27" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC27" s="4" t="n">
-        <v>39.28</v>
+        <v>41.11</v>
       </c>
       <c r="AD27" s="4" t="n">
-        <v>53.72</v>
+        <v>55.24</v>
       </c>
       <c r="AE27" s="4" t="n">
         <v>0</v>
@@ -3829,7 +3829,7 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>3.86</v>
+        <v>3.85</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>76.7</v>
@@ -3870,7 +3870,7 @@
         <v>7</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="W28" s="5" t="n">
         <v>0</v>
@@ -3895,10 +3895,10 @@
         <v>0</v>
       </c>
       <c r="AC28" s="4" t="n">
-        <v>50</v>
+        <v>49.99</v>
       </c>
       <c r="AD28" s="4" t="n">
-        <v>46.28</v>
+        <v>46.29</v>
       </c>
       <c r="AE28" s="4" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
         <v>20</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>22.4</v>
+        <v>22.39</v>
       </c>
       <c r="W29" s="5" t="n">
         <v>34960533</v>
@@ -4059,7 +4059,7 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>14.38</v>
+        <v>14.4</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>99.2</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="AA30" s="4" t="n">
-        <v>35.09</v>
+        <v>35.08</v>
       </c>
       <c r="AB30" s="4" t="n">
         <v>0.8</v>
@@ -4128,7 +4128,7 @@
         <v>49.48</v>
       </c>
       <c r="AD30" s="4" t="n">
-        <v>15.43</v>
+        <v>15.44</v>
       </c>
       <c r="AE30" s="4" t="n">
         <v>0</v>
@@ -4172,13 +4172,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-8.640000000000001</v>
+        <v>-9.49</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>7.7</v>
+        <v>5.4</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>92.3</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -4204,16 +4204,16 @@
         <v>-18.12</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>39.66</v>
+        <v>38.81</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>47</v>
+        <v>50.67</v>
       </c>
       <c r="U31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-8.16</v>
+        <v>-9.69</v>
       </c>
       <c r="W31" s="5" t="n">
         <v>753609</v>
@@ -4232,16 +4232,16 @@
         </is>
       </c>
       <c r="AA31" s="4" t="n">
-        <v>1.87</v>
+        <v>2.09</v>
       </c>
       <c r="AB31" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC31" s="4" t="n">
-        <v>44.83</v>
+        <v>44.31</v>
       </c>
       <c r="AD31" s="4" t="n">
-        <v>53.3</v>
+        <v>53.6</v>
       </c>
       <c r="AE31" s="4" t="n">
         <v>0</v>
@@ -4394,13 +4394,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-14.15</v>
+        <v>-12.49</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>99.2</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -4426,16 +4426,16 @@
         <v>-30.12</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>33.69</v>
+        <v>32.8</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>48.98</v>
+        <v>46.09</v>
       </c>
       <c r="U33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-13.99</v>
+        <v>-12.62</v>
       </c>
       <c r="W33" s="5" t="n">
         <v>0</v>
@@ -4454,16 +4454,16 @@
         </is>
       </c>
       <c r="AA33" s="4" t="n">
-        <v>7.78</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="AB33" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC33" s="4" t="n">
-        <v>39.58</v>
+        <v>39.4</v>
       </c>
       <c r="AD33" s="4" t="n">
-        <v>52.64</v>
+        <v>50.64</v>
       </c>
       <c r="AE33" s="4" t="n">
         <v>0</v>
@@ -4511,13 +4511,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-3.45</v>
+        <v>-3.44</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>74</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -4543,13 +4543,13 @@
         <v>-13.88</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>46.92</v>
+        <v>46.93</v>
       </c>
       <c r="T34" s="4" t="n">
         <v>48.49</v>
       </c>
       <c r="U34" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="V34" s="4" t="n">
         <v>-0.96</v>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-13.77</v>
+        <v>-13.78</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>0.8</v>
@@ -4669,7 +4669,7 @@
         <v>5</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-3.77</v>
+        <v>-3.79</v>
       </c>
       <c r="W35" s="5" t="n">
         <v>0</v>
@@ -4694,10 +4694,10 @@
         <v>0</v>
       </c>
       <c r="AC35" s="4" t="n">
-        <v>42.54</v>
+        <v>42.53</v>
       </c>
       <c r="AD35" s="4" t="n">
-        <v>56.12</v>
+        <v>56.13</v>
       </c>
       <c r="AE35" s="4" t="n">
         <v>0</v>
@@ -4782,7 +4782,7 @@
         <v>9</v>
       </c>
       <c r="V36" s="4" t="n">
-        <v>3.61</v>
+        <v>3.6</v>
       </c>
       <c r="W36" s="5" t="n">
         <v>1426778</v>
@@ -4957,13 +4957,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>-2.5</v>
+        <v>-2.9</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>31.1</v>
+        <v>28.3</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>68.90000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -4971,13 +4971,13 @@
         </is>
       </c>
       <c r="M38" s="4" t="n">
-        <v>-2.48</v>
+        <v>-2.34</v>
       </c>
       <c r="N38" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="P38" s="4" t="n">
         <v>-0.4</v>
@@ -4989,16 +4989,16 @@
         <v>-13.8</v>
       </c>
       <c r="S38" s="4" t="n">
-        <v>35.9</v>
+        <v>36.59</v>
       </c>
       <c r="T38" s="4" t="n">
-        <v>47.09</v>
+        <v>47.19</v>
       </c>
       <c r="U38" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V38" s="4" t="n">
-        <v>-10.55</v>
+        <v>-10.37</v>
       </c>
       <c r="W38" s="5" t="n">
         <v>0</v>
@@ -5017,16 +5017,16 @@
         </is>
       </c>
       <c r="AA38" s="4" t="n">
-        <v>45.43</v>
+        <v>45.27</v>
       </c>
       <c r="AB38" s="4" t="n">
-        <v>31.1</v>
+        <v>28.3</v>
       </c>
       <c r="AC38" s="4" t="n">
         <v>3.8</v>
       </c>
       <c r="AD38" s="4" t="n">
-        <v>49.57</v>
+        <v>49.73</v>
       </c>
       <c r="AE38" s="4" t="n">
         <v>1.2</v>
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>-24.46</v>
+        <v>-24.23</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>0.1</v>
@@ -5084,13 +5084,13 @@
         </is>
       </c>
       <c r="M39" s="4" t="n">
-        <v>-29.7</v>
+        <v>-29.47</v>
       </c>
       <c r="N39" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O39" s="4" t="n">
-        <v>-24.46</v>
+        <v>-24.23</v>
       </c>
       <c r="P39" s="4" t="n">
         <v>-1.48</v>
@@ -5122,10 +5122,10 @@
         <v>0</v>
       </c>
       <c r="AC39" s="4" t="n">
-        <v>37.77</v>
+        <v>37.89</v>
       </c>
       <c r="AD39" s="4" t="n">
-        <v>62.23</v>
+        <v>62.11</v>
       </c>
       <c r="AE39" s="4" t="n">
         <v>0</v>
@@ -5173,13 +5173,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>54.4</v>
+        <v>55.6</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>45.6</v>
+        <v>44.4</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -5187,13 +5187,13 @@
         </is>
       </c>
       <c r="M40" s="4" t="n">
-        <v>-7.92</v>
+        <v>-7.68</v>
       </c>
       <c r="N40" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>1.45</v>
+        <v>1.68</v>
       </c>
       <c r="P40" s="4" t="n">
         <v>-0.12</v>
@@ -5231,10 +5231,10 @@
         <v>0</v>
       </c>
       <c r="AC40" s="4" t="n">
-        <v>50.31</v>
+        <v>50.39</v>
       </c>
       <c r="AD40" s="4" t="n">
-        <v>49.69</v>
+        <v>49.61</v>
       </c>
       <c r="AE40" s="4" t="n">
         <v>0</v>
@@ -5282,7 +5282,7 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>-37.8</v>
+        <v>-37.56</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>0</v>
@@ -5296,13 +5296,13 @@
         </is>
       </c>
       <c r="M41" s="4" t="n">
-        <v>-40.47</v>
+        <v>-40.24</v>
       </c>
       <c r="N41" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O41" s="4" t="n">
-        <v>-37.8</v>
+        <v>-37.56</v>
       </c>
       <c r="P41" s="4" t="n">
         <v>-2.33</v>
@@ -5334,10 +5334,10 @@
         <v>0</v>
       </c>
       <c r="AC41" s="4" t="n">
-        <v>31.1</v>
+        <v>31.22</v>
       </c>
       <c r="AD41" s="4" t="n">
-        <v>68.90000000000001</v>
+        <v>68.78</v>
       </c>
       <c r="AE41" s="4" t="n">
         <v>0</v>
@@ -5385,7 +5385,7 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>-58.01</v>
+        <v>-57.77</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>0</v>
@@ -5399,13 +5399,13 @@
         </is>
       </c>
       <c r="M42" s="4" t="n">
-        <v>-60.72</v>
+        <v>-60.49</v>
       </c>
       <c r="N42" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>-58.01</v>
+        <v>-57.77</v>
       </c>
       <c r="P42" s="4" t="n">
         <v>-2.23</v>
@@ -5437,10 +5437,10 @@
         <v>0</v>
       </c>
       <c r="AC42" s="4" t="n">
-        <v>21</v>
+        <v>21.11</v>
       </c>
       <c r="AD42" s="4" t="n">
-        <v>79</v>
+        <v>78.89</v>
       </c>
       <c r="AE42" s="4" t="n">
         <v>0</v>
@@ -5488,13 +5488,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>-19.7</v>
+        <v>-19.47</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>99.8</v>
+        <v>99.7</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -5502,13 +5502,13 @@
         </is>
       </c>
       <c r="M43" s="4" t="n">
-        <v>-24.26</v>
+        <v>-24.03</v>
       </c>
       <c r="N43" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O43" s="4" t="n">
-        <v>-19.7</v>
+        <v>-19.47</v>
       </c>
       <c r="P43" s="4" t="n">
         <v>-0.5</v>
@@ -5540,10 +5540,10 @@
         <v>0</v>
       </c>
       <c r="AC43" s="4" t="n">
-        <v>40.15</v>
+        <v>40.26</v>
       </c>
       <c r="AD43" s="4" t="n">
-        <v>59.85</v>
+        <v>59.74</v>
       </c>
       <c r="AE43" s="4" t="n">
         <v>0</v>
@@ -5591,7 +5591,7 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>-27.28</v>
+        <v>-27.05</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>0</v>
@@ -5605,13 +5605,13 @@
         </is>
       </c>
       <c r="M44" s="4" t="n">
-        <v>-29.78</v>
+        <v>-29.55</v>
       </c>
       <c r="N44" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O44" s="4" t="n">
-        <v>-27.28</v>
+        <v>-27.05</v>
       </c>
       <c r="P44" s="4" t="n">
         <v>-2.05</v>
@@ -5643,10 +5643,10 @@
         <v>0</v>
       </c>
       <c r="AC44" s="4" t="n">
-        <v>36.36</v>
+        <v>36.47</v>
       </c>
       <c r="AD44" s="4" t="n">
-        <v>63.64</v>
+        <v>63.53</v>
       </c>
       <c r="AE44" s="4" t="n">
         <v>0</v>
@@ -5694,7 +5694,7 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>37.42</v>
+        <v>37.65</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>100</v>
@@ -5708,13 +5708,13 @@
         </is>
       </c>
       <c r="M45" s="4" t="n">
-        <v>24.45</v>
+        <v>24.69</v>
       </c>
       <c r="N45" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O45" s="4" t="n">
-        <v>37.42</v>
+        <v>37.65</v>
       </c>
       <c r="P45" s="4" t="n">
         <v>1.49</v>
@@ -5746,10 +5746,10 @@
         <v>0</v>
       </c>
       <c r="AC45" s="4" t="n">
-        <v>68.70999999999999</v>
+        <v>68.83</v>
       </c>
       <c r="AD45" s="4" t="n">
-        <v>31.29</v>
+        <v>31.17</v>
       </c>
       <c r="AE45" s="4" t="n">
         <v>0</v>
@@ -6227,7 +6227,7 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>6.9</v>
+        <v>6.89</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>87.2</v>
@@ -6268,7 +6268,7 @@
         <v>1</v>
       </c>
       <c r="V50" s="4" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="W50" s="5" t="n">
         <v>5038605</v>
@@ -7208,7 +7208,7 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>21.03</v>
+        <v>21.02</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>99.8</v>
@@ -7228,7 +7228,7 @@
         <v>7.28</v>
       </c>
       <c r="O59" s="4" t="n">
-        <v>21.03</v>
+        <v>21.02</v>
       </c>
       <c r="P59" s="4" t="n">
         <v>0.18</v>
@@ -7325,7 +7325,7 @@
         </is>
       </c>
       <c r="M60" s="4" t="n">
-        <v>27.5</v>
+        <v>27.49</v>
       </c>
       <c r="N60" s="4" t="n">
         <v>7.28</v>
@@ -7363,10 +7363,10 @@
         <v>0</v>
       </c>
       <c r="AC60" s="4" t="n">
-        <v>67.56999999999999</v>
+        <v>67.56</v>
       </c>
       <c r="AD60" s="4" t="n">
-        <v>32.43</v>
+        <v>32.44</v>
       </c>
       <c r="AE60" s="4" t="n">
         <v>0</v>
@@ -7634,7 +7634,7 @@
         </is>
       </c>
       <c r="M63" s="4" t="n">
-        <v>-18.56</v>
+        <v>-18.57</v>
       </c>
       <c r="N63" s="4" t="n">
         <v>7.28</v>
@@ -7836,13 +7836,13 @@
         </is>
       </c>
       <c r="M65" s="4" t="n">
-        <v>16.31</v>
+        <v>16.3</v>
       </c>
       <c r="N65" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O65" s="4" t="n">
-        <v>23.72</v>
+        <v>23.71</v>
       </c>
       <c r="P65" s="4" t="n">
         <v>0</v>
@@ -7939,7 +7939,7 @@
         </is>
       </c>
       <c r="M66" s="4" t="n">
-        <v>38.85</v>
+        <v>38.84</v>
       </c>
       <c r="N66" s="4" t="n">
         <v>7.28</v>
@@ -8028,7 +8028,7 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>32.43</v>
+        <v>32.42</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>100</v>
@@ -8048,7 +8048,7 @@
         <v>7.28</v>
       </c>
       <c r="O67" s="4" t="n">
-        <v>32.43</v>
+        <v>32.42</v>
       </c>
       <c r="P67" s="4" t="n">
         <v>2.68</v>
@@ -8183,10 +8183,10 @@
         <v>0</v>
       </c>
       <c r="AC68" s="4" t="n">
-        <v>72.34999999999999</v>
+        <v>72.34</v>
       </c>
       <c r="AD68" s="4" t="n">
-        <v>27.65</v>
+        <v>27.66</v>
       </c>
       <c r="AE68" s="4" t="n">
         <v>0</v>
@@ -8244,13 +8244,13 @@
         </is>
       </c>
       <c r="M69" s="4" t="n">
-        <v>73.70999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="N69" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O69" s="4" t="n">
-        <v>80.68000000000001</v>
+        <v>80.67</v>
       </c>
       <c r="P69" s="4" t="n">
         <v>0</v>
@@ -8347,7 +8347,7 @@
         </is>
       </c>
       <c r="M70" s="4" t="n">
-        <v>80.45999999999999</v>
+        <v>80.45</v>
       </c>
       <c r="N70" s="4" t="n">
         <v>7.28</v>
@@ -8488,10 +8488,10 @@
         <v>0</v>
       </c>
       <c r="AC71" s="4" t="n">
-        <v>61.7</v>
+        <v>61.69</v>
       </c>
       <c r="AD71" s="4" t="n">
-        <v>38.3</v>
+        <v>38.31</v>
       </c>
       <c r="AE71" s="4" t="n">
         <v>0</v>
@@ -8559,7 +8559,7 @@
         <v>7.28</v>
       </c>
       <c r="O72" s="4" t="n">
-        <v>49.45</v>
+        <v>49.44</v>
       </c>
       <c r="P72" s="4" t="n">
         <v>0</v>
@@ -8656,7 +8656,7 @@
         </is>
       </c>
       <c r="M73" s="4" t="n">
-        <v>53.48</v>
+        <v>53.47</v>
       </c>
       <c r="N73" s="4" t="n">
         <v>7.28</v>
@@ -8745,7 +8745,7 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>64.64</v>
+        <v>64.63</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>100</v>
@@ -8765,7 +8765,7 @@
         <v>7.28</v>
       </c>
       <c r="O74" s="4" t="n">
-        <v>64.64</v>
+        <v>64.63</v>
       </c>
       <c r="P74" s="4" t="n">
         <v>3.2</v>
@@ -8848,7 +8848,7 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>50.74</v>
+        <v>50.73</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>100</v>
@@ -8862,13 +8862,13 @@
         </is>
       </c>
       <c r="M75" s="4" t="n">
-        <v>44.83</v>
+        <v>44.82</v>
       </c>
       <c r="N75" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O75" s="4" t="n">
-        <v>50.74</v>
+        <v>50.73</v>
       </c>
       <c r="P75" s="4" t="n">
         <v>3.64</v>
@@ -8965,7 +8965,7 @@
         </is>
       </c>
       <c r="M76" s="4" t="n">
-        <v>34.76</v>
+        <v>34.75</v>
       </c>
       <c r="N76" s="4" t="n">
         <v>7.28</v>
@@ -9003,10 +9003,10 @@
         <v>0</v>
       </c>
       <c r="AC76" s="4" t="n">
-        <v>72.76000000000001</v>
+        <v>72.75</v>
       </c>
       <c r="AD76" s="4" t="n">
-        <v>27.24</v>
+        <v>27.25</v>
       </c>
       <c r="AE76" s="4" t="n">
         <v>0</v>
@@ -9068,7 +9068,7 @@
         </is>
       </c>
       <c r="M77" s="4" t="n">
-        <v>38.32</v>
+        <v>38.31</v>
       </c>
       <c r="N77" s="4" t="n">
         <v>7.28</v>
@@ -9106,10 +9106,10 @@
         <v>0</v>
       </c>
       <c r="AC77" s="4" t="n">
-        <v>76.04000000000001</v>
+        <v>76.03</v>
       </c>
       <c r="AD77" s="4" t="n">
-        <v>23.96</v>
+        <v>23.97</v>
       </c>
       <c r="AE77" s="4" t="n">
         <v>0</v>
@@ -9157,7 +9157,7 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>-26.76</v>
+        <v>-26.77</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>0</v>
@@ -9177,7 +9177,7 @@
         <v>7.28</v>
       </c>
       <c r="O78" s="4" t="n">
-        <v>-26.76</v>
+        <v>-26.77</v>
       </c>
       <c r="P78" s="4" t="n">
         <v>-2.46</v>
@@ -9260,7 +9260,7 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>22.63</v>
+        <v>22.62</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>99.90000000000001</v>
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="M79" s="4" t="n">
-        <v>11.46</v>
+        <v>11.45</v>
       </c>
       <c r="N79" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O79" s="4" t="n">
-        <v>22.63</v>
+        <v>22.62</v>
       </c>
       <c r="P79" s="4" t="n">
         <v>0.89</v>
@@ -9383,7 +9383,7 @@
         <v>7.28</v>
       </c>
       <c r="O80" s="4" t="n">
-        <v>9.58</v>
+        <v>9.57</v>
       </c>
       <c r="P80" s="4" t="n">
         <v>0.28</v>
@@ -9421,10 +9421,10 @@
         <v>0</v>
       </c>
       <c r="AC80" s="4" t="n">
-        <v>54.32</v>
+        <v>54.31</v>
       </c>
       <c r="AD80" s="4" t="n">
-        <v>45.68</v>
+        <v>45.69</v>
       </c>
       <c r="AE80" s="4" t="n">
         <v>0</v>
@@ -9486,7 +9486,7 @@
         </is>
       </c>
       <c r="M81" s="4" t="n">
-        <v>-17.06</v>
+        <v>-17.07</v>
       </c>
       <c r="N81" s="4" t="n">
         <v>7.28</v>
@@ -9575,7 +9575,7 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>38.24</v>
+        <v>38.23</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>100</v>
@@ -9595,7 +9595,7 @@
         <v>7.28</v>
       </c>
       <c r="O82" s="4" t="n">
-        <v>38.24</v>
+        <v>38.23</v>
       </c>
       <c r="P82" s="4" t="n">
         <v>1.22</v>
@@ -9678,7 +9678,7 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>21.54</v>
+        <v>21.53</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>99.8</v>
@@ -9698,7 +9698,7 @@
         <v>7.28</v>
       </c>
       <c r="O83" s="4" t="n">
-        <v>21.54</v>
+        <v>21.53</v>
       </c>
       <c r="P83" s="4" t="n">
         <v>0.58</v>
@@ -9777,7 +9777,7 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>27.62</v>
+        <v>27.61</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>100</v>
@@ -9797,7 +9797,7 @@
         <v>7.28</v>
       </c>
       <c r="O84" s="4" t="n">
-        <v>27.62</v>
+        <v>27.61</v>
       </c>
       <c r="P84" s="4" t="n">
         <v>0.64</v>
@@ -9880,7 +9880,7 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>28.66</v>
+        <v>28.65</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>100</v>
@@ -9900,7 +9900,7 @@
         <v>7.28</v>
       </c>
       <c r="O85" s="4" t="n">
-        <v>28.66</v>
+        <v>28.65</v>
       </c>
       <c r="P85" s="4" t="n">
         <v>1.78</v>
@@ -9983,7 +9983,7 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>41.8</v>
+        <v>41.79</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>100</v>
@@ -9997,13 +9997,13 @@
         </is>
       </c>
       <c r="M86" s="4" t="n">
-        <v>29.46</v>
+        <v>29.45</v>
       </c>
       <c r="N86" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O86" s="4" t="n">
-        <v>41.8</v>
+        <v>41.79</v>
       </c>
       <c r="P86" s="4" t="n">
         <v>2.46</v>
@@ -10100,13 +10100,13 @@
         </is>
       </c>
       <c r="M87" s="4" t="n">
-        <v>41.02</v>
+        <v>41.01</v>
       </c>
       <c r="N87" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O87" s="4" t="n">
-        <v>55.14</v>
+        <v>55.13</v>
       </c>
       <c r="P87" s="4" t="n">
         <v>0</v>
@@ -10241,10 +10241,10 @@
         <v>0</v>
       </c>
       <c r="AC88" s="4" t="n">
-        <v>76.62</v>
+        <v>76.61</v>
       </c>
       <c r="AD88" s="4" t="n">
-        <v>23.38</v>
+        <v>23.39</v>
       </c>
       <c r="AE88" s="4" t="n">
         <v>0</v>
@@ -10292,7 +10292,7 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>17.88</v>
+        <v>17.87</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>99.59999999999999</v>
@@ -10306,13 +10306,13 @@
         </is>
       </c>
       <c r="M89" s="4" t="n">
-        <v>17.56</v>
+        <v>17.55</v>
       </c>
       <c r="N89" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O89" s="4" t="n">
-        <v>17.88</v>
+        <v>17.87</v>
       </c>
       <c r="P89" s="4" t="n">
         <v>1.34</v>
@@ -10409,7 +10409,7 @@
         </is>
       </c>
       <c r="M90" s="4" t="n">
-        <v>29.58</v>
+        <v>29.57</v>
       </c>
       <c r="N90" s="4" t="n">
         <v>7.28</v>
@@ -10447,10 +10447,10 @@
         <v>0</v>
       </c>
       <c r="AC90" s="4" t="n">
-        <v>70.63</v>
+        <v>70.62</v>
       </c>
       <c r="AD90" s="4" t="n">
-        <v>29.37</v>
+        <v>29.38</v>
       </c>
       <c r="AE90" s="4" t="n">
         <v>0</v>
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="M91" s="4" t="n">
-        <v>15.93</v>
+        <v>15.92</v>
       </c>
       <c r="N91" s="4" t="n">
         <v>7.28</v>
@@ -10550,10 +10550,10 @@
         <v>0</v>
       </c>
       <c r="AC91" s="4" t="n">
-        <v>66.86</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="AD91" s="4" t="n">
-        <v>33.14</v>
+        <v>33.15</v>
       </c>
       <c r="AE91" s="4" t="n">
         <v>0</v>
@@ -10615,13 +10615,13 @@
         </is>
       </c>
       <c r="M92" s="4" t="n">
-        <v>58.49</v>
+        <v>58.48</v>
       </c>
       <c r="N92" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O92" s="4" t="n">
-        <v>69.58</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="P92" s="4" t="n">
         <v>0</v>
@@ -10821,7 +10821,7 @@
         </is>
       </c>
       <c r="M94" s="4" t="n">
-        <v>43.08</v>
+        <v>43.07</v>
       </c>
       <c r="N94" s="4" t="n">
         <v>7.28</v>
@@ -10930,7 +10930,7 @@
         <v>7.28</v>
       </c>
       <c r="O95" s="4" t="n">
-        <v>78.34</v>
+        <v>78.33</v>
       </c>
       <c r="P95" s="4" t="n">
         <v>0</v>
@@ -11009,7 +11009,7 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>27.79</v>
+        <v>27.78</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>100</v>
@@ -11023,13 +11023,13 @@
         </is>
       </c>
       <c r="M96" s="4" t="n">
-        <v>18.64</v>
+        <v>18.63</v>
       </c>
       <c r="N96" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O96" s="4" t="n">
-        <v>27.79</v>
+        <v>27.78</v>
       </c>
       <c r="P96" s="4" t="n">
         <v>0</v>
@@ -11112,7 +11112,7 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>29.3</v>
+        <v>29.29</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>100</v>
@@ -11126,13 +11126,13 @@
         </is>
       </c>
       <c r="M97" s="4" t="n">
-        <v>15.66</v>
+        <v>15.65</v>
       </c>
       <c r="N97" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O97" s="4" t="n">
-        <v>29.3</v>
+        <v>29.29</v>
       </c>
       <c r="P97" s="4" t="n">
         <v>2.21</v>
@@ -11229,13 +11229,13 @@
         </is>
       </c>
       <c r="M98" s="4" t="n">
-        <v>-10.56</v>
+        <v>-10.57</v>
       </c>
       <c r="N98" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O98" s="4" t="n">
-        <v>-2.92</v>
+        <v>-2.93</v>
       </c>
       <c r="P98" s="4" t="n">
         <v>0</v>
@@ -11318,7 +11318,7 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>32.97</v>
+        <v>32.96</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>100</v>
@@ -11332,13 +11332,13 @@
         </is>
       </c>
       <c r="M99" s="4" t="n">
-        <v>19.2</v>
+        <v>19.19</v>
       </c>
       <c r="N99" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O99" s="4" t="n">
-        <v>32.97</v>
+        <v>32.96</v>
       </c>
       <c r="P99" s="4" t="n">
         <v>2.69</v>
@@ -11435,7 +11435,7 @@
         </is>
       </c>
       <c r="M100" s="4" t="n">
-        <v>16.44</v>
+        <v>16.43</v>
       </c>
       <c r="N100" s="4" t="n">
         <v>7.28</v>
@@ -11538,7 +11538,7 @@
         </is>
       </c>
       <c r="M101" s="4" t="n">
-        <v>56.41</v>
+        <v>56.4</v>
       </c>
       <c r="N101" s="4" t="n">
         <v>7.28</v>
@@ -11627,7 +11627,7 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>60.76</v>
+        <v>60.75</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>100</v>
@@ -11647,7 +11647,7 @@
         <v>7.28</v>
       </c>
       <c r="O102" s="4" t="n">
-        <v>60.76</v>
+        <v>60.75</v>
       </c>
       <c r="P102" s="4" t="n">
         <v>2.02</v>
@@ -11744,7 +11744,7 @@
         </is>
       </c>
       <c r="M103" s="4" t="n">
-        <v>7.88</v>
+        <v>7.87</v>
       </c>
       <c r="N103" s="4" t="n">
         <v>7.28</v>
@@ -11833,7 +11833,7 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>41.19</v>
+        <v>41.18</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>100</v>
@@ -11853,7 +11853,7 @@
         <v>7.28</v>
       </c>
       <c r="O104" s="4" t="n">
-        <v>41.19</v>
+        <v>41.18</v>
       </c>
       <c r="P104" s="4" t="n">
         <v>1.75</v>
@@ -12035,7 +12035,7 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>11.51</v>
+        <v>11.5</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>98.8</v>
@@ -12049,13 +12049,13 @@
         </is>
       </c>
       <c r="M106" s="4" t="n">
-        <v>5.25</v>
+        <v>5.24</v>
       </c>
       <c r="N106" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O106" s="4" t="n">
-        <v>14.02</v>
+        <v>14.01</v>
       </c>
       <c r="P106" s="4" t="n">
         <v>0.63</v>
@@ -12158,7 +12158,7 @@
         </is>
       </c>
       <c r="M107" s="4" t="n">
-        <v>14.17</v>
+        <v>14.16</v>
       </c>
       <c r="N107" s="4" t="n">
         <v>7.28</v>
@@ -12196,10 +12196,10 @@
         <v>0</v>
       </c>
       <c r="AC107" s="4" t="n">
-        <v>61.66</v>
+        <v>61.65</v>
       </c>
       <c r="AD107" s="4" t="n">
-        <v>38.34</v>
+        <v>38.35</v>
       </c>
       <c r="AE107" s="4" t="n">
         <v>0</v>
@@ -12299,10 +12299,10 @@
         <v>0</v>
       </c>
       <c r="AC108" s="4" t="n">
-        <v>65.39</v>
+        <v>65.38</v>
       </c>
       <c r="AD108" s="4" t="n">
-        <v>34.61</v>
+        <v>34.62</v>
       </c>
       <c r="AE108" s="4" t="n">
         <v>0</v>
@@ -12350,7 +12350,7 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>29.22</v>
+        <v>29.21</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>100</v>
@@ -12364,13 +12364,13 @@
         </is>
       </c>
       <c r="M109" s="4" t="n">
-        <v>21.06</v>
+        <v>21.05</v>
       </c>
       <c r="N109" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O109" s="4" t="n">
-        <v>29.22</v>
+        <v>29.21</v>
       </c>
       <c r="P109" s="4" t="n">
         <v>0</v>
@@ -12505,10 +12505,10 @@
         <v>0</v>
       </c>
       <c r="AC110" s="4" t="n">
-        <v>70.84999999999999</v>
+        <v>70.84</v>
       </c>
       <c r="AD110" s="4" t="n">
-        <v>29.15</v>
+        <v>29.16</v>
       </c>
       <c r="AE110" s="4" t="n">
         <v>0</v>
@@ -12932,7 +12932,7 @@
         <v>1</v>
       </c>
       <c r="V114" s="4" t="n">
-        <v>-7.42</v>
+        <v>-7.43</v>
       </c>
       <c r="W114" s="5" t="n">
         <v>13041221</v>
@@ -13347,13 +13347,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>9</v>
+        <v>8.98</v>
       </c>
       <c r="J118" s="4" t="n">
-        <v>93.3</v>
+        <v>93.2</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="L118" t="inlineStr">
         <is>
@@ -13388,7 +13388,7 @@
         <v>1</v>
       </c>
       <c r="V118" s="4" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="W118" s="5" t="n">
         <v>8578254</v>
@@ -13413,10 +13413,10 @@
         <v>0</v>
       </c>
       <c r="AC118" s="4" t="n">
-        <v>52.47</v>
+        <v>52.46</v>
       </c>
       <c r="AD118" s="4" t="n">
-        <v>43.81</v>
+        <v>43.82</v>
       </c>
       <c r="AE118" s="4" t="n">
         <v>0</v>
@@ -14744,13 +14744,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>1.12</v>
+        <v>-1.07</v>
       </c>
       <c r="J131" s="4" t="n">
-        <v>57.9</v>
+        <v>42.4</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>42.1</v>
+        <v>57.6</v>
       </c>
       <c r="L131" t="inlineStr">
         <is>
@@ -14775,12 +14775,18 @@
       <c r="R131" s="4" t="n">
         <v>-12.62</v>
       </c>
-      <c r="S131" s="4" t="n"/>
-      <c r="T131" s="4" t="n"/>
+      <c r="S131" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="T131" s="4" t="n">
+        <v>45</v>
+      </c>
       <c r="U131" t="n">
-        <v>0</v>
-      </c>
-      <c r="V131" s="4" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="V131" s="4" t="n">
+        <v>-3</v>
+      </c>
       <c r="W131" s="5" t="n">
         <v>2137358</v>
       </c>
@@ -14804,10 +14810,10 @@
         <v>0</v>
       </c>
       <c r="AC131" s="4" t="n">
-        <v>49.55</v>
+        <v>48.48</v>
       </c>
       <c r="AD131" s="4" t="n">
-        <v>48.46</v>
+        <v>49.53</v>
       </c>
       <c r="AE131" s="4" t="n">
         <v>0</v>
@@ -16749,7 +16755,7 @@
         <v>1</v>
       </c>
       <c r="V149" s="4" t="n">
-        <v>11.6</v>
+        <v>11.59</v>
       </c>
       <c r="W149" s="5" t="n">
         <v>5093834</v>
@@ -16936,13 +16942,13 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>-2.81</v>
+        <v>-2.82</v>
       </c>
       <c r="J151" s="4" t="n">
-        <v>30.3</v>
+        <v>30.2</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>69.7</v>
+        <v>69.8</v>
       </c>
       <c r="L151" t="inlineStr">
         <is>
@@ -16977,7 +16983,7 @@
         <v>2</v>
       </c>
       <c r="V151" s="4" t="n">
-        <v>-1.98</v>
+        <v>-2.02</v>
       </c>
       <c r="W151" s="5" t="n">
         <v>1339984</v>
@@ -16994,10 +17000,10 @@
         <v>0</v>
       </c>
       <c r="AC151" s="4" t="n">
-        <v>48.6</v>
+        <v>48.59</v>
       </c>
       <c r="AD151" s="4" t="n">
-        <v>51.4</v>
+        <v>51.41</v>
       </c>
       <c r="AE151" s="4" t="n">
         <v>0</v>
@@ -17152,13 +17158,13 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>-6.65</v>
+        <v>-6.62</v>
       </c>
       <c r="J153" s="4" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>86.40000000000001</v>
+        <v>86.3</v>
       </c>
       <c r="L153" t="inlineStr">
         <is>
@@ -17166,13 +17172,13 @@
         </is>
       </c>
       <c r="M153" s="4" t="n">
-        <v>-11.89</v>
+        <v>-11.86</v>
       </c>
       <c r="N153" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O153" s="4" t="n">
-        <v>-6.65</v>
+        <v>-6.62</v>
       </c>
       <c r="P153" s="4" t="n">
         <v>-1.74</v>
@@ -17204,10 +17210,10 @@
         <v>0</v>
       </c>
       <c r="AC153" s="4" t="n">
-        <v>46.68</v>
+        <v>46.69</v>
       </c>
       <c r="AD153" s="4" t="n">
-        <v>53.32</v>
+        <v>53.31</v>
       </c>
       <c r="AE153" s="4" t="n">
         <v>0</v>
@@ -17255,7 +17261,7 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>25.9</v>
+        <v>25.92</v>
       </c>
       <c r="J154" s="4" t="n">
         <v>100</v>
@@ -17269,13 +17275,13 @@
         </is>
       </c>
       <c r="M154" s="4" t="n">
-        <v>11.97</v>
+        <v>12</v>
       </c>
       <c r="N154" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O154" s="4" t="n">
-        <v>25.9</v>
+        <v>25.92</v>
       </c>
       <c r="P154" s="4" t="n">
         <v>1.22</v>
@@ -17307,10 +17313,10 @@
         <v>0</v>
       </c>
       <c r="AC154" s="4" t="n">
-        <v>62.95</v>
+        <v>62.96</v>
       </c>
       <c r="AD154" s="4" t="n">
-        <v>37.05</v>
+        <v>37.04</v>
       </c>
       <c r="AE154" s="4" t="n">
         <v>0</v>
@@ -17358,7 +17364,7 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>-18.06</v>
+        <v>-18.05</v>
       </c>
       <c r="J155" s="4" t="n">
         <v>0.4</v>
@@ -17372,13 +17378,13 @@
         </is>
       </c>
       <c r="M155" s="4" t="n">
-        <v>-26.79</v>
+        <v>-26.77</v>
       </c>
       <c r="N155" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O155" s="4" t="n">
-        <v>-27.26</v>
+        <v>-27.24</v>
       </c>
       <c r="P155" s="4" t="n">
         <v>-1.64</v>
@@ -17467,7 +17473,7 @@
         </is>
       </c>
       <c r="I156" s="4" t="n">
-        <v>67.13</v>
+        <v>67.16</v>
       </c>
       <c r="J156" s="4" t="n">
         <v>100</v>
@@ -17481,13 +17487,13 @@
         </is>
       </c>
       <c r="M156" s="4" t="n">
-        <v>57.97</v>
+        <v>57.99</v>
       </c>
       <c r="N156" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O156" s="4" t="n">
-        <v>67.13</v>
+        <v>67.16</v>
       </c>
       <c r="P156" s="4" t="n">
         <v>0</v>
@@ -17519,10 +17525,10 @@
         <v>0</v>
       </c>
       <c r="AC156" s="4" t="n">
-        <v>83.56999999999999</v>
+        <v>83.58</v>
       </c>
       <c r="AD156" s="4" t="n">
-        <v>16.43</v>
+        <v>16.42</v>
       </c>
       <c r="AE156" s="4" t="n">
         <v>0</v>
@@ -17570,7 +17576,7 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>85.59</v>
+        <v>85.61</v>
       </c>
       <c r="J157" s="4" t="n">
         <v>100</v>
@@ -17584,13 +17590,13 @@
         </is>
       </c>
       <c r="M157" s="4" t="n">
-        <v>76.37</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="N157" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O157" s="4" t="n">
-        <v>85.59</v>
+        <v>85.61</v>
       </c>
       <c r="P157" s="4" t="n">
         <v>0</v>
@@ -17622,10 +17628,10 @@
         <v>0</v>
       </c>
       <c r="AC157" s="4" t="n">
-        <v>92.79000000000001</v>
+        <v>92.81</v>
       </c>
       <c r="AD157" s="4" t="n">
-        <v>7.21</v>
+        <v>7.19</v>
       </c>
       <c r="AE157" s="4" t="n">
         <v>0</v>
@@ -17673,7 +17679,7 @@
         </is>
       </c>
       <c r="I158" s="4" t="n">
-        <v>65.08</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J158" s="4" t="n">
         <v>100</v>
@@ -17687,13 +17693,13 @@
         </is>
       </c>
       <c r="M158" s="4" t="n">
-        <v>53.5</v>
+        <v>53.52</v>
       </c>
       <c r="N158" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O158" s="4" t="n">
-        <v>65.08</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="P158" s="4" t="n">
         <v>2.26</v>
@@ -17725,10 +17731,10 @@
         <v>0</v>
       </c>
       <c r="AC158" s="4" t="n">
-        <v>82.54000000000001</v>
+        <v>82.55</v>
       </c>
       <c r="AD158" s="4" t="n">
-        <v>17.46</v>
+        <v>17.45</v>
       </c>
       <c r="AE158" s="4" t="n">
         <v>0</v>
@@ -17776,7 +17782,7 @@
         </is>
       </c>
       <c r="I159" s="4" t="n">
-        <v>-11.39</v>
+        <v>-11.38</v>
       </c>
       <c r="J159" s="4" t="n">
         <v>1.3</v>
@@ -17790,13 +17796,13 @@
         </is>
       </c>
       <c r="M159" s="4" t="n">
-        <v>-18.77</v>
+        <v>-18.75</v>
       </c>
       <c r="N159" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O159" s="4" t="n">
-        <v>-18.81</v>
+        <v>-18.79</v>
       </c>
       <c r="P159" s="4" t="n">
         <v>-0.67</v>
@@ -17834,10 +17840,10 @@
         <v>0</v>
       </c>
       <c r="AC159" s="4" t="n">
-        <v>44.3</v>
+        <v>44.31</v>
       </c>
       <c r="AD159" s="4" t="n">
-        <v>55.7</v>
+        <v>55.69</v>
       </c>
       <c r="AE159" s="4" t="n">
         <v>0</v>
@@ -17885,7 +17891,7 @@
         </is>
       </c>
       <c r="I160" s="4" t="n">
-        <v>-27.84</v>
+        <v>-27.82</v>
       </c>
       <c r="J160" s="4" t="n">
         <v>0</v>
@@ -17899,13 +17905,13 @@
         </is>
       </c>
       <c r="M160" s="4" t="n">
-        <v>-26.61</v>
+        <v>-26.58</v>
       </c>
       <c r="N160" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O160" s="4" t="n">
-        <v>-27.84</v>
+        <v>-27.82</v>
       </c>
       <c r="P160" s="4" t="n">
         <v>-2.2</v>
@@ -17937,10 +17943,10 @@
         <v>0</v>
       </c>
       <c r="AC160" s="4" t="n">
-        <v>36.08</v>
+        <v>36.09</v>
       </c>
       <c r="AD160" s="4" t="n">
-        <v>63.92</v>
+        <v>63.91</v>
       </c>
       <c r="AE160" s="4" t="n">
         <v>0</v>
@@ -17988,7 +17994,7 @@
         </is>
       </c>
       <c r="I161" s="4" t="n">
-        <v>-28.58</v>
+        <v>-28.55</v>
       </c>
       <c r="J161" s="4" t="n">
         <v>0</v>
@@ -18002,13 +18008,13 @@
         </is>
       </c>
       <c r="M161" s="4" t="n">
-        <v>-30.93</v>
+        <v>-30.9</v>
       </c>
       <c r="N161" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O161" s="4" t="n">
-        <v>-28.58</v>
+        <v>-28.55</v>
       </c>
       <c r="P161" s="4" t="n">
         <v>-1.19</v>
@@ -18040,10 +18046,10 @@
         <v>0</v>
       </c>
       <c r="AC161" s="4" t="n">
-        <v>35.71</v>
+        <v>35.72</v>
       </c>
       <c r="AD161" s="4" t="n">
-        <v>64.29000000000001</v>
+        <v>64.28</v>
       </c>
       <c r="AE161" s="4" t="n">
         <v>0</v>
@@ -18087,7 +18093,7 @@
         </is>
       </c>
       <c r="I162" s="4" t="n">
-        <v>-14.14</v>
+        <v>-14.11</v>
       </c>
       <c r="J162" s="4" t="n">
         <v>0.8</v>
@@ -18101,13 +18107,13 @@
         </is>
       </c>
       <c r="M162" s="4" t="n">
-        <v>-17.87</v>
+        <v>-17.84</v>
       </c>
       <c r="N162" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O162" s="4" t="n">
-        <v>-14.14</v>
+        <v>-14.11</v>
       </c>
       <c r="P162" s="4" t="n">
         <v>-2.54</v>
@@ -18139,10 +18145,10 @@
         <v>0</v>
       </c>
       <c r="AC162" s="4" t="n">
-        <v>42.93</v>
+        <v>42.94</v>
       </c>
       <c r="AD162" s="4" t="n">
-        <v>57.07</v>
+        <v>57.06</v>
       </c>
       <c r="AE162" s="4" t="n">
         <v>0</v>
@@ -18186,7 +18192,7 @@
         </is>
       </c>
       <c r="I163" s="4" t="n">
-        <v>-10.65</v>
+        <v>-10.66</v>
       </c>
       <c r="J163" s="4" t="n">
         <v>2.6</v>
@@ -18200,13 +18206,13 @@
         </is>
       </c>
       <c r="M163" s="4" t="n">
-        <v>-20.3</v>
+        <v>-20.27</v>
       </c>
       <c r="N163" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O163" s="4" t="n">
-        <v>-15.43</v>
+        <v>-15.41</v>
       </c>
       <c r="P163" s="4" t="n">
         <v>-2.09</v>
@@ -18227,7 +18233,7 @@
         <v>1</v>
       </c>
       <c r="V163" s="4" t="n">
-        <v>0.35</v>
+        <v>0.28</v>
       </c>
       <c r="W163" s="5" t="n">
         <v>128402</v>
@@ -18295,7 +18301,7 @@
         </is>
       </c>
       <c r="I164" s="4" t="n">
-        <v>-9.880000000000001</v>
+        <v>-9.85</v>
       </c>
       <c r="J164" s="4" t="n">
         <v>4.5</v>
@@ -18309,13 +18315,13 @@
         </is>
       </c>
       <c r="M164" s="4" t="n">
-        <v>-9.76</v>
+        <v>-9.74</v>
       </c>
       <c r="N164" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O164" s="4" t="n">
-        <v>-9.880000000000001</v>
+        <v>-9.85</v>
       </c>
       <c r="P164" s="4" t="n">
         <v>-1.94</v>
@@ -18347,10 +18353,10 @@
         <v>0</v>
       </c>
       <c r="AC164" s="4" t="n">
-        <v>45.06</v>
+        <v>45.07</v>
       </c>
       <c r="AD164" s="4" t="n">
-        <v>54.94</v>
+        <v>54.93</v>
       </c>
       <c r="AE164" s="4" t="n">
         <v>0</v>
@@ -18394,7 +18400,7 @@
         </is>
       </c>
       <c r="I165" s="4" t="n">
-        <v>52.68</v>
+        <v>52.7</v>
       </c>
       <c r="J165" s="4" t="n">
         <v>100</v>
@@ -18408,13 +18414,13 @@
         </is>
       </c>
       <c r="M165" s="4" t="n">
-        <v>45.13</v>
+        <v>45.15</v>
       </c>
       <c r="N165" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O165" s="4" t="n">
-        <v>52.68</v>
+        <v>52.7</v>
       </c>
       <c r="P165" s="4" t="n">
         <v>0</v>
@@ -18446,10 +18452,10 @@
         <v>0</v>
       </c>
       <c r="AC165" s="4" t="n">
-        <v>76.34</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="AD165" s="4" t="n">
-        <v>23.66</v>
+        <v>23.65</v>
       </c>
       <c r="AE165" s="4" t="n">
         <v>0</v>
@@ -18497,7 +18503,7 @@
         </is>
       </c>
       <c r="I166" s="4" t="n">
-        <v>-19.97</v>
+        <v>-19.95</v>
       </c>
       <c r="J166" s="4" t="n">
         <v>0.2</v>
@@ -18511,13 +18517,13 @@
         </is>
       </c>
       <c r="M166" s="4" t="n">
-        <v>-34.21</v>
+        <v>-34.19</v>
       </c>
       <c r="N166" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O166" s="4" t="n">
-        <v>-19.97</v>
+        <v>-19.95</v>
       </c>
       <c r="P166" s="4" t="n">
         <v>0.6</v>
@@ -18549,10 +18555,10 @@
         <v>0</v>
       </c>
       <c r="AC166" s="4" t="n">
-        <v>40.01</v>
+        <v>40.03</v>
       </c>
       <c r="AD166" s="4" t="n">
-        <v>59.99</v>
+        <v>59.97</v>
       </c>
       <c r="AE166" s="4" t="n">
         <v>0</v>
@@ -18828,13 +18834,13 @@
         </is>
       </c>
       <c r="M169" s="4" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="N169" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O169" s="4" t="n">
-        <v>17.2</v>
+        <v>17.21</v>
       </c>
       <c r="P169" s="4" t="n">
         <v>0.17</v>
@@ -18927,7 +18933,7 @@
         </is>
       </c>
       <c r="I170" s="4" t="n">
-        <v>5.32</v>
+        <v>5.33</v>
       </c>
       <c r="J170" s="4" t="n">
         <v>82</v>
@@ -18941,13 +18947,13 @@
         </is>
       </c>
       <c r="M170" s="4" t="n">
-        <v>-1.14</v>
+        <v>-1.13</v>
       </c>
       <c r="N170" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O170" s="4" t="n">
-        <v>5.62</v>
+        <v>5.63</v>
       </c>
       <c r="P170" s="4" t="n">
         <v>0.31</v>
@@ -18993,10 +18999,10 @@
         <v>0</v>
       </c>
       <c r="AC170" s="4" t="n">
-        <v>49.89</v>
+        <v>49.9</v>
       </c>
       <c r="AD170" s="4" t="n">
-        <v>44.85</v>
+        <v>44.84</v>
       </c>
       <c r="AE170" s="4" t="n">
         <v>2.63</v>
@@ -19044,7 +19050,7 @@
         </is>
       </c>
       <c r="I171" s="4" t="n">
-        <v>8.369999999999999</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="J171" s="4" t="n">
         <v>91.59999999999999</v>
@@ -19058,13 +19064,13 @@
         </is>
       </c>
       <c r="M171" s="4" t="n">
-        <v>3.95</v>
+        <v>3.96</v>
       </c>
       <c r="N171" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O171" s="4" t="n">
-        <v>9.81</v>
+        <v>9.82</v>
       </c>
       <c r="P171" s="4" t="n">
         <v>0.25</v>
@@ -19102,10 +19108,10 @@
         <v>0</v>
       </c>
       <c r="AC171" s="4" t="n">
-        <v>54.18</v>
+        <v>54.19</v>
       </c>
       <c r="AD171" s="4" t="n">
-        <v>45.82</v>
+        <v>45.81</v>
       </c>
       <c r="AE171" s="4" t="n">
         <v>0</v>
@@ -19149,7 +19155,7 @@
         </is>
       </c>
       <c r="I172" s="4" t="n">
-        <v>-17.35</v>
+        <v>-17.34</v>
       </c>
       <c r="J172" s="4" t="n">
         <v>0.4</v>
@@ -19163,13 +19169,13 @@
         </is>
       </c>
       <c r="M172" s="4" t="n">
-        <v>-23.12</v>
+        <v>-23.11</v>
       </c>
       <c r="N172" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O172" s="4" t="n">
-        <v>-17.35</v>
+        <v>-17.34</v>
       </c>
       <c r="P172" s="4" t="n">
         <v>-0.89</v>
@@ -19252,7 +19258,7 @@
         </is>
       </c>
       <c r="I173" s="4" t="n">
-        <v>-32.06</v>
+        <v>-32.07</v>
       </c>
       <c r="J173" s="4" t="n">
         <v>0</v>
@@ -19369,7 +19375,7 @@
         </is>
       </c>
       <c r="I174" s="4" t="n">
-        <v>-24.65</v>
+        <v>-24.66</v>
       </c>
       <c r="J174" s="4" t="n">
         <v>0.1</v>
@@ -19383,13 +19389,13 @@
         </is>
       </c>
       <c r="M174" s="4" t="n">
-        <v>-25.59</v>
+        <v>-25.6</v>
       </c>
       <c r="N174" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O174" s="4" t="n">
-        <v>-25.4</v>
+        <v>-25.41</v>
       </c>
       <c r="P174" s="4" t="n">
         <v>-1.45</v>
@@ -19429,10 +19435,10 @@
         <v>0</v>
       </c>
       <c r="AC174" s="4" t="n">
-        <v>33.91</v>
+        <v>33.9</v>
       </c>
       <c r="AD174" s="4" t="n">
-        <v>56.09</v>
+        <v>56.1</v>
       </c>
       <c r="AE174" s="4" t="n">
         <v>5</v>
@@ -22182,7 +22188,7 @@
         </is>
       </c>
       <c r="I201" s="4" t="n">
-        <v>-26.77</v>
+        <v>-26.83</v>
       </c>
       <c r="J201" s="4" t="n">
         <v>0</v>
@@ -22196,13 +22202,13 @@
         </is>
       </c>
       <c r="M201" s="4" t="n">
-        <v>-26.66</v>
+        <v>-26.71</v>
       </c>
       <c r="N201" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O201" s="4" t="n">
-        <v>-27.31</v>
+        <v>-27.36</v>
       </c>
       <c r="P201" s="4" t="n">
         <v>-2.18</v>
@@ -22242,10 +22248,10 @@
         <v>0</v>
       </c>
       <c r="AC201" s="4" t="n">
-        <v>35.63</v>
+        <v>35.61</v>
       </c>
       <c r="AD201" s="4" t="n">
-        <v>61.69</v>
+        <v>61.71</v>
       </c>
       <c r="AE201" s="4" t="n">
         <v>0</v>
@@ -22293,7 +22299,7 @@
         </is>
       </c>
       <c r="I202" s="4" t="n">
-        <v>-12.21</v>
+        <v>-12.26</v>
       </c>
       <c r="J202" s="4" t="n">
         <v>1.1</v>
@@ -22307,13 +22313,13 @@
         </is>
       </c>
       <c r="M202" s="4" t="n">
-        <v>-14.23</v>
+        <v>-14.29</v>
       </c>
       <c r="N202" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O202" s="4" t="n">
-        <v>-12.77</v>
+        <v>-12.83</v>
       </c>
       <c r="P202" s="4" t="n">
         <v>-0.23</v>
@@ -22353,10 +22359,10 @@
         <v>0</v>
       </c>
       <c r="AC202" s="4" t="n">
-        <v>42.65</v>
+        <v>42.62</v>
       </c>
       <c r="AD202" s="4" t="n">
-        <v>54.51</v>
+        <v>54.54</v>
       </c>
       <c r="AE202" s="4" t="n">
         <v>0</v>
@@ -22404,7 +22410,7 @@
         </is>
       </c>
       <c r="I203" s="4" t="n">
-        <v>26.24</v>
+        <v>26.18</v>
       </c>
       <c r="J203" s="4" t="n">
         <v>100</v>
@@ -22418,13 +22424,13 @@
         </is>
       </c>
       <c r="M203" s="4" t="n">
-        <v>8.74</v>
+        <v>8.69</v>
       </c>
       <c r="N203" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O203" s="4" t="n">
-        <v>25.65</v>
+        <v>25.59</v>
       </c>
       <c r="P203" s="4" t="n">
         <v>2.88</v>
@@ -22464,10 +22470,10 @@
         <v>0</v>
       </c>
       <c r="AC203" s="4" t="n">
-        <v>61.26</v>
+        <v>61.24</v>
       </c>
       <c r="AD203" s="4" t="n">
-        <v>35.8</v>
+        <v>35.82</v>
       </c>
       <c r="AE203" s="4" t="n">
         <v>0</v>
@@ -22515,7 +22521,7 @@
         </is>
       </c>
       <c r="I204" s="4" t="n">
-        <v>-17.45</v>
+        <v>-17.5</v>
       </c>
       <c r="J204" s="4" t="n">
         <v>0.4</v>
@@ -22529,13 +22535,13 @@
         </is>
       </c>
       <c r="M204" s="4" t="n">
-        <v>-18.62</v>
+        <v>-18.67</v>
       </c>
       <c r="N204" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O204" s="4" t="n">
-        <v>-18.03</v>
+        <v>-18.08</v>
       </c>
       <c r="P204" s="4" t="n">
         <v>-0.98</v>
@@ -22575,10 +22581,10 @@
         <v>0</v>
       </c>
       <c r="AC204" s="4" t="n">
-        <v>40.09</v>
+        <v>40.06</v>
       </c>
       <c r="AD204" s="4" t="n">
-        <v>57.03</v>
+        <v>57.06</v>
       </c>
       <c r="AE204" s="4" t="n">
         <v>0</v>
@@ -25697,7 +25703,7 @@
         </is>
       </c>
       <c r="I234" s="4" t="n">
-        <v>29.47</v>
+        <v>29.45</v>
       </c>
       <c r="J234" s="4" t="n">
         <v>100</v>
@@ -25711,13 +25717,13 @@
         </is>
       </c>
       <c r="M234" s="4" t="n">
-        <v>22.45</v>
+        <v>22.44</v>
       </c>
       <c r="N234" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O234" s="4" t="n">
-        <v>33.21</v>
+        <v>33.2</v>
       </c>
       <c r="P234" s="4" t="n">
         <v>0.66</v>
@@ -25738,7 +25744,7 @@
         <v>1</v>
       </c>
       <c r="V234" s="4" t="n">
-        <v>22.69</v>
+        <v>22.66</v>
       </c>
       <c r="W234" s="5" t="n">
         <v>531050</v>
@@ -25802,13 +25808,13 @@
         </is>
       </c>
       <c r="I235" s="4" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="J235" s="4" t="n">
-        <v>50.7</v>
+        <v>49.6</v>
       </c>
       <c r="K235" s="4" t="n">
-        <v>49.3</v>
+        <v>50.4</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -25816,13 +25822,13 @@
         </is>
       </c>
       <c r="M235" s="4" t="n">
-        <v>-8.69</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="N235" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O235" s="4" t="n">
-        <v>-2.28</v>
+        <v>-2.29</v>
       </c>
       <c r="P235" s="4" t="n">
         <v>0.14</v>
@@ -25843,7 +25849,7 @@
         <v>8</v>
       </c>
       <c r="V235" s="4" t="n">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="W235" s="5" t="n">
         <v>2671904</v>
@@ -25860,10 +25866,10 @@
         <v>0</v>
       </c>
       <c r="AC235" s="4" t="n">
-        <v>50.01</v>
+        <v>50</v>
       </c>
       <c r="AD235" s="4" t="n">
-        <v>49.99</v>
+        <v>50</v>
       </c>
       <c r="AE235" s="4" t="n">
         <v>0</v>
@@ -26244,13 +26250,13 @@
         </is>
       </c>
       <c r="I239" s="4" t="n">
-        <v>-0.43</v>
+        <v>-0.44</v>
       </c>
       <c r="J239" s="4" t="n">
-        <v>47</v>
+        <v>46.9</v>
       </c>
       <c r="K239" s="4" t="n">
-        <v>53</v>
+        <v>53.1</v>
       </c>
       <c r="L239" t="inlineStr">
         <is>
@@ -26285,7 +26291,7 @@
         <v>4</v>
       </c>
       <c r="V239" s="4" t="n">
-        <v>-0.73</v>
+        <v>-0.77</v>
       </c>
       <c r="W239" s="5" t="n">
         <v>4310699</v>
@@ -26310,10 +26316,10 @@
         <v>0</v>
       </c>
       <c r="AC239" s="4" t="n">
-        <v>48.66</v>
+        <v>48.65</v>
       </c>
       <c r="AD239" s="4" t="n">
-        <v>49.07</v>
+        <v>49.08</v>
       </c>
       <c r="AE239" s="4" t="n">
         <v>0</v>
@@ -26624,7 +26630,7 @@
         <v>2</v>
       </c>
       <c r="V242" s="4" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W242" s="5" t="n">
         <v>3665521</v>
@@ -26649,10 +26655,10 @@
         <v>0</v>
       </c>
       <c r="AC242" s="4" t="n">
-        <v>50.94</v>
+        <v>50.93</v>
       </c>
       <c r="AD242" s="4" t="n">
-        <v>46.79</v>
+        <v>46.8</v>
       </c>
       <c r="AE242" s="4" t="n">
         <v>0</v>
@@ -27465,7 +27471,7 @@
         </is>
       </c>
       <c r="I250" s="4" t="n">
-        <v>13.53</v>
+        <v>13.52</v>
       </c>
       <c r="J250" s="4" t="n">
         <v>99.09999999999999</v>
@@ -27479,7 +27485,7 @@
         </is>
       </c>
       <c r="M250" s="4" t="n">
-        <v>7.66</v>
+        <v>7.65</v>
       </c>
       <c r="N250" s="4" t="n">
         <v>7.28</v>
@@ -27506,7 +27512,7 @@
         <v>2</v>
       </c>
       <c r="V250" s="4" t="n">
-        <v>10.3</v>
+        <v>10.24</v>
       </c>
       <c r="W250" s="5" t="n">
         <v>1452273</v>
@@ -27523,10 +27529,10 @@
         <v>0</v>
       </c>
       <c r="AC250" s="4" t="n">
-        <v>56.77</v>
+        <v>56.76</v>
       </c>
       <c r="AD250" s="4" t="n">
-        <v>43.23</v>
+        <v>43.24</v>
       </c>
       <c r="AE250" s="4" t="n">
         <v>0</v>
@@ -28149,10 +28155,10 @@
         <v>0</v>
       </c>
       <c r="AC256" s="4" t="n">
-        <v>45.85</v>
+        <v>45.84</v>
       </c>
       <c r="AD256" s="4" t="n">
-        <v>54.15</v>
+        <v>54.16</v>
       </c>
       <c r="AE256" s="4" t="n">
         <v>0</v>
@@ -28311,7 +28317,7 @@
         </is>
       </c>
       <c r="I258" s="4" t="n">
-        <v>-2.72</v>
+        <v>-2.73</v>
       </c>
       <c r="J258" s="4" t="n">
         <v>30.9</v>
@@ -28352,7 +28358,7 @@
         <v>1</v>
       </c>
       <c r="V258" s="4" t="n">
-        <v>3.02</v>
+        <v>2.98</v>
       </c>
       <c r="W258" s="5" t="n">
         <v>1953675</v>
@@ -29090,7 +29096,7 @@
         </is>
       </c>
       <c r="I265" s="4" t="n">
-        <v>-28.93</v>
+        <v>-29.31</v>
       </c>
       <c r="J265" s="4" t="n">
         <v>0</v>
@@ -29104,13 +29110,13 @@
         </is>
       </c>
       <c r="M265" s="4" t="n">
-        <v>-32.71</v>
+        <v>-33.09</v>
       </c>
       <c r="N265" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O265" s="4" t="n">
-        <v>-29.23</v>
+        <v>-29.61</v>
       </c>
       <c r="P265" s="4" t="n">
         <v>-0.32</v>
@@ -29150,10 +29156,10 @@
         <v>0</v>
       </c>
       <c r="AC265" s="4" t="n">
-        <v>35</v>
+        <v>34.82</v>
       </c>
       <c r="AD265" s="4" t="n">
-        <v>63.5</v>
+        <v>63.68</v>
       </c>
       <c r="AE265" s="4" t="n">
         <v>0</v>
@@ -29201,7 +29207,7 @@
         </is>
       </c>
       <c r="I266" s="4" t="n">
-        <v>38.53</v>
+        <v>38.15</v>
       </c>
       <c r="J266" s="4" t="n">
         <v>100</v>
@@ -29215,13 +29221,13 @@
         </is>
       </c>
       <c r="M266" s="4" t="n">
-        <v>25.69</v>
+        <v>25.31</v>
       </c>
       <c r="N266" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O266" s="4" t="n">
-        <v>38.6</v>
+        <v>38.22</v>
       </c>
       <c r="P266" s="4" t="n">
         <v>1.61</v>
@@ -29261,10 +29267,10 @@
         <v>0</v>
       </c>
       <c r="AC266" s="4" t="n">
-        <v>68.23</v>
+        <v>68.04000000000001</v>
       </c>
       <c r="AD266" s="4" t="n">
-        <v>30.27</v>
+        <v>30.46</v>
       </c>
       <c r="AE266" s="4" t="n">
         <v>0</v>
@@ -29312,7 +29318,7 @@
         </is>
       </c>
       <c r="I267" s="4" t="n">
-        <v>-20.51</v>
+        <v>-20.89</v>
       </c>
       <c r="J267" s="4" t="n">
         <v>0.2</v>
@@ -29326,13 +29332,13 @@
         </is>
       </c>
       <c r="M267" s="4" t="n">
-        <v>-24.89</v>
+        <v>-25.27</v>
       </c>
       <c r="N267" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O267" s="4" t="n">
-        <v>-20.81</v>
+        <v>-21.19</v>
       </c>
       <c r="P267" s="4" t="n">
         <v>-1.06</v>
@@ -29372,10 +29378,10 @@
         <v>0</v>
       </c>
       <c r="AC267" s="4" t="n">
-        <v>39.15</v>
+        <v>38.96</v>
       </c>
       <c r="AD267" s="4" t="n">
-        <v>59.35</v>
+        <v>59.54</v>
       </c>
       <c r="AE267" s="4" t="n">
         <v>0</v>
@@ -29423,7 +29429,7 @@
         </is>
       </c>
       <c r="I268" s="4" t="n">
-        <v>-38.33</v>
+        <v>-38.71</v>
       </c>
       <c r="J268" s="4" t="n">
         <v>0</v>
@@ -29437,13 +29443,13 @@
         </is>
       </c>
       <c r="M268" s="4" t="n">
-        <v>-38.52</v>
+        <v>-38.9</v>
       </c>
       <c r="N268" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O268" s="4" t="n">
-        <v>-38.25</v>
+        <v>-38.63</v>
       </c>
       <c r="P268" s="4" t="n">
         <v>-1.75</v>
@@ -29483,10 +29489,10 @@
         <v>0</v>
       </c>
       <c r="AC268" s="4" t="n">
-        <v>30.37</v>
+        <v>30.19</v>
       </c>
       <c r="AD268" s="4" t="n">
-        <v>68.13</v>
+        <v>68.31</v>
       </c>
       <c r="AE268" s="4" t="n">
         <v>0</v>
@@ -29530,13 +29536,13 @@
         </is>
       </c>
       <c r="I269" s="4" t="n">
-        <v>0.86</v>
+        <v>0.9</v>
       </c>
       <c r="J269" s="4" t="n">
-        <v>56.1</v>
+        <v>56.4</v>
       </c>
       <c r="K269" s="4" t="n">
-        <v>43.9</v>
+        <v>43.6</v>
       </c>
       <c r="L269" t="inlineStr">
         <is>
@@ -29544,13 +29550,13 @@
         </is>
       </c>
       <c r="M269" s="4" t="n">
-        <v>-6.39</v>
+        <v>-6.26</v>
       </c>
       <c r="N269" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O269" s="4" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="P269" s="4" t="n">
         <v>0.02</v>
@@ -29571,7 +29577,7 @@
         <v>6</v>
       </c>
       <c r="V269" s="4" t="n">
-        <v>0.78</v>
+        <v>0.73</v>
       </c>
       <c r="W269" s="5" t="n">
         <v>3690160</v>
@@ -29596,10 +29602,10 @@
         <v>0</v>
       </c>
       <c r="AC269" s="4" t="n">
-        <v>49.09</v>
+        <v>49.11</v>
       </c>
       <c r="AD269" s="4" t="n">
-        <v>48.25</v>
+        <v>48.23</v>
       </c>
       <c r="AE269" s="4" t="n">
         <v>0</v>
@@ -29647,7 +29653,7 @@
         </is>
       </c>
       <c r="I270" s="4" t="n">
-        <v>-24.11</v>
+        <v>-24.05</v>
       </c>
       <c r="J270" s="4" t="n">
         <v>0.1</v>
@@ -29661,13 +29667,13 @@
         </is>
       </c>
       <c r="M270" s="4" t="n">
-        <v>-25.35</v>
+        <v>-25.22</v>
       </c>
       <c r="N270" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O270" s="4" t="n">
-        <v>-26.04</v>
+        <v>-25.9</v>
       </c>
       <c r="P270" s="4" t="n">
         <v>-2.65</v>
@@ -29688,7 +29694,7 @@
         <v>1</v>
       </c>
       <c r="V270" s="4" t="n">
-        <v>-20.26</v>
+        <v>-20.36</v>
       </c>
       <c r="W270" s="5" t="n">
         <v>30654</v>
@@ -29713,10 +29719,10 @@
         <v>0</v>
       </c>
       <c r="AC270" s="4" t="n">
-        <v>33.15</v>
+        <v>33.18</v>
       </c>
       <c r="AD270" s="4" t="n">
-        <v>54.21</v>
+        <v>54.18</v>
       </c>
       <c r="AE270" s="4" t="n">
         <v>3.64</v>
@@ -29764,13 +29770,13 @@
         </is>
       </c>
       <c r="I271" s="4" t="n">
-        <v>7.02</v>
+        <v>7.01</v>
       </c>
       <c r="J271" s="4" t="n">
-        <v>87.59999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="K271" s="4" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="L271" t="inlineStr">
         <is>
@@ -29805,7 +29811,7 @@
         <v>7</v>
       </c>
       <c r="V271" s="4" t="n">
-        <v>7.08</v>
+        <v>7.07</v>
       </c>
       <c r="W271" s="5" t="n">
         <v>5572578</v>
@@ -29881,7 +29887,7 @@
         </is>
       </c>
       <c r="I272" s="4" t="n">
-        <v>48.91</v>
+        <v>48.9</v>
       </c>
       <c r="J272" s="4" t="n">
         <v>100</v>
@@ -30448,13 +30454,13 @@
         </is>
       </c>
       <c r="M277" s="4" t="n">
-        <v>-9.94</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="N277" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O277" s="4" t="n">
-        <v>-7.88</v>
+        <v>-7.89</v>
       </c>
       <c r="P277" s="4" t="n">
         <v>-1.32</v>
@@ -30475,7 +30481,7 @@
         <v>1</v>
       </c>
       <c r="V277" s="4" t="n">
-        <v>-7.01</v>
+        <v>-7.02</v>
       </c>
       <c r="W277" s="5" t="n">
         <v>390475</v>
@@ -30551,7 +30557,7 @@
         </is>
       </c>
       <c r="I278" s="4" t="n">
-        <v>-14.38</v>
+        <v>-14.39</v>
       </c>
       <c r="J278" s="4" t="n">
         <v>0.7</v>
@@ -30571,7 +30577,7 @@
         <v>7.28</v>
       </c>
       <c r="O278" s="4" t="n">
-        <v>-13.94</v>
+        <v>-13.95</v>
       </c>
       <c r="P278" s="4" t="n">
         <v>-1.85</v>
@@ -30662,7 +30668,7 @@
         </is>
       </c>
       <c r="I279" s="4" t="n">
-        <v>-7.55</v>
+        <v>-7.56</v>
       </c>
       <c r="J279" s="4" t="n">
         <v>10.8</v>
@@ -30676,7 +30682,7 @@
         </is>
       </c>
       <c r="M279" s="4" t="n">
-        <v>-12.27</v>
+        <v>-12.28</v>
       </c>
       <c r="N279" s="4" t="n">
         <v>7.28</v>
@@ -30703,7 +30709,7 @@
         <v>1</v>
       </c>
       <c r="V279" s="4" t="n">
-        <v>-5.08</v>
+        <v>-5.09</v>
       </c>
       <c r="W279" s="5" t="n">
         <v>2809837</v>
@@ -30771,7 +30777,7 @@
         </is>
       </c>
       <c r="I280" s="4" t="n">
-        <v>-12.21</v>
+        <v>-12.22</v>
       </c>
       <c r="J280" s="4" t="n">
         <v>1.1</v>
@@ -30884,13 +30890,13 @@
         </is>
       </c>
       <c r="I281" s="4" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="J281" s="4" t="n">
-        <v>51.2</v>
+        <v>51</v>
       </c>
       <c r="K281" s="4" t="n">
-        <v>48.8</v>
+        <v>49</v>
       </c>
       <c r="L281" t="inlineStr">
         <is>
@@ -30904,7 +30910,7 @@
         <v>7.28</v>
       </c>
       <c r="O281" s="4" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="P281" s="4" t="n">
         <v>0.96</v>
@@ -30925,7 +30931,7 @@
         <v>1</v>
       </c>
       <c r="V281" s="4" t="n">
-        <v>-2.15</v>
+        <v>-2.22</v>
       </c>
       <c r="W281" s="5" t="n">
         <v>5401765</v>
@@ -30950,10 +30956,10 @@
         <v>0</v>
       </c>
       <c r="AC281" s="4" t="n">
-        <v>49.07</v>
+        <v>49.06</v>
       </c>
       <c r="AD281" s="4" t="n">
-        <v>48.9</v>
+        <v>48.91</v>
       </c>
       <c r="AE281" s="4" t="n">
         <v>0</v>
@@ -31001,7 +31007,7 @@
         </is>
       </c>
       <c r="I282" s="4" t="n">
-        <v>62.97</v>
+        <v>62.96</v>
       </c>
       <c r="J282" s="4" t="n">
         <v>100</v>
@@ -31021,7 +31027,7 @@
         <v>7.28</v>
       </c>
       <c r="O282" s="4" t="n">
-        <v>62.97</v>
+        <v>62.96</v>
       </c>
       <c r="P282" s="4" t="n">
         <v>1.41</v>
@@ -31104,7 +31110,7 @@
         </is>
       </c>
       <c r="I283" s="4" t="n">
-        <v>-9.68</v>
+        <v>-9.69</v>
       </c>
       <c r="J283" s="4" t="n">
         <v>4.9</v>
@@ -31124,7 +31130,7 @@
         <v>7.28</v>
       </c>
       <c r="O283" s="4" t="n">
-        <v>-10.05</v>
+        <v>-10.06</v>
       </c>
       <c r="P283" s="4" t="n">
         <v>-0.24</v>
@@ -31435,13 +31441,13 @@
         </is>
       </c>
       <c r="I286" s="4" t="n">
-        <v>-5.66</v>
+        <v>-5.54</v>
       </c>
       <c r="J286" s="4" t="n">
-        <v>16.9</v>
+        <v>17.3</v>
       </c>
       <c r="K286" s="4" t="n">
-        <v>83.09999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="L286" t="inlineStr">
         <is>
@@ -31449,13 +31455,13 @@
         </is>
       </c>
       <c r="M286" s="4" t="n">
-        <v>-10.11</v>
+        <v>-9.94</v>
       </c>
       <c r="N286" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O286" s="4" t="n">
-        <v>-8.859999999999999</v>
+        <v>-8.69</v>
       </c>
       <c r="P286" s="4" t="n">
         <v>-0.53</v>
@@ -31501,10 +31507,10 @@
         <v>0</v>
       </c>
       <c r="AC286" s="4" t="n">
-        <v>44.9</v>
+        <v>44.95</v>
       </c>
       <c r="AD286" s="4" t="n">
-        <v>50.28</v>
+        <v>50.23</v>
       </c>
       <c r="AE286" s="4" t="n">
         <v>2.41</v>
@@ -31548,13 +31554,13 @@
         </is>
       </c>
       <c r="I287" s="4" t="n">
-        <v>12.64</v>
+        <v>12.02</v>
       </c>
       <c r="J287" s="4" t="n">
-        <v>99</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="K287" s="4" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="L287" t="inlineStr">
         <is>
@@ -31562,13 +31568,13 @@
         </is>
       </c>
       <c r="M287" s="4" t="n">
-        <v>7.75</v>
+        <v>7.92</v>
       </c>
       <c r="N287" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O287" s="4" t="n">
-        <v>15.34</v>
+        <v>15.52</v>
       </c>
       <c r="P287" s="4" t="n">
         <v>0.68</v>
@@ -31580,16 +31586,16 @@
         <v>4.68</v>
       </c>
       <c r="S287" s="4" t="n">
-        <v>46</v>
+        <v>46.79</v>
       </c>
       <c r="T287" s="4" t="n">
-        <v>42</v>
+        <v>41.21</v>
       </c>
       <c r="U287" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V287" s="4" t="n">
-        <v>5.3</v>
+        <v>7.21</v>
       </c>
       <c r="W287" s="5" t="n">
         <v>4854805</v>
@@ -31608,16 +31614,16 @@
         </is>
       </c>
       <c r="AA287" s="4" t="n">
-        <v>2.16</v>
+        <v>1.18</v>
       </c>
       <c r="AB287" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC287" s="4" t="n">
-        <v>55.1</v>
+        <v>55.35</v>
       </c>
       <c r="AD287" s="4" t="n">
-        <v>42.74</v>
+        <v>43.47</v>
       </c>
       <c r="AE287" s="4" t="n">
         <v>0</v>
@@ -31665,7 +31671,7 @@
         </is>
       </c>
       <c r="I288" s="4" t="n">
-        <v>-52.21</v>
+        <v>-52.04</v>
       </c>
       <c r="J288" s="4" t="n">
         <v>0</v>
@@ -31679,13 +31685,13 @@
         </is>
       </c>
       <c r="M288" s="4" t="n">
-        <v>-51.06</v>
+        <v>-50.89</v>
       </c>
       <c r="N288" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O288" s="4" t="n">
-        <v>-52.01</v>
+        <v>-51.84</v>
       </c>
       <c r="P288" s="4" t="n">
         <v>-2.32</v>
@@ -31725,10 +31731,10 @@
         <v>0</v>
       </c>
       <c r="AC288" s="4" t="n">
-        <v>22.95</v>
+        <v>23.03</v>
       </c>
       <c r="AD288" s="4" t="n">
-        <v>73.09</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="AE288" s="4" t="n">
         <v>1.98</v>
@@ -31772,7 +31778,7 @@
         </is>
       </c>
       <c r="I289" s="4" t="n">
-        <v>6.6</v>
+        <v>6.58</v>
       </c>
       <c r="J289" s="4" t="n">
         <v>86.2</v>
@@ -31786,13 +31792,13 @@
         </is>
       </c>
       <c r="M289" s="4" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="N289" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O289" s="4" t="n">
-        <v>7.66</v>
+        <v>7.64</v>
       </c>
       <c r="P289" s="4" t="n">
         <v>-0.15</v>
@@ -31813,7 +31819,7 @@
         <v>1</v>
       </c>
       <c r="V289" s="4" t="n">
-        <v>4.69</v>
+        <v>4.66</v>
       </c>
       <c r="W289" s="5" t="n">
         <v>3015195</v>
@@ -31830,10 +31836,10 @@
         <v>0</v>
       </c>
       <c r="AC289" s="4" t="n">
-        <v>53.3</v>
+        <v>53.29</v>
       </c>
       <c r="AD289" s="4" t="n">
-        <v>46.7</v>
+        <v>46.71</v>
       </c>
       <c r="AE289" s="4" t="n">
         <v>0</v>
@@ -31881,7 +31887,7 @@
         </is>
       </c>
       <c r="I290" s="4" t="n">
-        <v>18.59</v>
+        <v>18.58</v>
       </c>
       <c r="J290" s="4" t="n">
         <v>99.7</v>
@@ -31895,13 +31901,13 @@
         </is>
       </c>
       <c r="M290" s="4" t="n">
-        <v>3.43</v>
+        <v>3.42</v>
       </c>
       <c r="N290" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O290" s="4" t="n">
-        <v>17.71</v>
+        <v>17.69</v>
       </c>
       <c r="P290" s="4" t="n">
         <v>0.93</v>
@@ -31922,7 +31928,7 @@
         <v>8</v>
       </c>
       <c r="V290" s="4" t="n">
-        <v>20.25</v>
+        <v>20.23</v>
       </c>
       <c r="W290" s="5" t="n">
         <v>4812156</v>
@@ -31947,10 +31953,10 @@
         <v>0</v>
       </c>
       <c r="AC290" s="4" t="n">
-        <v>58.2</v>
+        <v>58.19</v>
       </c>
       <c r="AD290" s="4" t="n">
-        <v>39.95</v>
+        <v>39.96</v>
       </c>
       <c r="AE290" s="4" t="n">
         <v>0</v>
@@ -32646,7 +32652,7 @@
         </is>
       </c>
       <c r="I297" s="4" t="n">
-        <v>7.57</v>
+        <v>7.55</v>
       </c>
       <c r="J297" s="4" t="n">
         <v>89.2</v>
@@ -32687,7 +32693,7 @@
         <v>2</v>
       </c>
       <c r="V297" s="4" t="n">
-        <v>6.27</v>
+        <v>6.2</v>
       </c>
       <c r="W297" s="5" t="n">
         <v>8193416</v>
@@ -32712,10 +32718,10 @@
         <v>0</v>
       </c>
       <c r="AC297" s="4" t="n">
-        <v>53.26</v>
+        <v>53.25</v>
       </c>
       <c r="AD297" s="4" t="n">
-        <v>45.77</v>
+        <v>45.78</v>
       </c>
       <c r="AE297" s="4" t="n">
         <v>0</v>
@@ -33633,7 +33639,7 @@
         </is>
       </c>
       <c r="I306" s="4" t="n">
-        <v>18.8</v>
+        <v>18.81</v>
       </c>
       <c r="J306" s="4" t="n">
         <v>99.7</v>
@@ -33740,13 +33746,13 @@
         </is>
       </c>
       <c r="I307" s="4" t="n">
-        <v>-0.52</v>
+        <v>-0.14</v>
       </c>
       <c r="J307" s="4" t="n">
-        <v>46.3</v>
+        <v>49</v>
       </c>
       <c r="K307" s="4" t="n">
-        <v>53.7</v>
+        <v>51</v>
       </c>
       <c r="L307" t="inlineStr">
         <is>
@@ -33754,13 +33760,13 @@
         </is>
       </c>
       <c r="M307" s="4" t="n">
-        <v>-11.79</v>
+        <v>-11.78</v>
       </c>
       <c r="N307" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O307" s="4" t="n">
-        <v>-5.28</v>
+        <v>-5.27</v>
       </c>
       <c r="P307" s="4" t="n">
         <v>-0.75</v>
@@ -33772,16 +33778,16 @@
         <v>-14.26</v>
       </c>
       <c r="S307" s="4" t="n">
-        <v>41.17</v>
+        <v>39.21</v>
       </c>
       <c r="T307" s="4" t="n">
-        <v>40.89</v>
+        <v>39.42</v>
       </c>
       <c r="U307" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V307" s="4" t="n">
-        <v>-0.02</v>
+        <v>-1.3</v>
       </c>
       <c r="W307" s="5" t="n">
         <v>790477</v>
@@ -33800,16 +33806,16 @@
         </is>
       </c>
       <c r="AA307" s="4" t="n">
-        <v>9.23</v>
+        <v>11.88</v>
       </c>
       <c r="AB307" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC307" s="4" t="n">
-        <v>45.15</v>
+        <v>44</v>
       </c>
       <c r="AD307" s="4" t="n">
-        <v>45.62</v>
+        <v>44.12</v>
       </c>
       <c r="AE307" s="4" t="n">
         <v>0</v>
@@ -33857,7 +33863,7 @@
         </is>
       </c>
       <c r="I308" s="4" t="n">
-        <v>15.35</v>
+        <v>15.36</v>
       </c>
       <c r="J308" s="4" t="n">
         <v>99.40000000000001</v>
@@ -33871,13 +33877,13 @@
         </is>
       </c>
       <c r="M308" s="4" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="N308" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O308" s="4" t="n">
-        <v>14.6</v>
+        <v>14.61</v>
       </c>
       <c r="P308" s="4" t="n">
         <v>0.21</v>
@@ -33917,10 +33923,10 @@
         <v>0</v>
       </c>
       <c r="AC308" s="4" t="n">
-        <v>56.34</v>
+        <v>56.35</v>
       </c>
       <c r="AD308" s="4" t="n">
-        <v>41.35</v>
+        <v>41.34</v>
       </c>
       <c r="AE308" s="4" t="n">
         <v>0</v>
@@ -33982,13 +33988,13 @@
         </is>
       </c>
       <c r="M309" s="4" t="n">
-        <v>6.07</v>
+        <v>6.08</v>
       </c>
       <c r="N309" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O309" s="4" t="n">
-        <v>20.22</v>
+        <v>20.23</v>
       </c>
       <c r="P309" s="4" t="n">
         <v>0.96</v>
@@ -34079,13 +34085,13 @@
         </is>
       </c>
       <c r="I310" s="4" t="n">
-        <v>-1.11</v>
+        <v>-1.14</v>
       </c>
       <c r="J310" s="4" t="n">
-        <v>42.1</v>
+        <v>41.9</v>
       </c>
       <c r="K310" s="4" t="n">
-        <v>57.9</v>
+        <v>58.1</v>
       </c>
       <c r="L310" t="inlineStr">
         <is>
@@ -34093,13 +34099,13 @@
         </is>
       </c>
       <c r="M310" s="4" t="n">
-        <v>-7.97</v>
+        <v>-8</v>
       </c>
       <c r="N310" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O310" s="4" t="n">
-        <v>-0.96</v>
+        <v>-0.99</v>
       </c>
       <c r="P310" s="4" t="n">
         <v>-0.75</v>
@@ -34137,10 +34143,10 @@
         <v>0</v>
       </c>
       <c r="AC310" s="4" t="n">
-        <v>49.45</v>
+        <v>49.43</v>
       </c>
       <c r="AD310" s="4" t="n">
-        <v>50.55</v>
+        <v>50.57</v>
       </c>
       <c r="AE310" s="4" t="n">
         <v>0</v>
@@ -34188,13 +34194,13 @@
         </is>
       </c>
       <c r="I311" s="4" t="n">
-        <v>-8.779999999999999</v>
+        <v>-8.81</v>
       </c>
       <c r="J311" s="4" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="K311" s="4" t="n">
-        <v>92.7</v>
+        <v>92.8</v>
       </c>
       <c r="L311" t="inlineStr">
         <is>
@@ -34202,13 +34208,13 @@
         </is>
       </c>
       <c r="M311" s="4" t="n">
-        <v>-10.83</v>
+        <v>-10.86</v>
       </c>
       <c r="N311" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O311" s="4" t="n">
-        <v>-8.779999999999999</v>
+        <v>-8.81</v>
       </c>
       <c r="P311" s="4" t="n">
         <v>-1.4</v>
@@ -34240,10 +34246,10 @@
         <v>0</v>
       </c>
       <c r="AC311" s="4" t="n">
-        <v>45.61</v>
+        <v>45.6</v>
       </c>
       <c r="AD311" s="4" t="n">
-        <v>54.39</v>
+        <v>54.4</v>
       </c>
       <c r="AE311" s="4" t="n">
         <v>0</v>
@@ -34291,7 +34297,7 @@
         </is>
       </c>
       <c r="I312" s="4" t="n">
-        <v>16.98</v>
+        <v>16.95</v>
       </c>
       <c r="J312" s="4" t="n">
         <v>99.59999999999999</v>
@@ -34305,13 +34311,13 @@
         </is>
       </c>
       <c r="M312" s="4" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="N312" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O312" s="4" t="n">
-        <v>16.98</v>
+        <v>16.95</v>
       </c>
       <c r="P312" s="4" t="n">
         <v>0.37</v>
@@ -34343,10 +34349,10 @@
         <v>0</v>
       </c>
       <c r="AC312" s="4" t="n">
-        <v>58.49</v>
+        <v>58.47</v>
       </c>
       <c r="AD312" s="4" t="n">
-        <v>41.51</v>
+        <v>41.53</v>
       </c>
       <c r="AE312" s="4" t="n">
         <v>0</v>
@@ -34394,7 +34400,7 @@
         </is>
       </c>
       <c r="I313" s="4" t="n">
-        <v>16.91</v>
+        <v>16.89</v>
       </c>
       <c r="J313" s="4" t="n">
         <v>99.5</v>
@@ -34408,13 +34414,13 @@
         </is>
       </c>
       <c r="M313" s="4" t="n">
-        <v>5.23</v>
+        <v>5.2</v>
       </c>
       <c r="N313" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O313" s="4" t="n">
-        <v>18.56</v>
+        <v>18.53</v>
       </c>
       <c r="P313" s="4" t="n">
         <v>1.55</v>
@@ -34460,10 +34466,10 @@
         <v>0</v>
       </c>
       <c r="AC313" s="4" t="n">
-        <v>57.53</v>
+        <v>57.52</v>
       </c>
       <c r="AD313" s="4" t="n">
-        <v>40.89</v>
+        <v>40.9</v>
       </c>
       <c r="AE313" s="4" t="n">
         <v>0</v>
@@ -34511,7 +34517,7 @@
         </is>
       </c>
       <c r="I314" s="4" t="n">
-        <v>60.97</v>
+        <v>60.94</v>
       </c>
       <c r="J314" s="4" t="n">
         <v>100</v>
@@ -34525,13 +34531,13 @@
         </is>
       </c>
       <c r="M314" s="4" t="n">
-        <v>49.15</v>
+        <v>49.12</v>
       </c>
       <c r="N314" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O314" s="4" t="n">
-        <v>60.97</v>
+        <v>60.94</v>
       </c>
       <c r="P314" s="4" t="n">
         <v>0</v>
@@ -34563,10 +34569,10 @@
         <v>0</v>
       </c>
       <c r="AC314" s="4" t="n">
-        <v>80.48999999999999</v>
+        <v>80.47</v>
       </c>
       <c r="AD314" s="4" t="n">
-        <v>19.51</v>
+        <v>19.53</v>
       </c>
       <c r="AE314" s="4" t="n">
         <v>0</v>
@@ -34614,7 +34620,7 @@
         </is>
       </c>
       <c r="I315" s="4" t="n">
-        <v>35.97</v>
+        <v>35.94</v>
       </c>
       <c r="J315" s="4" t="n">
         <v>100</v>
@@ -34628,13 +34634,13 @@
         </is>
       </c>
       <c r="M315" s="4" t="n">
-        <v>13.92</v>
+        <v>13.89</v>
       </c>
       <c r="N315" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O315" s="4" t="n">
-        <v>35.97</v>
+        <v>35.94</v>
       </c>
       <c r="P315" s="4" t="n">
         <v>2.81</v>
@@ -34666,10 +34672,10 @@
         <v>0</v>
       </c>
       <c r="AC315" s="4" t="n">
-        <v>67.98999999999999</v>
+        <v>67.97</v>
       </c>
       <c r="AD315" s="4" t="n">
-        <v>32.01</v>
+        <v>32.03</v>
       </c>
       <c r="AE315" s="4" t="n">
         <v>0</v>
@@ -34713,7 +34719,7 @@
         </is>
       </c>
       <c r="I316" s="4" t="n">
-        <v>59.79</v>
+        <v>59.76</v>
       </c>
       <c r="J316" s="4" t="n">
         <v>100</v>
@@ -34727,13 +34733,13 @@
         </is>
       </c>
       <c r="M316" s="4" t="n">
-        <v>52.39</v>
+        <v>52.35</v>
       </c>
       <c r="N316" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O316" s="4" t="n">
-        <v>60.61</v>
+        <v>60.57</v>
       </c>
       <c r="P316" s="4" t="n">
         <v>0</v>
@@ -34773,10 +34779,10 @@
         <v>0</v>
       </c>
       <c r="AC316" s="4" t="n">
-        <v>77.89</v>
+        <v>77.87</v>
       </c>
       <c r="AD316" s="4" t="n">
-        <v>19.6</v>
+        <v>19.62</v>
       </c>
       <c r="AE316" s="4" t="n">
         <v>0</v>
@@ -34824,7 +34830,7 @@
         </is>
       </c>
       <c r="I317" s="4" t="n">
-        <v>63.21</v>
+        <v>63.17</v>
       </c>
       <c r="J317" s="4" t="n">
         <v>100</v>
@@ -34838,13 +34844,13 @@
         </is>
       </c>
       <c r="M317" s="4" t="n">
-        <v>48.86</v>
+        <v>48.83</v>
       </c>
       <c r="N317" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O317" s="4" t="n">
-        <v>63.21</v>
+        <v>63.17</v>
       </c>
       <c r="P317" s="4" t="n">
         <v>0</v>
@@ -34876,10 +34882,10 @@
         <v>0</v>
       </c>
       <c r="AC317" s="4" t="n">
-        <v>81.59999999999999</v>
+        <v>81.59</v>
       </c>
       <c r="AD317" s="4" t="n">
-        <v>18.4</v>
+        <v>18.41</v>
       </c>
       <c r="AE317" s="4" t="n">
         <v>0</v>
@@ -34927,7 +34933,7 @@
         </is>
       </c>
       <c r="I318" s="4" t="n">
-        <v>61.93</v>
+        <v>61.9</v>
       </c>
       <c r="J318" s="4" t="n">
         <v>100</v>
@@ -34941,13 +34947,13 @@
         </is>
       </c>
       <c r="M318" s="4" t="n">
-        <v>45.61</v>
+        <v>45.57</v>
       </c>
       <c r="N318" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O318" s="4" t="n">
-        <v>61.93</v>
+        <v>61.9</v>
       </c>
       <c r="P318" s="4" t="n">
         <v>0</v>
@@ -34979,10 +34985,10 @@
         <v>0</v>
       </c>
       <c r="AC318" s="4" t="n">
-        <v>80.95999999999999</v>
+        <v>80.95</v>
       </c>
       <c r="AD318" s="4" t="n">
-        <v>19.04</v>
+        <v>19.05</v>
       </c>
       <c r="AE318" s="4" t="n">
         <v>0</v>
@@ -35026,7 +35032,7 @@
         </is>
       </c>
       <c r="I319" s="4" t="n">
-        <v>75.09</v>
+        <v>75.06</v>
       </c>
       <c r="J319" s="4" t="n">
         <v>100</v>
@@ -35040,13 +35046,13 @@
         </is>
       </c>
       <c r="M319" s="4" t="n">
-        <v>65.44</v>
+        <v>65.41</v>
       </c>
       <c r="N319" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O319" s="4" t="n">
-        <v>75.09</v>
+        <v>75.06</v>
       </c>
       <c r="P319" s="4" t="n">
         <v>2.36</v>
@@ -35078,10 +35084,10 @@
         <v>0</v>
       </c>
       <c r="AC319" s="4" t="n">
-        <v>87.54000000000001</v>
+        <v>87.53</v>
       </c>
       <c r="AD319" s="4" t="n">
-        <v>12.46</v>
+        <v>12.47</v>
       </c>
       <c r="AE319" s="4" t="n">
         <v>0</v>
@@ -35129,7 +35135,7 @@
         </is>
       </c>
       <c r="I320" s="4" t="n">
-        <v>-17.56</v>
+        <v>-17.59</v>
       </c>
       <c r="J320" s="4" t="n">
         <v>0.4</v>
@@ -35143,13 +35149,13 @@
         </is>
       </c>
       <c r="M320" s="4" t="n">
-        <v>-19.83</v>
+        <v>-19.86</v>
       </c>
       <c r="N320" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O320" s="4" t="n">
-        <v>-17.56</v>
+        <v>-17.59</v>
       </c>
       <c r="P320" s="4" t="n">
         <v>-2.09</v>
@@ -35181,10 +35187,10 @@
         <v>0</v>
       </c>
       <c r="AC320" s="4" t="n">
-        <v>41.22</v>
+        <v>41.21</v>
       </c>
       <c r="AD320" s="4" t="n">
-        <v>58.78</v>
+        <v>58.79</v>
       </c>
       <c r="AE320" s="4" t="n">
         <v>0</v>
@@ -35228,7 +35234,7 @@
         </is>
       </c>
       <c r="I321" s="4" t="n">
-        <v>75.53</v>
+        <v>75.5</v>
       </c>
       <c r="J321" s="4" t="n">
         <v>100</v>
@@ -35242,13 +35248,13 @@
         </is>
       </c>
       <c r="M321" s="4" t="n">
-        <v>67.55</v>
+        <v>67.51000000000001</v>
       </c>
       <c r="N321" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O321" s="4" t="n">
-        <v>75.75</v>
+        <v>75.72</v>
       </c>
       <c r="P321" s="4" t="n">
         <v>1.31</v>
@@ -35288,10 +35294,10 @@
         <v>0</v>
       </c>
       <c r="AC321" s="4" t="n">
-        <v>83.94</v>
+        <v>83.92</v>
       </c>
       <c r="AD321" s="4" t="n">
-        <v>11.7</v>
+        <v>11.72</v>
       </c>
       <c r="AE321" s="4" t="n">
         <v>2.18</v>
@@ -35335,7 +35341,7 @@
         </is>
       </c>
       <c r="I322" s="4" t="n">
-        <v>75.34999999999999</v>
+        <v>75.31999999999999</v>
       </c>
       <c r="J322" s="4" t="n">
         <v>100</v>
@@ -35349,13 +35355,13 @@
         </is>
       </c>
       <c r="M322" s="4" t="n">
-        <v>66.23</v>
+        <v>66.2</v>
       </c>
       <c r="N322" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O322" s="4" t="n">
-        <v>75.34999999999999</v>
+        <v>75.31999999999999</v>
       </c>
       <c r="P322" s="4" t="n">
         <v>0</v>
@@ -35387,10 +35393,10 @@
         <v>0</v>
       </c>
       <c r="AC322" s="4" t="n">
-        <v>87.68000000000001</v>
+        <v>87.66</v>
       </c>
       <c r="AD322" s="4" t="n">
-        <v>12.32</v>
+        <v>12.34</v>
       </c>
       <c r="AE322" s="4" t="n">
         <v>0</v>
@@ -35438,7 +35444,7 @@
         </is>
       </c>
       <c r="I323" s="4" t="n">
-        <v>53.69</v>
+        <v>53.65</v>
       </c>
       <c r="J323" s="4" t="n">
         <v>100</v>
@@ -35452,13 +35458,13 @@
         </is>
       </c>
       <c r="M323" s="4" t="n">
-        <v>39.82</v>
+        <v>39.79</v>
       </c>
       <c r="N323" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O323" s="4" t="n">
-        <v>53.69</v>
+        <v>53.65</v>
       </c>
       <c r="P323" s="4" t="n">
         <v>3.31</v>
@@ -35490,10 +35496,10 @@
         <v>0</v>
       </c>
       <c r="AC323" s="4" t="n">
-        <v>76.84</v>
+        <v>76.83</v>
       </c>
       <c r="AD323" s="4" t="n">
-        <v>23.16</v>
+        <v>23.17</v>
       </c>
       <c r="AE323" s="4" t="n">
         <v>0</v>
@@ -35541,7 +35547,7 @@
         </is>
       </c>
       <c r="I324" s="4" t="n">
-        <v>71.56</v>
+        <v>71.53</v>
       </c>
       <c r="J324" s="4" t="n">
         <v>100</v>
@@ -35555,13 +35561,13 @@
         </is>
       </c>
       <c r="M324" s="4" t="n">
-        <v>56.04</v>
+        <v>56.01</v>
       </c>
       <c r="N324" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O324" s="4" t="n">
-        <v>71.81</v>
+        <v>71.78</v>
       </c>
       <c r="P324" s="4" t="n">
         <v>0</v>
@@ -35601,10 +35607,10 @@
         <v>0</v>
       </c>
       <c r="AC324" s="4" t="n">
-        <v>81.48999999999999</v>
+        <v>81.47</v>
       </c>
       <c r="AD324" s="4" t="n">
-        <v>13.51</v>
+        <v>13.53</v>
       </c>
       <c r="AE324" s="4" t="n">
         <v>1.5</v>
@@ -35652,7 +35658,7 @@
         </is>
       </c>
       <c r="I325" s="4" t="n">
-        <v>52.52</v>
+        <v>52.49</v>
       </c>
       <c r="J325" s="4" t="n">
         <v>100</v>
@@ -35666,13 +35672,13 @@
         </is>
       </c>
       <c r="M325" s="4" t="n">
-        <v>37.01</v>
+        <v>36.98</v>
       </c>
       <c r="N325" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O325" s="4" t="n">
-        <v>52.52</v>
+        <v>52.49</v>
       </c>
       <c r="P325" s="4" t="n">
         <v>0</v>
@@ -35704,10 +35710,10 @@
         <v>0</v>
       </c>
       <c r="AC325" s="4" t="n">
-        <v>76.26000000000001</v>
+        <v>76.23999999999999</v>
       </c>
       <c r="AD325" s="4" t="n">
-        <v>23.74</v>
+        <v>23.76</v>
       </c>
       <c r="AE325" s="4" t="n">
         <v>0</v>
@@ -35755,7 +35761,7 @@
         </is>
       </c>
       <c r="I326" s="4" t="n">
-        <v>5.03</v>
+        <v>5.01</v>
       </c>
       <c r="J326" s="4" t="n">
         <v>80.90000000000001</v>
@@ -35769,13 +35775,13 @@
         </is>
       </c>
       <c r="M326" s="4" t="n">
-        <v>3.58</v>
+        <v>3.55</v>
       </c>
       <c r="N326" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O326" s="4" t="n">
-        <v>6.89</v>
+        <v>6.86</v>
       </c>
       <c r="P326" s="4" t="n">
         <v>0.06</v>
@@ -35796,7 +35802,7 @@
         <v>4</v>
       </c>
       <c r="V326" s="4" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="W326" s="5" t="n">
         <v>9665461</v>
@@ -35813,10 +35819,10 @@
         <v>0</v>
       </c>
       <c r="AC326" s="4" t="n">
-        <v>52.51</v>
+        <v>52.5</v>
       </c>
       <c r="AD326" s="4" t="n">
-        <v>47.49</v>
+        <v>47.5</v>
       </c>
       <c r="AE326" s="4" t="n">
         <v>0</v>
@@ -35864,7 +35870,7 @@
         </is>
       </c>
       <c r="I327" s="4" t="n">
-        <v>20.13</v>
+        <v>20.11</v>
       </c>
       <c r="J327" s="4" t="n">
         <v>99.8</v>
@@ -35878,13 +35884,13 @@
         </is>
       </c>
       <c r="M327" s="4" t="n">
-        <v>4.99</v>
+        <v>4.96</v>
       </c>
       <c r="N327" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O327" s="4" t="n">
-        <v>23.44</v>
+        <v>23.41</v>
       </c>
       <c r="P327" s="4" t="n">
         <v>2.45</v>
@@ -35922,10 +35928,10 @@
         <v>0</v>
       </c>
       <c r="AC327" s="4" t="n">
-        <v>60.06</v>
+        <v>60.05</v>
       </c>
       <c r="AD327" s="4" t="n">
-        <v>39.94</v>
+        <v>39.95</v>
       </c>
       <c r="AE327" s="4" t="n">
         <v>0</v>
@@ -35973,7 +35979,7 @@
         </is>
       </c>
       <c r="I328" s="4" t="n">
-        <v>15.87</v>
+        <v>15.84</v>
       </c>
       <c r="J328" s="4" t="n">
         <v>99.40000000000001</v>
@@ -35987,13 +35993,13 @@
         </is>
       </c>
       <c r="M328" s="4" t="n">
-        <v>2.74</v>
+        <v>2.71</v>
       </c>
       <c r="N328" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O328" s="4" t="n">
-        <v>15.87</v>
+        <v>15.84</v>
       </c>
       <c r="P328" s="4" t="n">
         <v>1.05</v>
@@ -36025,10 +36031,10 @@
         <v>0</v>
       </c>
       <c r="AC328" s="4" t="n">
-        <v>57.93</v>
+        <v>57.92</v>
       </c>
       <c r="AD328" s="4" t="n">
-        <v>42.07</v>
+        <v>42.08</v>
       </c>
       <c r="AE328" s="4" t="n">
         <v>0</v>
@@ -36076,7 +36082,7 @@
         </is>
       </c>
       <c r="I329" s="4" t="n">
-        <v>31.71</v>
+        <v>31.68</v>
       </c>
       <c r="J329" s="4" t="n">
         <v>100</v>
@@ -36090,13 +36096,13 @@
         </is>
       </c>
       <c r="M329" s="4" t="n">
-        <v>15.86</v>
+        <v>15.83</v>
       </c>
       <c r="N329" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O329" s="4" t="n">
-        <v>31.71</v>
+        <v>31.68</v>
       </c>
       <c r="P329" s="4" t="n">
         <v>1.82</v>
@@ -36128,10 +36134,10 @@
         <v>0</v>
       </c>
       <c r="AC329" s="4" t="n">
-        <v>65.84999999999999</v>
+        <v>65.84</v>
       </c>
       <c r="AD329" s="4" t="n">
-        <v>34.15</v>
+        <v>34.16</v>
       </c>
       <c r="AE329" s="4" t="n">
         <v>0</v>
@@ -36175,13 +36181,13 @@
         </is>
       </c>
       <c r="I330" s="4" t="n">
-        <v>-7.06</v>
+        <v>-7.08</v>
       </c>
       <c r="J330" s="4" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="K330" s="4" t="n">
-        <v>87.7</v>
+        <v>87.8</v>
       </c>
       <c r="L330" t="inlineStr">
         <is>
@@ -36189,13 +36195,13 @@
         </is>
       </c>
       <c r="M330" s="4" t="n">
-        <v>-19.12</v>
+        <v>-19.15</v>
       </c>
       <c r="N330" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O330" s="4" t="n">
-        <v>-13.17</v>
+        <v>-13.21</v>
       </c>
       <c r="P330" s="4" t="n">
         <v>-0.47</v>
@@ -36216,7 +36222,7 @@
         <v>7</v>
       </c>
       <c r="V330" s="4" t="n">
-        <v>-1.03</v>
+        <v>-1.04</v>
       </c>
       <c r="W330" s="5" t="n">
         <v>7184413</v>
@@ -36233,10 +36239,10 @@
         <v>0</v>
       </c>
       <c r="AC330" s="4" t="n">
-        <v>46.47</v>
+        <v>46.46</v>
       </c>
       <c r="AD330" s="4" t="n">
-        <v>53.53</v>
+        <v>53.54</v>
       </c>
       <c r="AE330" s="4" t="n">
         <v>0</v>
@@ -36284,7 +36290,7 @@
         </is>
       </c>
       <c r="I331" s="4" t="n">
-        <v>25.37</v>
+        <v>25.34</v>
       </c>
       <c r="J331" s="4" t="n">
         <v>99.90000000000001</v>
@@ -36298,13 +36304,13 @@
         </is>
       </c>
       <c r="M331" s="4" t="n">
-        <v>9.01</v>
+        <v>8.98</v>
       </c>
       <c r="N331" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O331" s="4" t="n">
-        <v>25.37</v>
+        <v>25.34</v>
       </c>
       <c r="P331" s="4" t="n">
         <v>1.43</v>
@@ -36336,10 +36342,10 @@
         <v>0</v>
       </c>
       <c r="AC331" s="4" t="n">
-        <v>62.69</v>
+        <v>62.67</v>
       </c>
       <c r="AD331" s="4" t="n">
-        <v>37.31</v>
+        <v>37.33</v>
       </c>
       <c r="AE331" s="4" t="n">
         <v>0</v>
@@ -36387,7 +36393,7 @@
         </is>
       </c>
       <c r="I332" s="4" t="n">
-        <v>-19.07</v>
+        <v>-19.09</v>
       </c>
       <c r="J332" s="4" t="n">
         <v>0.3</v>
@@ -36401,13 +36407,13 @@
         </is>
       </c>
       <c r="M332" s="4" t="n">
-        <v>-20.4</v>
+        <v>-20.43</v>
       </c>
       <c r="N332" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O332" s="4" t="n">
-        <v>-18.85</v>
+        <v>-18.89</v>
       </c>
       <c r="P332" s="4" t="n">
         <v>-1.08</v>
@@ -36428,7 +36434,7 @@
         <v>1</v>
       </c>
       <c r="V332" s="4" t="n">
-        <v>-19.43</v>
+        <v>-19.45</v>
       </c>
       <c r="W332" s="5" t="n">
         <v>584417</v>
@@ -36445,10 +36451,10 @@
         <v>0</v>
       </c>
       <c r="AC332" s="4" t="n">
-        <v>40.47</v>
+        <v>40.45</v>
       </c>
       <c r="AD332" s="4" t="n">
-        <v>59.53</v>
+        <v>59.55</v>
       </c>
       <c r="AE332" s="4" t="n">
         <v>0</v>
@@ -36496,7 +36502,7 @@
         </is>
       </c>
       <c r="I333" s="4" t="n">
-        <v>-19.53</v>
+        <v>-19.56</v>
       </c>
       <c r="J333" s="4" t="n">
         <v>0.3</v>
@@ -36510,13 +36516,13 @@
         </is>
       </c>
       <c r="M333" s="4" t="n">
-        <v>-22.26</v>
+        <v>-22.29</v>
       </c>
       <c r="N333" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O333" s="4" t="n">
-        <v>-19.53</v>
+        <v>-19.56</v>
       </c>
       <c r="P333" s="4" t="n">
         <v>-1.42</v>
@@ -36548,10 +36554,10 @@
         <v>0</v>
       </c>
       <c r="AC333" s="4" t="n">
-        <v>40.24</v>
+        <v>40.22</v>
       </c>
       <c r="AD333" s="4" t="n">
-        <v>59.76</v>
+        <v>59.78</v>
       </c>
       <c r="AE333" s="4" t="n">
         <v>0</v>
@@ -36599,7 +36605,7 @@
         </is>
       </c>
       <c r="I334" s="4" t="n">
-        <v>30.29</v>
+        <v>30.25</v>
       </c>
       <c r="J334" s="4" t="n">
         <v>100</v>
@@ -36613,13 +36619,13 @@
         </is>
       </c>
       <c r="M334" s="4" t="n">
-        <v>19.59</v>
+        <v>19.55</v>
       </c>
       <c r="N334" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O334" s="4" t="n">
-        <v>30.29</v>
+        <v>30.25</v>
       </c>
       <c r="P334" s="4" t="n">
         <v>2.45</v>
@@ -36651,10 +36657,10 @@
         <v>0</v>
       </c>
       <c r="AC334" s="4" t="n">
-        <v>65.14</v>
+        <v>65.13</v>
       </c>
       <c r="AD334" s="4" t="n">
-        <v>34.86</v>
+        <v>34.87</v>
       </c>
       <c r="AE334" s="4" t="n">
         <v>0</v>
@@ -36702,7 +36708,7 @@
         </is>
       </c>
       <c r="I335" s="4" t="n">
-        <v>39.02</v>
+        <v>38.99</v>
       </c>
       <c r="J335" s="4" t="n">
         <v>100</v>
@@ -36716,13 +36722,13 @@
         </is>
       </c>
       <c r="M335" s="4" t="n">
-        <v>21.28</v>
+        <v>21.25</v>
       </c>
       <c r="N335" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O335" s="4" t="n">
-        <v>39.02</v>
+        <v>38.99</v>
       </c>
       <c r="P335" s="4" t="n">
         <v>0</v>
@@ -36754,10 +36760,10 @@
         <v>0</v>
       </c>
       <c r="AC335" s="4" t="n">
-        <v>69.51000000000001</v>
+        <v>69.48999999999999</v>
       </c>
       <c r="AD335" s="4" t="n">
-        <v>30.49</v>
+        <v>30.51</v>
       </c>
       <c r="AE335" s="4" t="n">
         <v>0</v>
@@ -37665,7 +37671,7 @@
         </is>
       </c>
       <c r="I344" s="4" t="n">
-        <v>9.710000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J344" s="4" t="n">
         <v>95.09999999999999</v>
@@ -37706,7 +37712,7 @@
         <v>2</v>
       </c>
       <c r="V344" s="4" t="n">
-        <v>-2.37</v>
+        <v>-2.39</v>
       </c>
       <c r="W344" s="5" t="n">
         <v>5584405</v>
@@ -37774,17 +37780,17 @@
         </is>
       </c>
       <c r="I345" s="4" t="n">
-        <v>-4.99</v>
+        <v>-3.49</v>
       </c>
       <c r="J345" s="4" t="n">
-        <v>19.2</v>
+        <v>25.7</v>
       </c>
       <c r="K345" s="4" t="n">
-        <v>80.8</v>
+        <v>74.3</v>
       </c>
       <c r="L345" t="inlineStr">
         <is>
-          <t>Likely R</t>
+          <t>Lean R</t>
         </is>
       </c>
       <c r="M345" s="4" t="n">
@@ -37806,16 +37812,16 @@
         <v>-7.86</v>
       </c>
       <c r="S345" s="4" t="n">
-        <v>41</v>
+        <v>44.6</v>
       </c>
       <c r="T345" s="4" t="n">
-        <v>47.01</v>
+        <v>45.2</v>
       </c>
       <c r="U345" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V345" s="4" t="n">
-        <v>-6.87</v>
+        <v>-2.68</v>
       </c>
       <c r="W345" s="5" t="n">
         <v>883182</v>
@@ -37834,16 +37840,16 @@
         </is>
       </c>
       <c r="AA345" s="4" t="n">
-        <v>1.98</v>
+        <v>3.2</v>
       </c>
       <c r="AB345" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC345" s="4" t="n">
-        <v>46.56</v>
+        <v>46.71</v>
       </c>
       <c r="AD345" s="4" t="n">
-        <v>51.46</v>
+        <v>50.09</v>
       </c>
       <c r="AE345" s="4" t="n">
         <v>0</v>
@@ -38311,7 +38317,7 @@
         </is>
       </c>
       <c r="I350" s="4" t="n">
-        <v>-1.07</v>
+        <v>-1.08</v>
       </c>
       <c r="J350" s="4" t="n">
         <v>42.4</v>
@@ -38352,7 +38358,7 @@
         <v>3</v>
       </c>
       <c r="V350" s="4" t="n">
-        <v>-2.55</v>
+        <v>-2.56</v>
       </c>
       <c r="W350" s="5" t="n">
         <v>1145777</v>
@@ -38377,10 +38383,10 @@
         <v>0</v>
       </c>
       <c r="AC350" s="4" t="n">
-        <v>48.27</v>
+        <v>48.26</v>
       </c>
       <c r="AD350" s="4" t="n">
-        <v>49.31</v>
+        <v>49.32</v>
       </c>
       <c r="AE350" s="4" t="n">
         <v>0</v>
@@ -38424,13 +38430,13 @@
         </is>
       </c>
       <c r="I351" s="4" t="n">
-        <v>-12</v>
+        <v>-11.79</v>
       </c>
       <c r="J351" s="4" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K351" s="4" t="n">
-        <v>98.90000000000001</v>
+        <v>98.8</v>
       </c>
       <c r="L351" t="inlineStr">
         <is>
@@ -38438,13 +38444,13 @@
         </is>
       </c>
       <c r="M351" s="4" t="n">
-        <v>-17.04</v>
+        <v>-16.83</v>
       </c>
       <c r="N351" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O351" s="4" t="n">
-        <v>-12</v>
+        <v>-11.79</v>
       </c>
       <c r="P351" s="4" t="n">
         <v>-1.68</v>
@@ -38476,10 +38482,10 @@
         <v>0</v>
       </c>
       <c r="AC351" s="4" t="n">
-        <v>44</v>
+        <v>44.1</v>
       </c>
       <c r="AD351" s="4" t="n">
-        <v>56</v>
+        <v>55.9</v>
       </c>
       <c r="AE351" s="4" t="n">
         <v>0</v>
@@ -38527,7 +38533,7 @@
         </is>
       </c>
       <c r="I352" s="4" t="n">
-        <v>-45.94</v>
+        <v>-45.74</v>
       </c>
       <c r="J352" s="4" t="n">
         <v>0</v>
@@ -38541,13 +38547,13 @@
         </is>
       </c>
       <c r="M352" s="4" t="n">
-        <v>-50.3</v>
+        <v>-50.1</v>
       </c>
       <c r="N352" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O352" s="4" t="n">
-        <v>-45.84</v>
+        <v>-45.63</v>
       </c>
       <c r="P352" s="4" t="n">
         <v>-1.23</v>
@@ -38587,10 +38593,10 @@
         <v>0</v>
       </c>
       <c r="AC352" s="4" t="n">
-        <v>26.47</v>
+        <v>26.57</v>
       </c>
       <c r="AD352" s="4" t="n">
-        <v>71.45999999999999</v>
+        <v>71.36</v>
       </c>
       <c r="AE352" s="4" t="n">
         <v>0</v>
@@ -38638,7 +38644,7 @@
         </is>
       </c>
       <c r="I353" s="4" t="n">
-        <v>-39.54</v>
+        <v>-39.34</v>
       </c>
       <c r="J353" s="4" t="n">
         <v>0</v>
@@ -38652,13 +38658,13 @@
         </is>
       </c>
       <c r="M353" s="4" t="n">
-        <v>-40.01</v>
+        <v>-39.8</v>
       </c>
       <c r="N353" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O353" s="4" t="n">
-        <v>-39.54</v>
+        <v>-39.34</v>
       </c>
       <c r="P353" s="4" t="n">
         <v>-2.1</v>
@@ -38690,10 +38696,10 @@
         <v>0</v>
       </c>
       <c r="AC353" s="4" t="n">
-        <v>30.23</v>
+        <v>30.33</v>
       </c>
       <c r="AD353" s="4" t="n">
-        <v>69.77</v>
+        <v>69.67</v>
       </c>
       <c r="AE353" s="4" t="n">
         <v>0</v>
@@ -38741,7 +38747,7 @@
         </is>
       </c>
       <c r="I354" s="4" t="n">
-        <v>-28.92</v>
+        <v>-28.72</v>
       </c>
       <c r="J354" s="4" t="n">
         <v>0</v>
@@ -38755,13 +38761,13 @@
         </is>
       </c>
       <c r="M354" s="4" t="n">
-        <v>-28.03</v>
+        <v>-27.83</v>
       </c>
       <c r="N354" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O354" s="4" t="n">
-        <v>-28.79</v>
+        <v>-28.58</v>
       </c>
       <c r="P354" s="4" t="n">
         <v>-2.45</v>
@@ -38801,10 +38807,10 @@
         <v>0</v>
       </c>
       <c r="AC354" s="4" t="n">
-        <v>34.6</v>
+        <v>34.7</v>
       </c>
       <c r="AD354" s="4" t="n">
-        <v>62.75</v>
+        <v>62.65</v>
       </c>
       <c r="AE354" s="4" t="n">
         <v>0</v>
@@ -38852,27 +38858,27 @@
         </is>
       </c>
       <c r="I355" s="4" t="n">
-        <v>-9.68</v>
+        <v>-9.56</v>
       </c>
       <c r="J355" s="4" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="K355" s="4" t="n">
-        <v>95.09999999999999</v>
+        <v>94.8</v>
       </c>
       <c r="L355" t="inlineStr">
         <is>
-          <t>Safe R</t>
+          <t>Likely R</t>
         </is>
       </c>
       <c r="M355" s="4" t="n">
-        <v>-13.79</v>
+        <v>-13.59</v>
       </c>
       <c r="N355" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O355" s="4" t="n">
-        <v>-10.85</v>
+        <v>-10.64</v>
       </c>
       <c r="P355" s="4" t="n">
         <v>-0.85</v>
@@ -38893,7 +38899,7 @@
         <v>1</v>
       </c>
       <c r="V355" s="4" t="n">
-        <v>-7.08</v>
+        <v>-7.12</v>
       </c>
       <c r="W355" s="5" t="n">
         <v>738967</v>
@@ -38918,10 +38924,10 @@
         <v>0</v>
       </c>
       <c r="AC355" s="4" t="n">
-        <v>43.79</v>
+        <v>43.85</v>
       </c>
       <c r="AD355" s="4" t="n">
-        <v>53.17</v>
+        <v>53.11</v>
       </c>
       <c r="AE355" s="4" t="n">
         <v>0</v>
@@ -39189,7 +39195,7 @@
         </is>
       </c>
       <c r="M358" s="4" t="n">
-        <v>47.51</v>
+        <v>47.5</v>
       </c>
       <c r="N358" s="4" t="n">
         <v>7.28</v>
@@ -39298,7 +39304,7 @@
         <v>7.28</v>
       </c>
       <c r="O359" s="4" t="n">
-        <v>19.16</v>
+        <v>19.15</v>
       </c>
       <c r="P359" s="4" t="n">
         <v>0.32</v>
@@ -39403,7 +39409,7 @@
         </is>
       </c>
       <c r="M360" s="4" t="n">
-        <v>8.24</v>
+        <v>8.23</v>
       </c>
       <c r="N360" s="4" t="n">
         <v>7.28</v>
@@ -39552,10 +39558,10 @@
         <v>0</v>
       </c>
       <c r="AC361" s="4" t="n">
-        <v>60.22</v>
+        <v>60.21</v>
       </c>
       <c r="AD361" s="4" t="n">
-        <v>39.78</v>
+        <v>39.79</v>
       </c>
       <c r="AE361" s="4" t="n">
         <v>0</v>
@@ -39606,10 +39612,10 @@
         <v>0.2</v>
       </c>
       <c r="J362" s="4" t="n">
-        <v>51.5</v>
+        <v>51.4</v>
       </c>
       <c r="K362" s="4" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="L362" t="inlineStr">
         <is>
@@ -39644,7 +39650,7 @@
         <v>6</v>
       </c>
       <c r="V362" s="4" t="n">
-        <v>-3.39</v>
+        <v>-3.4</v>
       </c>
       <c r="W362" s="5" t="n">
         <v>2895901</v>
@@ -40231,7 +40237,7 @@
         </is>
       </c>
       <c r="I368" s="4" t="n">
-        <v>6.56</v>
+        <v>6.55</v>
       </c>
       <c r="J368" s="4" t="n">
         <v>86.09999999999999</v>
@@ -40272,7 +40278,7 @@
         <v>2</v>
       </c>
       <c r="V368" s="4" t="n">
-        <v>5.9</v>
+        <v>5.87</v>
       </c>
       <c r="W368" s="5" t="n">
         <v>4991635</v>
@@ -40289,10 +40295,10 @@
         <v>0</v>
       </c>
       <c r="AC368" s="4" t="n">
-        <v>53.28</v>
+        <v>53.27</v>
       </c>
       <c r="AD368" s="4" t="n">
-        <v>46.72</v>
+        <v>46.73</v>
       </c>
       <c r="AE368" s="4" t="n">
         <v>0</v>
@@ -40552,7 +40558,7 @@
         </is>
       </c>
       <c r="I371" s="4" t="n">
-        <v>9.59</v>
+        <v>9.58</v>
       </c>
       <c r="J371" s="4" t="n">
         <v>94.8</v>
@@ -40593,7 +40599,7 @@
         <v>5</v>
       </c>
       <c r="V371" s="4" t="n">
-        <v>3.57</v>
+        <v>3.55</v>
       </c>
       <c r="W371" s="5" t="n">
         <v>8689754</v>
@@ -41598,13 +41604,13 @@
         </is>
       </c>
       <c r="I381" s="4" t="n">
-        <v>-0.7</v>
+        <v>-0.84</v>
       </c>
       <c r="J381" s="4" t="n">
-        <v>45.1</v>
+        <v>44.1</v>
       </c>
       <c r="K381" s="4" t="n">
-        <v>54.9</v>
+        <v>55.9</v>
       </c>
       <c r="L381" t="inlineStr">
         <is>
@@ -41612,13 +41618,13 @@
         </is>
       </c>
       <c r="M381" s="4" t="n">
-        <v>-7.42</v>
+        <v>-7.62</v>
       </c>
       <c r="N381" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O381" s="4" t="n">
-        <v>-0.06</v>
+        <v>-0.25</v>
       </c>
       <c r="P381" s="4" t="n">
         <v>0.53</v>
@@ -41639,7 +41645,7 @@
         <v>3</v>
       </c>
       <c r="V381" s="4" t="n">
-        <v>-2.58</v>
+        <v>-2.63</v>
       </c>
       <c r="W381" s="5" t="n">
         <v>4429295</v>
@@ -41664,10 +41670,10 @@
         <v>0</v>
       </c>
       <c r="AC381" s="4" t="n">
-        <v>48.88</v>
+        <v>48.81</v>
       </c>
       <c r="AD381" s="4" t="n">
-        <v>49.57</v>
+        <v>49.64</v>
       </c>
       <c r="AE381" s="4" t="n">
         <v>0</v>
@@ -41715,13 +41721,13 @@
         </is>
       </c>
       <c r="I382" s="4" t="n">
-        <v>-8.140000000000001</v>
+        <v>-8.33</v>
       </c>
       <c r="J382" s="4" t="n">
-        <v>9.1</v>
+        <v>8.5</v>
       </c>
       <c r="K382" s="4" t="n">
-        <v>90.90000000000001</v>
+        <v>91.5</v>
       </c>
       <c r="L382" t="inlineStr">
         <is>
@@ -41729,13 +41735,13 @@
         </is>
       </c>
       <c r="M382" s="4" t="n">
-        <v>-8.609999999999999</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="N382" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O382" s="4" t="n">
-        <v>-8.039999999999999</v>
+        <v>-8.23</v>
       </c>
       <c r="P382" s="4" t="n">
         <v>-1.92</v>
@@ -41775,10 +41781,10 @@
         <v>0</v>
       </c>
       <c r="AC382" s="4" t="n">
-        <v>44.99</v>
+        <v>44.9</v>
       </c>
       <c r="AD382" s="4" t="n">
-        <v>52.97</v>
+        <v>53.06</v>
       </c>
       <c r="AE382" s="4" t="n">
         <v>0</v>
@@ -41826,7 +41832,7 @@
         </is>
       </c>
       <c r="I383" s="4" t="n">
-        <v>-37.63</v>
+        <v>-37.83</v>
       </c>
       <c r="J383" s="4" t="n">
         <v>0</v>
@@ -41840,13 +41846,13 @@
         </is>
       </c>
       <c r="M383" s="4" t="n">
-        <v>-37.07</v>
+        <v>-37.26</v>
       </c>
       <c r="N383" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O383" s="4" t="n">
-        <v>-37.98</v>
+        <v>-38.17</v>
       </c>
       <c r="P383" s="4" t="n">
         <v>-1.21</v>
@@ -41886,10 +41892,10 @@
         <v>0</v>
       </c>
       <c r="AC383" s="4" t="n">
-        <v>30.65</v>
+        <v>30.55</v>
       </c>
       <c r="AD383" s="4" t="n">
-        <v>67.64</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="AE383" s="4" t="n">
         <v>0</v>
@@ -41937,7 +41943,7 @@
         </is>
       </c>
       <c r="I384" s="4" t="n">
-        <v>-13.73</v>
+        <v>-13.93</v>
       </c>
       <c r="J384" s="4" t="n">
         <v>0.8</v>
@@ -41951,13 +41957,13 @@
         </is>
       </c>
       <c r="M384" s="4" t="n">
-        <v>-17.91</v>
+        <v>-18.1</v>
       </c>
       <c r="N384" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O384" s="4" t="n">
-        <v>-14.18</v>
+        <v>-14.38</v>
       </c>
       <c r="P384" s="4" t="n">
         <v>-1.92</v>
@@ -41997,10 +42003,10 @@
         <v>0</v>
       </c>
       <c r="AC384" s="4" t="n">
-        <v>42.17</v>
+        <v>42.07</v>
       </c>
       <c r="AD384" s="4" t="n">
-        <v>55.59</v>
+        <v>55.69</v>
       </c>
       <c r="AE384" s="4" t="n">
         <v>0</v>
@@ -42044,13 +42050,13 @@
         </is>
       </c>
       <c r="I385" s="4" t="n">
-        <v>-11.17</v>
+        <v>-11.36</v>
       </c>
       <c r="J385" s="4" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="K385" s="4" t="n">
-        <v>98.5</v>
+        <v>98.7</v>
       </c>
       <c r="L385" t="inlineStr">
         <is>
@@ -42058,13 +42064,13 @@
         </is>
       </c>
       <c r="M385" s="4" t="n">
-        <v>-16.88</v>
+        <v>-17.08</v>
       </c>
       <c r="N385" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O385" s="4" t="n">
-        <v>-11.17</v>
+        <v>-11.36</v>
       </c>
       <c r="P385" s="4" t="n">
         <v>-1.09</v>
@@ -42096,10 +42102,10 @@
         <v>0</v>
       </c>
       <c r="AC385" s="4" t="n">
-        <v>44.42</v>
+        <v>44.32</v>
       </c>
       <c r="AD385" s="4" t="n">
-        <v>55.58</v>
+        <v>55.68</v>
       </c>
       <c r="AE385" s="4" t="n">
         <v>0</v>
@@ -42147,7 +42153,7 @@
         </is>
       </c>
       <c r="I386" s="4" t="n">
-        <v>39.63</v>
+        <v>39.44</v>
       </c>
       <c r="J386" s="4" t="n">
         <v>100</v>
@@ -42161,13 +42167,13 @@
         </is>
       </c>
       <c r="M386" s="4" t="n">
-        <v>30.84</v>
+        <v>30.65</v>
       </c>
       <c r="N386" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O386" s="4" t="n">
-        <v>39.63</v>
+        <v>39.44</v>
       </c>
       <c r="P386" s="4" t="n">
         <v>0</v>
@@ -42199,10 +42205,10 @@
         <v>0</v>
       </c>
       <c r="AC386" s="4" t="n">
-        <v>69.81999999999999</v>
+        <v>69.72</v>
       </c>
       <c r="AD386" s="4" t="n">
-        <v>30.18</v>
+        <v>30.28</v>
       </c>
       <c r="AE386" s="4" t="n">
         <v>0</v>
@@ -42250,7 +42256,7 @@
         </is>
       </c>
       <c r="I387" s="4" t="n">
-        <v>-15.56</v>
+        <v>-15.72</v>
       </c>
       <c r="J387" s="4" t="n">
         <v>0.6</v>
@@ -42264,13 +42270,13 @@
         </is>
       </c>
       <c r="M387" s="4" t="n">
-        <v>-19.48</v>
+        <v>-19.67</v>
       </c>
       <c r="N387" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O387" s="4" t="n">
-        <v>-17.68</v>
+        <v>-17.87</v>
       </c>
       <c r="P387" s="4" t="n">
         <v>-0.88</v>
@@ -42308,10 +42314,10 @@
         <v>0</v>
       </c>
       <c r="AC387" s="4" t="n">
-        <v>42.22</v>
+        <v>42.14</v>
       </c>
       <c r="AD387" s="4" t="n">
-        <v>57.78</v>
+        <v>57.86</v>
       </c>
       <c r="AE387" s="4" t="n">
         <v>0</v>
@@ -42464,7 +42470,7 @@
         </is>
       </c>
       <c r="I389" s="4" t="n">
-        <v>-51.28</v>
+        <v>-50.89</v>
       </c>
       <c r="J389" s="4" t="n">
         <v>0</v>
@@ -42478,13 +42484,13 @@
         </is>
       </c>
       <c r="M389" s="4" t="n">
-        <v>-53.76</v>
+        <v>-53.36</v>
       </c>
       <c r="N389" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O389" s="4" t="n">
-        <v>-51.2</v>
+        <v>-50.8</v>
       </c>
       <c r="P389" s="4" t="n">
         <v>-1.36</v>
@@ -42524,10 +42530,10 @@
         <v>0</v>
       </c>
       <c r="AC389" s="4" t="n">
-        <v>23.96</v>
+        <v>24.16</v>
       </c>
       <c r="AD389" s="4" t="n">
-        <v>74.41</v>
+        <v>74.20999999999999</v>
       </c>
       <c r="AE389" s="4" t="n">
         <v>0</v>
@@ -42575,7 +42581,7 @@
         </is>
       </c>
       <c r="I390" s="4" t="n">
-        <v>-28.73</v>
+        <v>-28.34</v>
       </c>
       <c r="J390" s="4" t="n">
         <v>0</v>
@@ -42589,13 +42595,13 @@
         </is>
       </c>
       <c r="M390" s="4" t="n">
-        <v>-29.59</v>
+        <v>-29.2</v>
       </c>
       <c r="N390" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O390" s="4" t="n">
-        <v>-28.63</v>
+        <v>-28.23</v>
       </c>
       <c r="P390" s="4" t="n">
         <v>-1.11</v>
@@ -42635,10 +42641,10 @@
         <v>0</v>
       </c>
       <c r="AC390" s="4" t="n">
-        <v>34.86</v>
+        <v>35.06</v>
       </c>
       <c r="AD390" s="4" t="n">
-        <v>62.98</v>
+        <v>62.78</v>
       </c>
       <c r="AE390" s="4" t="n">
         <v>0</v>
@@ -42686,7 +42692,7 @@
         </is>
       </c>
       <c r="I391" s="4" t="n">
-        <v>-30.38</v>
+        <v>-29.99</v>
       </c>
       <c r="J391" s="4" t="n">
         <v>0</v>
@@ -42700,13 +42706,13 @@
         </is>
       </c>
       <c r="M391" s="4" t="n">
-        <v>-31.41</v>
+        <v>-31.01</v>
       </c>
       <c r="N391" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O391" s="4" t="n">
-        <v>-30.28</v>
+        <v>-29.89</v>
       </c>
       <c r="P391" s="4" t="n">
         <v>-2.04</v>
@@ -42746,10 +42752,10 @@
         <v>0</v>
       </c>
       <c r="AC391" s="4" t="n">
-        <v>34.11</v>
+        <v>34.31</v>
       </c>
       <c r="AD391" s="4" t="n">
-        <v>63.89</v>
+        <v>63.69</v>
       </c>
       <c r="AE391" s="4" t="n">
         <v>0</v>
@@ -42797,7 +42803,7 @@
         </is>
       </c>
       <c r="I392" s="4" t="n">
-        <v>-13.03</v>
+        <v>-12.63</v>
       </c>
       <c r="J392" s="4" t="n">
         <v>1</v>
@@ -42811,13 +42817,13 @@
         </is>
       </c>
       <c r="M392" s="4" t="n">
-        <v>-18.38</v>
+        <v>-17.98</v>
       </c>
       <c r="N392" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O392" s="4" t="n">
-        <v>-12.91</v>
+        <v>-12.52</v>
       </c>
       <c r="P392" s="4" t="n">
         <v>-1.22</v>
@@ -42857,10 +42863,10 @@
         <v>0</v>
       </c>
       <c r="AC392" s="4" t="n">
-        <v>42.52</v>
+        <v>42.71</v>
       </c>
       <c r="AD392" s="4" t="n">
-        <v>55.25</v>
+        <v>55.06</v>
       </c>
       <c r="AE392" s="4" t="n">
         <v>0</v>
@@ -42904,13 +42910,13 @@
         </is>
       </c>
       <c r="I393" s="4" t="n">
-        <v>-8.69</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="J393" s="4" t="n">
-        <v>7.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K393" s="4" t="n">
-        <v>92.5</v>
+        <v>91.8</v>
       </c>
       <c r="L393" t="inlineStr">
         <is>
@@ -42918,13 +42924,13 @@
         </is>
       </c>
       <c r="M393" s="4" t="n">
-        <v>-16.46</v>
+        <v>-16.06</v>
       </c>
       <c r="N393" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O393" s="4" t="n">
-        <v>-9.109999999999999</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="P393" s="4" t="n">
         <v>0.48</v>
@@ -42945,7 +42951,7 @@
         <v>2</v>
       </c>
       <c r="V393" s="4" t="n">
-        <v>-7.99</v>
+        <v>-8</v>
       </c>
       <c r="W393" s="5" t="n">
         <v>3380345</v>
@@ -42970,10 +42976,10 @@
         <v>0</v>
       </c>
       <c r="AC393" s="4" t="n">
-        <v>45.43</v>
+        <v>45.54</v>
       </c>
       <c r="AD393" s="4" t="n">
-        <v>54.07</v>
+        <v>53.96</v>
       </c>
       <c r="AE393" s="4" t="n">
         <v>0</v>
@@ -43017,7 +43023,7 @@
         </is>
       </c>
       <c r="I394" s="4" t="n">
-        <v>-16.79</v>
+        <v>-16.39</v>
       </c>
       <c r="J394" s="4" t="n">
         <v>0.5</v>
@@ -43031,13 +43037,13 @@
         </is>
       </c>
       <c r="M394" s="4" t="n">
-        <v>-21.41</v>
+        <v>-21.02</v>
       </c>
       <c r="N394" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O394" s="4" t="n">
-        <v>-16.69</v>
+        <v>-16.29</v>
       </c>
       <c r="P394" s="4" t="n">
         <v>-1.92</v>
@@ -43077,10 +43083,10 @@
         <v>0</v>
       </c>
       <c r="AC394" s="4" t="n">
-        <v>40.74</v>
+        <v>40.94</v>
       </c>
       <c r="AD394" s="4" t="n">
-        <v>57.19</v>
+        <v>56.99</v>
       </c>
       <c r="AE394" s="4" t="n">
         <v>0</v>
@@ -43128,13 +43134,13 @@
         </is>
       </c>
       <c r="I395" s="4" t="n">
-        <v>-13.4</v>
+        <v>-13</v>
       </c>
       <c r="J395" s="4" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="K395" s="4" t="n">
-        <v>99.09999999999999</v>
+        <v>99</v>
       </c>
       <c r="L395" t="inlineStr">
         <is>
@@ -43142,13 +43148,13 @@
         </is>
       </c>
       <c r="M395" s="4" t="n">
-        <v>-17.79</v>
+        <v>-17.4</v>
       </c>
       <c r="N395" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O395" s="4" t="n">
-        <v>-13.29</v>
+        <v>-12.89</v>
       </c>
       <c r="P395" s="4" t="n">
         <v>-0.55</v>
@@ -43188,10 +43194,10 @@
         <v>0</v>
       </c>
       <c r="AC395" s="4" t="n">
-        <v>42.37</v>
+        <v>42.56</v>
       </c>
       <c r="AD395" s="4" t="n">
-        <v>55.47</v>
+        <v>55.28</v>
       </c>
       <c r="AE395" s="4" t="n">
         <v>0</v>
@@ -43239,7 +43245,7 @@
         </is>
       </c>
       <c r="I396" s="4" t="n">
-        <v>-16.4</v>
+        <v>-16.01</v>
       </c>
       <c r="J396" s="4" t="n">
         <v>0.5</v>
@@ -43253,13 +43259,13 @@
         </is>
       </c>
       <c r="M396" s="4" t="n">
-        <v>-15.59</v>
+        <v>-15.19</v>
       </c>
       <c r="N396" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O396" s="4" t="n">
-        <v>-16.31</v>
+        <v>-15.91</v>
       </c>
       <c r="P396" s="4" t="n">
         <v>-2.15</v>
@@ -43299,10 +43305,10 @@
         <v>0</v>
       </c>
       <c r="AC396" s="4" t="n">
-        <v>41.04</v>
+        <v>41.24</v>
       </c>
       <c r="AD396" s="4" t="n">
-        <v>57.15</v>
+        <v>56.95</v>
       </c>
       <c r="AE396" s="4" t="n">
         <v>0</v>
@@ -43346,13 +43352,13 @@
         </is>
       </c>
       <c r="I397" s="4" t="n">
-        <v>-6.79</v>
+        <v>-6.5</v>
       </c>
       <c r="J397" s="4" t="n">
-        <v>13.2</v>
+        <v>14.1</v>
       </c>
       <c r="K397" s="4" t="n">
-        <v>86.8</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="L397" t="inlineStr">
         <is>
@@ -43360,13 +43366,13 @@
         </is>
       </c>
       <c r="M397" s="4" t="n">
-        <v>-14.44</v>
+        <v>-14.05</v>
       </c>
       <c r="N397" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O397" s="4" t="n">
-        <v>-7.3</v>
+        <v>-6.9</v>
       </c>
       <c r="P397" s="4" t="n">
         <v>0.16</v>
@@ -43387,7 +43393,7 @@
         <v>1</v>
       </c>
       <c r="V397" s="4" t="n">
-        <v>-5.08</v>
+        <v>-5.09</v>
       </c>
       <c r="W397" s="5" t="n">
         <v>3642697</v>
@@ -43412,10 +43418,10 @@
         <v>0</v>
       </c>
       <c r="AC397" s="4" t="n">
-        <v>45.83</v>
+        <v>45.97</v>
       </c>
       <c r="AD397" s="4" t="n">
-        <v>52.51</v>
+        <v>52.37</v>
       </c>
       <c r="AE397" s="4" t="n">
         <v>0</v>
@@ -43463,7 +43469,7 @@
         </is>
       </c>
       <c r="I398" s="4" t="n">
-        <v>-40.15</v>
+        <v>-40.14</v>
       </c>
       <c r="J398" s="4" t="n">
         <v>0</v>
@@ -43483,7 +43489,7 @@
         <v>7.28</v>
       </c>
       <c r="O398" s="4" t="n">
-        <v>-40.15</v>
+        <v>-40.14</v>
       </c>
       <c r="P398" s="4" t="n">
         <v>-2.66</v>
@@ -43877,7 +43883,7 @@
         </is>
       </c>
       <c r="I402" s="4" t="n">
-        <v>-11.86</v>
+        <v>-11.85</v>
       </c>
       <c r="J402" s="4" t="n">
         <v>1.2</v>
@@ -43897,7 +43903,7 @@
         <v>7.28</v>
       </c>
       <c r="O402" s="4" t="n">
-        <v>-11.86</v>
+        <v>-11.85</v>
       </c>
       <c r="P402" s="4" t="n">
         <v>-2.18</v>
@@ -44103,7 +44109,7 @@
         <v>7.28</v>
       </c>
       <c r="O404" s="4" t="n">
-        <v>44.1</v>
+        <v>44.11</v>
       </c>
       <c r="P404" s="4" t="n">
         <v>1.84</v>
@@ -44292,10 +44298,10 @@
         <v>-4.8</v>
       </c>
       <c r="J406" s="4" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="K406" s="4" t="n">
-        <v>80.09999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="L406" t="inlineStr">
         <is>
@@ -44309,7 +44315,7 @@
         <v>7.28</v>
       </c>
       <c r="O406" s="4" t="n">
-        <v>-3.39</v>
+        <v>-3.38</v>
       </c>
       <c r="P406" s="4" t="n">
         <v>-1.73</v>
@@ -44330,7 +44336,7 @@
         <v>2</v>
       </c>
       <c r="V406" s="4" t="n">
-        <v>-6.36</v>
+        <v>-6.38</v>
       </c>
       <c r="W406" s="5" t="n">
         <v>152003</v>
@@ -44397,10 +44403,10 @@
         <v>-9.68</v>
       </c>
       <c r="J407" s="4" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="K407" s="4" t="n">
-        <v>95</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="L407" t="inlineStr">
         <is>
@@ -44408,13 +44414,13 @@
         </is>
       </c>
       <c r="M407" s="4" t="n">
-        <v>-15.8</v>
+        <v>-15.79</v>
       </c>
       <c r="N407" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O407" s="4" t="n">
-        <v>-9.82</v>
+        <v>-9.81</v>
       </c>
       <c r="P407" s="4" t="n">
         <v>-1.37</v>
@@ -44435,7 +44441,7 @@
         <v>1</v>
       </c>
       <c r="V407" s="4" t="n">
-        <v>-9.43</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="W407" s="5" t="n">
         <v>531014</v>
@@ -44503,7 +44509,7 @@
         </is>
       </c>
       <c r="I408" s="4" t="n">
-        <v>-24.26</v>
+        <v>-24.25</v>
       </c>
       <c r="J408" s="4" t="n">
         <v>0.1</v>
@@ -44517,13 +44523,13 @@
         </is>
       </c>
       <c r="M408" s="4" t="n">
-        <v>-28.49</v>
+        <v>-28.48</v>
       </c>
       <c r="N408" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O408" s="4" t="n">
-        <v>-24.26</v>
+        <v>-24.25</v>
       </c>
       <c r="P408" s="4" t="n">
         <v>-2.29</v>
@@ -44620,7 +44626,7 @@
         </is>
       </c>
       <c r="M409" s="4" t="n">
-        <v>-17.44</v>
+        <v>-17.43</v>
       </c>
       <c r="N409" s="4" t="n">
         <v>7.28</v>
@@ -44761,10 +44767,10 @@
         <v>0</v>
       </c>
       <c r="AC410" s="4" t="n">
-        <v>31.21</v>
+        <v>31.22</v>
       </c>
       <c r="AD410" s="4" t="n">
-        <v>68.79000000000001</v>
+        <v>68.78</v>
       </c>
       <c r="AE410" s="4" t="n">
         <v>0</v>
@@ -45024,7 +45030,7 @@
         </is>
       </c>
       <c r="I413" s="4" t="n">
-        <v>41.91</v>
+        <v>41.92</v>
       </c>
       <c r="J413" s="4" t="n">
         <v>100</v>
@@ -45044,7 +45050,7 @@
         <v>7.28</v>
       </c>
       <c r="O413" s="4" t="n">
-        <v>41.91</v>
+        <v>41.92</v>
       </c>
       <c r="P413" s="4" t="n">
         <v>2.26</v>
@@ -45141,7 +45147,7 @@
         </is>
       </c>
       <c r="M414" s="4" t="n">
-        <v>-15.27</v>
+        <v>-15.26</v>
       </c>
       <c r="N414" s="4" t="n">
         <v>7.28</v>
@@ -45343,7 +45349,7 @@
         </is>
       </c>
       <c r="M416" s="4" t="n">
-        <v>-45.45</v>
+        <v>-45.44</v>
       </c>
       <c r="N416" s="4" t="n">
         <v>7.28</v>
@@ -45446,7 +45452,7 @@
         </is>
       </c>
       <c r="M417" s="4" t="n">
-        <v>37.7</v>
+        <v>37.71</v>
       </c>
       <c r="N417" s="4" t="n">
         <v>7.28</v>
@@ -45630,7 +45636,7 @@
         </is>
       </c>
       <c r="I419" s="4" t="n">
-        <v>-10.11</v>
+        <v>-10.1</v>
       </c>
       <c r="J419" s="4" t="n">
         <v>3.9</v>
@@ -45650,7 +45656,7 @@
         <v>7.28</v>
       </c>
       <c r="O419" s="4" t="n">
-        <v>-10.11</v>
+        <v>-10.1</v>
       </c>
       <c r="P419" s="4" t="n">
         <v>-0.96</v>
@@ -45860,7 +45866,7 @@
         </is>
       </c>
       <c r="M421" s="4" t="n">
-        <v>-10.69</v>
+        <v>-10.68</v>
       </c>
       <c r="N421" s="4" t="n">
         <v>7.28</v>
@@ -46052,7 +46058,7 @@
         </is>
       </c>
       <c r="I423" s="4" t="n">
-        <v>-19.42</v>
+        <v>-19.41</v>
       </c>
       <c r="J423" s="4" t="n">
         <v>0.3</v>
@@ -46112,10 +46118,10 @@
         <v>0</v>
       </c>
       <c r="AC423" s="4" t="n">
-        <v>39.49</v>
+        <v>39.5</v>
       </c>
       <c r="AD423" s="4" t="n">
-        <v>58.53</v>
+        <v>58.52</v>
       </c>
       <c r="AE423" s="4" t="n">
         <v>0</v>
@@ -46266,7 +46272,7 @@
         </is>
       </c>
       <c r="I425" s="4" t="n">
-        <v>19.29</v>
+        <v>19.31</v>
       </c>
       <c r="J425" s="4" t="n">
         <v>99.7</v>
@@ -46298,16 +46304,16 @@
         <v>-10.45</v>
       </c>
       <c r="S425" s="4" t="n">
-        <v>43.81</v>
+        <v>48.81</v>
       </c>
       <c r="T425" s="4" t="n">
-        <v>35.25</v>
+        <v>34.64</v>
       </c>
       <c r="U425" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V425" s="4" t="n">
-        <v>10.96</v>
+        <v>13.97</v>
       </c>
       <c r="W425" s="5" t="n">
         <v>2992065</v>
@@ -46326,16 +46332,16 @@
         </is>
       </c>
       <c r="AA425" s="4" t="n">
-        <v>5.25</v>
+        <v>2.68</v>
       </c>
       <c r="AB425" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC425" s="4" t="n">
-        <v>56.51</v>
+        <v>58.06</v>
       </c>
       <c r="AD425" s="4" t="n">
-        <v>38.24</v>
+        <v>39.26</v>
       </c>
       <c r="AE425" s="4" t="n">
         <v>0</v>
@@ -46397,7 +46403,7 @@
         </is>
       </c>
       <c r="M426" s="4" t="n">
-        <v>40.22</v>
+        <v>40.23</v>
       </c>
       <c r="N426" s="4" t="n">
         <v>7.28</v>
@@ -46599,7 +46605,7 @@
         </is>
       </c>
       <c r="M428" s="4" t="n">
-        <v>-16.2</v>
+        <v>-16.19</v>
       </c>
       <c r="N428" s="4" t="n">
         <v>7.28</v>
@@ -46744,10 +46750,10 @@
         <v>0</v>
       </c>
       <c r="AC429" s="4" t="n">
-        <v>47.4</v>
+        <v>47.41</v>
       </c>
       <c r="AD429" s="4" t="n">
-        <v>52.6</v>
+        <v>52.59</v>
       </c>
       <c r="AE429" s="4" t="n">
         <v>0</v>
@@ -46791,7 +46797,7 @@
         </is>
       </c>
       <c r="I430" s="4" t="n">
-        <v>49.2</v>
+        <v>49.21</v>
       </c>
       <c r="J430" s="4" t="n">
         <v>100</v>
@@ -46811,7 +46817,7 @@
         <v>7.28</v>
       </c>
       <c r="O430" s="4" t="n">
-        <v>49.2</v>
+        <v>49.21</v>
       </c>
       <c r="P430" s="4" t="n">
         <v>0</v>
@@ -46894,7 +46900,7 @@
         </is>
       </c>
       <c r="I431" s="4" t="n">
-        <v>12.06</v>
+        <v>12.05</v>
       </c>
       <c r="J431" s="4" t="n">
         <v>98.90000000000001</v>
@@ -46935,7 +46941,7 @@
         <v>3</v>
       </c>
       <c r="V431" s="4" t="n">
-        <v>4.84</v>
+        <v>4.83</v>
       </c>
       <c r="W431" s="5" t="n">
         <v>4956873</v>
@@ -47116,7 +47122,7 @@
         </is>
       </c>
       <c r="I433" s="4" t="n">
-        <v>-14.98</v>
+        <v>-14.97</v>
       </c>
       <c r="J433" s="4" t="n">
         <v>0.7</v>
@@ -47136,7 +47142,7 @@
         <v>7.28</v>
       </c>
       <c r="O433" s="4" t="n">
-        <v>-14.98</v>
+        <v>-14.97</v>
       </c>
       <c r="P433" s="4" t="n">
         <v>-2.1</v>
@@ -47338,7 +47344,7 @@
         <v>7.28</v>
       </c>
       <c r="O435" s="4" t="n">
-        <v>-10.36</v>
+        <v>-10.35</v>
       </c>
       <c r="P435" s="4" t="n">
         <v>-1.95</v>
@@ -47425,7 +47431,7 @@
         </is>
       </c>
       <c r="I436" s="4" t="n">
-        <v>40.26</v>
+        <v>40.24</v>
       </c>
       <c r="J436" s="4" t="n">
         <v>100</v>
@@ -47466,7 +47472,7 @@
         <v>1</v>
       </c>
       <c r="V436" s="4" t="n">
-        <v>42.92</v>
+        <v>42.84</v>
       </c>
       <c r="W436" s="5" t="n">
         <v>2657116</v>
@@ -47491,10 +47497,10 @@
         <v>0</v>
       </c>
       <c r="AC436" s="4" t="n">
-        <v>66.84</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="AD436" s="4" t="n">
-        <v>28.46</v>
+        <v>28.48</v>
       </c>
       <c r="AE436" s="4" t="n">
         <v>0</v>
@@ -47542,7 +47548,7 @@
         </is>
       </c>
       <c r="I437" s="4" t="n">
-        <v>-18.5</v>
+        <v>-18.51</v>
       </c>
       <c r="J437" s="4" t="n">
         <v>0.3</v>
@@ -47583,7 +47589,7 @@
         <v>3</v>
       </c>
       <c r="V437" s="4" t="n">
-        <v>-3.1</v>
+        <v>-3.12</v>
       </c>
       <c r="W437" s="5" t="n">
         <v>138382</v>
@@ -47659,7 +47665,7 @@
         </is>
       </c>
       <c r="I438" s="4" t="n">
-        <v>-33.21</v>
+        <v>-33.23</v>
       </c>
       <c r="J438" s="4" t="n">
         <v>0</v>
@@ -47700,7 +47706,7 @@
         <v>1</v>
       </c>
       <c r="V438" s="4" t="n">
-        <v>-17.08</v>
+        <v>-17.12</v>
       </c>
       <c r="W438" s="5" t="n">
         <v>91625</v>
@@ -47725,10 +47731,10 @@
         <v>0</v>
       </c>
       <c r="AC438" s="4" t="n">
-        <v>29.22</v>
+        <v>29.21</v>
       </c>
       <c r="AD438" s="4" t="n">
-        <v>58.27</v>
+        <v>58.28</v>
       </c>
       <c r="AE438" s="4" t="n">
         <v>6.01</v>
@@ -47776,7 +47782,7 @@
         </is>
       </c>
       <c r="I439" s="4" t="n">
-        <v>-22.85</v>
+        <v>-22.86</v>
       </c>
       <c r="J439" s="4" t="n">
         <v>0.1</v>
@@ -47817,7 +47823,7 @@
         <v>2</v>
       </c>
       <c r="V439" s="4" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="W439" s="5" t="n">
         <v>83970</v>
@@ -47842,10 +47848,10 @@
         <v>0</v>
       </c>
       <c r="AC439" s="4" t="n">
-        <v>33.94</v>
+        <v>33.93</v>
       </c>
       <c r="AD439" s="4" t="n">
-        <v>54.03</v>
+        <v>54.04</v>
       </c>
       <c r="AE439" s="4" t="n">
         <v>7</v>
@@ -47896,10 +47902,10 @@
         <v>0.33</v>
       </c>
       <c r="J440" s="4" t="n">
-        <v>52.4</v>
+        <v>52.3</v>
       </c>
       <c r="K440" s="4" t="n">
-        <v>47.6</v>
+        <v>47.7</v>
       </c>
       <c r="L440" t="inlineStr">
         <is>
@@ -47934,7 +47940,7 @@
         <v>4</v>
       </c>
       <c r="V440" s="4" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="W440" s="5" t="n">
         <v>4192970</v>
@@ -47951,10 +47957,10 @@
         <v>0</v>
       </c>
       <c r="AC440" s="4" t="n">
-        <v>50.17</v>
+        <v>50.16</v>
       </c>
       <c r="AD440" s="4" t="n">
-        <v>49.83</v>
+        <v>49.84</v>
       </c>
       <c r="AE440" s="4" t="n">
         <v>0</v>
@@ -48341,7 +48347,7 @@
         </is>
       </c>
       <c r="I444" s="4" t="n">
-        <v>-3.8</v>
+        <v>-3.81</v>
       </c>
       <c r="J444" s="4" t="n">
         <v>23.6</v>
@@ -48382,7 +48388,7 @@
         <v>3</v>
       </c>
       <c r="V444" s="4" t="n">
-        <v>-5.06</v>
+        <v>-5.07</v>
       </c>
       <c r="W444" s="5" t="n">
         <v>3472774</v>
@@ -49114,7 +49120,7 @@
         </is>
       </c>
       <c r="I451" s="4" t="n">
-        <v>33.11</v>
+        <v>33.1</v>
       </c>
       <c r="J451" s="4" t="n">
         <v>100</v>
@@ -49134,7 +49140,7 @@
         <v>7.28</v>
       </c>
       <c r="O451" s="4" t="n">
-        <v>39.14</v>
+        <v>39.13</v>
       </c>
       <c r="P451" s="4" t="n">
         <v>1.29</v>
@@ -49155,7 +49161,7 @@
         <v>4</v>
       </c>
       <c r="V451" s="4" t="n">
-        <v>25.04</v>
+        <v>25.02</v>
       </c>
       <c r="W451" s="5" t="n">
         <v>1149111</v>
@@ -49180,10 +49186,10 @@
         <v>0</v>
       </c>
       <c r="AC451" s="4" t="n">
-        <v>65.48999999999999</v>
+        <v>65.48</v>
       </c>
       <c r="AD451" s="4" t="n">
-        <v>32.91</v>
+        <v>32.92</v>
       </c>
       <c r="AE451" s="4" t="n">
         <v>0</v>
@@ -50269,7 +50275,7 @@
         </is>
       </c>
       <c r="I462" s="4" t="n">
-        <v>-1.58</v>
+        <v>-1.59</v>
       </c>
       <c r="J462" s="4" t="n">
         <v>38.8</v>
@@ -50310,7 +50316,7 @@
         <v>4</v>
       </c>
       <c r="V462" s="4" t="n">
-        <v>-1.85</v>
+        <v>-1.86</v>
       </c>
       <c r="W462" s="5" t="n">
         <v>1610305</v>
@@ -50495,13 +50501,13 @@
         </is>
       </c>
       <c r="M464" s="4" t="n">
-        <v>-5.39</v>
+        <v>-5.4</v>
       </c>
       <c r="N464" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O464" s="4" t="n">
-        <v>8.6</v>
+        <v>8.59</v>
       </c>
       <c r="P464" s="4" t="n">
         <v>0.35</v>
@@ -50612,7 +50618,7 @@
         </is>
       </c>
       <c r="M465" s="4" t="n">
-        <v>54.15</v>
+        <v>54.14</v>
       </c>
       <c r="N465" s="4" t="n">
         <v>7.28</v>
@@ -50709,7 +50715,7 @@
         </is>
       </c>
       <c r="I466" s="4" t="n">
-        <v>-22.25</v>
+        <v>-22.26</v>
       </c>
       <c r="J466" s="4" t="n">
         <v>0.1</v>
@@ -50729,7 +50735,7 @@
         <v>7.28</v>
       </c>
       <c r="O466" s="4" t="n">
-        <v>-22.25</v>
+        <v>-22.26</v>
       </c>
       <c r="P466" s="4" t="n">
         <v>-2.46</v>
@@ -51028,7 +51034,7 @@
         </is>
       </c>
       <c r="I469" s="4" t="n">
-        <v>-11.85</v>
+        <v>-11.86</v>
       </c>
       <c r="J469" s="4" t="n">
         <v>1.2</v>
@@ -51042,13 +51048,13 @@
         </is>
       </c>
       <c r="M469" s="4" t="n">
-        <v>-15.03</v>
+        <v>-15.04</v>
       </c>
       <c r="N469" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O469" s="4" t="n">
-        <v>-11.85</v>
+        <v>-11.86</v>
       </c>
       <c r="P469" s="4" t="n">
         <v>-1.46</v>
@@ -51452,13 +51458,13 @@
         </is>
       </c>
       <c r="I473" s="4" t="n">
-        <v>2.84</v>
+        <v>2.61</v>
       </c>
       <c r="J473" s="4" t="n">
-        <v>70.2</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="K473" s="4" t="n">
-        <v>29.8</v>
+        <v>31.1</v>
       </c>
       <c r="L473" t="inlineStr">
         <is>
@@ -51466,13 +51472,13 @@
         </is>
       </c>
       <c r="M473" s="4" t="n">
-        <v>-11.23</v>
+        <v>-11.02</v>
       </c>
       <c r="N473" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O473" s="4" t="n">
-        <v>-0.48</v>
+        <v>-0.28</v>
       </c>
       <c r="P473" s="4" t="n">
         <v>0.41</v>
@@ -51484,16 +51490,16 @@
         <v>-13.8</v>
       </c>
       <c r="S473" s="4" t="n">
-        <v>48.63</v>
+        <v>48.48</v>
       </c>
       <c r="T473" s="4" t="n">
-        <v>45.61</v>
+        <v>45.55</v>
       </c>
       <c r="U473" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="V473" s="4" t="n">
-        <v>4.13</v>
+        <v>3.66</v>
       </c>
       <c r="W473" s="5" t="n">
         <v>32623722</v>
@@ -51510,10 +51516,10 @@
         <v>0</v>
       </c>
       <c r="AC473" s="4" t="n">
-        <v>49.74</v>
+        <v>49.69</v>
       </c>
       <c r="AD473" s="4" t="n">
-        <v>47.76</v>
+        <v>47.81</v>
       </c>
       <c r="AE473" s="4" t="n">
         <v>2.5</v>
@@ -51557,7 +51563,7 @@
         </is>
       </c>
       <c r="I474" s="4" t="n">
-        <v>-20.47</v>
+        <v>-20.34</v>
       </c>
       <c r="J474" s="4" t="n">
         <v>0.2</v>
@@ -51571,13 +51577,13 @@
         </is>
       </c>
       <c r="M474" s="4" t="n">
-        <v>-25.86</v>
+        <v>-25.6</v>
       </c>
       <c r="N474" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O474" s="4" t="n">
-        <v>-21.26</v>
+        <v>-21</v>
       </c>
       <c r="P474" s="4" t="n">
         <v>-3.12</v>
@@ -51615,10 +51621,10 @@
         <v>0</v>
       </c>
       <c r="AC474" s="4" t="n">
-        <v>39.76</v>
+        <v>39.83</v>
       </c>
       <c r="AD474" s="4" t="n">
-        <v>60.24</v>
+        <v>60.17</v>
       </c>
       <c r="AE474" s="4" t="n">
         <v>0</v>
@@ -52114,7 +52120,7 @@
         </is>
       </c>
       <c r="I479" s="4" t="n">
-        <v>12.24</v>
+        <v>12.29</v>
       </c>
       <c r="J479" s="4" t="n">
         <v>98.90000000000001</v>
@@ -52128,13 +52134,13 @@
         </is>
       </c>
       <c r="M479" s="4" t="n">
-        <v>-1.04</v>
+        <v>-1.02</v>
       </c>
       <c r="N479" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O479" s="4" t="n">
-        <v>14.31</v>
+        <v>14.33</v>
       </c>
       <c r="P479" s="4" t="n">
         <v>1.46</v>
@@ -52146,16 +52152,16 @@
         <v>-2.21</v>
       </c>
       <c r="S479" s="4" t="n">
-        <v>51.59</v>
+        <v>51.4</v>
       </c>
       <c r="T479" s="4" t="n">
-        <v>42.31</v>
+        <v>42.16</v>
       </c>
       <c r="U479" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V479" s="4" t="n">
-        <v>10.51</v>
+        <v>10.48</v>
       </c>
       <c r="W479" s="5" t="n">
         <v>110426538</v>
@@ -52172,10 +52178,10 @@
         <v>0</v>
       </c>
       <c r="AC479" s="4" t="n">
-        <v>56.12</v>
+        <v>56.14</v>
       </c>
       <c r="AD479" s="4" t="n">
-        <v>43.88</v>
+        <v>43.86</v>
       </c>
       <c r="AE479" s="4" t="n">
         <v>0</v>
@@ -52219,13 +52225,13 @@
         </is>
       </c>
       <c r="I480" s="4" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="J480" s="4" t="n">
-        <v>61.3</v>
+        <v>61.6</v>
       </c>
       <c r="K480" s="4" t="n">
-        <v>38.7</v>
+        <v>38.4</v>
       </c>
       <c r="L480" t="inlineStr">
         <is>
@@ -52233,13 +52239,13 @@
         </is>
       </c>
       <c r="M480" s="4" t="n">
-        <v>-6.61</v>
+        <v>-6.6</v>
       </c>
       <c r="N480" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O480" s="4" t="n">
-        <v>-0.85</v>
+        <v>-0.84</v>
       </c>
       <c r="P480" s="4" t="n">
         <v>0.13</v>
@@ -52251,7 +52257,7 @@
         <v>-13.45</v>
       </c>
       <c r="S480" s="4" t="n">
-        <v>47.19</v>
+        <v>47.16</v>
       </c>
       <c r="T480" s="4" t="n">
         <v>45.21</v>
@@ -52260,7 +52266,7 @@
         <v>30</v>
       </c>
       <c r="V480" s="4" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="W480" s="5" t="n">
         <v>20152882</v>
@@ -52285,10 +52291,10 @@
         <v>0</v>
       </c>
       <c r="AC480" s="4" t="n">
-        <v>50.55</v>
+        <v>50.57</v>
       </c>
       <c r="AD480" s="4" t="n">
-        <v>48.95</v>
+        <v>48.93</v>
       </c>
       <c r="AE480" s="4" t="n">
         <v>0</v>
@@ -52336,7 +52342,7 @@
         </is>
       </c>
       <c r="I481" s="4" t="n">
-        <v>-12.08</v>
+        <v>-12.09</v>
       </c>
       <c r="J481" s="4" t="n">
         <v>1</v>
@@ -52350,7 +52356,7 @@
         </is>
       </c>
       <c r="M481" s="4" t="n">
-        <v>-29.04</v>
+        <v>-29.05</v>
       </c>
       <c r="N481" s="4" t="n">
         <v>7.28</v>
@@ -52377,7 +52383,7 @@
         <v>7</v>
       </c>
       <c r="V481" s="4" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="W481" s="5" t="n">
         <v>0</v>
@@ -52396,7 +52402,7 @@
         </is>
       </c>
       <c r="AA481" s="4" t="n">
-        <v>41.77</v>
+        <v>41.76</v>
       </c>
       <c r="AB481" s="4" t="n">
         <v>1</v>
@@ -52405,7 +52411,7 @@
         <v>0</v>
       </c>
       <c r="AD481" s="4" t="n">
-        <v>53.84</v>
+        <v>53.85</v>
       </c>
       <c r="AE481" s="4" t="n">
         <v>4.39</v>
@@ -52449,7 +52455,7 @@
         </is>
       </c>
       <c r="I482" s="4" t="n">
-        <v>17.36</v>
+        <v>17.35</v>
       </c>
       <c r="J482" s="4" t="n">
         <v>99.59999999999999</v>
@@ -52490,7 +52496,7 @@
         <v>1</v>
       </c>
       <c r="V482" s="4" t="n">
-        <v>10.42</v>
+        <v>10.41</v>
       </c>
       <c r="W482" s="5" t="n">
         <v>7089488</v>
@@ -52566,13 +52572,13 @@
         </is>
       </c>
       <c r="I483" s="4" t="n">
-        <v>-1.25</v>
+        <v>-1.37</v>
       </c>
       <c r="J483" s="4" t="n">
-        <v>41.1</v>
+        <v>40.3</v>
       </c>
       <c r="K483" s="4" t="n">
-        <v>58.9</v>
+        <v>59.7</v>
       </c>
       <c r="L483" t="inlineStr">
         <is>
@@ -52580,13 +52586,13 @@
         </is>
       </c>
       <c r="M483" s="4" t="n">
-        <v>-13.87</v>
+        <v>-13.9</v>
       </c>
       <c r="N483" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O483" s="4" t="n">
-        <v>-7.54</v>
+        <v>-7.57</v>
       </c>
       <c r="P483" s="4" t="n">
         <v>0.57</v>
@@ -52598,16 +52604,16 @@
         <v>-16.41</v>
       </c>
       <c r="S483" s="4" t="n">
-        <v>46.49</v>
+        <v>46.38</v>
       </c>
       <c r="T483" s="4" t="n">
-        <v>45.14</v>
+        <v>45.05</v>
       </c>
       <c r="U483" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V483" s="4" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="W483" s="5" t="n">
         <v>13533711</v>
@@ -52632,10 +52638,10 @@
         <v>0</v>
       </c>
       <c r="AC483" s="4" t="n">
-        <v>48.4</v>
+        <v>48.34</v>
       </c>
       <c r="AD483" s="4" t="n">
-        <v>49.62</v>
+        <v>49.68</v>
       </c>
       <c r="AE483" s="4" t="n">
         <v>0</v>
@@ -52792,7 +52798,7 @@
         </is>
       </c>
       <c r="I485" s="4" t="n">
-        <v>-16.69</v>
+        <v>-16.7</v>
       </c>
       <c r="J485" s="4" t="n">
         <v>0.5</v>
@@ -52833,7 +52839,7 @@
         <v>2</v>
       </c>
       <c r="V485" s="4" t="n">
-        <v>-5.79</v>
+        <v>-5.82</v>
       </c>
       <c r="W485" s="5" t="n">
         <v>4015530</v>
@@ -53018,13 +53024,13 @@
         </is>
       </c>
       <c r="I487" s="4" t="n">
-        <v>2.49</v>
+        <v>2.44</v>
       </c>
       <c r="J487" s="4" t="n">
-        <v>67.7</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="K487" s="4" t="n">
-        <v>32.3</v>
+        <v>33.1</v>
       </c>
       <c r="L487" t="inlineStr">
         <is>
@@ -53050,16 +53056,16 @@
         <v>7.09</v>
       </c>
       <c r="S487" s="4" t="n">
-        <v>48.73</v>
+        <v>48.66</v>
       </c>
       <c r="T487" s="4" t="n">
-        <v>46.63</v>
+        <v>46.61</v>
       </c>
       <c r="U487" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="V487" s="4" t="n">
-        <v>3.06</v>
+        <v>2.99</v>
       </c>
       <c r="W487" s="5" t="n">
         <v>20431280</v>
@@ -53076,10 +53082,10 @@
         <v>0</v>
       </c>
       <c r="AC487" s="4" t="n">
-        <v>51.24</v>
+        <v>51.22</v>
       </c>
       <c r="AD487" s="4" t="n">
-        <v>48.76</v>
+        <v>48.78</v>
       </c>
       <c r="AE487" s="4" t="n">
         <v>0</v>
@@ -53123,13 +53129,13 @@
         </is>
       </c>
       <c r="I488" s="4" t="n">
-        <v>6.47</v>
+        <v>6.44</v>
       </c>
       <c r="J488" s="4" t="n">
-        <v>85.8</v>
+        <v>85.7</v>
       </c>
       <c r="K488" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="L488" t="inlineStr">
         <is>
@@ -53155,16 +53161,16 @@
         <v>-1.44</v>
       </c>
       <c r="S488" s="4" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
       <c r="T488" s="4" t="n">
-        <v>45.73</v>
+        <v>45.71</v>
       </c>
       <c r="U488" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="V488" s="4" t="n">
-        <v>3.87</v>
+        <v>3.79</v>
       </c>
       <c r="W488" s="5" t="n">
         <v>45175567</v>
@@ -53189,10 +53195,10 @@
         <v>0</v>
       </c>
       <c r="AC488" s="4" t="n">
-        <v>51.74</v>
+        <v>51.72</v>
       </c>
       <c r="AD488" s="4" t="n">
-        <v>45.45</v>
+        <v>45.47</v>
       </c>
       <c r="AE488" s="4" t="n">
         <v>2.31</v>
@@ -53236,7 +53242,7 @@
         </is>
       </c>
       <c r="I489" s="4" t="n">
-        <v>7.62</v>
+        <v>7.61</v>
       </c>
       <c r="J489" s="4" t="n">
         <v>89.40000000000001</v>
@@ -53277,7 +53283,7 @@
         <v>14</v>
       </c>
       <c r="V489" s="4" t="n">
-        <v>4.03</v>
+        <v>4.02</v>
       </c>
       <c r="W489" s="5" t="n">
         <v>10301879</v>
@@ -53353,17 +53359,17 @@
         </is>
       </c>
       <c r="I490" s="4" t="n">
-        <v>-9.220000000000001</v>
+        <v>-10.74</v>
       </c>
       <c r="J490" s="4" t="n">
-        <v>6.1</v>
+        <v>2.4</v>
       </c>
       <c r="K490" s="4" t="n">
-        <v>93.90000000000001</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="L490" t="inlineStr">
         <is>
-          <t>Likely R</t>
+          <t>Safe R</t>
         </is>
       </c>
       <c r="M490" s="4" t="n">
@@ -53385,16 +53391,16 @@
         <v>-23.15</v>
       </c>
       <c r="S490" s="4" t="n">
-        <v>45.03</v>
+        <v>39.49</v>
       </c>
       <c r="T490" s="4" t="n">
-        <v>49.71</v>
+        <v>45.44</v>
       </c>
       <c r="U490" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V490" s="4" t="n">
-        <v>-4.94</v>
+        <v>-6.9</v>
       </c>
       <c r="W490" s="5" t="n">
         <v>3926491</v>
@@ -53413,16 +53419,16 @@
         </is>
       </c>
       <c r="AA490" s="4" t="n">
-        <v>1.24</v>
+        <v>3.54</v>
       </c>
       <c r="AB490" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC490" s="4" t="n">
-        <v>44.83</v>
+        <v>43.05</v>
       </c>
       <c r="AD490" s="4" t="n">
-        <v>53.93</v>
+        <v>53.41</v>
       </c>
       <c r="AE490" s="4" t="n">
         <v>0</v>
@@ -53466,7 +53472,7 @@
         </is>
       </c>
       <c r="I491" s="4" t="n">
-        <v>-20.87</v>
+        <v>-20.54</v>
       </c>
       <c r="J491" s="4" t="n">
         <v>0</v>
@@ -53498,16 +53504,16 @@
         <v>-20.58</v>
       </c>
       <c r="S491" s="4" t="n">
-        <v>21.12</v>
+        <v>21.13</v>
       </c>
       <c r="T491" s="4" t="n">
-        <v>43.36</v>
+        <v>43.53</v>
       </c>
       <c r="U491" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V491" s="4" t="n">
-        <v>-20.35</v>
+        <v>-20.45</v>
       </c>
       <c r="W491" s="5" t="n">
         <v>190540</v>
@@ -53526,16 +53532,16 @@
         </is>
       </c>
       <c r="AA491" s="4" t="n">
-        <v>28.45</v>
+        <v>28.51</v>
       </c>
       <c r="AB491" s="4" t="n">
         <v>0.2</v>
       </c>
       <c r="AC491" s="4" t="n">
-        <v>18.58</v>
+        <v>18.78</v>
       </c>
       <c r="AD491" s="4" t="n">
-        <v>49.31</v>
+        <v>49.05</v>
       </c>
       <c r="AE491" s="4" t="n">
         <v>3.66</v>
@@ -53579,7 +53585,7 @@
         </is>
       </c>
       <c r="I492" s="4" t="n">
-        <v>10.04</v>
+        <v>10.02</v>
       </c>
       <c r="J492" s="4" t="n">
         <v>95.90000000000001</v>
@@ -53620,7 +53626,7 @@
         <v>43</v>
       </c>
       <c r="V492" s="4" t="n">
-        <v>12.2</v>
+        <v>12.18</v>
       </c>
       <c r="W492" s="5" t="n">
         <v>47190466</v>
@@ -53645,10 +53651,10 @@
         <v>0</v>
       </c>
       <c r="AC492" s="4" t="n">
-        <v>53.54</v>
+        <v>53.53</v>
       </c>
       <c r="AD492" s="4" t="n">
-        <v>43.77</v>
+        <v>43.78</v>
       </c>
       <c r="AE492" s="4" t="n">
         <v>1.87</v>
@@ -53696,13 +53702,13 @@
         </is>
       </c>
       <c r="I493" s="4" t="n">
-        <v>-0.28</v>
+        <v>-0.01</v>
       </c>
       <c r="J493" s="4" t="n">
-        <v>48</v>
+        <v>49.9</v>
       </c>
       <c r="K493" s="4" t="n">
-        <v>52</v>
+        <v>50.1</v>
       </c>
       <c r="L493" t="inlineStr">
         <is>
@@ -53710,13 +53716,13 @@
         </is>
       </c>
       <c r="M493" s="4" t="n">
-        <v>-17.83</v>
+        <v>-17.65</v>
       </c>
       <c r="N493" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O493" s="4" t="n">
-        <v>-2.36</v>
+        <v>-2.19</v>
       </c>
       <c r="P493" s="4" t="n">
         <v>0.03</v>
@@ -53728,16 +53734,16 @@
         <v>-20.84</v>
       </c>
       <c r="S493" s="4" t="n">
-        <v>47.15</v>
+        <v>46.86</v>
       </c>
       <c r="T493" s="4" t="n">
-        <v>46.14</v>
+        <v>45.88</v>
       </c>
       <c r="U493" t="n">
         <v>11</v>
       </c>
       <c r="V493" s="4" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="W493" s="5" t="n">
         <v>0</v>
@@ -53756,16 +53762,16 @@
         </is>
       </c>
       <c r="AA493" s="4" t="n">
-        <v>48.77</v>
+        <v>48.9</v>
       </c>
       <c r="AB493" s="4" t="n">
-        <v>48</v>
+        <v>49.9</v>
       </c>
       <c r="AC493" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AD493" s="4" t="n">
-        <v>49.05</v>
+        <v>48.92</v>
       </c>
       <c r="AE493" s="4" t="n">
         <v>2.18</v>
@@ -53809,13 +53815,13 @@
         </is>
       </c>
       <c r="I494" s="4" t="n">
-        <v>9.25</v>
+        <v>9.19</v>
       </c>
       <c r="J494" s="4" t="n">
-        <v>93.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="K494" s="4" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="L494" t="inlineStr">
         <is>
@@ -53823,13 +53829,13 @@
         </is>
       </c>
       <c r="M494" s="4" t="n">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="N494" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O494" s="4" t="n">
-        <v>11.43</v>
+        <v>11.42</v>
       </c>
       <c r="P494" s="4" t="n">
         <v>0.32</v>
@@ -53841,16 +53847,16 @@
         <v>2.82</v>
       </c>
       <c r="S494" s="4" t="n">
-        <v>49.57</v>
+        <v>49.59</v>
       </c>
       <c r="T494" s="4" t="n">
-        <v>43.4</v>
+        <v>43.43</v>
       </c>
       <c r="U494" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="V494" s="4" t="n">
-        <v>7.02</v>
+        <v>7.13</v>
       </c>
       <c r="W494" s="5" t="n">
         <v>21500073</v>
@@ -53875,10 +53881,10 @@
         <v>0</v>
       </c>
       <c r="AC494" s="4" t="n">
-        <v>54.35</v>
+        <v>54.32</v>
       </c>
       <c r="AD494" s="4" t="n">
-        <v>45.15</v>
+        <v>45.18</v>
       </c>
       <c r="AE494" s="4" t="n">
         <v>0</v>
@@ -54149,10 +54155,10 @@
         <v>4.22</v>
       </c>
       <c r="J497" s="4" t="n">
-        <v>78.09999999999999</v>
+        <v>78</v>
       </c>
       <c r="K497" s="4" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="L497" t="inlineStr">
         <is>
@@ -54178,16 +54184,16 @@
         <v>-11.31</v>
       </c>
       <c r="S497" s="4" t="n">
-        <v>49.15</v>
+        <v>49.16</v>
       </c>
       <c r="T497" s="4" t="n">
         <v>43.93</v>
       </c>
       <c r="U497" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V497" s="4" t="n">
-        <v>5.77</v>
+        <v>5.76</v>
       </c>
       <c r="W497" s="5" t="n">
         <v>61686820</v>
@@ -54259,7 +54265,7 @@
         </is>
       </c>
       <c r="I498" s="4" t="n">
-        <v>-27.7</v>
+        <v>-27.52</v>
       </c>
       <c r="J498" s="4" t="n">
         <v>0</v>
@@ -54273,13 +54279,13 @@
         </is>
       </c>
       <c r="M498" s="4" t="n">
-        <v>-30.01</v>
+        <v>-29.79</v>
       </c>
       <c r="N498" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O498" s="4" t="n">
-        <v>-29.44</v>
+        <v>-29.22</v>
       </c>
       <c r="P498" s="4" t="n">
         <v>-3.23</v>
@@ -54325,10 +54331,10 @@
         <v>0</v>
       </c>
       <c r="AC498" s="4" t="n">
-        <v>33.76</v>
+        <v>33.84</v>
       </c>
       <c r="AD498" s="4" t="n">
-        <v>59.62</v>
+        <v>59.54</v>
       </c>
       <c r="AE498" s="4" t="n">
         <v>2.62</v>
@@ -54528,7 +54534,7 @@
         <v>6</v>
       </c>
       <c r="V500" s="4" t="n">
-        <v>30.01</v>
+        <v>30</v>
       </c>
       <c r="W500" s="5" t="n">
         <v>3649514</v>
@@ -54553,10 +54559,10 @@
         <v>0</v>
       </c>
       <c r="AC500" s="4" t="n">
-        <v>60.18</v>
+        <v>60.17</v>
       </c>
       <c r="AD500" s="4" t="n">
-        <v>33.86</v>
+        <v>33.87</v>
       </c>
       <c r="AE500" s="4" t="n">
         <v>0</v>
@@ -54604,13 +54610,13 @@
         </is>
       </c>
       <c r="I501" s="4" t="n">
-        <v>-2.25</v>
+        <v>-2.35</v>
       </c>
       <c r="J501" s="4" t="n">
-        <v>34.2</v>
+        <v>33.5</v>
       </c>
       <c r="K501" s="4" t="n">
-        <v>65.8</v>
+        <v>66.5</v>
       </c>
       <c r="L501" t="inlineStr">
         <is>
@@ -54618,13 +54624,13 @@
         </is>
       </c>
       <c r="M501" s="4" t="n">
-        <v>-14.24</v>
+        <v>-14.45</v>
       </c>
       <c r="N501" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O501" s="4" t="n">
-        <v>-5</v>
+        <v>-5.21</v>
       </c>
       <c r="P501" s="4" t="n">
         <v>0.77</v>
@@ -54645,7 +54651,7 @@
         <v>6</v>
       </c>
       <c r="V501" s="4" t="n">
-        <v>-0.45</v>
+        <v>-0.46</v>
       </c>
       <c r="W501" s="5" t="n">
         <v>20173697</v>
@@ -54670,10 +54676,10 @@
         <v>0</v>
       </c>
       <c r="AC501" s="4" t="n">
-        <v>47.03</v>
+        <v>46.98</v>
       </c>
       <c r="AD501" s="4" t="n">
-        <v>49.19</v>
+        <v>49.24</v>
       </c>
       <c r="AE501" s="4" t="n">
         <v>1.87</v>
@@ -54721,13 +54727,13 @@
         </is>
       </c>
       <c r="I502" s="4" t="n">
-        <v>-12.58</v>
+        <v>-13.97</v>
       </c>
       <c r="J502" s="4" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K502" s="4" t="n">
-        <v>99</v>
+        <v>99.2</v>
       </c>
       <c r="L502" t="inlineStr">
         <is>
@@ -54753,16 +54759,16 @@
         <v>-29.98</v>
       </c>
       <c r="S502" s="4" t="n">
-        <v>44.44</v>
+        <v>41.31</v>
       </c>
       <c r="T502" s="4" t="n">
-        <v>46.59</v>
+        <v>49.71</v>
       </c>
       <c r="U502" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V502" s="4" t="n">
-        <v>-3.21</v>
+        <v>-7.72</v>
       </c>
       <c r="W502" s="5" t="n">
         <v>0</v>
@@ -54781,16 +54787,16 @@
         </is>
       </c>
       <c r="AA502" s="4" t="n">
-        <v>43.71</v>
+        <v>43.01</v>
       </c>
       <c r="AB502" s="4" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AC502" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AD502" s="4" t="n">
-        <v>56.29</v>
+        <v>56.99</v>
       </c>
       <c r="AE502" s="4" t="n">
         <v>0</v>
@@ -54838,7 +54844,7 @@
         </is>
       </c>
       <c r="I503" s="4" t="n">
-        <v>-26.13</v>
+        <v>-25.81</v>
       </c>
       <c r="J503" s="4" t="n">
         <v>0</v>
@@ -54852,13 +54858,13 @@
         </is>
       </c>
       <c r="M503" s="4" t="n">
-        <v>-24.61</v>
+        <v>-24.19</v>
       </c>
       <c r="N503" s="4" t="n">
         <v>7.28</v>
       </c>
       <c r="O503" s="4" t="n">
-        <v>-27.64</v>
+        <v>-27.22</v>
       </c>
       <c r="P503" s="4" t="n">
         <v>-3.52</v>
@@ -54904,10 +54910,10 @@
         <v>0</v>
       </c>
       <c r="AC503" s="4" t="n">
-        <v>34.87</v>
+        <v>35.02</v>
       </c>
       <c r="AD503" s="4" t="n">
-        <v>59.55</v>
+        <v>59.4</v>
       </c>
       <c r="AE503" s="4" t="n">
         <v>0</v>
@@ -54951,7 +54957,7 @@
         </is>
       </c>
       <c r="I504" s="4" t="n">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
       <c r="J504" s="4" t="n">
         <v>73.2</v>
@@ -54989,10 +54995,10 @@
         <v>45.47</v>
       </c>
       <c r="U504" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="V504" s="4" t="n">
-        <v>4.26</v>
+        <v>4.25</v>
       </c>
       <c r="W504" s="5" t="n">
         <v>128772835</v>
@@ -55495,7 +55501,7 @@
         </is>
       </c>
       <c r="J2" s="4" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="K2" t="n">
         <v>17</v>
@@ -55507,7 +55513,7 @@
         <v>21</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -55570,7 +55576,7 @@
         <v>10</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -55621,7 +55627,7 @@
         </is>
       </c>
       <c r="J4" s="4" t="n">
-        <v>30.9</v>
+        <v>31</v>
       </c>
       <c r="K4" t="n">
         <v>30</v>
@@ -55633,7 +55639,7 @@
         <v>41</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -56555,13 +56561,13 @@
         <v>88</v>
       </c>
       <c r="L20" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M20" t="n">
         <v>110</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>38.7</v>
+        <v>38.8</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -56619,7 +56625,7 @@
         <v>34</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -58521,7 +58527,7 @@
         </is>
       </c>
       <c r="J54" s="4" t="n">
-        <v>227.4</v>
+        <v>227.3</v>
       </c>
       <c r="K54" t="n">
         <v>222</v>
@@ -59043,7 +59049,7 @@
         </is>
       </c>
       <c r="J63" s="4" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="K63" t="n">
         <v>22</v>
@@ -59507,7 +59513,7 @@
         </is>
       </c>
       <c r="J71" s="4" t="n">
-        <v>45</v>
+        <v>44.8</v>
       </c>
       <c r="K71" t="n">
         <v>42</v>
@@ -59519,7 +59525,7 @@
         <v>67</v>
       </c>
       <c r="N71" s="4" t="n">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>

--- a/output/nowcast.xlsx
+++ b/output/nowcast.xlsx
@@ -575,7 +575,7 @@
         <v>244</v>
       </c>
       <c r="E9" t="n">
-        <v>92.3</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="F9" t="n">
         <v>218</v>
@@ -591,16 +591,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>27.2</v>
+        <v>27.3</v>
       </c>
       <c r="C10" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="D10" t="n">
         <v>28</v>
       </c>
       <c r="E10" t="n">
-        <v>72.7</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="F10" t="n">
         <v>26</v>
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>20.52</v>
+        <v>20.45</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>99.8</v>
@@ -1494,10 +1494,10 @@
         <v>7.57</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>19.67</v>
+        <v>19.6</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Q7" s="4" t="n">
         <v>0</v>
@@ -1518,10 +1518,10 @@
         <v>17.5</v>
       </c>
       <c r="W7" s="5" t="n">
-        <v>6951032</v>
+        <v>8740361</v>
       </c>
       <c r="X7" s="5" t="n">
-        <v>2935521</v>
+        <v>4115917</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1540,10 +1540,10 @@
         <v>0</v>
       </c>
       <c r="AC7" s="4" t="n">
-        <v>58.09</v>
+        <v>58.06</v>
       </c>
       <c r="AD7" s="4" t="n">
-        <v>38.31</v>
+        <v>38.34</v>
       </c>
       <c r="AE7" s="4" t="n">
         <v>0</v>
@@ -2243,7 +2243,7 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>20.52</v>
+        <v>21.09</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>99.8</v>
@@ -2263,10 +2263,10 @@
         <v>7.57</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>22.3</v>
+        <v>23.15</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>1.84</v>
+        <v>2.69</v>
       </c>
       <c r="Q14" s="4" t="n">
         <v>-0.02</v>
@@ -2287,10 +2287,10 @@
         <v>17.74</v>
       </c>
       <c r="W14" s="5" t="n">
-        <v>25619035</v>
+        <v>91778931</v>
       </c>
       <c r="X14" s="5" t="n">
-        <v>2166962</v>
+        <v>2501525</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -2309,10 +2309,10 @@
         <v>0</v>
       </c>
       <c r="AC14" s="4" t="n">
-        <v>56.65</v>
+        <v>56.92</v>
       </c>
       <c r="AD14" s="4" t="n">
-        <v>37.36</v>
+        <v>37.09</v>
       </c>
       <c r="AE14" s="4" t="n">
         <v>0</v>
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>14.67</v>
+        <v>14.63</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>99.2</v>
+        <v>99.3</v>
       </c>
       <c r="K30" s="4" t="n">
         <v>0</v>
@@ -4119,16 +4119,16 @@
         </is>
       </c>
       <c r="AA30" s="4" t="n">
-        <v>34.99</v>
+        <v>34.96</v>
       </c>
       <c r="AB30" s="4" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="AC30" s="4" t="n">
-        <v>49.66</v>
+        <v>49.6</v>
       </c>
       <c r="AD30" s="4" t="n">
-        <v>15.36</v>
+        <v>15.44</v>
       </c>
       <c r="AE30" s="4" t="n">
         <v>0</v>
@@ -4960,10 +4960,10 @@
         <v>-2.51</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>32.5</v>
+        <v>30.9</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>67.5</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -5020,7 +5020,7 @@
         <v>45.46</v>
       </c>
       <c r="AB38" s="4" t="n">
-        <v>32.5</v>
+        <v>30.9</v>
       </c>
       <c r="AC38" s="4" t="n">
         <v>3.8</v>
@@ -12552,7 +12552,7 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>73.7</v>
+        <v>73.69</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>100</v>
@@ -12566,13 +12566,13 @@
         </is>
       </c>
       <c r="M111" s="4" t="n">
-        <v>64.01000000000001</v>
+        <v>64</v>
       </c>
       <c r="N111" s="4" t="n">
         <v>7.57</v>
       </c>
       <c r="O111" s="4" t="n">
-        <v>73.2</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="P111" s="4" t="n">
         <v>1.28</v>
@@ -12612,10 +12612,10 @@
         <v>0</v>
       </c>
       <c r="AC111" s="4" t="n">
-        <v>81.02</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="AD111" s="4" t="n">
-        <v>12.26</v>
+        <v>12.27</v>
       </c>
       <c r="AE111" s="4" t="n">
         <v>3.36</v>
@@ -12663,7 +12663,7 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>56.34</v>
+        <v>56.32</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>100</v>
@@ -12677,13 +12677,13 @@
         </is>
       </c>
       <c r="M112" s="4" t="n">
-        <v>45.75</v>
+        <v>45.73</v>
       </c>
       <c r="N112" s="4" t="n">
         <v>7.57</v>
       </c>
       <c r="O112" s="4" t="n">
-        <v>55.61</v>
+        <v>55.59</v>
       </c>
       <c r="P112" s="4" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AC112" s="4" t="n">
-        <v>75.31999999999999</v>
+        <v>75.31</v>
       </c>
       <c r="AD112" s="4" t="n">
-        <v>21.03</v>
+        <v>21.04</v>
       </c>
       <c r="AE112" s="4" t="n">
         <v>0</v>
@@ -12774,13 +12774,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="J113" s="4" t="n">
-        <v>66.09999999999999</v>
+        <v>66</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>33.9</v>
+        <v>34</v>
       </c>
       <c r="L113" t="inlineStr">
         <is>
@@ -12788,13 +12788,13 @@
         </is>
       </c>
       <c r="M113" s="4" t="n">
-        <v>-4.71</v>
+        <v>-4.73</v>
       </c>
       <c r="N113" s="4" t="n">
         <v>7.57</v>
       </c>
       <c r="O113" s="4" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="P113" s="4" t="n">
         <v>-0.83</v>
@@ -12840,10 +12840,10 @@
         <v>0</v>
       </c>
       <c r="AC113" s="4" t="n">
-        <v>49.47</v>
+        <v>49.46</v>
       </c>
       <c r="AD113" s="4" t="n">
-        <v>47.25</v>
+        <v>47.26</v>
       </c>
       <c r="AE113" s="4" t="n">
         <v>0</v>
@@ -12891,13 +12891,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>-2.03</v>
+        <v>-2.04</v>
       </c>
       <c r="J114" s="4" t="n">
-        <v>35.7</v>
+        <v>35.6</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>64.3</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="L114" t="inlineStr">
         <is>
@@ -12905,13 +12905,13 @@
         </is>
       </c>
       <c r="M114" s="4" t="n">
-        <v>-14.21</v>
+        <v>-14.23</v>
       </c>
       <c r="N114" s="4" t="n">
         <v>7.57</v>
       </c>
       <c r="O114" s="4" t="n">
-        <v>-1.92</v>
+        <v>-1.93</v>
       </c>
       <c r="P114" s="4" t="n">
         <v>1.67</v>
@@ -12957,10 +12957,10 @@
         <v>0</v>
       </c>
       <c r="AC114" s="4" t="n">
-        <v>44.58</v>
+        <v>44.57</v>
       </c>
       <c r="AD114" s="4" t="n">
-        <v>46.42</v>
+        <v>46.43</v>
       </c>
       <c r="AE114" s="4" t="n">
         <v>0</v>
@@ -13008,13 +13008,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>-3.44</v>
+        <v>-3.45</v>
       </c>
       <c r="J115" s="4" t="n">
-        <v>26</v>
+        <v>25.9</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>74</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L115" t="inlineStr">
         <is>
@@ -13022,13 +13022,13 @@
         </is>
       </c>
       <c r="M115" s="4" t="n">
-        <v>-5.26</v>
+        <v>-5.27</v>
       </c>
       <c r="N115" s="4" t="n">
         <v>7.57</v>
       </c>
       <c r="O115" s="4" t="n">
-        <v>-3.78</v>
+        <v>-3.8</v>
       </c>
       <c r="P115" s="4" t="n">
         <v>0.25</v>
@@ -13074,10 +13074,10 @@
         <v>0</v>
       </c>
       <c r="AC115" s="4" t="n">
-        <v>46.07</v>
+        <v>46.06</v>
       </c>
       <c r="AD115" s="4" t="n">
-        <v>49.35</v>
+        <v>49.36</v>
       </c>
       <c r="AE115" s="4" t="n">
         <v>4.08</v>
@@ -13125,7 +13125,7 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>37.01</v>
+        <v>36.99</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>100</v>
@@ -13139,13 +13139,13 @@
         </is>
       </c>
       <c r="M116" s="4" t="n">
-        <v>26.03</v>
+        <v>26.01</v>
       </c>
       <c r="N116" s="4" t="n">
         <v>7.57</v>
       </c>
       <c r="O116" s="4" t="n">
-        <v>36.46</v>
+        <v>36.44</v>
       </c>
       <c r="P116" s="4" t="n">
         <v>0</v>
@@ -13185,10 +13185,10 @@
         <v>0</v>
       </c>
       <c r="AC116" s="4" t="n">
-        <v>63.44</v>
+        <v>63.43</v>
       </c>
       <c r="AD116" s="4" t="n">
-        <v>29.16</v>
+        <v>29.17</v>
       </c>
       <c r="AE116" s="4" t="n">
         <v>3.7</v>
@@ -13236,7 +13236,7 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>32.58</v>
+        <v>32.57</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>100</v>
@@ -13250,13 +13250,13 @@
         </is>
       </c>
       <c r="M117" s="4" t="n">
-        <v>19.75</v>
+        <v>19.74</v>
       </c>
       <c r="N117" s="4" t="n">
         <v>7.57</v>
       </c>
       <c r="O117" s="4" t="n">
-        <v>32.02</v>
+        <v>32.01</v>
       </c>
       <c r="P117" s="4" t="n">
         <v>2.03</v>
@@ -13347,7 +13347,7 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>9.42</v>
+        <v>9.41</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>94.40000000000001</v>
@@ -13361,13 +13361,13 @@
         </is>
       </c>
       <c r="M118" s="4" t="n">
-        <v>4.66</v>
+        <v>4.65</v>
       </c>
       <c r="N118" s="4" t="n">
         <v>7.57</v>
       </c>
       <c r="O118" s="4" t="n">
-        <v>11.66</v>
+        <v>11.64</v>
       </c>
       <c r="P118" s="4" t="n">
         <v>0.33</v>
@@ -13413,10 +13413,10 @@
         <v>0</v>
       </c>
       <c r="AC118" s="4" t="n">
-        <v>52.68</v>
+        <v>52.67</v>
       </c>
       <c r="AD118" s="4" t="n">
-        <v>43.6</v>
+        <v>43.61</v>
       </c>
       <c r="AE118" s="4" t="n">
         <v>0</v>
@@ -19492,7 +19492,7 @@
         </is>
       </c>
       <c r="I175" s="4" t="n">
-        <v>48.57</v>
+        <v>48.7</v>
       </c>
       <c r="J175" s="4" t="n">
         <v>100</v>
@@ -19506,13 +19506,13 @@
         </is>
       </c>
       <c r="M175" s="4" t="n">
-        <v>38.92</v>
+        <v>39.05</v>
       </c>
       <c r="N175" s="4" t="n">
         <v>7.57</v>
       </c>
       <c r="O175" s="4" t="n">
-        <v>48.57</v>
+        <v>48.7</v>
       </c>
       <c r="P175" s="4" t="n">
         <v>1.09</v>
@@ -19544,10 +19544,10 @@
         <v>0</v>
       </c>
       <c r="AC175" s="4" t="n">
-        <v>74.29000000000001</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="AD175" s="4" t="n">
-        <v>25.71</v>
+        <v>25.65</v>
       </c>
       <c r="AE175" s="4" t="n">
         <v>0</v>
@@ -19591,7 +19591,7 @@
         </is>
       </c>
       <c r="I176" s="4" t="n">
-        <v>46.99</v>
+        <v>47.12</v>
       </c>
       <c r="J176" s="4" t="n">
         <v>100</v>
@@ -19605,13 +19605,13 @@
         </is>
       </c>
       <c r="M176" s="4" t="n">
-        <v>39.06</v>
+        <v>39.19</v>
       </c>
       <c r="N176" s="4" t="n">
         <v>7.57</v>
       </c>
       <c r="O176" s="4" t="n">
-        <v>46.99</v>
+        <v>47.12</v>
       </c>
       <c r="P176" s="4" t="n">
         <v>0</v>
@@ -19643,10 +19643,10 @@
         <v>0</v>
       </c>
       <c r="AC176" s="4" t="n">
-        <v>73.48999999999999</v>
+        <v>73.56</v>
       </c>
       <c r="AD176" s="4" t="n">
-        <v>26.51</v>
+        <v>26.44</v>
       </c>
       <c r="AE176" s="4" t="n">
         <v>0</v>
@@ -19694,7 +19694,7 @@
         </is>
       </c>
       <c r="I177" s="4" t="n">
-        <v>52.52</v>
+        <v>52.65</v>
       </c>
       <c r="J177" s="4" t="n">
         <v>100</v>
@@ -19708,13 +19708,13 @@
         </is>
       </c>
       <c r="M177" s="4" t="n">
-        <v>38.26</v>
+        <v>38.39</v>
       </c>
       <c r="N177" s="4" t="n">
         <v>7.57</v>
       </c>
       <c r="O177" s="4" t="n">
-        <v>52.52</v>
+        <v>52.65</v>
       </c>
       <c r="P177" s="4" t="n">
         <v>2.48</v>
@@ -19746,10 +19746,10 @@
         <v>0</v>
       </c>
       <c r="AC177" s="4" t="n">
-        <v>76.26000000000001</v>
+        <v>76.33</v>
       </c>
       <c r="AD177" s="4" t="n">
-        <v>23.74</v>
+        <v>23.67</v>
       </c>
       <c r="AE177" s="4" t="n">
         <v>0</v>
@@ -19793,7 +19793,7 @@
         </is>
       </c>
       <c r="I178" s="4" t="n">
-        <v>41.91</v>
+        <v>42.02</v>
       </c>
       <c r="J178" s="4" t="n">
         <v>100</v>
@@ -19807,13 +19807,13 @@
         </is>
       </c>
       <c r="M178" s="4" t="n">
-        <v>37.35</v>
+        <v>37.48</v>
       </c>
       <c r="N178" s="4" t="n">
         <v>7.57</v>
       </c>
       <c r="O178" s="4" t="n">
-        <v>47.15</v>
+        <v>47.28</v>
       </c>
       <c r="P178" s="4" t="n">
         <v>0</v>
@@ -19859,10 +19859,10 @@
         <v>0</v>
       </c>
       <c r="AC178" s="4" t="n">
-        <v>62.55</v>
+        <v>62.59</v>
       </c>
       <c r="AD178" s="4" t="n">
-        <v>25.6</v>
+        <v>25.56</v>
       </c>
       <c r="AE178" s="4" t="n">
         <v>2.85</v>
@@ -19910,7 +19910,7 @@
         </is>
       </c>
       <c r="I179" s="4" t="n">
-        <v>50.78</v>
+        <v>50.91</v>
       </c>
       <c r="J179" s="4" t="n">
         <v>100</v>
@@ -19924,13 +19924,13 @@
         </is>
       </c>
       <c r="M179" s="4" t="n">
-        <v>41.78</v>
+        <v>41.91</v>
       </c>
       <c r="N179" s="4" t="n">
         <v>7.57</v>
       </c>
       <c r="O179" s="4" t="n">
-        <v>50.78</v>
+        <v>50.91</v>
       </c>
       <c r="P179" s="4" t="n">
         <v>0</v>
@@ -19962,10 +19962,10 @@
         <v>0</v>
       </c>
       <c r="AC179" s="4" t="n">
-        <v>75.39</v>
+        <v>75.45999999999999</v>
       </c>
       <c r="AD179" s="4" t="n">
-        <v>24.61</v>
+        <v>24.54</v>
       </c>
       <c r="AE179" s="4" t="n">
         <v>0</v>
@@ -20013,7 +20013,7 @@
         </is>
       </c>
       <c r="I180" s="4" t="n">
-        <v>22.23</v>
+        <v>22.36</v>
       </c>
       <c r="J180" s="4" t="n">
         <v>99.90000000000001</v>
@@ -20027,13 +20027,13 @@
         </is>
       </c>
       <c r="M180" s="4" t="n">
-        <v>10.3</v>
+        <v>10.43</v>
       </c>
       <c r="N180" s="4" t="n">
         <v>7.57</v>
       </c>
       <c r="O180" s="4" t="n">
-        <v>22.23</v>
+        <v>22.36</v>
       </c>
       <c r="P180" s="4" t="n">
         <v>1.39</v>
@@ -20065,10 +20065,10 @@
         <v>0</v>
       </c>
       <c r="AC180" s="4" t="n">
-        <v>61.12</v>
+        <v>61.18</v>
       </c>
       <c r="AD180" s="4" t="n">
-        <v>38.88</v>
+        <v>38.82</v>
       </c>
       <c r="AE180" s="4" t="n">
         <v>0</v>
@@ -20112,7 +20112,7 @@
         </is>
       </c>
       <c r="I181" s="4" t="n">
-        <v>77.81</v>
+        <v>77.94</v>
       </c>
       <c r="J181" s="4" t="n">
         <v>100</v>
@@ -20126,13 +20126,13 @@
         </is>
       </c>
       <c r="M181" s="4" t="n">
-        <v>71.95999999999999</v>
+        <v>72.09</v>
       </c>
       <c r="N181" s="4" t="n">
         <v>7.57</v>
       </c>
       <c r="O181" s="4" t="n">
-        <v>77.81</v>
+        <v>77.94</v>
       </c>
       <c r="P181" s="4" t="n">
         <v>-0.07000000000000001</v>
@@ -20164,10 +20164,10 @@
         <v>0</v>
       </c>
       <c r="AC181" s="4" t="n">
-        <v>88.91</v>
+        <v>88.97</v>
       </c>
       <c r="AD181" s="4" t="n">
-        <v>11.09</v>
+        <v>11.03</v>
       </c>
       <c r="AE181" s="4" t="n">
         <v>0</v>
@@ -20211,7 +20211,7 @@
         </is>
       </c>
       <c r="I182" s="4" t="n">
-        <v>21.11</v>
+        <v>21.24</v>
       </c>
       <c r="J182" s="4" t="n">
         <v>99.8</v>
@@ -20225,13 +20225,13 @@
         </is>
       </c>
       <c r="M182" s="4" t="n">
-        <v>12.71</v>
+        <v>12.84</v>
       </c>
       <c r="N182" s="4" t="n">
         <v>7.57</v>
       </c>
       <c r="O182" s="4" t="n">
-        <v>21.11</v>
+        <v>21.24</v>
       </c>
       <c r="P182" s="4" t="n">
         <v>0.75</v>
@@ -20263,10 +20263,10 @@
         <v>0</v>
       </c>
       <c r="AC182" s="4" t="n">
-        <v>60.56</v>
+        <v>60.62</v>
       </c>
       <c r="AD182" s="4" t="n">
-        <v>39.44</v>
+        <v>39.38</v>
       </c>
       <c r="AE182" s="4" t="n">
         <v>0</v>
@@ -20310,7 +20310,7 @@
         </is>
       </c>
       <c r="I183" s="4" t="n">
-        <v>49.22</v>
+        <v>49.35</v>
       </c>
       <c r="J183" s="4" t="n">
         <v>100</v>
@@ -20324,13 +20324,13 @@
         </is>
       </c>
       <c r="M183" s="4" t="n">
-        <v>41.97</v>
+        <v>42.1</v>
       </c>
       <c r="N183" s="4" t="n">
         <v>7.57</v>
       </c>
       <c r="O183" s="4" t="n">
-        <v>49.22</v>
+        <v>49.35</v>
       </c>
       <c r="P183" s="4" t="n">
         <v>0</v>
@@ -20362,10 +20362,10 @@
         <v>0</v>
       </c>
       <c r="AC183" s="4" t="n">
-        <v>74.61</v>
+        <v>74.67</v>
       </c>
       <c r="AD183" s="4" t="n">
-        <v>25.39</v>
+        <v>25.33</v>
       </c>
       <c r="AE183" s="4" t="n">
         <v>0</v>
@@ -20413,7 +20413,7 @@
         </is>
       </c>
       <c r="I184" s="4" t="n">
-        <v>35.39</v>
+        <v>35.52</v>
       </c>
       <c r="J184" s="4" t="n">
         <v>100</v>
@@ -20427,13 +20427,13 @@
         </is>
       </c>
       <c r="M184" s="4" t="n">
-        <v>26.65</v>
+        <v>26.78</v>
       </c>
       <c r="N184" s="4" t="n">
         <v>7.57</v>
       </c>
       <c r="O184" s="4" t="n">
-        <v>35.39</v>
+        <v>35.52</v>
       </c>
       <c r="P184" s="4" t="n">
         <v>0</v>
@@ -20465,10 +20465,10 @@
         <v>0</v>
       </c>
       <c r="AC184" s="4" t="n">
-        <v>67.69</v>
+        <v>67.76000000000001</v>
       </c>
       <c r="AD184" s="4" t="n">
-        <v>32.31</v>
+        <v>32.24</v>
       </c>
       <c r="AE184" s="4" t="n">
         <v>0</v>
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="I185" s="4" t="n">
-        <v>26.79</v>
+        <v>26.92</v>
       </c>
       <c r="J185" s="4" t="n">
         <v>100</v>
@@ -20530,13 +20530,13 @@
         </is>
       </c>
       <c r="M185" s="4" t="n">
-        <v>15.74</v>
+        <v>15.87</v>
       </c>
       <c r="N185" s="4" t="n">
         <v>7.57</v>
       </c>
       <c r="O185" s="4" t="n">
-        <v>26.79</v>
+        <v>26.92</v>
       </c>
       <c r="P185" s="4" t="n">
         <v>1.28</v>
@@ -20568,10 +20568,10 @@
         <v>0</v>
       </c>
       <c r="AC185" s="4" t="n">
-        <v>63.4</v>
+        <v>63.46</v>
       </c>
       <c r="AD185" s="4" t="n">
-        <v>36.6</v>
+        <v>36.54</v>
       </c>
       <c r="AE185" s="4" t="n">
         <v>0</v>
@@ -20619,7 +20619,7 @@
         </is>
       </c>
       <c r="I186" s="4" t="n">
-        <v>-39.55</v>
+        <v>-39.42</v>
       </c>
       <c r="J186" s="4" t="n">
         <v>0</v>
@@ -20633,13 +20633,13 @@
         </is>
       </c>
       <c r="M186" s="4" t="n">
-        <v>-40.65</v>
+        <v>-40.52</v>
       </c>
       <c r="N186" s="4" t="n">
         <v>7.57</v>
       </c>
       <c r="O186" s="4" t="n">
-        <v>-39.55</v>
+        <v>-39.42</v>
       </c>
       <c r="P186" s="4" t="n">
         <v>-1.55</v>
@@ -20671,10 +20671,10 @@
         <v>0</v>
       </c>
       <c r="AC186" s="4" t="n">
-        <v>30.22</v>
+        <v>30.29</v>
       </c>
       <c r="AD186" s="4" t="n">
-        <v>69.78</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="AE186" s="4" t="n">
         <v>0</v>
@@ -20722,7 +20722,7 @@
         </is>
       </c>
       <c r="I187" s="4" t="n">
-        <v>28.79</v>
+        <v>28.92</v>
       </c>
       <c r="J187" s="4" t="n">
         <v>100</v>
@@ -20736,13 +20736,13 @@
         </is>
       </c>
       <c r="M187" s="4" t="n">
-        <v>14.1</v>
+        <v>14.23</v>
       </c>
       <c r="N187" s="4" t="n">
         <v>7.57</v>
       </c>
       <c r="O187" s="4" t="n">
-        <v>28.79</v>
+        <v>28.92</v>
       </c>
       <c r="P187" s="4" t="n">
         <v>1.42</v>
@@ -20774,10 +20774,10 @@
         <v>0</v>
       </c>
       <c r="AC187" s="4" t="n">
-        <v>64.39</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="AD187" s="4" t="n">
-        <v>35.61</v>
+        <v>35.54</v>
       </c>
       <c r="AE187" s="4" t="n">
         <v>0</v>
@@ -20825,7 +20825,7 @@
         </is>
       </c>
       <c r="I188" s="4" t="n">
-        <v>25.43</v>
+        <v>25.56</v>
       </c>
       <c r="J188" s="4" t="n">
         <v>99.90000000000001</v>
@@ -20839,13 +20839,13 @@
         </is>
       </c>
       <c r="M188" s="4" t="n">
-        <v>10.13</v>
+        <v>10.26</v>
       </c>
       <c r="N188" s="4" t="n">
         <v>7.57</v>
       </c>
       <c r="O188" s="4" t="n">
-        <v>25.43</v>
+        <v>25.56</v>
       </c>
       <c r="P188" s="4" t="n">
         <v>1.83</v>
@@ -20877,10 +20877,10 @@
         <v>0</v>
       </c>
       <c r="AC188" s="4" t="n">
-        <v>62.72</v>
+        <v>62.78</v>
       </c>
       <c r="AD188" s="4" t="n">
-        <v>37.28</v>
+        <v>37.22</v>
       </c>
       <c r="AE188" s="4" t="n">
         <v>0</v>
@@ -20928,7 +20928,7 @@
         </is>
       </c>
       <c r="I189" s="4" t="n">
-        <v>-33.42</v>
+        <v>-33.29</v>
       </c>
       <c r="J189" s="4" t="n">
         <v>0</v>
@@ -20942,13 +20942,13 @@
         </is>
       </c>
       <c r="M189" s="4" t="n">
-        <v>-36.93</v>
+        <v>-36.8</v>
       </c>
       <c r="N189" s="4" t="n">
         <v>7.57</v>
       </c>
       <c r="O189" s="4" t="n">
-        <v>-33.42</v>
+        <v>-33.29</v>
       </c>
       <c r="P189" s="4" t="n">
         <v>-1.49</v>
@@ -20980,10 +20980,10 @@
         <v>0</v>
       </c>
       <c r="AC189" s="4" t="n">
-        <v>33.29</v>
+        <v>33.36</v>
       </c>
       <c r="AD189" s="4" t="n">
-        <v>66.70999999999999</v>
+        <v>66.64</v>
       </c>
       <c r="AE189" s="4" t="n">
         <v>0</v>
@@ -21031,7 +21031,7 @@
         </is>
       </c>
       <c r="I190" s="4" t="n">
-        <v>-15.89</v>
+        <v>-15.76</v>
       </c>
       <c r="J190" s="4" t="n">
         <v>0.6</v>
@@ -21045,13 +21045,13 @@
         </is>
       </c>
       <c r="M190" s="4" t="n">
-        <v>-19.64</v>
+        <v>-19.51</v>
       </c>
       <c r="N190" s="4" t="n">
         <v>7.57</v>
       </c>
       <c r="O190" s="4" t="n">
-        <v>-15.89</v>
+        <v>-15.76</v>
       </c>
       <c r="P190" s="4" t="n">
         <v>-1.4</v>
@@ -21083,10 +21083,10 @@
         <v>0</v>
       </c>
       <c r="AC190" s="4" t="n">
-        <v>42.06</v>
+        <v>42.12</v>
       </c>
       <c r="AD190" s="4" t="n">
-        <v>57.94</v>
+        <v>57.88</v>
       </c>
       <c r="AE190" s="4" t="n">
         <v>0</v>
@@ -21134,7 +21134,7 @@
         </is>
       </c>
       <c r="I191" s="4" t="n">
-        <v>22.39</v>
+        <v>22.52</v>
       </c>
       <c r="J191" s="4" t="n">
         <v>99.90000000000001</v>
@@ -21148,13 +21148,13 @@
         </is>
       </c>
       <c r="M191" s="4" t="n">
-        <v>8.99</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="N191" s="4" t="n">
         <v>7.57</v>
       </c>
       <c r="O191" s="4" t="n">
-        <v>22.39</v>
+        <v>22.52</v>
       </c>
       <c r="P191" s="4" t="n">
         <v>1.34</v>
@@ -21186,10 +21186,10 @@
         <v>0</v>
       </c>
       <c r="AC191" s="4" t="n">
-        <v>61.19</v>
+        <v>61.26</v>
       </c>
       <c r="AD191" s="4" t="n">
-        <v>38.81</v>
+        <v>38.74</v>
       </c>
       <c r="AE191" s="4" t="n">
         <v>0</v>
@@ -25817,10 +25817,10 @@
         <v>0.35</v>
       </c>
       <c r="J235" s="4" t="n">
-        <v>52.3</v>
+        <v>52.5</v>
       </c>
       <c r="K235" s="4" t="n">
-        <v>47.7</v>
+        <v>47.5</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -29542,7 +29542,7 @@
         </is>
       </c>
       <c r="I269" s="4" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="J269" s="4" t="n">
         <v>59.3</v>
@@ -29556,13 +29556,13 @@
         </is>
       </c>
       <c r="M269" s="4" t="n">
-        <v>-6.07</v>
+        <v>-6.06</v>
       </c>
       <c r="N269" s="4" t="n">
         <v>7.57</v>
       </c>
       <c r="O269" s="4" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="P269" s="4" t="n">
         <v>0.02</v>
@@ -29659,7 +29659,7 @@
         </is>
       </c>
       <c r="I270" s="4" t="n">
-        <v>-23.64</v>
+        <v>-23.63</v>
       </c>
       <c r="J270" s="4" t="n">
         <v>0.1</v>
@@ -29673,13 +29673,13 @@
         </is>
       </c>
       <c r="M270" s="4" t="n">
-        <v>-25.03</v>
+        <v>-25.02</v>
       </c>
       <c r="N270" s="4" t="n">
         <v>7.57</v>
       </c>
       <c r="O270" s="4" t="n">
-        <v>-25.43</v>
+        <v>-25.42</v>
       </c>
       <c r="P270" s="4" t="n">
         <v>-2.65</v>
@@ -51467,10 +51467,10 @@
         <v>2.93</v>
       </c>
       <c r="J473" s="4" t="n">
-        <v>71</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="K473" s="4" t="n">
-        <v>29</v>
+        <v>29.6</v>
       </c>
       <c r="L473" t="inlineStr">
         <is>
@@ -51795,7 +51795,7 @@
         </is>
       </c>
       <c r="I476" s="4" t="n">
-        <v>28.18</v>
+        <v>28.16</v>
       </c>
       <c r="J476" s="4" t="n">
         <v>100</v>
@@ -51809,13 +51809,13 @@
         </is>
       </c>
       <c r="M476" s="4" t="n">
-        <v>13.78</v>
+        <v>13.77</v>
       </c>
       <c r="N476" s="4" t="n">
         <v>7.57</v>
       </c>
       <c r="O476" s="4" t="n">
-        <v>27.84</v>
+        <v>27.82</v>
       </c>
       <c r="P476" s="4" t="n">
         <v>2.94</v>
@@ -51855,10 +51855,10 @@
         <v>0</v>
       </c>
       <c r="AC476" s="4" t="n">
-        <v>56.91</v>
+        <v>56.9</v>
       </c>
       <c r="AD476" s="4" t="n">
-        <v>31.89</v>
+        <v>31.9</v>
       </c>
       <c r="AE476" s="4" t="n">
         <v>3.6</v>
@@ -52461,7 +52461,7 @@
         </is>
       </c>
       <c r="I482" s="4" t="n">
-        <v>18.12</v>
+        <v>18.18</v>
       </c>
       <c r="J482" s="4" t="n">
         <v>99.7</v>
@@ -52475,13 +52475,13 @@
         </is>
       </c>
       <c r="M482" s="4" t="n">
-        <v>15.25</v>
+        <v>15.4</v>
       </c>
       <c r="N482" s="4" t="n">
         <v>7.57</v>
       </c>
       <c r="O482" s="4" t="n">
-        <v>23.05</v>
+        <v>23.19</v>
       </c>
       <c r="P482" s="4" t="n">
         <v>0.22</v>
@@ -52527,10 +52527,10 @@
         <v>0</v>
       </c>
       <c r="AC482" s="4" t="n">
-        <v>57.36</v>
+        <v>57.39</v>
       </c>
       <c r="AD482" s="4" t="n">
-        <v>39.76</v>
+        <v>39.73</v>
       </c>
       <c r="AE482" s="4" t="n">
         <v>0</v>
@@ -53033,10 +53033,10 @@
         <v>2.76</v>
       </c>
       <c r="J487" s="4" t="n">
-        <v>69.3</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="K487" s="4" t="n">
-        <v>30.7</v>
+        <v>30.4</v>
       </c>
       <c r="L487" t="inlineStr">
         <is>
@@ -53538,16 +53538,16 @@
         </is>
       </c>
       <c r="AA491" s="4" t="n">
-        <v>29.27</v>
+        <v>29.25</v>
       </c>
       <c r="AB491" s="4" t="n">
         <v>0.3</v>
       </c>
       <c r="AC491" s="4" t="n">
-        <v>18.4</v>
+        <v>18.43</v>
       </c>
       <c r="AD491" s="4" t="n">
-        <v>48.67</v>
+        <v>48.66</v>
       </c>
       <c r="AE491" s="4" t="n">
         <v>3.66</v>

--- a/output/nowcast.xlsx
+++ b/output/nowcast.xlsx
@@ -541,16 +541,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>52.9</v>
+        <v>52.8</v>
       </c>
       <c r="C8" t="n">
-        <v>47.1</v>
+        <v>47.2</v>
       </c>
       <c r="D8" t="n">
         <v>54</v>
       </c>
       <c r="E8" t="n">
-        <v>73.59999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="F8" t="n">
         <v>51</v>
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>247.2</v>
+        <v>247</v>
       </c>
       <c r="C9" t="n">
-        <v>187.8</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
         <v>244</v>
       </c>
       <c r="E9" t="n">
-        <v>92.3</v>
+        <v>92.2</v>
       </c>
       <c r="F9" t="n">
         <v>218</v>
@@ -600,7 +600,7 @@
         <v>28</v>
       </c>
       <c r="E10" t="n">
-        <v>73</v>
+        <v>74.3</v>
       </c>
       <c r="F10" t="n">
         <v>26</v>
@@ -4059,7 +4059,7 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>14.73</v>
+        <v>14.69</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>99.3</v>
@@ -4119,16 +4119,16 @@
         </is>
       </c>
       <c r="AA30" s="4" t="n">
-        <v>34.94</v>
+        <v>34.95</v>
       </c>
       <c r="AB30" s="4" t="n">
         <v>0.7</v>
       </c>
       <c r="AC30" s="4" t="n">
-        <v>49.67</v>
+        <v>49.64</v>
       </c>
       <c r="AD30" s="4" t="n">
-        <v>15.39</v>
+        <v>15.42</v>
       </c>
       <c r="AE30" s="4" t="n">
         <v>0</v>
@@ -4960,10 +4960,10 @@
         <v>-2.45</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>31.3</v>
+        <v>32.1</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>68.7</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -5020,7 +5020,7 @@
         <v>45.49</v>
       </c>
       <c r="AB38" s="4" t="n">
-        <v>31.3</v>
+        <v>32.1</v>
       </c>
       <c r="AC38" s="4" t="n">
         <v>3.8</v>
@@ -13008,13 +13008,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>-3.51</v>
+        <v>-1.7</v>
       </c>
       <c r="J115" s="4" t="n">
-        <v>25.6</v>
+        <v>38</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>74.40000000000001</v>
+        <v>62</v>
       </c>
       <c r="L115" t="inlineStr">
         <is>
@@ -13040,16 +13040,16 @@
         <v>-9.34</v>
       </c>
       <c r="S115" s="4" t="n">
-        <v>43.99</v>
+        <v>44.47</v>
       </c>
       <c r="T115" s="4" t="n">
-        <v>45</v>
+        <v>41.23</v>
       </c>
       <c r="U115" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V115" s="4" t="n">
-        <v>-1.52</v>
+        <v>0.71</v>
       </c>
       <c r="W115" s="5" t="n">
         <v>4968409</v>
@@ -13068,16 +13068,16 @@
         </is>
       </c>
       <c r="AA115" s="4" t="n">
-        <v>0.5</v>
+        <v>1.41</v>
       </c>
       <c r="AB115" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC115" s="4" t="n">
-        <v>46.04</v>
+        <v>46.45</v>
       </c>
       <c r="AD115" s="4" t="n">
-        <v>49.38</v>
+        <v>48.06</v>
       </c>
       <c r="AE115" s="4" t="n">
         <v>4.08</v>
@@ -25817,10 +25817,10 @@
         <v>0.37</v>
       </c>
       <c r="J235" s="4" t="n">
-        <v>52.3</v>
+        <v>53.1</v>
       </c>
       <c r="K235" s="4" t="n">
-        <v>47.7</v>
+        <v>46.9</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -29542,13 +29542,13 @@
         </is>
       </c>
       <c r="I269" s="4" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="J269" s="4" t="n">
-        <v>66.40000000000001</v>
+        <v>66.2</v>
       </c>
       <c r="K269" s="4" t="n">
-        <v>33.6</v>
+        <v>33.8</v>
       </c>
       <c r="L269" t="inlineStr">
         <is>
@@ -29556,13 +29556,13 @@
         </is>
       </c>
       <c r="M269" s="4" t="n">
-        <v>-6.06</v>
+        <v>-6.11</v>
       </c>
       <c r="N269" s="4" t="n">
         <v>7.56</v>
       </c>
       <c r="O269" s="4" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="P269" s="4" t="n">
         <v>0.15</v>
@@ -29608,10 +29608,10 @@
         <v>0</v>
       </c>
       <c r="AC269" s="4" t="n">
-        <v>50.75</v>
+        <v>50.74</v>
       </c>
       <c r="AD269" s="4" t="n">
-        <v>48.45</v>
+        <v>48.46</v>
       </c>
       <c r="AE269" s="4" t="n">
         <v>0</v>
@@ -29659,7 +29659,7 @@
         </is>
       </c>
       <c r="I270" s="4" t="n">
-        <v>-23.66</v>
+        <v>-23.7</v>
       </c>
       <c r="J270" s="4" t="n">
         <v>0.1</v>
@@ -29673,13 +29673,13 @@
         </is>
       </c>
       <c r="M270" s="4" t="n">
-        <v>-25.02</v>
+        <v>-25.07</v>
       </c>
       <c r="N270" s="4" t="n">
         <v>7.56</v>
       </c>
       <c r="O270" s="4" t="n">
-        <v>-25.43</v>
+        <v>-25.48</v>
       </c>
       <c r="P270" s="4" t="n">
         <v>-2.65</v>
@@ -29725,10 +29725,10 @@
         <v>0</v>
       </c>
       <c r="AC270" s="4" t="n">
-        <v>33.35</v>
+        <v>33.33</v>
       </c>
       <c r="AD270" s="4" t="n">
-        <v>54.01</v>
+        <v>54.03</v>
       </c>
       <c r="AE270" s="4" t="n">
         <v>3.64</v>
@@ -51467,10 +51467,10 @@
         <v>2.91</v>
       </c>
       <c r="J473" s="4" t="n">
-        <v>71.40000000000001</v>
+        <v>70.7</v>
       </c>
       <c r="K473" s="4" t="n">
-        <v>28.6</v>
+        <v>29.3</v>
       </c>
       <c r="L473" t="inlineStr">
         <is>
@@ -53033,10 +53033,10 @@
         <v>2.75</v>
       </c>
       <c r="J487" s="4" t="n">
-        <v>69.09999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="K487" s="4" t="n">
-        <v>30.9</v>
+        <v>31.5</v>
       </c>
       <c r="L487" t="inlineStr">
         <is>
@@ -53478,7 +53478,7 @@
         </is>
       </c>
       <c r="I491" s="4" t="n">
-        <v>-19.37</v>
+        <v>-19.55</v>
       </c>
       <c r="J491" s="4" t="n">
         <v>0</v>
@@ -53538,16 +53538,16 @@
         </is>
       </c>
       <c r="AA491" s="4" t="n">
-        <v>29.29</v>
+        <v>29.2</v>
       </c>
       <c r="AB491" s="4" t="n">
         <v>0.3</v>
       </c>
       <c r="AC491" s="4" t="n">
-        <v>18.4</v>
+        <v>18.38</v>
       </c>
       <c r="AD491" s="4" t="n">
-        <v>48.66</v>
+        <v>48.76</v>
       </c>
       <c r="AE491" s="4" t="n">
         <v>3.66</v>

--- a/output/nowcast.xlsx
+++ b/output/nowcast.xlsx
@@ -547,10 +547,10 @@
         <v>47</v>
       </c>
       <c r="D8" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E8" t="n">
-        <v>74.7</v>
+        <v>74.8</v>
       </c>
       <c r="F8" t="n">
         <v>51</v>
@@ -575,7 +575,7 @@
         <v>244</v>
       </c>
       <c r="E9" t="n">
-        <v>91.7</v>
+        <v>91.8</v>
       </c>
       <c r="F9" t="n">
         <v>218</v>
@@ -600,7 +600,7 @@
         <v>28</v>
       </c>
       <c r="E10" t="n">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="F10" t="n">
         <v>26</v>
@@ -2356,13 +2356,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-5.37</v>
+        <v>-5.46</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>17.8</v>
+        <v>17.5</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>82.2</v>
+        <v>82.5</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -2388,16 +2388,16 @@
         <v>-16.41</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>45.1</v>
+        <v>45.65</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>48.47</v>
+        <v>49.39</v>
       </c>
       <c r="U15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-3.01</v>
+        <v>-3.45</v>
       </c>
       <c r="W15" s="5" t="n">
         <v>0</v>
@@ -2414,10 +2414,10 @@
         <v>0</v>
       </c>
       <c r="AC15" s="4" t="n">
-        <v>47.31</v>
+        <v>47.27</v>
       </c>
       <c r="AD15" s="4" t="n">
-        <v>52.69</v>
+        <v>52.73</v>
       </c>
       <c r="AE15" s="4" t="n">
         <v>0</v>
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>14.76</v>
+        <v>14.8</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>99.2</v>
+        <v>99.3</v>
       </c>
       <c r="K30" s="4" t="n">
         <v>0</v>
@@ -4119,16 +4119,16 @@
         </is>
       </c>
       <c r="AA30" s="4" t="n">
-        <v>34.95</v>
+        <v>34.92</v>
       </c>
       <c r="AB30" s="4" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="AC30" s="4" t="n">
-        <v>49.71</v>
+        <v>49.73</v>
       </c>
       <c r="AD30" s="4" t="n">
-        <v>15.34</v>
+        <v>15.35</v>
       </c>
       <c r="AE30" s="4" t="n">
         <v>0</v>
@@ -4960,10 +4960,10 @@
         <v>-1.91</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>35.1</v>
+        <v>36.5</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>64.90000000000001</v>
+        <v>63.5</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -5020,7 +5020,7 @@
         <v>45.76</v>
       </c>
       <c r="AB38" s="4" t="n">
-        <v>35.1</v>
+        <v>36.5</v>
       </c>
       <c r="AC38" s="4" t="n">
         <v>3.8</v>
@@ -22200,7 +22200,7 @@
         </is>
       </c>
       <c r="I201" s="4" t="n">
-        <v>-25.55</v>
+        <v>-25.54</v>
       </c>
       <c r="J201" s="4" t="n">
         <v>0.1</v>
@@ -22214,13 +22214,13 @@
         </is>
       </c>
       <c r="M201" s="4" t="n">
-        <v>-26.27</v>
+        <v>-26.26</v>
       </c>
       <c r="N201" s="4" t="n">
         <v>7.65</v>
       </c>
       <c r="O201" s="4" t="n">
-        <v>-26.09</v>
+        <v>-26.08</v>
       </c>
       <c r="P201" s="4" t="n">
         <v>-1.72</v>
@@ -22311,7 +22311,7 @@
         </is>
       </c>
       <c r="I202" s="4" t="n">
-        <v>-8.4</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="J202" s="4" t="n">
         <v>8.4</v>
@@ -22325,13 +22325,13 @@
         </is>
       </c>
       <c r="M202" s="4" t="n">
-        <v>-13.84</v>
+        <v>-13.83</v>
       </c>
       <c r="N202" s="4" t="n">
         <v>7.65</v>
       </c>
       <c r="O202" s="4" t="n">
-        <v>-11.97</v>
+        <v>-11.96</v>
       </c>
       <c r="P202" s="4" t="n">
         <v>-0.19</v>
@@ -22428,7 +22428,7 @@
         </is>
       </c>
       <c r="I203" s="4" t="n">
-        <v>26.99</v>
+        <v>27</v>
       </c>
       <c r="J203" s="4" t="n">
         <v>100</v>
@@ -22442,13 +22442,13 @@
         </is>
       </c>
       <c r="M203" s="4" t="n">
-        <v>9.130000000000001</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="N203" s="4" t="n">
         <v>7.65</v>
       </c>
       <c r="O203" s="4" t="n">
-        <v>26.4</v>
+        <v>26.41</v>
       </c>
       <c r="P203" s="4" t="n">
         <v>2.88</v>
@@ -22539,7 +22539,7 @@
         </is>
       </c>
       <c r="I204" s="4" t="n">
-        <v>-16.65</v>
+        <v>-16.64</v>
       </c>
       <c r="J204" s="4" t="n">
         <v>0.5</v>
@@ -22553,13 +22553,13 @@
         </is>
       </c>
       <c r="M204" s="4" t="n">
-        <v>-18.23</v>
+        <v>-18.22</v>
       </c>
       <c r="N204" s="4" t="n">
         <v>7.65</v>
       </c>
       <c r="O204" s="4" t="n">
-        <v>-17.23</v>
+        <v>-17.22</v>
       </c>
       <c r="P204" s="4" t="n">
         <v>-0.95</v>
@@ -22599,10 +22599,10 @@
         <v>0</v>
       </c>
       <c r="AC204" s="4" t="n">
-        <v>40.47</v>
+        <v>40.48</v>
       </c>
       <c r="AD204" s="4" t="n">
-        <v>56.65</v>
+        <v>56.64</v>
       </c>
       <c r="AE204" s="4" t="n">
         <v>0</v>
@@ -25829,10 +25829,10 @@
         <v>0.13</v>
       </c>
       <c r="J235" s="4" t="n">
-        <v>50.6</v>
+        <v>51.1</v>
       </c>
       <c r="K235" s="4" t="n">
-        <v>49.4</v>
+        <v>48.9</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -29560,13 +29560,13 @@
         </is>
       </c>
       <c r="I269" s="4" t="n">
-        <v>4.01</v>
+        <v>4</v>
       </c>
       <c r="J269" s="4" t="n">
-        <v>77.3</v>
+        <v>77.2</v>
       </c>
       <c r="K269" s="4" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="L269" t="inlineStr">
         <is>
@@ -29574,13 +29574,13 @@
         </is>
       </c>
       <c r="M269" s="4" t="n">
-        <v>-5.57</v>
+        <v>-5.59</v>
       </c>
       <c r="N269" s="4" t="n">
         <v>7.65</v>
       </c>
       <c r="O269" s="4" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="P269" s="4" t="n">
         <v>0.11</v>
@@ -29677,7 +29677,7 @@
         </is>
       </c>
       <c r="I270" s="4" t="n">
-        <v>-18.77</v>
+        <v>-18.78</v>
       </c>
       <c r="J270" s="4" t="n">
         <v>0.3</v>
@@ -29691,13 +29691,13 @@
         </is>
       </c>
       <c r="M270" s="4" t="n">
-        <v>-24.53</v>
+        <v>-24.55</v>
       </c>
       <c r="N270" s="4" t="n">
         <v>7.65</v>
       </c>
       <c r="O270" s="4" t="n">
-        <v>-24.86</v>
+        <v>-24.88</v>
       </c>
       <c r="P270" s="4" t="n">
         <v>-2.67</v>
@@ -29743,10 +29743,10 @@
         <v>0</v>
       </c>
       <c r="AC270" s="4" t="n">
-        <v>33.09</v>
+        <v>33.08</v>
       </c>
       <c r="AD270" s="4" t="n">
-        <v>48.38</v>
+        <v>48.39</v>
       </c>
       <c r="AE270" s="4" t="n">
         <v>3.64</v>
@@ -51485,10 +51485,10 @@
         <v>2.99</v>
       </c>
       <c r="J473" s="4" t="n">
-        <v>71.3</v>
+        <v>72.5</v>
       </c>
       <c r="K473" s="4" t="n">
-        <v>28.7</v>
+        <v>27.5</v>
       </c>
       <c r="L473" t="inlineStr">
         <is>
@@ -52596,13 +52596,13 @@
         </is>
       </c>
       <c r="I483" s="4" t="n">
-        <v>-0.11</v>
+        <v>0.01</v>
       </c>
       <c r="J483" s="4" t="n">
-        <v>49.2</v>
+        <v>50.1</v>
       </c>
       <c r="K483" s="4" t="n">
-        <v>50.8</v>
+        <v>49.9</v>
       </c>
       <c r="L483" t="inlineStr">
         <is>
@@ -52610,13 +52610,13 @@
         </is>
       </c>
       <c r="M483" s="4" t="n">
-        <v>-13.66</v>
+        <v>-13.69</v>
       </c>
       <c r="N483" s="4" t="n">
         <v>7.65</v>
       </c>
       <c r="O483" s="4" t="n">
-        <v>-6.9</v>
+        <v>-6.93</v>
       </c>
       <c r="P483" s="4" t="n">
         <v>0.63</v>
@@ -52628,16 +52628,16 @@
         <v>-16.41</v>
       </c>
       <c r="S483" s="4" t="n">
-        <v>47.73</v>
+        <v>48.05</v>
       </c>
       <c r="T483" s="4" t="n">
-        <v>44.86</v>
+        <v>45.26</v>
       </c>
       <c r="U483" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V483" s="4" t="n">
-        <v>3.35</v>
+        <v>3.18</v>
       </c>
       <c r="W483" s="5" t="n">
         <v>19175044</v>
@@ -52656,16 +52656,16 @@
         </is>
       </c>
       <c r="AA483" s="4" t="n">
-        <v>1.56</v>
+        <v>1.89</v>
       </c>
       <c r="AB483" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC483" s="4" t="n">
-        <v>49.17</v>
+        <v>49.06</v>
       </c>
       <c r="AD483" s="4" t="n">
-        <v>49.27</v>
+        <v>49.05</v>
       </c>
       <c r="AE483" s="4" t="n">
         <v>0</v>
@@ -53051,10 +53051,10 @@
         <v>2.95</v>
       </c>
       <c r="J487" s="4" t="n">
-        <v>71.2</v>
+        <v>71.3</v>
       </c>
       <c r="K487" s="4" t="n">
-        <v>28.8</v>
+        <v>28.7</v>
       </c>
       <c r="L487" t="inlineStr">
         <is>
@@ -53496,7 +53496,7 @@
         </is>
       </c>
       <c r="I491" s="4" t="n">
-        <v>-17.91</v>
+        <v>-17.9</v>
       </c>
       <c r="J491" s="4" t="n">
         <v>0</v>
@@ -53556,16 +53556,16 @@
         </is>
       </c>
       <c r="AA491" s="4" t="n">
-        <v>29.77</v>
+        <v>29.81</v>
       </c>
       <c r="AB491" s="4" t="n">
         <v>0.4</v>
       </c>
       <c r="AC491" s="4" t="n">
-        <v>18.89</v>
+        <v>18.82</v>
       </c>
       <c r="AD491" s="4" t="n">
-        <v>47.68</v>
+        <v>47.71</v>
       </c>
       <c r="AE491" s="4" t="n">
         <v>3.66</v>

--- a/output/nowcast.xlsx
+++ b/output/nowcast.xlsx
@@ -541,16 +541,16 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="C8" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="D8" t="n">
         <v>53</v>
       </c>
-      <c r="C8" t="n">
-        <v>47</v>
-      </c>
-      <c r="D8" t="n">
-        <v>54</v>
-      </c>
       <c r="E8" t="n">
-        <v>74.5</v>
+        <v>73.8</v>
       </c>
       <c r="F8" t="n">
         <v>51</v>
@@ -566,10 +566,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>246.9</v>
+        <v>247.3</v>
       </c>
       <c r="C9" t="n">
-        <v>188.1</v>
+        <v>187.7</v>
       </c>
       <c r="D9" t="n">
         <v>244</v>
@@ -591,16 +591,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>27.4</v>
+        <v>27.3</v>
       </c>
       <c r="C10" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="D10" t="n">
         <v>28</v>
       </c>
       <c r="E10" t="n">
-        <v>73.59999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="F10" t="n">
         <v>26</v>
@@ -3038,17 +3038,17 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-6.83</v>
+        <v>-10.2</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>13</v>
+        <v>3.7</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>87</v>
+        <v>96.3</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Likely R</t>
+          <t>Safe R</t>
         </is>
       </c>
       <c r="M21" s="4" t="n">
@@ -3070,16 +3070,16 @@
         <v>-20.84</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>40.83</v>
+        <v>40.27</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>43.54</v>
+        <v>47.86</v>
       </c>
       <c r="U21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-2.3</v>
+        <v>-7.36</v>
       </c>
       <c r="W21" s="5" t="n">
         <v>0</v>
@@ -3098,16 +3098,16 @@
         </is>
       </c>
       <c r="AA21" s="4" t="n">
-        <v>2.32</v>
+        <v>1.28</v>
       </c>
       <c r="AB21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC21" s="4" t="n">
-        <v>45.5</v>
+        <v>44.33</v>
       </c>
       <c r="AD21" s="4" t="n">
-        <v>52.18</v>
+        <v>54.39</v>
       </c>
       <c r="AE21" s="4" t="n">
         <v>0</v>
@@ -4059,7 +4059,7 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>14.72</v>
+        <v>14.67</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>99.3</v>
@@ -4119,16 +4119,16 @@
         </is>
       </c>
       <c r="AA30" s="4" t="n">
-        <v>34.96</v>
+        <v>34.99</v>
       </c>
       <c r="AB30" s="4" t="n">
         <v>0.7</v>
       </c>
       <c r="AC30" s="4" t="n">
-        <v>49.68</v>
+        <v>49.66</v>
       </c>
       <c r="AD30" s="4" t="n">
-        <v>15.36</v>
+        <v>15.35</v>
       </c>
       <c r="AE30" s="4" t="n">
         <v>0</v>
@@ -4511,13 +4511,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-3.27</v>
+        <v>-3.24</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>27.2</v>
+        <v>27.4</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>72.8</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -4549,10 +4549,10 @@
         <v>48.89</v>
       </c>
       <c r="U34" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-1.31</v>
+        <v>-1.32</v>
       </c>
       <c r="W34" s="5" t="n">
         <v>21687161</v>
@@ -4571,7 +4571,7 @@
         </is>
       </c>
       <c r="AA34" s="4" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="AB34" s="4" t="n">
         <v>0</v>
@@ -4580,7 +4580,7 @@
         <v>48.12</v>
       </c>
       <c r="AD34" s="4" t="n">
-        <v>51.36</v>
+        <v>51.35</v>
       </c>
       <c r="AE34" s="4" t="n">
         <v>0</v>
@@ -4960,10 +4960,10 @@
         <v>-1.93</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>35.6</v>
+        <v>34.7</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>64.40000000000001</v>
+        <v>65.3</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -5020,7 +5020,7 @@
         <v>45.75</v>
       </c>
       <c r="AB38" s="4" t="n">
-        <v>35.6</v>
+        <v>34.7</v>
       </c>
       <c r="AC38" s="4" t="n">
         <v>3.8</v>
@@ -25835,10 +25835,10 @@
         <v>0.1</v>
       </c>
       <c r="J235" s="4" t="n">
-        <v>50.9</v>
+        <v>50.6</v>
       </c>
       <c r="K235" s="4" t="n">
-        <v>49.1</v>
+        <v>49.4</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -29566,7 +29566,7 @@
         </is>
       </c>
       <c r="I269" s="4" t="n">
-        <v>3.96</v>
+        <v>3.97</v>
       </c>
       <c r="J269" s="4" t="n">
         <v>77.09999999999999</v>
@@ -29580,13 +29580,13 @@
         </is>
       </c>
       <c r="M269" s="4" t="n">
-        <v>-5.61</v>
+        <v>-5.58</v>
       </c>
       <c r="N269" s="4" t="n">
         <v>7.64</v>
       </c>
       <c r="O269" s="4" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="P269" s="4" t="n">
         <v>0.11</v>
@@ -29683,7 +29683,7 @@
         </is>
       </c>
       <c r="I270" s="4" t="n">
-        <v>-18.89</v>
+        <v>-18.87</v>
       </c>
       <c r="J270" s="4" t="n">
         <v>0.3</v>
@@ -29697,13 +29697,13 @@
         </is>
       </c>
       <c r="M270" s="4" t="n">
-        <v>-24.57</v>
+        <v>-24.54</v>
       </c>
       <c r="N270" s="4" t="n">
         <v>7.64</v>
       </c>
       <c r="O270" s="4" t="n">
-        <v>-24.91</v>
+        <v>-24.88</v>
       </c>
       <c r="P270" s="4" t="n">
         <v>-2.67</v>
@@ -29749,10 +29749,10 @@
         <v>0</v>
       </c>
       <c r="AC270" s="4" t="n">
-        <v>33.04</v>
+        <v>33.05</v>
       </c>
       <c r="AD270" s="4" t="n">
-        <v>48.43</v>
+        <v>48.42</v>
       </c>
       <c r="AE270" s="4" t="n">
         <v>3.64</v>
@@ -31471,13 +31471,13 @@
         </is>
       </c>
       <c r="I286" s="4" t="n">
-        <v>-4.05</v>
+        <v>-4.57</v>
       </c>
       <c r="J286" s="4" t="n">
-        <v>22.6</v>
+        <v>20.7</v>
       </c>
       <c r="K286" s="4" t="n">
-        <v>77.40000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="L286" t="inlineStr">
         <is>
@@ -31485,13 +31485,13 @@
         </is>
       </c>
       <c r="M286" s="4" t="n">
-        <v>-9.699999999999999</v>
+        <v>-10.54</v>
       </c>
       <c r="N286" s="4" t="n">
         <v>7.64</v>
       </c>
       <c r="O286" s="4" t="n">
-        <v>-7.87</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="P286" s="4" t="n">
         <v>-0.32</v>
@@ -31537,10 +31537,10 @@
         <v>0</v>
       </c>
       <c r="AC286" s="4" t="n">
-        <v>45.66</v>
+        <v>45.41</v>
       </c>
       <c r="AD286" s="4" t="n">
-        <v>49.52</v>
+        <v>49.77</v>
       </c>
       <c r="AE286" s="4" t="n">
         <v>2.41</v>
@@ -31584,7 +31584,7 @@
         </is>
       </c>
       <c r="I287" s="4" t="n">
-        <v>13.05</v>
+        <v>12.53</v>
       </c>
       <c r="J287" s="4" t="n">
         <v>99</v>
@@ -31598,13 +31598,13 @@
         </is>
       </c>
       <c r="M287" s="4" t="n">
-        <v>8.16</v>
+        <v>7.32</v>
       </c>
       <c r="N287" s="4" t="n">
         <v>7.64</v>
       </c>
       <c r="O287" s="4" t="n">
-        <v>16.09</v>
+        <v>15.25</v>
       </c>
       <c r="P287" s="4" t="n">
         <v>0.64</v>
@@ -31650,10 +31650,10 @@
         <v>0</v>
       </c>
       <c r="AC287" s="4" t="n">
-        <v>55.86</v>
+        <v>55.6</v>
       </c>
       <c r="AD287" s="4" t="n">
-        <v>42.96</v>
+        <v>43.22</v>
       </c>
       <c r="AE287" s="4" t="n">
         <v>0</v>
@@ -31701,7 +31701,7 @@
         </is>
       </c>
       <c r="I288" s="4" t="n">
-        <v>-51.2</v>
+        <v>-52.04</v>
       </c>
       <c r="J288" s="4" t="n">
         <v>0</v>
@@ -31715,13 +31715,13 @@
         </is>
       </c>
       <c r="M288" s="4" t="n">
-        <v>-50.65</v>
+        <v>-51.49</v>
       </c>
       <c r="N288" s="4" t="n">
         <v>7.64</v>
       </c>
       <c r="O288" s="4" t="n">
-        <v>-51.01</v>
+        <v>-51.85</v>
       </c>
       <c r="P288" s="4" t="n">
         <v>-2.09</v>
@@ -31761,10 +31761,10 @@
         <v>0</v>
       </c>
       <c r="AC288" s="4" t="n">
-        <v>23.43</v>
+        <v>23.03</v>
       </c>
       <c r="AD288" s="4" t="n">
-        <v>72.61</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="AE288" s="4" t="n">
         <v>1.98</v>
@@ -43551,10 +43551,10 @@
         <v>0</v>
       </c>
       <c r="AC398" s="4" t="n">
-        <v>30.2</v>
+        <v>30.21</v>
       </c>
       <c r="AD398" s="4" t="n">
-        <v>69.8</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="AE398" s="4" t="n">
         <v>0</v>
@@ -43612,7 +43612,7 @@
         </is>
       </c>
       <c r="M399" s="4" t="n">
-        <v>-17.77</v>
+        <v>-17.76</v>
       </c>
       <c r="N399" s="4" t="n">
         <v>7.64</v>
@@ -43656,10 +43656,10 @@
         <v>0</v>
       </c>
       <c r="AC399" s="4" t="n">
-        <v>45.12</v>
+        <v>45.13</v>
       </c>
       <c r="AD399" s="4" t="n">
-        <v>54.88</v>
+        <v>54.87</v>
       </c>
       <c r="AE399" s="4" t="n">
         <v>0</v>
@@ -43759,10 +43759,10 @@
         <v>0</v>
       </c>
       <c r="AC400" s="4" t="n">
-        <v>44.11</v>
+        <v>44.12</v>
       </c>
       <c r="AD400" s="4" t="n">
-        <v>55.89</v>
+        <v>55.88</v>
       </c>
       <c r="AE400" s="4" t="n">
         <v>0</v>
@@ -43824,7 +43824,7 @@
         </is>
       </c>
       <c r="M401" s="4" t="n">
-        <v>-18.42</v>
+        <v>-18.41</v>
       </c>
       <c r="N401" s="4" t="n">
         <v>7.64</v>
@@ -43913,7 +43913,7 @@
         </is>
       </c>
       <c r="I402" s="4" t="n">
-        <v>-11.25</v>
+        <v>-11.24</v>
       </c>
       <c r="J402" s="4" t="n">
         <v>1.3</v>
@@ -43927,13 +43927,13 @@
         </is>
       </c>
       <c r="M402" s="4" t="n">
-        <v>-15.26</v>
+        <v>-15.25</v>
       </c>
       <c r="N402" s="4" t="n">
         <v>7.64</v>
       </c>
       <c r="O402" s="4" t="n">
-        <v>-11.25</v>
+        <v>-11.24</v>
       </c>
       <c r="P402" s="4" t="n">
         <v>-2.02</v>
@@ -44030,7 +44030,7 @@
         </is>
       </c>
       <c r="M403" s="4" t="n">
-        <v>-17.34</v>
+        <v>-17.33</v>
       </c>
       <c r="N403" s="4" t="n">
         <v>7.64</v>
@@ -44068,10 +44068,10 @@
         <v>0</v>
       </c>
       <c r="AC403" s="4" t="n">
-        <v>42.61</v>
+        <v>42.62</v>
       </c>
       <c r="AD403" s="4" t="n">
-        <v>57.39</v>
+        <v>57.38</v>
       </c>
       <c r="AE403" s="4" t="n">
         <v>0</v>
@@ -44119,7 +44119,7 @@
         </is>
       </c>
       <c r="I404" s="4" t="n">
-        <v>43.82</v>
+        <v>43.83</v>
       </c>
       <c r="J404" s="4" t="n">
         <v>100</v>
@@ -44133,13 +44133,13 @@
         </is>
       </c>
       <c r="M404" s="4" t="n">
-        <v>31.99</v>
+        <v>32</v>
       </c>
       <c r="N404" s="4" t="n">
         <v>7.64</v>
       </c>
       <c r="O404" s="4" t="n">
-        <v>44.54</v>
+        <v>44.55</v>
       </c>
       <c r="P404" s="4" t="n">
         <v>1.83</v>
@@ -44179,10 +44179,10 @@
         <v>0</v>
       </c>
       <c r="AC404" s="4" t="n">
-        <v>69.83</v>
+        <v>69.84</v>
       </c>
       <c r="AD404" s="4" t="n">
-        <v>27.28</v>
+        <v>27.27</v>
       </c>
       <c r="AE404" s="4" t="n">
         <v>0</v>
@@ -44226,7 +44226,7 @@
         </is>
       </c>
       <c r="I405" s="4" t="n">
-        <v>-14.31</v>
+        <v>-14.3</v>
       </c>
       <c r="J405" s="4" t="n">
         <v>0.8</v>
@@ -44240,13 +44240,13 @@
         </is>
       </c>
       <c r="M405" s="4" t="n">
-        <v>-20.05</v>
+        <v>-20.04</v>
       </c>
       <c r="N405" s="4" t="n">
         <v>7.64</v>
       </c>
       <c r="O405" s="4" t="n">
-        <v>-14.31</v>
+        <v>-14.3</v>
       </c>
       <c r="P405" s="4" t="n">
         <v>-2.73</v>
@@ -44339,13 +44339,13 @@
         </is>
       </c>
       <c r="M406" s="4" t="n">
-        <v>-11.02</v>
+        <v>-11.01</v>
       </c>
       <c r="N406" s="4" t="n">
         <v>7.64</v>
       </c>
       <c r="O406" s="4" t="n">
-        <v>-2.92</v>
+        <v>-2.91</v>
       </c>
       <c r="P406" s="4" t="n">
         <v>-1.72</v>
@@ -44430,13 +44430,13 @@
         </is>
       </c>
       <c r="I407" s="4" t="n">
-        <v>-9.25</v>
+        <v>-9.24</v>
       </c>
       <c r="J407" s="4" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="K407" s="4" t="n">
-        <v>94</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="L407" t="inlineStr">
         <is>
@@ -44539,7 +44539,7 @@
         </is>
       </c>
       <c r="I408" s="4" t="n">
-        <v>-23.79</v>
+        <v>-23.78</v>
       </c>
       <c r="J408" s="4" t="n">
         <v>0.1</v>
@@ -44559,7 +44559,7 @@
         <v>7.64</v>
       </c>
       <c r="O408" s="4" t="n">
-        <v>-23.79</v>
+        <v>-23.78</v>
       </c>
       <c r="P408" s="4" t="n">
         <v>-2.28</v>
@@ -44642,7 +44642,7 @@
         </is>
       </c>
       <c r="I409" s="4" t="n">
-        <v>-15.23</v>
+        <v>-15.22</v>
       </c>
       <c r="J409" s="4" t="n">
         <v>0.6</v>
@@ -44662,7 +44662,7 @@
         <v>7.64</v>
       </c>
       <c r="O409" s="4" t="n">
-        <v>-15.23</v>
+        <v>-15.22</v>
       </c>
       <c r="P409" s="4" t="n">
         <v>0</v>
@@ -44745,7 +44745,7 @@
         </is>
       </c>
       <c r="I410" s="4" t="n">
-        <v>-37.13</v>
+        <v>-37.12</v>
       </c>
       <c r="J410" s="4" t="n">
         <v>0</v>
@@ -44759,13 +44759,13 @@
         </is>
       </c>
       <c r="M410" s="4" t="n">
-        <v>-40.99</v>
+        <v>-40.98</v>
       </c>
       <c r="N410" s="4" t="n">
         <v>7.64</v>
       </c>
       <c r="O410" s="4" t="n">
-        <v>-37.13</v>
+        <v>-37.12</v>
       </c>
       <c r="P410" s="4" t="n">
         <v>-2.44</v>
@@ -44848,7 +44848,7 @@
         </is>
       </c>
       <c r="I411" s="4" t="n">
-        <v>-16.15</v>
+        <v>-16.14</v>
       </c>
       <c r="J411" s="4" t="n">
         <v>0.5</v>
@@ -44862,13 +44862,13 @@
         </is>
       </c>
       <c r="M411" s="4" t="n">
-        <v>-18.4</v>
+        <v>-18.39</v>
       </c>
       <c r="N411" s="4" t="n">
         <v>7.64</v>
       </c>
       <c r="O411" s="4" t="n">
-        <v>-16.15</v>
+        <v>-16.14</v>
       </c>
       <c r="P411" s="4" t="n">
         <v>-1.94</v>
@@ -44951,7 +44951,7 @@
         </is>
       </c>
       <c r="I412" s="4" t="n">
-        <v>4.97</v>
+        <v>4.98</v>
       </c>
       <c r="J412" s="4" t="n">
         <v>80.8</v>
@@ -44965,13 +44965,13 @@
         </is>
       </c>
       <c r="M412" s="4" t="n">
-        <v>-7.09</v>
+        <v>-7.08</v>
       </c>
       <c r="N412" s="4" t="n">
         <v>7.64</v>
       </c>
       <c r="O412" s="4" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="P412" s="4" t="n">
         <v>0.15</v>
@@ -45112,10 +45112,10 @@
         <v>0</v>
       </c>
       <c r="AC413" s="4" t="n">
-        <v>71.19</v>
+        <v>71.2</v>
       </c>
       <c r="AD413" s="4" t="n">
-        <v>28.81</v>
+        <v>28.8</v>
       </c>
       <c r="AE413" s="4" t="n">
         <v>0</v>
@@ -45163,7 +45163,7 @@
         </is>
       </c>
       <c r="I414" s="4" t="n">
-        <v>-12.99</v>
+        <v>-12.98</v>
       </c>
       <c r="J414" s="4" t="n">
         <v>1</v>
@@ -45183,7 +45183,7 @@
         <v>7.64</v>
       </c>
       <c r="O414" s="4" t="n">
-        <v>-12.99</v>
+        <v>-12.98</v>
       </c>
       <c r="P414" s="4" t="n">
         <v>-1.7</v>
@@ -45266,7 +45266,7 @@
         </is>
       </c>
       <c r="I415" s="4" t="n">
-        <v>74.64</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="J415" s="4" t="n">
         <v>100</v>
@@ -45280,13 +45280,13 @@
         </is>
       </c>
       <c r="M415" s="4" t="n">
-        <v>64.05</v>
+        <v>64.06</v>
       </c>
       <c r="N415" s="4" t="n">
         <v>7.64</v>
       </c>
       <c r="O415" s="4" t="n">
-        <v>74.64</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="P415" s="4" t="n">
         <v>0</v>
@@ -45468,7 +45468,7 @@
         </is>
       </c>
       <c r="I417" s="4" t="n">
-        <v>52.73</v>
+        <v>52.74</v>
       </c>
       <c r="J417" s="4" t="n">
         <v>100</v>
@@ -45488,7 +45488,7 @@
         <v>7.64</v>
       </c>
       <c r="O417" s="4" t="n">
-        <v>52.73</v>
+        <v>52.74</v>
       </c>
       <c r="P417" s="4" t="n">
         <v>1.26</v>
@@ -45581,7 +45581,7 @@
         </is>
       </c>
       <c r="M418" s="4" t="n">
-        <v>-15.68</v>
+        <v>-15.67</v>
       </c>
       <c r="N418" s="4" t="n">
         <v>7.64</v>
@@ -45619,10 +45619,10 @@
         <v>0</v>
       </c>
       <c r="AC418" s="4" t="n">
-        <v>45.74</v>
+        <v>45.75</v>
       </c>
       <c r="AD418" s="4" t="n">
-        <v>54.26</v>
+        <v>54.25</v>
       </c>
       <c r="AE418" s="4" t="n">
         <v>0</v>
@@ -45666,7 +45666,7 @@
         </is>
       </c>
       <c r="I419" s="4" t="n">
-        <v>-9.65</v>
+        <v>-9.640000000000001</v>
       </c>
       <c r="J419" s="4" t="n">
         <v>5</v>
@@ -45680,13 +45680,13 @@
         </is>
       </c>
       <c r="M419" s="4" t="n">
-        <v>-16.26</v>
+        <v>-16.25</v>
       </c>
       <c r="N419" s="4" t="n">
         <v>7.64</v>
       </c>
       <c r="O419" s="4" t="n">
-        <v>-9.65</v>
+        <v>-9.640000000000001</v>
       </c>
       <c r="P419" s="4" t="n">
         <v>-0.96</v>
@@ -45718,10 +45718,10 @@
         <v>0</v>
       </c>
       <c r="AC419" s="4" t="n">
-        <v>45.17</v>
+        <v>45.18</v>
       </c>
       <c r="AD419" s="4" t="n">
-        <v>54.83</v>
+        <v>54.82</v>
       </c>
       <c r="AE419" s="4" t="n">
         <v>0</v>
@@ -45779,7 +45779,7 @@
         </is>
       </c>
       <c r="M420" s="4" t="n">
-        <v>-7.26</v>
+        <v>-7.25</v>
       </c>
       <c r="N420" s="4" t="n">
         <v>7.64</v>
@@ -45934,10 +45934,10 @@
         <v>0</v>
       </c>
       <c r="AC421" s="4" t="n">
-        <v>45.5</v>
+        <v>45.51</v>
       </c>
       <c r="AD421" s="4" t="n">
-        <v>54.5</v>
+        <v>54.49</v>
       </c>
       <c r="AE421" s="4" t="n">
         <v>0</v>
@@ -46108,7 +46108,7 @@
         <v>7.64</v>
       </c>
       <c r="O423" s="4" t="n">
-        <v>-19.39</v>
+        <v>-19.38</v>
       </c>
       <c r="P423" s="4" t="n">
         <v>-3.4</v>
@@ -46199,7 +46199,7 @@
         </is>
       </c>
       <c r="I424" s="4" t="n">
-        <v>-10.08</v>
+        <v>-10.07</v>
       </c>
       <c r="J424" s="4" t="n">
         <v>4</v>
@@ -46213,13 +46213,13 @@
         </is>
       </c>
       <c r="M424" s="4" t="n">
-        <v>-15.18</v>
+        <v>-15.17</v>
       </c>
       <c r="N424" s="4" t="n">
         <v>7.64</v>
       </c>
       <c r="O424" s="4" t="n">
-        <v>-10.08</v>
+        <v>-10.07</v>
       </c>
       <c r="P424" s="4" t="n">
         <v>-1.03</v>
@@ -46302,7 +46302,7 @@
         </is>
       </c>
       <c r="I425" s="4" t="n">
-        <v>20.14</v>
+        <v>20.15</v>
       </c>
       <c r="J425" s="4" t="n">
         <v>99.8</v>
@@ -46316,13 +46316,13 @@
         </is>
       </c>
       <c r="M425" s="4" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="N425" s="4" t="n">
         <v>7.64</v>
       </c>
       <c r="O425" s="4" t="n">
-        <v>24.05</v>
+        <v>24.06</v>
       </c>
       <c r="P425" s="4" t="n">
         <v>0.73</v>
@@ -46518,7 +46518,7 @@
         </is>
       </c>
       <c r="I427" s="4" t="n">
-        <v>66.76000000000001</v>
+        <v>66.77</v>
       </c>
       <c r="J427" s="4" t="n">
         <v>100</v>
@@ -46538,7 +46538,7 @@
         <v>7.64</v>
       </c>
       <c r="O427" s="4" t="n">
-        <v>66.76000000000001</v>
+        <v>66.77</v>
       </c>
       <c r="P427" s="4" t="n">
         <v>1.78</v>
@@ -46641,7 +46641,7 @@
         <v>7.64</v>
       </c>
       <c r="O428" s="4" t="n">
-        <v>-14.21</v>
+        <v>-14.2</v>
       </c>
       <c r="P428" s="4" t="n">
         <v>-1.15</v>
@@ -46728,13 +46728,13 @@
         </is>
       </c>
       <c r="I429" s="4" t="n">
-        <v>-4.78</v>
+        <v>-4.77</v>
       </c>
       <c r="J429" s="4" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="K429" s="4" t="n">
-        <v>80.09999999999999</v>
+        <v>80</v>
       </c>
       <c r="L429" t="inlineStr">
         <is>
@@ -46742,13 +46742,13 @@
         </is>
       </c>
       <c r="M429" s="4" t="n">
-        <v>-10.95</v>
+        <v>-10.94</v>
       </c>
       <c r="N429" s="4" t="n">
         <v>7.64</v>
       </c>
       <c r="O429" s="4" t="n">
-        <v>-4.78</v>
+        <v>-4.77</v>
       </c>
       <c r="P429" s="4" t="n">
         <v>-1.73</v>
@@ -46841,7 +46841,7 @@
         </is>
       </c>
       <c r="M430" s="4" t="n">
-        <v>42.19</v>
+        <v>42.2</v>
       </c>
       <c r="N430" s="4" t="n">
         <v>7.64</v>
@@ -46944,13 +46944,13 @@
         </is>
       </c>
       <c r="M431" s="4" t="n">
-        <v>-0.37</v>
+        <v>-0.36</v>
       </c>
       <c r="N431" s="4" t="n">
         <v>7.64</v>
       </c>
       <c r="O431" s="4" t="n">
-        <v>14.9</v>
+        <v>14.91</v>
       </c>
       <c r="P431" s="4" t="n">
         <v>0.31</v>
@@ -47046,10 +47046,10 @@
         <v>3.89</v>
       </c>
       <c r="J432" s="4" t="n">
-        <v>76.8</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K432" s="4" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="L432" t="inlineStr">
         <is>
@@ -47063,7 +47063,7 @@
         <v>7.64</v>
       </c>
       <c r="O432" s="4" t="n">
-        <v>6.67</v>
+        <v>6.68</v>
       </c>
       <c r="P432" s="4" t="n">
         <v>0.02</v>
@@ -47152,7 +47152,7 @@
         </is>
       </c>
       <c r="I433" s="4" t="n">
-        <v>-14.55</v>
+        <v>-14.54</v>
       </c>
       <c r="J433" s="4" t="n">
         <v>0.7</v>
@@ -47166,13 +47166,13 @@
         </is>
       </c>
       <c r="M433" s="4" t="n">
-        <v>-17.98</v>
+        <v>-17.97</v>
       </c>
       <c r="N433" s="4" t="n">
         <v>7.64</v>
       </c>
       <c r="O433" s="4" t="n">
-        <v>-14.55</v>
+        <v>-14.54</v>
       </c>
       <c r="P433" s="4" t="n">
         <v>-2.12</v>
@@ -47255,7 +47255,7 @@
         </is>
       </c>
       <c r="I434" s="4" t="n">
-        <v>74.78</v>
+        <v>74.79000000000001</v>
       </c>
       <c r="J434" s="4" t="n">
         <v>100</v>
@@ -47269,13 +47269,13 @@
         </is>
       </c>
       <c r="M434" s="4" t="n">
-        <v>64.81</v>
+        <v>64.81999999999999</v>
       </c>
       <c r="N434" s="4" t="n">
         <v>7.64</v>
       </c>
       <c r="O434" s="4" t="n">
-        <v>74.78</v>
+        <v>74.79000000000001</v>
       </c>
       <c r="P434" s="4" t="n">
         <v>1.55</v>
@@ -47354,13 +47354,13 @@
         </is>
       </c>
       <c r="I435" s="4" t="n">
-        <v>-10.43</v>
+        <v>-10.42</v>
       </c>
       <c r="J435" s="4" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K435" s="4" t="n">
-        <v>96.90000000000001</v>
+        <v>96.8</v>
       </c>
       <c r="L435" t="inlineStr">
         <is>
@@ -47368,7 +47368,7 @@
         </is>
       </c>
       <c r="M435" s="4" t="n">
-        <v>-15.42</v>
+        <v>-15.41</v>
       </c>
       <c r="N435" s="4" t="n">
         <v>7.64</v>
@@ -51491,10 +51491,10 @@
         <v>2.51</v>
       </c>
       <c r="J473" s="4" t="n">
-        <v>67.59999999999999</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="K473" s="4" t="n">
-        <v>32.4</v>
+        <v>31.4</v>
       </c>
       <c r="L473" t="inlineStr">
         <is>
@@ -53057,10 +53057,10 @@
         <v>2.93</v>
       </c>
       <c r="J487" s="4" t="n">
-        <v>70.8</v>
+        <v>72</v>
       </c>
       <c r="K487" s="4" t="n">
-        <v>29.2</v>
+        <v>28</v>
       </c>
       <c r="L487" t="inlineStr">
         <is>
@@ -53502,7 +53502,7 @@
         </is>
       </c>
       <c r="I491" s="4" t="n">
-        <v>-18.03</v>
+        <v>-17.91</v>
       </c>
       <c r="J491" s="4" t="n">
         <v>0</v>
@@ -53562,7 +53562,7 @@
         </is>
       </c>
       <c r="AA491" s="4" t="n">
-        <v>29.73</v>
+        <v>29.79</v>
       </c>
       <c r="AB491" s="4" t="n">
         <v>0.4</v>
@@ -53571,7 +53571,7 @@
         <v>18.86</v>
       </c>
       <c r="AD491" s="4" t="n">
-        <v>47.75</v>
+        <v>47.69</v>
       </c>
       <c r="AE491" s="4" t="n">
         <v>3.66</v>
@@ -53732,27 +53732,27 @@
         </is>
       </c>
       <c r="I493" s="4" t="n">
-        <v>0.02</v>
+        <v>-2.01</v>
       </c>
       <c r="J493" s="4" t="n">
-        <v>50.1</v>
+        <v>35.5</v>
       </c>
       <c r="K493" s="4" t="n">
-        <v>49.9</v>
+        <v>64.5</v>
       </c>
       <c r="L493" t="inlineStr">
         <is>
-          <t>Toss-up</t>
+          <t>Lean R</t>
         </is>
       </c>
       <c r="M493" s="4" t="n">
-        <v>-17.41</v>
+        <v>-18.25</v>
       </c>
       <c r="N493" s="4" t="n">
         <v>7.64</v>
       </c>
       <c r="O493" s="4" t="n">
-        <v>-1.48</v>
+        <v>-2.32</v>
       </c>
       <c r="P493" s="4" t="n">
         <v>0.14</v>
@@ -53764,16 +53764,16 @@
         <v>-20.84</v>
       </c>
       <c r="S493" s="4" t="n">
-        <v>46.74</v>
+        <v>45.14</v>
       </c>
       <c r="T493" s="4" t="n">
-        <v>46.37</v>
+        <v>47.36</v>
       </c>
       <c r="U493" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V493" s="4" t="n">
-        <v>0.92</v>
+        <v>-1.91</v>
       </c>
       <c r="W493" s="5" t="n">
         <v>0</v>
@@ -53792,16 +53792,16 @@
         </is>
       </c>
       <c r="AA493" s="4" t="n">
-        <v>48.92</v>
+        <v>47.9</v>
       </c>
       <c r="AB493" s="4" t="n">
-        <v>50.1</v>
+        <v>35.5</v>
       </c>
       <c r="AC493" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AD493" s="4" t="n">
-        <v>48.9</v>
+        <v>49.92</v>
       </c>
       <c r="AE493" s="4" t="n">
         <v>2.18</v>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="M504" s="4" t="n">
-        <v>-9.279999999999999</v>
+        <v>-9.27</v>
       </c>
       <c r="N504" s="4" t="n">
         <v>7.64</v>
       </c>
       <c r="O504" s="4" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="P504" s="4" t="n">
         <v>0.3</v>
@@ -55019,16 +55019,16 @@
         <v>-13.88</v>
       </c>
       <c r="S504" s="4" t="n">
-        <v>49.33</v>
+        <v>49.3</v>
       </c>
       <c r="T504" s="4" t="n">
-        <v>45.66</v>
+        <v>45.65</v>
       </c>
       <c r="U504" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="V504" s="4" t="n">
-        <v>4.29</v>
+        <v>4.27</v>
       </c>
       <c r="W504" s="5" t="n">
         <v>146349912</v>
@@ -55047,7 +55047,7 @@
         </is>
       </c>
       <c r="AA504" s="4" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="AB504" s="4" t="n">
         <v>0</v>
@@ -55056,7 +55056,7 @@
         <v>51.47</v>
       </c>
       <c r="AD504" s="4" t="n">
-        <v>47.88</v>
+        <v>47.89</v>
       </c>
       <c r="AE504" s="4" t="n">
         <v>0</v>
@@ -58499,7 +58499,7 @@
         </is>
       </c>
       <c r="J53" s="4" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="K53" t="n">
         <v>19</v>
